--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -490,17 +490,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Version 2, réécrite d'après tes deux corrections</t>
+          <t>Version 3 — après ta remarque sur Victor Carré</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -509,147 +509,179 @@
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="50" customHeight="1">
+    <row r="3" ht="52" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Le squelette</t>
+          <t>Le reproche</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Salutation, rappel de son article avec le crédit qui lui revient, le pont vers les 2 missions, l'annonce sur sa propre ligne, la rareté de l'occasion et la demande de suite, la chaîne de bénéfices, la clôture.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="50" customHeight="1">
+          <t>« Aucune présentation, mise en contexte. » Juste. Le courriel demandait à quelqu'un de s'intéresser à une entreprise dont il n'a jamais entendu parler et à une matière qu'il ne connaît pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Ce que j'avais mal fait</t>
+          <t>Ce que j'ai ajouté</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>J'écrivais de la communication de crise pour une bonne nouvelle : je m'excusais du virage, je nommais ce qu'il avait coûté, je répétais qu'un achat ne sauve pas un papillon, et je rappelais partout que je ne peux pas dire l'issue. Tout ça est parti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="50" customHeight="1">
+          <t>Une vraie présentation en tête de tous les courriels froids : qui je suis, ce qu'est Lasclay, ce qu'est l'asclépiade — sous le nom de « petits cochons », que tout le monde reconnaît ici — ce que la fibre fait, ce qu'on en fabrique, et le lien avec le monarque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Le pont que j'avais raté</t>
+          <t>Et un « pourquoi vous »</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Le changement de modèle devait libérer du temps pour les 2 missions. Dragons' Den est donc l'aboutissement de la décision que ces journalistes ont racontée, pas un changement de sujet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="50" customHeight="1">
+          <t>Chaque courriel dit maintenant explicitement pourquoi je lui écris à lui. La raison vient de sa région quand l'asclépiade y a une histoire réelle (Saint-Tite, Granby, le Lac-Saint-Jean), de son sujet sinon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Une accroche régionale retirée</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>« Notre atelier est dans Limoilou » n'est pas une accroche locale pour un journal de Charlevoix. La Capitale-Nationale passe au thématique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>La colonne Registre</t>
+          <t>Les quatre de la liste chaude</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>tu ou vous, liste déroulante. Chloé est au « tu », Larocque au « vous ». Ça ne se devine pas : bascule-la et je relance. Toute la liste froide est au « vous ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Salutations</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Liste chaude au vouvoiement : « Bonjour M. Larocque ». Liste froide : « Bonjour Prénom Nom », parce que deviner M. ou Mme sur 219 inconnus produirait des erreurs. Six fiches FPJQ mal formées sont signalées.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Repris mot pour mot</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Larocque et Pouliot sont exactement tes textes, à un « t'en faire part » près.</t>
-        </is>
-      </c>
+          <t>Roberge, Laforest, Goubau et Dostie n'avaient aucun historique documenté et donc aucune présentation. Ils en ont une maintenant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Ce qui n'a pas bougé</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="50" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Les trois colonnes jaunes</t>
+          <t>Ton squelette</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TA VERSION, CE QUI N'ALLAIT PAS, Verdict. Comme la dernière fois : quelques réécritures sur des cas différents valent mieux que 256 verdicts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Rappels</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr"/>
+          <t>Présentation, pourquoi vous, les 2 missions, l'annonce sur sa propre ligne, la rareté et la demande de suite, la chaîne ventes-cultivateurs-monarques, la clôture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Larocque et Pouliot</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Repris mot pour mot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Registre</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Liste déroulante tu/vous. Chloé au « tu », tout le reste au « vous ». Bascule, je relance.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Rappels</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Diffusion</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Jeudi 17 septembre 2026, 20 h (20 h 30 NT), CBC et CBC Gem. Saison 21, épisode 1. Prévente le samedi 12 septembre à 9 h.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Jeudi 17 septembre 2026, 20 h (20 h 30 NT), CBC et CBC Gem. Prévente le samedi 12 septembre à 9 h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Ne pas envoyer</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Anne-Sophie Roy à l'adresse Québecor. Annie Lafrance et Francis Higgins en liste froide.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="50" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Courriels manquants</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Sophie Poisson, Caroline Bertrand, Karine Benoist, Antoine Stab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Salutations à vérifier</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Six fiches FPJQ mal formées, signalées dans la colonne Précaution du chiffrier de travail.</t>
         </is>
       </c>
     </row>
@@ -676,8 +708,8 @@
     <col width="32" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="80" customWidth="1" min="11" max="11"/>
+    <col width="84" customWidth="1" min="10" max="10"/>
+    <col width="84" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
@@ -730,7 +762,7 @@
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>Brouillon v2</t>
+          <t>Brouillon v3</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
@@ -749,7 +781,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="175" customHeight="1">
+    <row r="2" ht="230" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -814,7 +846,7 @@
       <c r="L2" s="10" t="inlineStr"/>
       <c r="M2" s="10" t="inlineStr"/>
     </row>
-    <row r="3" ht="175" customHeight="1">
+    <row r="3" ht="230" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -872,7 +904,7 @@
       <c r="L3" s="10" t="inlineStr"/>
       <c r="M3" s="10" t="inlineStr"/>
     </row>
-    <row r="4" ht="175" customHeight="1">
+    <row r="4" ht="230" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -943,7 +975,7 @@
       <c r="L4" s="10" t="inlineStr"/>
       <c r="M4" s="10" t="inlineStr"/>
     </row>
-    <row r="5" ht="175" customHeight="1">
+    <row r="5" ht="230" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1000,7 +1032,7 @@
       <c r="L5" s="10" t="inlineStr"/>
       <c r="M5" s="10" t="inlineStr"/>
     </row>
-    <row r="6" ht="175" customHeight="1">
+    <row r="6" ht="230" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1058,7 +1090,7 @@
       <c r="L6" s="10" t="inlineStr"/>
       <c r="M6" s="10" t="inlineStr"/>
     </row>
-    <row r="7" ht="175" customHeight="1">
+    <row r="7" ht="230" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1116,7 +1148,7 @@
       <c r="L7" s="10" t="inlineStr"/>
       <c r="M7" s="10" t="inlineStr"/>
     </row>
-    <row r="8" ht="175" customHeight="1">
+    <row r="8" ht="230" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1174,7 +1206,7 @@
       <c r="L8" s="10" t="inlineStr"/>
       <c r="M8" s="10" t="inlineStr"/>
     </row>
-    <row r="9" ht="175" customHeight="1">
+    <row r="9" ht="230" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1232,7 +1264,7 @@
       <c r="L9" s="10" t="inlineStr"/>
       <c r="M9" s="10" t="inlineStr"/>
     </row>
-    <row r="10" ht="175" customHeight="1">
+    <row r="10" ht="230" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1290,7 +1322,7 @@
       <c r="L10" s="10" t="inlineStr"/>
       <c r="M10" s="10" t="inlineStr"/>
     </row>
-    <row r="11" ht="175" customHeight="1">
+    <row r="11" ht="230" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1348,7 +1380,7 @@
       <c r="L11" s="10" t="inlineStr"/>
       <c r="M11" s="10" t="inlineStr"/>
     </row>
-    <row r="12" ht="175" customHeight="1">
+    <row r="12" ht="230" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1406,7 +1438,7 @@
       <c r="L12" s="10" t="inlineStr"/>
       <c r="M12" s="10" t="inlineStr"/>
     </row>
-    <row r="13" ht="175" customHeight="1">
+    <row r="13" ht="230" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1464,7 +1496,7 @@
       <c r="L13" s="10" t="inlineStr"/>
       <c r="M13" s="10" t="inlineStr"/>
     </row>
-    <row r="14" ht="175" customHeight="1">
+    <row r="14" ht="230" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1522,7 +1554,7 @@
       <c r="L14" s="10" t="inlineStr"/>
       <c r="M14" s="10" t="inlineStr"/>
     </row>
-    <row r="15" ht="175" customHeight="1">
+    <row r="15" ht="230" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1580,7 +1612,7 @@
       <c r="L15" s="10" t="inlineStr"/>
       <c r="M15" s="10" t="inlineStr"/>
     </row>
-    <row r="16" ht="175" customHeight="1">
+    <row r="16" ht="230" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1637,7 +1669,7 @@
       <c r="L16" s="10" t="inlineStr"/>
       <c r="M16" s="10" t="inlineStr"/>
     </row>
-    <row r="17" ht="175" customHeight="1">
+    <row r="17" ht="230" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1695,7 +1727,7 @@
       <c r="L17" s="10" t="inlineStr"/>
       <c r="M17" s="10" t="inlineStr"/>
     </row>
-    <row r="18" ht="175" customHeight="1">
+    <row r="18" ht="230" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1753,7 +1785,7 @@
       <c r="L18" s="10" t="inlineStr"/>
       <c r="M18" s="10" t="inlineStr"/>
     </row>
-    <row r="19" ht="175" customHeight="1">
+    <row r="19" ht="230" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1811,7 +1843,7 @@
       <c r="L19" s="10" t="inlineStr"/>
       <c r="M19" s="10" t="inlineStr"/>
     </row>
-    <row r="20" ht="175" customHeight="1">
+    <row r="20" ht="230" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1869,7 +1901,7 @@
       <c r="L20" s="10" t="inlineStr"/>
       <c r="M20" s="10" t="inlineStr"/>
     </row>
-    <row r="21" ht="175" customHeight="1">
+    <row r="21" ht="230" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1927,7 +1959,7 @@
       <c r="L21" s="10" t="inlineStr"/>
       <c r="M21" s="10" t="inlineStr"/>
     </row>
-    <row r="22" ht="175" customHeight="1">
+    <row r="22" ht="230" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1985,7 +2017,7 @@
       <c r="L22" s="10" t="inlineStr"/>
       <c r="M22" s="10" t="inlineStr"/>
     </row>
-    <row r="23" ht="175" customHeight="1">
+    <row r="23" ht="230" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2043,7 +2075,7 @@
       <c r="L23" s="10" t="inlineStr"/>
       <c r="M23" s="10" t="inlineStr"/>
     </row>
-    <row r="24" ht="175" customHeight="1">
+    <row r="24" ht="230" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2101,7 +2133,7 @@
       <c r="L24" s="10" t="inlineStr"/>
       <c r="M24" s="10" t="inlineStr"/>
     </row>
-    <row r="25" ht="175" customHeight="1">
+    <row r="25" ht="230" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2159,7 +2191,7 @@
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr"/>
     </row>
-    <row r="26" ht="175" customHeight="1">
+    <row r="26" ht="230" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2210,7 +2242,7 @@
       <c r="L26" s="10" t="inlineStr"/>
       <c r="M26" s="10" t="inlineStr"/>
     </row>
-    <row r="27" ht="175" customHeight="1">
+    <row r="27" ht="230" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2268,7 +2300,7 @@
       <c r="L27" s="10" t="inlineStr"/>
       <c r="M27" s="10" t="inlineStr"/>
     </row>
-    <row r="28" ht="175" customHeight="1">
+    <row r="28" ht="230" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2318,7 +2350,7 @@
       <c r="L28" s="10" t="inlineStr"/>
       <c r="M28" s="10" t="inlineStr"/>
     </row>
-    <row r="29" ht="175" customHeight="1">
+    <row r="29" ht="230" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2355,7 +2387,7 @@
       <c r="J29" s="9" t="inlineStr">
         <is>
           <t>Bonjour Mme Roberge,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2368,7 +2400,7 @@
       <c r="L29" s="10" t="inlineStr"/>
       <c r="M29" s="10" t="inlineStr"/>
     </row>
-    <row r="30" ht="175" customHeight="1">
+    <row r="30" ht="230" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2405,7 +2437,7 @@
       <c r="J30" s="9" t="inlineStr">
         <is>
           <t>Bonjour Mme Laforest,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile. L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et la soie attachée à ses graines est un isolant creux, très léger et naturellement hydrophobe.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2418,7 +2450,7 @@
       <c r="L30" s="10" t="inlineStr"/>
       <c r="M30" s="10" t="inlineStr"/>
     </row>
-    <row r="31" ht="175" customHeight="1">
+    <row r="31" ht="230" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2476,7 +2508,7 @@
       <c r="L31" s="10" t="inlineStr"/>
       <c r="M31" s="10" t="inlineStr"/>
     </row>
-    <row r="32" ht="175" customHeight="1">
+    <row r="32" ht="230" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2526,7 +2558,7 @@
       <c r="L32" s="10" t="inlineStr"/>
       <c r="M32" s="10" t="inlineStr"/>
     </row>
-    <row r="33" ht="175" customHeight="1">
+    <row r="33" ht="230" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2576,7 +2608,7 @@
       <c r="L33" s="10" t="inlineStr"/>
       <c r="M33" s="10" t="inlineStr"/>
     </row>
-    <row r="34" ht="175" customHeight="1">
+    <row r="34" ht="230" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2613,7 +2645,7 @@
       <c r="J34" s="9" t="inlineStr">
         <is>
           <t>Bonjour Mme Goubau,
-Vous couvrez le textile et la mode, alors voici une matière que peu de gens ont vue de près. La soie d'asclépiade est une fibre creuse et hydrophobe attachée aux graines d'une plante que les agriculteurs arrachent depuis 50 ans. On en fait de l'isolant pour des manteaux, des mitaines et des tuques.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. Vous couvrez le textile et la mode, alors voici une matière que peu de gens ont vue de près : la soie d'asclépiade, une fibre creuse et naturellement hydrophobe attachée aux graines d'une plante que les agriculteurs arrachent de leurs champs depuis 50 ans. On la transforme en isolant, et on en fait des manteaux, des mitaines et des tuques.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2626,7 +2658,7 @@
       <c r="L34" s="10" t="inlineStr"/>
       <c r="M34" s="10" t="inlineStr"/>
     </row>
-    <row r="35" ht="175" customHeight="1">
+    <row r="35" ht="230" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2663,7 +2695,7 @@
       <c r="J35" s="9" t="inlineStr">
         <is>
           <t>Bonjour Mme Dostie,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile. La fibre est attachée aux graines de la plante : elle est creuse, très légère et naturellement hydrophobe.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2676,7 +2708,7 @@
       <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr"/>
     </row>
-    <row r="36" ht="175" customHeight="1">
+    <row r="36" ht="230" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2730,7 +2762,7 @@
       <c r="L36" s="10" t="inlineStr"/>
       <c r="M36" s="10" t="inlineStr"/>
     </row>
-    <row r="37" ht="175" customHeight="1">
+    <row r="37" ht="230" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2784,7 +2816,7 @@
       <c r="L37" s="10" t="inlineStr"/>
       <c r="M37" s="10" t="inlineStr"/>
     </row>
-    <row r="38" ht="175" customHeight="1">
+    <row r="38" ht="230" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2838,7 +2870,7 @@
       <c r="L38" s="10" t="inlineStr"/>
       <c r="M38" s="10" t="inlineStr"/>
     </row>
-    <row r="39" ht="175" customHeight="1">
+    <row r="39" ht="230" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -2906,7 +2938,7 @@
       <c r="L39" s="10" t="inlineStr"/>
       <c r="M39" s="10" t="inlineStr"/>
     </row>
-    <row r="40" ht="175" customHeight="1">
+    <row r="40" ht="230" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -2955,12 +2987,13 @@
       <c r="J40" s="9" t="inlineStr">
         <is>
           <t>Bonjour Zoé Allemand,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est une vivace indigène qui pousse avec peu d'intrants, ce qui en fait une culture intéressante pour des régions où les grandes cultures rendent mal.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -2969,7 +3002,7 @@
       <c r="L40" s="10" t="inlineStr"/>
       <c r="M40" s="10" t="inlineStr"/>
     </row>
-    <row r="41" ht="175" customHeight="1">
+    <row r="41" ht="230" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3018,12 +3051,13 @@
       <c r="J41" s="9" t="inlineStr">
         <is>
           <t>Bonjour Victoria Bakos,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3032,7 +3066,7 @@
       <c r="L41" s="10" t="inlineStr"/>
       <c r="M41" s="10" t="inlineStr"/>
     </row>
-    <row r="42" ht="175" customHeight="1">
+    <row r="42" ht="230" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3081,9 +3115,10 @@
       <c r="J42" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-Émélie Bernier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -3095,7 +3130,7 @@
       <c r="L42" s="10" t="inlineStr"/>
       <c r="M42" s="10" t="inlineStr"/>
     </row>
-    <row r="43" ht="175" customHeight="1">
+    <row r="43" ht="230" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3144,12 +3179,13 @@
       <c r="J43" s="9" t="inlineStr">
         <is>
           <t>Bonjour Normand Blouin,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3158,7 +3194,7 @@
       <c r="L43" s="10" t="inlineStr"/>
       <c r="M43" s="10" t="inlineStr"/>
     </row>
-    <row r="44" ht="175" customHeight="1">
+    <row r="44" ht="230" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3207,9 +3243,10 @@
       <c r="J44" s="9" t="inlineStr">
         <is>
           <t>Bonjour Louise Bourbonnais,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -3221,7 +3258,7 @@
       <c r="L44" s="10" t="inlineStr"/>
       <c r="M44" s="10" t="inlineStr"/>
     </row>
-    <row r="45" ht="175" customHeight="1">
+    <row r="45" ht="230" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3270,12 +3307,13 @@
       <c r="J45" s="9" t="inlineStr">
         <is>
           <t>Bonjour Francois Bourque,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3284,7 +3322,7 @@
       <c r="L45" s="10" t="inlineStr"/>
       <c r="M45" s="10" t="inlineStr"/>
     </row>
-    <row r="46" ht="175" customHeight="1">
+    <row r="46" ht="230" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3333,12 +3371,13 @@
       <c r="J46" s="9" t="inlineStr">
         <is>
           <t>Bonjour Ariane Boyer,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est une vivace indigène qui pousse avec peu d'intrants, ce qui en fait une culture intéressante pour des régions où les grandes cultures rendent mal.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3347,7 +3386,7 @@
       <c r="L46" s="10" t="inlineStr"/>
       <c r="M46" s="10" t="inlineStr"/>
     </row>
-    <row r="47" ht="175" customHeight="1">
+    <row r="47" ht="230" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3396,9 +3435,10 @@
       <c r="J47" s="9" t="inlineStr">
         <is>
           <t>Bonjour Gilbert Bégin,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -3410,7 +3450,7 @@
       <c r="L47" s="10" t="inlineStr"/>
       <c r="M47" s="10" t="inlineStr"/>
     </row>
-    <row r="48" ht="175" customHeight="1">
+    <row r="48" ht="230" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3459,9 +3499,10 @@
       <c r="J48" s="9" t="inlineStr">
         <is>
           <t>Bonjour Papa Moussa Camara,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -3473,7 +3514,7 @@
       <c r="L48" s="10" t="inlineStr"/>
       <c r="M48" s="10" t="inlineStr"/>
     </row>
-    <row r="49" ht="175" customHeight="1">
+    <row r="49" ht="230" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3522,9 +3563,10 @@
       <c r="J49" s="9" t="inlineStr">
         <is>
           <t>Bonjour Victor Carré,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -3536,7 +3578,7 @@
       <c r="L49" s="10" t="inlineStr"/>
       <c r="M49" s="10" t="inlineStr"/>
     </row>
-    <row r="50" ht="175" customHeight="1">
+    <row r="50" ht="230" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3585,12 +3627,13 @@
       <c r="J50" s="9" t="inlineStr">
         <is>
           <t>Bonjour Eric Chabot,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3599,7 +3642,7 @@
       <c r="L50" s="10" t="inlineStr"/>
       <c r="M50" s="10" t="inlineStr"/>
     </row>
-    <row r="51" ht="175" customHeight="1">
+    <row r="51" ht="230" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3648,9 +3691,10 @@
       <c r="J51" s="9" t="inlineStr">
         <is>
           <t>Bonjour Tristan Champagne-Lessard,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -3662,7 +3706,7 @@
       <c r="L51" s="10" t="inlineStr"/>
       <c r="M51" s="10" t="inlineStr"/>
     </row>
-    <row r="52" ht="175" customHeight="1">
+    <row r="52" ht="230" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3711,12 +3755,13 @@
       <c r="J52" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jean-Marc Chevalier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3725,7 +3770,7 @@
       <c r="L52" s="10" t="inlineStr"/>
       <c r="M52" s="10" t="inlineStr"/>
     </row>
-    <row r="53" ht="175" customHeight="1">
+    <row r="53" ht="230" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3774,12 +3819,13 @@
       <c r="J53" s="9" t="inlineStr">
         <is>
           <t>Bonjour Simon Chrétien,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3788,7 +3834,7 @@
       <c r="L53" s="10" t="inlineStr"/>
       <c r="M53" s="10" t="inlineStr"/>
     </row>
-    <row r="54" ht="175" customHeight="1">
+    <row r="54" ht="230" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3837,9 +3883,10 @@
       <c r="J54" s="9" t="inlineStr">
         <is>
           <t>Bonjour Maxime Corneau,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -3851,7 +3898,7 @@
       <c r="L54" s="10" t="inlineStr"/>
       <c r="M54" s="10" t="inlineStr"/>
     </row>
-    <row r="55" ht="175" customHeight="1">
+    <row r="55" ht="230" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3900,12 +3947,13 @@
       <c r="J55" s="9" t="inlineStr">
         <is>
           <t>Bonjour Aurélia Crémoux,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3914,7 +3962,7 @@
       <c r="L55" s="10" t="inlineStr"/>
       <c r="M55" s="10" t="inlineStr"/>
     </row>
-    <row r="56" ht="175" customHeight="1">
+    <row r="56" ht="230" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3963,12 +4011,13 @@
       <c r="J56" s="9" t="inlineStr">
         <is>
           <t>Bonjour Catherine Dallaire,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'Estrie compte encore des producteurs d'asclépiade, et une des premières usines de transformation de la fibre était à Granby.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -3977,7 +4026,7 @@
       <c r="L56" s="10" t="inlineStr"/>
       <c r="M56" s="10" t="inlineStr"/>
     </row>
-    <row r="57" ht="175" customHeight="1">
+    <row r="57" ht="230" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4044,7 +4093,7 @@
       <c r="L57" s="10" t="inlineStr"/>
       <c r="M57" s="10" t="inlineStr"/>
     </row>
-    <row r="58" ht="175" customHeight="1">
+    <row r="58" ht="230" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4093,12 +4142,13 @@
       <c r="J58" s="9" t="inlineStr">
         <is>
           <t>Bonjour Anaïs Desjardins,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4107,7 +4157,7 @@
       <c r="L58" s="10" t="inlineStr"/>
       <c r="M58" s="10" t="inlineStr"/>
     </row>
-    <row r="59" ht="175" customHeight="1">
+    <row r="59" ht="230" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4156,12 +4206,13 @@
       <c r="J59" s="9" t="inlineStr">
         <is>
           <t>Bonjour Simon Dominé,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4170,7 +4221,7 @@
       <c r="L59" s="10" t="inlineStr"/>
       <c r="M59" s="10" t="inlineStr"/>
     </row>
-    <row r="60" ht="175" customHeight="1">
+    <row r="60" ht="230" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4219,8 +4270,10 @@
       <c r="J60" s="9" t="inlineStr">
         <is>
           <t>Bonjour Karl-Ivann Dubé,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -4232,7 +4285,7 @@
       <c r="L60" s="10" t="inlineStr"/>
       <c r="M60" s="10" t="inlineStr"/>
     </row>
-    <row r="61" ht="175" customHeight="1">
+    <row r="61" ht="230" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4281,8 +4334,10 @@
       <c r="J61" s="9" t="inlineStr">
         <is>
           <t>Bonjour André Fauteux,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -4294,7 +4349,7 @@
       <c r="L61" s="10" t="inlineStr"/>
       <c r="M61" s="10" t="inlineStr"/>
     </row>
-    <row r="62" ht="175" customHeight="1">
+    <row r="62" ht="230" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4343,12 +4398,13 @@
       <c r="J62" s="9" t="inlineStr">
         <is>
           <t>Bonjour Myriam Fimbry,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4357,7 +4413,7 @@
       <c r="L62" s="10" t="inlineStr"/>
       <c r="M62" s="10" t="inlineStr"/>
     </row>
-    <row r="63" ht="175" customHeight="1">
+    <row r="63" ht="230" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4406,8 +4462,10 @@
       <c r="J63" s="9" t="inlineStr">
         <is>
           <t>Bonjour Étienne Fortin-Gauthier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -4419,7 +4477,7 @@
       <c r="L63" s="10" t="inlineStr"/>
       <c r="M63" s="10" t="inlineStr"/>
     </row>
-    <row r="64" ht="175" customHeight="1">
+    <row r="64" ht="230" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4468,9 +4526,10 @@
       <c r="J64" s="9" t="inlineStr">
         <is>
           <t>Bonjour Johanne Fournier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est une vivace indigène qui pousse avec peu d'intrants, ce qui en fait une culture intéressante pour des régions où les grandes cultures rendent mal.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -4482,7 +4541,7 @@
       <c r="L64" s="10" t="inlineStr"/>
       <c r="M64" s="10" t="inlineStr"/>
     </row>
-    <row r="65" ht="175" customHeight="1">
+    <row r="65" ht="230" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4531,12 +4590,13 @@
       <c r="J65" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jean Garon,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4545,7 +4605,7 @@
       <c r="L65" s="10" t="inlineStr"/>
       <c r="M65" s="10" t="inlineStr"/>
     </row>
-    <row r="66" ht="175" customHeight="1">
+    <row r="66" ht="230" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4594,8 +4654,10 @@
       <c r="J66" s="9" t="inlineStr">
         <is>
           <t>Bonjour Cécile Gladel,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -4607,7 +4669,7 @@
       <c r="L66" s="10" t="inlineStr"/>
       <c r="M66" s="10" t="inlineStr"/>
     </row>
-    <row r="67" ht="175" customHeight="1">
+    <row r="67" ht="230" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4656,12 +4718,13 @@
       <c r="J67" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marieke Glorieux-Stryckman,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4670,7 +4733,7 @@
       <c r="L67" s="10" t="inlineStr"/>
       <c r="M67" s="10" t="inlineStr"/>
     </row>
-    <row r="68" ht="175" customHeight="1">
+    <row r="68" ht="230" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4719,12 +4782,13 @@
       <c r="J68" s="9" t="inlineStr">
         <is>
           <t>Bonjour Maude Goyer,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4733,7 +4797,7 @@
       <c r="L68" s="10" t="inlineStr"/>
       <c r="M68" s="10" t="inlineStr"/>
     </row>
-    <row r="69" ht="175" customHeight="1">
+    <row r="69" ht="230" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4782,12 +4846,13 @@
       <c r="J69" s="9" t="inlineStr">
         <is>
           <t>Bonjour Pauline Gravel,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4796,7 +4861,7 @@
       <c r="L69" s="10" t="inlineStr"/>
       <c r="M69" s="10" t="inlineStr"/>
     </row>
-    <row r="70" ht="175" customHeight="1">
+    <row r="70" ht="230" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4845,9 +4910,10 @@
       <c r="J70" s="9" t="inlineStr">
         <is>
           <t>Bonjour Bernard Hervieux,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -4859,7 +4925,7 @@
       <c r="L70" s="10" t="inlineStr"/>
       <c r="M70" s="10" t="inlineStr"/>
     </row>
-    <row r="71" ht="175" customHeight="1">
+    <row r="71" ht="230" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4908,12 +4974,13 @@
       <c r="J71" s="9" t="inlineStr">
         <is>
           <t>Bonjour Leïla Jolin-Dahel,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4922,7 +4989,7 @@
       <c r="L71" s="10" t="inlineStr"/>
       <c r="M71" s="10" t="inlineStr"/>
     </row>
-    <row r="72" ht="175" customHeight="1">
+    <row r="72" ht="230" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4971,12 +5038,13 @@
       <c r="J72" s="9" t="inlineStr">
         <is>
           <t>Bonjour Kodjo Edjinam Nulagnon LOGO,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est une vivace indigène qui pousse avec peu d'intrants, ce qui en fait une culture intéressante pour des régions où les grandes cultures rendent mal.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -4985,7 +5053,7 @@
       <c r="L72" s="10" t="inlineStr"/>
       <c r="M72" s="10" t="inlineStr"/>
     </row>
-    <row r="73" ht="175" customHeight="1">
+    <row r="73" ht="230" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5034,12 +5102,13 @@
       <c r="J73" s="9" t="inlineStr">
         <is>
           <t>Bonjour Annie Labrecque,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5048,7 +5117,7 @@
       <c r="L73" s="10" t="inlineStr"/>
       <c r="M73" s="10" t="inlineStr"/>
     </row>
-    <row r="74" ht="175" customHeight="1">
+    <row r="74" ht="230" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5097,9 +5166,10 @@
       <c r="J74" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marianne Lachapelle,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'Estrie compte encore des producteurs d'asclépiade, et une des premières usines de transformation de la fibre était à Granby.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -5111,7 +5181,7 @@
       <c r="L74" s="10" t="inlineStr"/>
       <c r="M74" s="10" t="inlineStr"/>
     </row>
-    <row r="75" ht="175" customHeight="1">
+    <row r="75" ht="230" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5160,12 +5230,13 @@
       <c r="J75" s="9" t="inlineStr">
         <is>
           <t>Bonjour Sophie Lachapelle,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5174,7 +5245,7 @@
       <c r="L75" s="10" t="inlineStr"/>
       <c r="M75" s="10" t="inlineStr"/>
     </row>
-    <row r="76" ht="175" customHeight="1">
+    <row r="76" ht="230" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5223,9 +5294,10 @@
       <c r="J76" s="9" t="inlineStr">
         <is>
           <t>Bonjour Alain Laforest,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -5237,7 +5309,7 @@
       <c r="L76" s="10" t="inlineStr"/>
       <c r="M76" s="10" t="inlineStr"/>
     </row>
-    <row r="77" ht="175" customHeight="1">
+    <row r="77" ht="230" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5286,9 +5358,10 @@
       <c r="J77" s="9" t="inlineStr">
         <is>
           <t>Bonjour Mikaël Lalancette,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -5300,7 +5373,7 @@
       <c r="L77" s="10" t="inlineStr"/>
       <c r="M77" s="10" t="inlineStr"/>
     </row>
-    <row r="78" ht="175" customHeight="1">
+    <row r="78" ht="230" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5349,12 +5422,13 @@
       <c r="J78" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jean-Luc Lavallée,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5363,7 +5437,7 @@
       <c r="L78" s="10" t="inlineStr"/>
       <c r="M78" s="10" t="inlineStr"/>
     </row>
-    <row r="79" ht="175" customHeight="1">
+    <row r="79" ht="230" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5412,12 +5486,13 @@
       <c r="J79" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jean-Francois Leblanc,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5426,7 +5501,7 @@
       <c r="L79" s="10" t="inlineStr"/>
       <c r="M79" s="10" t="inlineStr"/>
     </row>
-    <row r="80" ht="175" customHeight="1">
+    <row r="80" ht="230" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5475,12 +5550,13 @@
       <c r="J80" s="9" t="inlineStr">
         <is>
           <t>Bonjour Julie Leduc,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5489,7 +5565,7 @@
       <c r="L80" s="10" t="inlineStr"/>
       <c r="M80" s="10" t="inlineStr"/>
     </row>
-    <row r="81" ht="175" customHeight="1">
+    <row r="81" ht="230" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5538,12 +5614,13 @@
       <c r="J81" s="9" t="inlineStr">
         <is>
           <t>Bonjour Annie Martin,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5552,7 +5629,7 @@
       <c r="L81" s="10" t="inlineStr"/>
       <c r="M81" s="10" t="inlineStr"/>
     </row>
-    <row r="82" ht="175" customHeight="1">
+    <row r="82" ht="230" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5620,7 +5697,7 @@
       <c r="L82" s="10" t="inlineStr"/>
       <c r="M82" s="10" t="inlineStr"/>
     </row>
-    <row r="83" ht="175" customHeight="1">
+    <row r="83" ht="230" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5669,12 +5746,13 @@
       <c r="J83" s="9" t="inlineStr">
         <is>
           <t>Bonjour Charles Mathieu,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5683,7 +5761,7 @@
       <c r="L83" s="10" t="inlineStr"/>
       <c r="M83" s="10" t="inlineStr"/>
     </row>
-    <row r="84" ht="175" customHeight="1">
+    <row r="84" ht="230" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5732,12 +5810,13 @@
       <c r="J84" s="9" t="inlineStr">
         <is>
           <t>Bonjour Clara Matthey-Jonais,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5746,7 +5825,7 @@
       <c r="L84" s="10" t="inlineStr"/>
       <c r="M84" s="10" t="inlineStr"/>
     </row>
-    <row r="85" ht="175" customHeight="1">
+    <row r="85" ht="230" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5795,12 +5874,13 @@
       <c r="J85" s="9" t="inlineStr">
         <is>
           <t>Bonjour Valérian Mazataud,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5809,7 +5889,7 @@
       <c r="L85" s="10" t="inlineStr"/>
       <c r="M85" s="10" t="inlineStr"/>
     </row>
-    <row r="86" ht="175" customHeight="1">
+    <row r="86" ht="230" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5858,8 +5938,10 @@
       <c r="J86" s="9" t="inlineStr">
         <is>
           <t>Bonjour Lili Mercure,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -5871,7 +5953,7 @@
       <c r="L86" s="10" t="inlineStr"/>
       <c r="M86" s="10" t="inlineStr"/>
     </row>
-    <row r="87" ht="175" customHeight="1">
+    <row r="87" ht="230" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5920,12 +6002,13 @@
       <c r="J87" s="9" t="inlineStr">
         <is>
           <t>Bonjour Nicolas Mesly,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5934,7 +6017,7 @@
       <c r="L87" s="10" t="inlineStr"/>
       <c r="M87" s="10" t="inlineStr"/>
     </row>
-    <row r="88" ht="175" customHeight="1">
+    <row r="88" ht="230" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5983,12 +6066,13 @@
       <c r="J88" s="9" t="inlineStr">
         <is>
           <t>Bonjour Nicolas Michaud,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -5997,7 +6081,7 @@
       <c r="L88" s="10" t="inlineStr"/>
       <c r="M88" s="10" t="inlineStr"/>
     </row>
-    <row r="89" ht="175" customHeight="1">
+    <row r="89" ht="230" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6046,12 +6130,13 @@
       <c r="J89" s="9" t="inlineStr">
         <is>
           <t>Bonjour Véronique Morin,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6060,7 +6145,7 @@
       <c r="L89" s="10" t="inlineStr"/>
       <c r="M89" s="10" t="inlineStr"/>
     </row>
-    <row r="90" ht="175" customHeight="1">
+    <row r="90" ht="230" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6109,8 +6194,10 @@
       <c r="J90" s="9" t="inlineStr">
         <is>
           <t>Bonjour Lila Mouch,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -6122,7 +6209,7 @@
       <c r="L90" s="10" t="inlineStr"/>
       <c r="M90" s="10" t="inlineStr"/>
     </row>
-    <row r="91" ht="175" customHeight="1">
+    <row r="91" ht="230" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6171,9 +6258,10 @@
       <c r="J91" s="9" t="inlineStr">
         <is>
           <t>Bonjour Olivier Mougeot,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -6185,7 +6273,7 @@
       <c r="L91" s="10" t="inlineStr"/>
       <c r="M91" s="10" t="inlineStr"/>
     </row>
-    <row r="92" ht="175" customHeight="1">
+    <row r="92" ht="230" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6234,12 +6322,13 @@
       <c r="J92" s="9" t="inlineStr">
         <is>
           <t>Bonjour Emmanuelle Mozayan-Verschaeve,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6248,7 +6337,7 @@
       <c r="L92" s="10" t="inlineStr"/>
       <c r="M92" s="10" t="inlineStr"/>
     </row>
-    <row r="93" ht="175" customHeight="1">
+    <row r="93" ht="230" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6297,12 +6386,13 @@
       <c r="J93" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jean-Benoît Nadeau,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6311,7 +6401,7 @@
       <c r="L93" s="10" t="inlineStr"/>
       <c r="M93" s="10" t="inlineStr"/>
     </row>
-    <row r="94" ht="175" customHeight="1">
+    <row r="94" ht="230" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6360,12 +6450,13 @@
       <c r="J94" s="9" t="inlineStr">
         <is>
           <t>Bonjour Yves Ouellet,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6374,7 +6465,7 @@
       <c r="L94" s="10" t="inlineStr"/>
       <c r="M94" s="10" t="inlineStr"/>
     </row>
-    <row r="95" ht="175" customHeight="1">
+    <row r="95" ht="230" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6423,12 +6514,13 @@
       <c r="J95" s="9" t="inlineStr">
         <is>
           <t>Bonjour Josée Panet-Raymond,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6437,7 +6529,7 @@
       <c r="L95" s="10" t="inlineStr"/>
       <c r="M95" s="10" t="inlineStr"/>
     </row>
-    <row r="96" ht="175" customHeight="1">
+    <row r="96" ht="230" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6486,12 +6578,13 @@
       <c r="J96" s="9" t="inlineStr">
         <is>
           <t>Bonjour Yannick Patelli,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6500,7 +6593,7 @@
       <c r="L96" s="10" t="inlineStr"/>
       <c r="M96" s="10" t="inlineStr"/>
     </row>
-    <row r="97" ht="175" customHeight="1">
+    <row r="97" ht="230" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6549,12 +6642,13 @@
       <c r="J97" s="9" t="inlineStr">
         <is>
           <t>Bonjour Félix Pedneault,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6563,7 +6657,7 @@
       <c r="L97" s="10" t="inlineStr"/>
       <c r="M97" s="10" t="inlineStr"/>
     </row>
-    <row r="98" ht="175" customHeight="1">
+    <row r="98" ht="230" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6612,12 +6706,13 @@
       <c r="J98" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-Eve Poulin,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est une vivace indigène qui pousse avec peu d'intrants, ce qui en fait une culture intéressante pour des régions où les grandes cultures rendent mal.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6626,7 +6721,7 @@
       <c r="L98" s="10" t="inlineStr"/>
       <c r="M98" s="10" t="inlineStr"/>
     </row>
-    <row r="99" ht="175" customHeight="1">
+    <row r="99" ht="230" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6675,12 +6770,13 @@
       <c r="J99" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-Hélène Proulx,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6689,7 +6785,7 @@
       <c r="L99" s="10" t="inlineStr"/>
       <c r="M99" s="10" t="inlineStr"/>
     </row>
-    <row r="100" ht="175" customHeight="1">
+    <row r="100" ht="230" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6738,8 +6834,10 @@
       <c r="J100" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jean-Hugues Roy,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -6751,7 +6849,7 @@
       <c r="L100" s="10" t="inlineStr"/>
       <c r="M100" s="10" t="inlineStr"/>
     </row>
-    <row r="101" ht="175" customHeight="1">
+    <row r="101" ht="230" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6800,9 +6898,10 @@
       <c r="J101" s="9" t="inlineStr">
         <is>
           <t>Bonjour Martin Roy,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Notre atelier est dans Limoilou, et c'est là que la soie d'asclépiade devient de l'isolant.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -6814,7 +6913,7 @@
       <c r="L101" s="10" t="inlineStr"/>
       <c r="M101" s="10" t="inlineStr"/>
     </row>
-    <row r="102" ht="175" customHeight="1">
+    <row r="102" ht="230" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6863,12 +6962,13 @@
       <c r="J102" s="9" t="inlineStr">
         <is>
           <t>Bonjour Sylvain Sarrazin,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6877,7 +6977,7 @@
       <c r="L102" s="10" t="inlineStr"/>
       <c r="M102" s="10" t="inlineStr"/>
     </row>
-    <row r="103" ht="175" customHeight="1">
+    <row r="103" ht="230" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6926,12 +7026,13 @@
       <c r="J103" s="9" t="inlineStr">
         <is>
           <t>Bonjour Pierre Sormany,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -6940,7 +7041,7 @@
       <c r="L103" s="10" t="inlineStr"/>
       <c r="M103" s="10" t="inlineStr"/>
     </row>
-    <row r="104" ht="175" customHeight="1">
+    <row r="104" ht="230" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6989,12 +7090,13 @@
       <c r="J104" s="9" t="inlineStr">
         <is>
           <t>Bonjour Scott Stevenson,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'Estrie compte encore des producteurs d'asclépiade, et une des premières usines de transformation de la fibre était à Granby.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7003,7 +7105,7 @@
       <c r="L104" s="10" t="inlineStr"/>
       <c r="M104" s="10" t="inlineStr"/>
     </row>
-    <row r="105" ht="175" customHeight="1">
+    <row r="105" ht="230" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7052,12 +7154,13 @@
       <c r="J105" s="9" t="inlineStr">
         <is>
           <t>Bonjour Michèle Tanganika,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7066,7 +7169,7 @@
       <c r="L105" s="10" t="inlineStr"/>
       <c r="M105" s="10" t="inlineStr"/>
     </row>
-    <row r="106" ht="175" customHeight="1">
+    <row r="106" ht="230" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7115,8 +7218,10 @@
       <c r="J106" s="9" t="inlineStr">
         <is>
           <t>Bonjour Stephane Tellier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -7128,7 +7233,7 @@
       <c r="L106" s="10" t="inlineStr"/>
       <c r="M106" s="10" t="inlineStr"/>
     </row>
-    <row r="107" ht="175" customHeight="1">
+    <row r="107" ht="230" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7177,9 +7282,10 @@
       <c r="J107" s="9" t="inlineStr">
         <is>
           <t>Bonjour Karine Tremblay,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'Estrie compte encore des producteurs d'asclépiade, et une des premières usines de transformation de la fibre était à Granby.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -7191,7 +7297,7 @@
       <c r="L107" s="10" t="inlineStr"/>
       <c r="M107" s="10" t="inlineStr"/>
     </row>
-    <row r="108" ht="175" customHeight="1">
+    <row r="108" ht="230" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7240,12 +7346,13 @@
       <c r="J108" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jean-Francois Venne,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7254,7 +7361,7 @@
       <c r="L108" s="10" t="inlineStr"/>
       <c r="M108" s="10" t="inlineStr"/>
     </row>
-    <row r="109" ht="175" customHeight="1">
+    <row r="109" ht="230" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7303,12 +7410,13 @@
       <c r="J109" s="9" t="inlineStr">
         <is>
           <t>Bonjour Shahram Yazdanpanah,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7317,7 +7425,7 @@
       <c r="L109" s="10" t="inlineStr"/>
       <c r="M109" s="10" t="inlineStr"/>
     </row>
-    <row r="110" ht="175" customHeight="1">
+    <row r="110" ht="230" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7366,12 +7474,13 @@
       <c r="J110" s="9" t="inlineStr">
         <is>
           <t>Bonjour Malika Alaoui,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7380,7 +7489,7 @@
       <c r="L110" s="10" t="inlineStr"/>
       <c r="M110" s="10" t="inlineStr"/>
     </row>
-    <row r="111" ht="175" customHeight="1">
+    <row r="111" ht="230" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7429,12 +7538,13 @@
       <c r="J111" s="9" t="inlineStr">
         <is>
           <t>Bonjour Yahia Arkat,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7443,7 +7553,7 @@
       <c r="L111" s="10" t="inlineStr"/>
       <c r="M111" s="10" t="inlineStr"/>
     </row>
-    <row r="112" ht="175" customHeight="1">
+    <row r="112" ht="230" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7492,12 +7602,13 @@
       <c r="J112" s="9" t="inlineStr">
         <is>
           <t>Bonjour MARC-OLIVIER BISSON,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7506,7 +7617,7 @@
       <c r="L112" s="10" t="inlineStr"/>
       <c r="M112" s="10" t="inlineStr"/>
     </row>
-    <row r="113" ht="175" customHeight="1">
+    <row r="113" ht="230" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7555,12 +7666,13 @@
       <c r="J113" s="9" t="inlineStr">
         <is>
           <t>Bonjour Maïté Belmir,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7569,7 +7681,7 @@
       <c r="L113" s="10" t="inlineStr"/>
       <c r="M113" s="10" t="inlineStr"/>
     </row>
-    <row r="114" ht="175" customHeight="1">
+    <row r="114" ht="230" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7618,12 +7730,13 @@
       <c r="J114" s="9" t="inlineStr">
         <is>
           <t>Bonjour André Bernard,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7632,7 +7745,7 @@
       <c r="L114" s="10" t="inlineStr"/>
       <c r="M114" s="10" t="inlineStr"/>
     </row>
-    <row r="115" ht="175" customHeight="1">
+    <row r="115" ht="230" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7681,12 +7794,13 @@
       <c r="J115" s="9" t="inlineStr">
         <is>
           <t>Bonjour Didier Bert,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7695,7 +7809,7 @@
       <c r="L115" s="10" t="inlineStr"/>
       <c r="M115" s="10" t="inlineStr"/>
     </row>
-    <row r="116" ht="175" customHeight="1">
+    <row r="116" ht="230" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7744,8 +7858,10 @@
       <c r="J116" s="9" t="inlineStr">
         <is>
           <t>Bonjour Sophie-Andrée Blondin,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -7757,7 +7873,7 @@
       <c r="L116" s="10" t="inlineStr"/>
       <c r="M116" s="10" t="inlineStr"/>
     </row>
-    <row r="117" ht="175" customHeight="1">
+    <row r="117" ht="230" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7806,9 +7922,10 @@
       <c r="J117" s="9" t="inlineStr">
         <is>
           <t>Bonjour Pierre Brochu,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'Estrie compte encore des producteurs d'asclépiade, et une des premières usines de transformation de la fibre était à Granby.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -7820,7 +7937,7 @@
       <c r="L117" s="10" t="inlineStr"/>
       <c r="M117" s="10" t="inlineStr"/>
     </row>
-    <row r="118" ht="175" customHeight="1">
+    <row r="118" ht="230" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7869,12 +7986,13 @@
       <c r="J118" s="9" t="inlineStr">
         <is>
           <t>Bonjour Gilles Bérubé,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7883,7 +8001,7 @@
       <c r="L118" s="10" t="inlineStr"/>
       <c r="M118" s="10" t="inlineStr"/>
     </row>
-    <row r="119" ht="175" customHeight="1">
+    <row r="119" ht="230" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7932,12 +8050,13 @@
       <c r="J119" s="9" t="inlineStr">
         <is>
           <t>Bonjour Daphné Cameron,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -7946,7 +8065,7 @@
       <c r="L119" s="10" t="inlineStr"/>
       <c r="M119" s="10" t="inlineStr"/>
     </row>
-    <row r="120" ht="175" customHeight="1">
+    <row r="120" ht="230" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7995,8 +8114,10 @@
       <c r="J120" s="9" t="inlineStr">
         <is>
           <t>Bonjour Godefroy Macaire Chabi,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -8008,7 +8129,7 @@
       <c r="L120" s="10" t="inlineStr"/>
       <c r="M120" s="10" t="inlineStr"/>
     </row>
-    <row r="121" ht="175" customHeight="1">
+    <row r="121" ht="230" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8057,12 +8178,13 @@
       <c r="J121" s="9" t="inlineStr">
         <is>
           <t>Bonjour Sara Champagne,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8071,7 +8193,7 @@
       <c r="L121" s="10" t="inlineStr"/>
       <c r="M121" s="10" t="inlineStr"/>
     </row>
-    <row r="122" ht="175" customHeight="1">
+    <row r="122" ht="230" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8120,12 +8242,13 @@
       <c r="J122" s="9" t="inlineStr">
         <is>
           <t>Bonjour Sarah Champagne,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8134,7 +8257,7 @@
       <c r="L122" s="10" t="inlineStr"/>
       <c r="M122" s="10" t="inlineStr"/>
     </row>
-    <row r="123" ht="175" customHeight="1">
+    <row r="123" ht="230" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8183,12 +8306,13 @@
       <c r="J123" s="9" t="inlineStr">
         <is>
           <t>Bonjour Éric-Pierre Champagne,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8197,7 +8321,7 @@
       <c r="L123" s="10" t="inlineStr"/>
       <c r="M123" s="10" t="inlineStr"/>
     </row>
-    <row r="124" ht="175" customHeight="1">
+    <row r="124" ht="230" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8246,12 +8370,13 @@
       <c r="J124" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marine Corniou,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8260,7 +8385,7 @@
       <c r="L124" s="10" t="inlineStr"/>
       <c r="M124" s="10" t="inlineStr"/>
     </row>
-    <row r="125" ht="175" customHeight="1">
+    <row r="125" ht="230" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8309,12 +8434,13 @@
       <c r="J125" s="9" t="inlineStr">
         <is>
           <t>Bonjour Catherine Crépeau,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8323,7 +8449,7 @@
       <c r="L125" s="10" t="inlineStr"/>
       <c r="M125" s="10" t="inlineStr"/>
     </row>
-    <row r="126" ht="175" customHeight="1">
+    <row r="126" ht="230" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8372,9 +8498,10 @@
       <c r="J126" s="9" t="inlineStr">
         <is>
           <t>Bonjour Laurence Dami-Houle,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est une vivace indigène qui pousse avec peu d'intrants, ce qui en fait une culture intéressante pour des régions où les grandes cultures rendent mal.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -8386,7 +8513,7 @@
       <c r="L126" s="10" t="inlineStr"/>
       <c r="M126" s="10" t="inlineStr"/>
     </row>
-    <row r="127" ht="175" customHeight="1">
+    <row r="127" ht="230" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8435,12 +8562,13 @@
       <c r="J127" s="9" t="inlineStr">
         <is>
           <t>Bonjour Amélie Daoust-Boisvert,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8449,7 +8577,7 @@
       <c r="L127" s="10" t="inlineStr"/>
       <c r="M127" s="10" t="inlineStr"/>
     </row>
-    <row r="128" ht="175" customHeight="1">
+    <row r="128" ht="230" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8498,9 +8626,10 @@
       <c r="J128" s="9" t="inlineStr">
         <is>
           <t>Bonjour Dominique Degré,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -8512,7 +8641,7 @@
       <c r="L128" s="10" t="inlineStr"/>
       <c r="M128" s="10" t="inlineStr"/>
     </row>
-    <row r="129" ht="175" customHeight="1">
+    <row r="129" ht="230" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8561,12 +8690,13 @@
       <c r="J129" s="9" t="inlineStr">
         <is>
           <t>Bonjour Quentin Dufranne,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8575,7 +8705,7 @@
       <c r="L129" s="10" t="inlineStr"/>
       <c r="M129" s="10" t="inlineStr"/>
     </row>
-    <row r="130" ht="175" customHeight="1">
+    <row r="130" ht="230" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8624,12 +8754,13 @@
       <c r="J130" s="9" t="inlineStr">
         <is>
           <t>Bonjour Ève Dumas,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8638,7 +8769,7 @@
       <c r="L130" s="10" t="inlineStr"/>
       <c r="M130" s="10" t="inlineStr"/>
     </row>
-    <row r="131" ht="175" customHeight="1">
+    <row r="131" ht="230" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8687,8 +8818,10 @@
       <c r="J131" s="9" t="inlineStr">
         <is>
           <t>Bonjour Michel Fortier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -8700,7 +8833,7 @@
       <c r="L131" s="10" t="inlineStr"/>
       <c r="M131" s="10" t="inlineStr"/>
     </row>
-    <row r="132" ht="175" customHeight="1">
+    <row r="132" ht="230" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8749,12 +8882,13 @@
       <c r="J132" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-Eve Fournier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8763,7 +8897,7 @@
       <c r="L132" s="10" t="inlineStr"/>
       <c r="M132" s="10" t="inlineStr"/>
     </row>
-    <row r="133" ht="175" customHeight="1">
+    <row r="133" ht="230" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8812,9 +8946,10 @@
       <c r="J133" s="9" t="inlineStr">
         <is>
           <t>Bonjour Raymond Fournier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -8826,7 +8961,7 @@
       <c r="L133" s="10" t="inlineStr"/>
       <c r="M133" s="10" t="inlineStr"/>
     </row>
-    <row r="134" ht="175" customHeight="1">
+    <row r="134" ht="230" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8875,12 +9010,13 @@
       <c r="J134" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-Pier Frappier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -8889,7 +9025,7 @@
       <c r="L134" s="10" t="inlineStr"/>
       <c r="M134" s="10" t="inlineStr"/>
     </row>
-    <row r="135" ht="175" customHeight="1">
+    <row r="135" ht="230" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8938,9 +9074,10 @@
       <c r="J135" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-Julie Gagnon,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -8952,7 +9089,7 @@
       <c r="L135" s="10" t="inlineStr"/>
       <c r="M135" s="10" t="inlineStr"/>
     </row>
-    <row r="136" ht="175" customHeight="1">
+    <row r="136" ht="230" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9001,12 +9138,13 @@
       <c r="J136" s="9" t="inlineStr">
         <is>
           <t>Bonjour Chloé Germain-Thérien,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec. La filière s'est cassée en 2018, mais des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9015,7 +9153,7 @@
       <c r="L136" s="10" t="inlineStr"/>
       <c r="M136" s="10" t="inlineStr"/>
     </row>
-    <row r="137" ht="175" customHeight="1">
+    <row r="137" ht="230" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9064,12 +9202,13 @@
       <c r="J137" s="9" t="inlineStr">
         <is>
           <t>Bonjour Charlotte Glorieux,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9078,7 +9217,7 @@
       <c r="L137" s="10" t="inlineStr"/>
       <c r="M137" s="10" t="inlineStr"/>
     </row>
-    <row r="138" ht="175" customHeight="1">
+    <row r="138" ht="230" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9127,12 +9266,13 @@
       <c r="J138" s="9" t="inlineStr">
         <is>
           <t>Bonjour Annie Hudon,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9141,7 +9281,7 @@
       <c r="L138" s="10" t="inlineStr"/>
       <c r="M138" s="10" t="inlineStr"/>
     </row>
-    <row r="139" ht="175" customHeight="1">
+    <row r="139" ht="230" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9190,12 +9330,13 @@
       <c r="J139" s="9" t="inlineStr">
         <is>
           <t>Bonjour Ahmed Kouaou,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9204,7 +9345,7 @@
       <c r="L139" s="10" t="inlineStr"/>
       <c r="M139" s="10" t="inlineStr"/>
     </row>
-    <row r="140" ht="175" customHeight="1">
+    <row r="140" ht="230" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9253,12 +9394,13 @@
       <c r="J140" s="9" t="inlineStr">
         <is>
           <t>Bonjour Tania Krywiak,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9267,7 +9409,7 @@
       <c r="L140" s="10" t="inlineStr"/>
       <c r="M140" s="10" t="inlineStr"/>
     </row>
-    <row r="141" ht="175" customHeight="1">
+    <row r="141" ht="230" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9316,9 +9458,10 @@
       <c r="J141" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jacinthe Lafrance,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec. La filière s'est cassée en 2018, mais des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -9330,7 +9473,7 @@
       <c r="L141" s="10" t="inlineStr"/>
       <c r="M141" s="10" t="inlineStr"/>
     </row>
-    <row r="142" ht="175" customHeight="1">
+    <row r="142" ht="230" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9379,12 +9522,13 @@
       <c r="J142" s="9" t="inlineStr">
         <is>
           <t>Bonjour Bruno Lamolet,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9393,7 +9537,7 @@
       <c r="L142" s="10" t="inlineStr"/>
       <c r="M142" s="10" t="inlineStr"/>
     </row>
-    <row r="143" ht="175" customHeight="1">
+    <row r="143" ht="230" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9442,12 +9586,13 @@
       <c r="J143" s="9" t="inlineStr">
         <is>
           <t>Bonjour Yvan Lamontagne,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'Estrie compte encore des producteurs d'asclépiade, et une des premières usines de transformation de la fibre était à Granby.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9456,7 +9601,7 @@
       <c r="L143" s="10" t="inlineStr"/>
       <c r="M143" s="10" t="inlineStr"/>
     </row>
-    <row r="144" ht="175" customHeight="1">
+    <row r="144" ht="230" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9505,12 +9650,13 @@
       <c r="J144" s="9" t="inlineStr">
         <is>
           <t>Bonjour Yves Langlois,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'Estrie compte encore des producteurs d'asclépiade, et une des premières usines de transformation de la fibre était à Granby.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9519,7 +9665,7 @@
       <c r="L144" s="10" t="inlineStr"/>
       <c r="M144" s="10" t="inlineStr"/>
     </row>
-    <row r="145" ht="175" customHeight="1">
+    <row r="145" ht="230" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9568,12 +9714,13 @@
       <c r="J145" s="9" t="inlineStr">
         <is>
           <t>Bonjour Anne Marie Lecomte,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9582,7 +9729,7 @@
       <c r="L145" s="10" t="inlineStr"/>
       <c r="M145" s="10" t="inlineStr"/>
     </row>
-    <row r="146" ht="175" customHeight="1">
+    <row r="146" ht="230" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9631,9 +9778,10 @@
       <c r="J146" s="9" t="inlineStr">
         <is>
           <t>Bonjour Stéphanie Mac Farlane,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -9645,7 +9793,7 @@
       <c r="L146" s="10" t="inlineStr"/>
       <c r="M146" s="10" t="inlineStr"/>
     </row>
-    <row r="147" ht="175" customHeight="1">
+    <row r="147" ht="230" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9694,9 +9842,10 @@
       <c r="J147" s="9" t="inlineStr">
         <is>
           <t>Bonjour Philippe Marois,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -9708,7 +9857,7 @@
       <c r="L147" s="10" t="inlineStr"/>
       <c r="M147" s="10" t="inlineStr"/>
     </row>
-    <row r="148" ht="175" customHeight="1">
+    <row r="148" ht="230" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9757,12 +9906,13 @@
       <c r="J148" s="9" t="inlineStr">
         <is>
           <t>Bonjour Gildas Meneu,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9771,7 +9921,7 @@
       <c r="L148" s="10" t="inlineStr"/>
       <c r="M148" s="10" t="inlineStr"/>
     </row>
-    <row r="149" ht="175" customHeight="1">
+    <row r="149" ht="230" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9820,8 +9970,10 @@
       <c r="J149" s="9" t="inlineStr">
         <is>
           <t>Bonjour Louis-Xavier Michaud,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -9833,7 +9985,7 @@
       <c r="L149" s="10" t="inlineStr"/>
       <c r="M149" s="10" t="inlineStr"/>
     </row>
-    <row r="150" ht="175" customHeight="1">
+    <row r="150" ht="230" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9882,12 +10034,13 @@
       <c r="J150" s="9" t="inlineStr">
         <is>
           <t>Bonjour Anne Montplaisir,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -9896,7 +10049,7 @@
       <c r="L150" s="10" t="inlineStr"/>
       <c r="M150" s="10" t="inlineStr"/>
     </row>
-    <row r="151" ht="175" customHeight="1">
+    <row r="151" ht="230" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9945,9 +10098,10 @@
       <c r="J151" s="9" t="inlineStr">
         <is>
           <t>Bonjour Karianne Nepton-Philippe,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est une vivace indigène qui pousse avec peu d'intrants, ce qui en fait une culture intéressante pour des régions où les grandes cultures rendent mal.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -9959,7 +10113,7 @@
       <c r="L151" s="10" t="inlineStr"/>
       <c r="M151" s="10" t="inlineStr"/>
     </row>
-    <row r="152" ht="175" customHeight="1">
+    <row r="152" ht="230" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10008,9 +10162,10 @@
       <c r="J152" s="9" t="inlineStr">
         <is>
           <t>Bonjour Geneviève Normand,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -10022,7 +10177,7 @@
       <c r="L152" s="10" t="inlineStr"/>
       <c r="M152" s="10" t="inlineStr"/>
     </row>
-    <row r="153" ht="175" customHeight="1">
+    <row r="153" ht="230" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10071,9 +10226,10 @@
       <c r="J153" s="9" t="inlineStr">
         <is>
           <t>Bonjour Carole Payer,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade se cultive dans votre région depuis la première vague de 2013, et plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -10085,7 +10241,7 @@
       <c r="L153" s="10" t="inlineStr"/>
       <c r="M153" s="10" t="inlineStr"/>
     </row>
-    <row r="154" ht="175" customHeight="1">
+    <row r="154" ht="230" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10134,12 +10290,13 @@
       <c r="J154" s="9" t="inlineStr">
         <is>
           <t>Bonjour Boris Proulx,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10148,7 +10305,7 @@
       <c r="L154" s="10" t="inlineStr"/>
       <c r="M154" s="10" t="inlineStr"/>
     </row>
-    <row r="155" ht="175" customHeight="1">
+    <row r="155" ht="230" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10197,12 +10354,13 @@
       <c r="J155" s="9" t="inlineStr">
         <is>
           <t>Bonjour Philippe Robitaille-Grou,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10211,7 +10369,7 @@
       <c r="L155" s="10" t="inlineStr"/>
       <c r="M155" s="10" t="inlineStr"/>
     </row>
-    <row r="156" ht="175" customHeight="1">
+    <row r="156" ht="230" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10260,12 +10418,13 @@
       <c r="J156" s="9" t="inlineStr">
         <is>
           <t>Bonjour Gwen Roley,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10274,7 +10433,7 @@
       <c r="L156" s="10" t="inlineStr"/>
       <c r="M156" s="10" t="inlineStr"/>
     </row>
-    <row r="157" ht="175" customHeight="1">
+    <row r="157" ht="230" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10323,12 +10482,13 @@
       <c r="J157" s="9" t="inlineStr">
         <is>
           <t>Bonjour Mathieu-Robert Sauvé,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10337,7 +10497,7 @@
       <c r="L157" s="10" t="inlineStr"/>
       <c r="M157" s="10" t="inlineStr"/>
     </row>
-    <row r="158" ht="175" customHeight="1">
+    <row r="158" ht="230" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10386,12 +10546,13 @@
       <c r="J158" s="9" t="inlineStr">
         <is>
           <t>Bonjour Pierre St-Arnaud,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Huit ans après l'effondrement de la première filière québécoise de l'asclépiade, on achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler des volumes, de la fenêtre de récolte et de ce qui reste à régler côté mécanisation, sans rien promettre que je ne peux pas tenir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10400,7 +10561,7 @@
       <c r="L158" s="10" t="inlineStr"/>
       <c r="M158" s="10" t="inlineStr"/>
     </row>
-    <row r="159" ht="175" customHeight="1">
+    <row r="159" ht="230" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10449,12 +10610,13 @@
       <c r="J159" s="9" t="inlineStr">
         <is>
           <t>Bonjour Katherine Tremblay,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10463,7 +10625,7 @@
       <c r="L159" s="10" t="inlineStr"/>
       <c r="M159" s="10" t="inlineStr"/>
     </row>
-    <row r="160" ht="175" customHeight="1">
+    <row r="160" ht="230" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10512,12 +10674,13 @@
       <c r="J160" s="9" t="inlineStr">
         <is>
           <t>Bonjour Michel Tremblay,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade se cultive dans votre région depuis la première vague de 2013, et plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10526,7 +10689,7 @@
       <c r="L160" s="10" t="inlineStr"/>
       <c r="M160" s="10" t="inlineStr"/>
     </row>
-    <row r="161" ht="175" customHeight="1">
+    <row r="161" ht="230" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10575,12 +10738,13 @@
       <c r="J161" s="9" t="inlineStr">
         <is>
           <t>Bonjour Martin Vallières,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10589,7 +10753,7 @@
       <c r="L161" s="10" t="inlineStr"/>
       <c r="M161" s="10" t="inlineStr"/>
     </row>
-    <row r="162" ht="175" customHeight="1">
+    <row r="162" ht="230" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10638,12 +10802,13 @@
       <c r="J162" s="9" t="inlineStr">
         <is>
           <t>Bonjour Yanick Villedieu,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10652,7 +10817,7 @@
       <c r="L162" s="10" t="inlineStr"/>
       <c r="M162" s="10" t="inlineStr"/>
     </row>
-    <row r="163" ht="175" customHeight="1">
+    <row r="163" ht="230" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -10701,12 +10866,13 @@
       <c r="J163" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jonathan Allard,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10715,7 +10881,7 @@
       <c r="L163" s="10" t="inlineStr"/>
       <c r="M163" s="10" t="inlineStr"/>
     </row>
-    <row r="164" ht="175" customHeight="1">
+    <row r="164" ht="230" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -10764,12 +10930,13 @@
       <c r="J164" s="9" t="inlineStr">
         <is>
           <t>Bonjour Anick Baribeau,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec. La filière s'est cassée en 2018, mais des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10778,7 +10945,7 @@
       <c r="L164" s="10" t="inlineStr"/>
       <c r="M164" s="10" t="inlineStr"/>
     </row>
-    <row r="165" ht="175" customHeight="1">
+    <row r="165" ht="230" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -10827,12 +10994,13 @@
       <c r="J165" s="9" t="inlineStr">
         <is>
           <t>Bonjour Félix-Antoine Beauchemin,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10841,7 +11009,7 @@
       <c r="L165" s="10" t="inlineStr"/>
       <c r="M165" s="10" t="inlineStr"/>
     </row>
-    <row r="166" ht="175" customHeight="1">
+    <row r="166" ht="230" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -10890,12 +11058,13 @@
       <c r="J166" s="9" t="inlineStr">
         <is>
           <t>Bonjour Karim Benessaieh,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10904,7 +11073,7 @@
       <c r="L166" s="10" t="inlineStr"/>
       <c r="M166" s="10" t="inlineStr"/>
     </row>
-    <row r="167" ht="175" customHeight="1">
+    <row r="167" ht="230" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -10953,12 +11122,13 @@
       <c r="J167" s="9" t="inlineStr">
         <is>
           <t>Bonjour Julia Bernier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade se cultive dans votre région depuis la première vague de 2013, et plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -10967,7 +11137,7 @@
       <c r="L167" s="10" t="inlineStr"/>
       <c r="M167" s="10" t="inlineStr"/>
     </row>
-    <row r="168" ht="175" customHeight="1">
+    <row r="168" ht="230" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11016,12 +11186,13 @@
       <c r="J168" s="9" t="inlineStr">
         <is>
           <t>Bonjour Karine Boivin Forcier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11030,7 +11201,7 @@
       <c r="L168" s="10" t="inlineStr"/>
       <c r="M168" s="10" t="inlineStr"/>
     </row>
-    <row r="169" ht="175" customHeight="1">
+    <row r="169" ht="230" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11079,8 +11250,10 @@
       <c r="J169" s="9" t="inlineStr">
         <is>
           <t>Bonjour Audrey Bonaque,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -11092,7 +11265,7 @@
       <c r="L169" s="10" t="inlineStr"/>
       <c r="M169" s="10" t="inlineStr"/>
     </row>
-    <row r="170" ht="175" customHeight="1">
+    <row r="170" ht="230" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11141,12 +11314,13 @@
       <c r="J170" s="9" t="inlineStr">
         <is>
           <t>Bonjour Luc Boulanger,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11155,7 +11329,7 @@
       <c r="L170" s="10" t="inlineStr"/>
       <c r="M170" s="10" t="inlineStr"/>
     </row>
-    <row r="171" ht="175" customHeight="1">
+    <row r="171" ht="230" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11204,8 +11378,10 @@
       <c r="J171" s="9" t="inlineStr">
         <is>
           <t>Bonjour Mario Boulianne,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -11217,7 +11393,7 @@
       <c r="L171" s="10" t="inlineStr"/>
       <c r="M171" s="10" t="inlineStr"/>
     </row>
-    <row r="172" ht="175" customHeight="1">
+    <row r="172" ht="230" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11266,12 +11442,13 @@
       <c r="J172" s="9" t="inlineStr">
         <is>
           <t>Bonjour Bernard Brault,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11280,7 +11457,7 @@
       <c r="L172" s="10" t="inlineStr"/>
       <c r="M172" s="10" t="inlineStr"/>
     </row>
-    <row r="173" ht="175" customHeight="1">
+    <row r="173" ht="230" customHeight="1">
       <c r="A173" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11329,12 +11506,13 @@
       <c r="J173" s="9" t="inlineStr">
         <is>
           <t>Bonjour Pierre Brisson,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11343,7 +11521,7 @@
       <c r="L173" s="10" t="inlineStr"/>
       <c r="M173" s="10" t="inlineStr"/>
     </row>
-    <row r="174" ht="175" customHeight="1">
+    <row r="174" ht="230" customHeight="1">
       <c r="A174" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11392,8 +11570,10 @@
       <c r="J174" s="9" t="inlineStr">
         <is>
           <t>Bonjour Laurence Brisson Dubreuil,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -11405,7 +11585,7 @@
       <c r="L174" s="10" t="inlineStr"/>
       <c r="M174" s="10" t="inlineStr"/>
     </row>
-    <row r="175" ht="175" customHeight="1">
+    <row r="175" ht="230" customHeight="1">
       <c r="A175" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11454,8 +11634,10 @@
       <c r="J175" s="9" t="inlineStr">
         <is>
           <t>Bonjour Nathaniel Bronner,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -11467,7 +11649,7 @@
       <c r="L175" s="10" t="inlineStr"/>
       <c r="M175" s="10" t="inlineStr"/>
     </row>
-    <row r="176" ht="175" customHeight="1">
+    <row r="176" ht="230" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11516,12 +11698,13 @@
       <c r="J176" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-France Bélanger,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11530,7 +11713,7 @@
       <c r="L176" s="10" t="inlineStr"/>
       <c r="M176" s="10" t="inlineStr"/>
     </row>
-    <row r="177" ht="175" customHeight="1">
+    <row r="177" ht="230" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11579,12 +11762,13 @@
       <c r="J177" s="9" t="inlineStr">
         <is>
           <t>Bonjour Diane Bérard,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11593,7 +11777,7 @@
       <c r="L177" s="10" t="inlineStr"/>
       <c r="M177" s="10" t="inlineStr"/>
     </row>
-    <row r="178" ht="175" customHeight="1">
+    <row r="178" ht="230" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11642,12 +11826,13 @@
       <c r="J178" s="9" t="inlineStr">
         <is>
           <t>Bonjour Julien Cayouette,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11656,7 +11841,7 @@
       <c r="L178" s="10" t="inlineStr"/>
       <c r="M178" s="10" t="inlineStr"/>
     </row>
-    <row r="179" ht="175" customHeight="1">
+    <row r="179" ht="230" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11705,8 +11890,10 @@
       <c r="J179" s="9" t="inlineStr">
         <is>
           <t>Bonjour Rudy Chabannes,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -11718,7 +11905,7 @@
       <c r="L179" s="10" t="inlineStr"/>
       <c r="M179" s="10" t="inlineStr"/>
     </row>
-    <row r="180" ht="175" customHeight="1">
+    <row r="180" ht="230" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11767,8 +11954,10 @@
       <c r="J180" s="9" t="inlineStr">
         <is>
           <t>Bonjour Denis-Martin Chabot,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -11780,7 +11969,7 @@
       <c r="L180" s="10" t="inlineStr"/>
       <c r="M180" s="10" t="inlineStr"/>
     </row>
-    <row r="181" ht="175" customHeight="1">
+    <row r="181" ht="230" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11829,8 +12018,10 @@
       <c r="J181" s="9" t="inlineStr">
         <is>
           <t>Bonjour Loubna Majda Chourouk,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -11842,7 +12033,7 @@
       <c r="L181" s="10" t="inlineStr"/>
       <c r="M181" s="10" t="inlineStr"/>
     </row>
-    <row r="182" ht="175" customHeight="1">
+    <row r="182" ht="230" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11891,12 +12082,13 @@
       <c r="J182" s="9" t="inlineStr">
         <is>
           <t>Bonjour Sarah Collardey,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -11905,7 +12097,7 @@
       <c r="L182" s="10" t="inlineStr"/>
       <c r="M182" s="10" t="inlineStr"/>
     </row>
-    <row r="183" ht="175" customHeight="1">
+    <row r="183" ht="230" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11954,9 +12146,10 @@
       <c r="J183" s="9" t="inlineStr">
         <is>
           <t>Bonjour Kathleen Couillard,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -11968,7 +12161,7 @@
       <c r="L183" s="10" t="inlineStr"/>
       <c r="M183" s="10" t="inlineStr"/>
     </row>
-    <row r="184" ht="175" customHeight="1">
+    <row r="184" ht="230" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12017,12 +12210,13 @@
       <c r="J184" s="9" t="inlineStr">
         <is>
           <t>Bonjour Oumou DIAKITÉ,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12031,7 +12225,7 @@
       <c r="L184" s="10" t="inlineStr"/>
       <c r="M184" s="10" t="inlineStr"/>
     </row>
-    <row r="185" ht="175" customHeight="1">
+    <row r="185" ht="230" customHeight="1">
       <c r="A185" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12080,12 +12274,13 @@
       <c r="J185" s="9" t="inlineStr">
         <is>
           <t>Bonjour Agnès Delavault,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12094,7 +12289,7 @@
       <c r="L185" s="10" t="inlineStr"/>
       <c r="M185" s="10" t="inlineStr"/>
     </row>
-    <row r="186" ht="175" customHeight="1">
+    <row r="186" ht="230" customHeight="1">
       <c r="A186" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12143,12 +12338,13 @@
       <c r="J186" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marcelin Delice,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12157,7 +12353,7 @@
       <c r="L186" s="10" t="inlineStr"/>
       <c r="M186" s="10" t="inlineStr"/>
     </row>
-    <row r="187" ht="175" customHeight="1">
+    <row r="187" ht="230" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12206,12 +12402,13 @@
       <c r="J187" s="9" t="inlineStr">
         <is>
           <t>Bonjour Alain Demers,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La soie d'asclépiade est une fibre creuse et naturellement hydrophobe attachée aux graines de la plante. On en fait l'isolant de nos manteaux, de nos mitaines et de nos sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester la fibre plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Et si vous voulez tester plutôt que me croire sur parole, je vous envoie un produit avec plaisir.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12220,7 +12417,7 @@
       <c r="L187" s="10" t="inlineStr"/>
       <c r="M187" s="10" t="inlineStr"/>
     </row>
-    <row r="188" ht="175" customHeight="1">
+    <row r="188" ht="230" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12269,12 +12466,13 @@
       <c r="J188" s="9" t="inlineStr">
         <is>
           <t>Bonjour Ivanoh Demers,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12283,7 +12481,7 @@
       <c r="L188" s="10" t="inlineStr"/>
       <c r="M188" s="10" t="inlineStr"/>
     </row>
-    <row r="189" ht="175" customHeight="1">
+    <row r="189" ht="230" customHeight="1">
       <c r="A189" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12332,12 +12530,13 @@
       <c r="J189" s="9" t="inlineStr">
         <is>
           <t>Bonjour Claude Deschênes,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12346,7 +12545,7 @@
       <c r="L189" s="10" t="inlineStr"/>
       <c r="M189" s="10" t="inlineStr"/>
     </row>
-    <row r="190" ht="175" customHeight="1">
+    <row r="190" ht="230" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12395,9 +12594,10 @@
       <c r="J190" s="9" t="inlineStr">
         <is>
           <t>Bonjour Thomas Deshaies,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'Estrie compte encore des producteurs d'asclépiade, et une des premières usines de transformation de la fibre était à Granby.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -12409,7 +12609,7 @@
       <c r="L190" s="10" t="inlineStr"/>
       <c r="M190" s="10" t="inlineStr"/>
     </row>
-    <row r="191" ht="175" customHeight="1">
+    <row r="191" ht="230" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12458,12 +12658,13 @@
       <c r="J191" s="9" t="inlineStr">
         <is>
           <t>Bonjour Claude Desjardins,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12472,7 +12673,7 @@
       <c r="L191" s="10" t="inlineStr"/>
       <c r="M191" s="10" t="inlineStr"/>
     </row>
-    <row r="192" ht="175" customHeight="1">
+    <row r="192" ht="230" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12521,12 +12722,13 @@
       <c r="J192" s="9" t="inlineStr">
         <is>
           <t>Bonjour Martine Deslauriers,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12535,7 +12737,7 @@
       <c r="L192" s="10" t="inlineStr"/>
       <c r="M192" s="10" t="inlineStr"/>
     </row>
-    <row r="193" ht="175" customHeight="1">
+    <row r="193" ht="230" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12584,8 +12786,10 @@
       <c r="J193" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-Claude Di Lillo,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -12597,7 +12801,7 @@
       <c r="L193" s="10" t="inlineStr"/>
       <c r="M193" s="10" t="inlineStr"/>
     </row>
-    <row r="194" ht="175" customHeight="1">
+    <row r="194" ht="230" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12646,8 +12850,10 @@
       <c r="J194" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jean-René Dufort,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -12659,7 +12865,7 @@
       <c r="L194" s="10" t="inlineStr"/>
       <c r="M194" s="10" t="inlineStr"/>
     </row>
-    <row r="195" ht="175" customHeight="1">
+    <row r="195" ht="230" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12708,12 +12914,13 @@
       <c r="J195" s="9" t="inlineStr">
         <is>
           <t>Bonjour Richard Dupaul,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12722,7 +12929,7 @@
       <c r="L195" s="10" t="inlineStr"/>
       <c r="M195" s="10" t="inlineStr"/>
     </row>
-    <row r="196" ht="175" customHeight="1">
+    <row r="196" ht="230" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12771,12 +12978,13 @@
       <c r="J196" s="9" t="inlineStr">
         <is>
           <t>Bonjour Stéphanie Dupuis,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12785,7 +12993,7 @@
       <c r="L196" s="10" t="inlineStr"/>
       <c r="M196" s="10" t="inlineStr"/>
     </row>
-    <row r="197" ht="175" customHeight="1">
+    <row r="197" ht="230" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12834,12 +13042,13 @@
       <c r="J197" s="9" t="inlineStr">
         <is>
           <t>Bonjour Maxim Fauteux,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12848,7 +13057,7 @@
       <c r="L197" s="10" t="inlineStr"/>
       <c r="M197" s="10" t="inlineStr"/>
     </row>
-    <row r="198" ht="175" customHeight="1">
+    <row r="198" ht="230" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12897,8 +13106,10 @@
       <c r="J198" s="9" t="inlineStr">
         <is>
           <t>Bonjour Ronald Georges,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -12910,7 +13121,7 @@
       <c r="L198" s="10" t="inlineStr"/>
       <c r="M198" s="10" t="inlineStr"/>
     </row>
-    <row r="199" ht="175" customHeight="1">
+    <row r="199" ht="230" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12959,12 +13170,13 @@
       <c r="J199" s="9" t="inlineStr">
         <is>
           <t>Bonjour Stéphane Giroux,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -12973,7 +13185,7 @@
       <c r="L199" s="10" t="inlineStr"/>
       <c r="M199" s="10" t="inlineStr"/>
     </row>
-    <row r="200" ht="175" customHeight="1">
+    <row r="200" ht="230" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13022,12 +13234,13 @@
       <c r="J200" s="9" t="inlineStr">
         <is>
           <t>Bonjour Zacharie Goudreault,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13036,7 +13249,7 @@
       <c r="L200" s="10" t="inlineStr"/>
       <c r="M200" s="10" t="inlineStr"/>
     </row>
-    <row r="201" ht="175" customHeight="1">
+    <row r="201" ht="230" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13085,12 +13298,13 @@
       <c r="J201" s="9" t="inlineStr">
         <is>
           <t>Bonjour Isabelle Grégoire,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13099,7 +13313,7 @@
       <c r="L201" s="10" t="inlineStr"/>
       <c r="M201" s="10" t="inlineStr"/>
     </row>
-    <row r="202" ht="175" customHeight="1">
+    <row r="202" ht="230" customHeight="1">
       <c r="A202" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13148,12 +13362,13 @@
       <c r="J202" s="9" t="inlineStr">
         <is>
           <t>Bonjour Chantal Guy,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13162,7 +13377,7 @@
       <c r="L202" s="10" t="inlineStr"/>
       <c r="M202" s="10" t="inlineStr"/>
     </row>
-    <row r="203" ht="175" customHeight="1">
+    <row r="203" ht="230" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13211,12 +13426,13 @@
       <c r="J203" s="9" t="inlineStr">
         <is>
           <t>Bonjour Matthieu Hains,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13225,7 +13441,7 @@
       <c r="L203" s="10" t="inlineStr"/>
       <c r="M203" s="10" t="inlineStr"/>
     </row>
-    <row r="204" ht="175" customHeight="1">
+    <row r="204" ht="230" customHeight="1">
       <c r="A204" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13280,7 +13496,7 @@
       <c r="L204" s="10" t="inlineStr"/>
       <c r="M204" s="10" t="inlineStr"/>
     </row>
-    <row r="205" ht="175" customHeight="1">
+    <row r="205" ht="230" customHeight="1">
       <c r="A205" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13329,12 +13545,13 @@
       <c r="J205" s="9" t="inlineStr">
         <is>
           <t>Bonjour ANGELO JEAN-BAPTISTE,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13343,7 +13560,7 @@
       <c r="L205" s="10" t="inlineStr"/>
       <c r="M205" s="10" t="inlineStr"/>
     </row>
-    <row r="206" ht="175" customHeight="1">
+    <row r="206" ht="230" customHeight="1">
       <c r="A206" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13392,12 +13609,13 @@
       <c r="J206" s="9" t="inlineStr">
         <is>
           <t>Bonjour Andréanne Joly,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13406,7 +13624,7 @@
       <c r="L206" s="10" t="inlineStr"/>
       <c r="M206" s="10" t="inlineStr"/>
     </row>
-    <row r="207" ht="175" customHeight="1">
+    <row r="207" ht="230" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13455,12 +13673,13 @@
       <c r="J207" s="9" t="inlineStr">
         <is>
           <t>Bonjour Hugo Joncas,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13469,7 +13688,7 @@
       <c r="L207" s="10" t="inlineStr"/>
       <c r="M207" s="10" t="inlineStr"/>
     </row>
-    <row r="208" ht="175" customHeight="1">
+    <row r="208" ht="230" customHeight="1">
       <c r="A208" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13518,8 +13737,10 @@
       <c r="J208" s="9" t="inlineStr">
         <is>
           <t>Bonjour Philémon La Frenière-Prémont,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -13531,7 +13752,7 @@
       <c r="L208" s="10" t="inlineStr"/>
       <c r="M208" s="10" t="inlineStr"/>
     </row>
-    <row r="209" ht="175" customHeight="1">
+    <row r="209" ht="230" customHeight="1">
       <c r="A209" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13580,8 +13801,10 @@
       <c r="J209" s="9" t="inlineStr">
         <is>
           <t>Bonjour Henri Laban,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -13593,7 +13816,7 @@
       <c r="L209" s="10" t="inlineStr"/>
       <c r="M209" s="10" t="inlineStr"/>
     </row>
-    <row r="210" ht="175" customHeight="1">
+    <row r="210" ht="230" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13648,7 +13871,7 @@
       <c r="L210" s="10" t="inlineStr"/>
       <c r="M210" s="10" t="inlineStr"/>
     </row>
-    <row r="211" ht="175" customHeight="1">
+    <row r="211" ht="230" customHeight="1">
       <c r="A211" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13697,12 +13920,13 @@
       <c r="J211" s="9" t="inlineStr">
         <is>
           <t>Bonjour Joannie Lafrenière,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13711,7 +13935,7 @@
       <c r="L211" s="10" t="inlineStr"/>
       <c r="M211" s="10" t="inlineStr"/>
     </row>
-    <row r="212" ht="175" customHeight="1">
+    <row r="212" ht="230" customHeight="1">
       <c r="A212" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13760,12 +13984,13 @@
       <c r="J212" s="9" t="inlineStr">
         <is>
           <t>Bonjour Angie Landry,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13774,7 +13999,7 @@
       <c r="L212" s="10" t="inlineStr"/>
       <c r="M212" s="10" t="inlineStr"/>
     </row>
-    <row r="213" ht="175" customHeight="1">
+    <row r="213" ht="230" customHeight="1">
       <c r="A213" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13823,12 +14048,13 @@
       <c r="J213" s="9" t="inlineStr">
         <is>
           <t>Bonjour Camille Langlade,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13837,7 +14063,7 @@
       <c r="L213" s="10" t="inlineStr"/>
       <c r="M213" s="10" t="inlineStr"/>
     </row>
-    <row r="214" ht="175" customHeight="1">
+    <row r="214" ht="230" customHeight="1">
       <c r="A214" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13886,8 +14112,10 @@
       <c r="J214" s="9" t="inlineStr">
         <is>
           <t>Bonjour Claudia Larochelle,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -13899,7 +14127,7 @@
       <c r="L214" s="10" t="inlineStr"/>
       <c r="M214" s="10" t="inlineStr"/>
     </row>
-    <row r="215" ht="175" customHeight="1">
+    <row r="215" ht="230" customHeight="1">
       <c r="A215" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13948,12 +14176,13 @@
       <c r="J215" s="9" t="inlineStr">
         <is>
           <t>Bonjour Étienne Leblanc,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -13962,7 +14191,7 @@
       <c r="L215" s="10" t="inlineStr"/>
       <c r="M215" s="10" t="inlineStr"/>
     </row>
-    <row r="216" ht="175" customHeight="1">
+    <row r="216" ht="230" customHeight="1">
       <c r="A216" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14011,12 +14240,13 @@
       <c r="J216" s="9" t="inlineStr">
         <is>
           <t>Bonjour Louise Leduc,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14025,7 +14255,7 @@
       <c r="L216" s="10" t="inlineStr"/>
       <c r="M216" s="10" t="inlineStr"/>
     </row>
-    <row r="217" ht="175" customHeight="1">
+    <row r="217" ht="230" customHeight="1">
       <c r="A217" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14074,12 +14304,13 @@
       <c r="J217" s="9" t="inlineStr">
         <is>
           <t>Bonjour Guillaume Longuépée,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14088,7 +14319,7 @@
       <c r="L217" s="10" t="inlineStr"/>
       <c r="M217" s="10" t="inlineStr"/>
     </row>
-    <row r="218" ht="175" customHeight="1">
+    <row r="218" ht="230" customHeight="1">
       <c r="A218" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14137,12 +14368,13 @@
       <c r="J218" s="9" t="inlineStr">
         <is>
           <t>Bonjour Roxane Léouzon,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14151,7 +14383,7 @@
       <c r="L218" s="10" t="inlineStr"/>
       <c r="M218" s="10" t="inlineStr"/>
     </row>
-    <row r="219" ht="175" customHeight="1">
+    <row r="219" ht="230" customHeight="1">
       <c r="A219" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14200,8 +14432,10 @@
       <c r="J219" s="9" t="inlineStr">
         <is>
           <t>Bonjour Ève Lévesque,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -14213,7 +14447,7 @@
       <c r="L219" s="10" t="inlineStr"/>
       <c r="M219" s="10" t="inlineStr"/>
     </row>
-    <row r="220" ht="175" customHeight="1">
+    <row r="220" ht="230" customHeight="1">
       <c r="A220" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14262,8 +14496,10 @@
       <c r="J220" s="9" t="inlineStr">
         <is>
           <t>Bonjour Sophie Mangado,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -14275,7 +14511,7 @@
       <c r="L220" s="10" t="inlineStr"/>
       <c r="M220" s="10" t="inlineStr"/>
     </row>
-    <row r="221" ht="175" customHeight="1">
+    <row r="221" ht="230" customHeight="1">
       <c r="A221" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14324,12 +14560,13 @@
       <c r="J221" s="9" t="inlineStr">
         <is>
           <t>Bonjour Colin McGregor,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14338,7 +14575,7 @@
       <c r="L221" s="10" t="inlineStr"/>
       <c r="M221" s="10" t="inlineStr"/>
     </row>
-    <row r="222" ht="175" customHeight="1">
+    <row r="222" ht="230" customHeight="1">
       <c r="A222" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14387,12 +14624,13 @@
       <c r="J222" s="9" t="inlineStr">
         <is>
           <t>Bonjour Isabelle Morin,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14401,7 +14639,7 @@
       <c r="L222" s="10" t="inlineStr"/>
       <c r="M222" s="10" t="inlineStr"/>
     </row>
-    <row r="223" ht="175" customHeight="1">
+    <row r="223" ht="230" customHeight="1">
       <c r="A223" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14450,12 +14688,13 @@
       <c r="J223" s="9" t="inlineStr">
         <is>
           <t>Bonjour Timothy Morson,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade se cultive dans votre région depuis la première vague de 2013, et plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14464,7 +14703,7 @@
       <c r="L223" s="10" t="inlineStr"/>
       <c r="M223" s="10" t="inlineStr"/>
     </row>
-    <row r="224" ht="175" customHeight="1">
+    <row r="224" ht="230" customHeight="1">
       <c r="A224" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14513,12 +14752,13 @@
       <c r="J224" s="9" t="inlineStr">
         <is>
           <t>Bonjour Rachid Najahi,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14527,7 +14767,7 @@
       <c r="L224" s="10" t="inlineStr"/>
       <c r="M224" s="10" t="inlineStr"/>
     </row>
-    <row r="225" ht="175" customHeight="1">
+    <row r="225" ht="230" customHeight="1">
       <c r="A225" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14576,8 +14816,10 @@
       <c r="J225" s="9" t="inlineStr">
         <is>
           <t>Bonjour Richard Olivier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -14589,7 +14831,7 @@
       <c r="L225" s="10" t="inlineStr"/>
       <c r="M225" s="10" t="inlineStr"/>
     </row>
-    <row r="226" ht="175" customHeight="1">
+    <row r="226" ht="230" customHeight="1">
       <c r="A226" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14638,9 +14880,10 @@
       <c r="J226" s="9" t="inlineStr">
         <is>
           <t>Bonjour MELISSA PELLETIER,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -14652,7 +14895,7 @@
       <c r="L226" s="10" t="inlineStr"/>
       <c r="M226" s="10" t="inlineStr"/>
     </row>
-    <row r="227" ht="175" customHeight="1">
+    <row r="227" ht="230" customHeight="1">
       <c r="A227" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14701,9 +14944,10 @@
       <c r="J227" s="9" t="inlineStr">
         <is>
           <t>Bonjour Isaac Peltz,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade se cultive dans votre région depuis la première vague de 2013, et plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -14715,7 +14959,7 @@
       <c r="L227" s="10" t="inlineStr"/>
       <c r="M227" s="10" t="inlineStr"/>
     </row>
-    <row r="228" ht="175" customHeight="1">
+    <row r="228" ht="230" customHeight="1">
       <c r="A228" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14764,12 +15008,13 @@
       <c r="J228" s="9" t="inlineStr">
         <is>
           <t>Bonjour Frédéric Perron,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -14778,7 +15023,7 @@
       <c r="L228" s="10" t="inlineStr"/>
       <c r="M228" s="10" t="inlineStr"/>
     </row>
-    <row r="229" ht="175" customHeight="1">
+    <row r="229" ht="230" customHeight="1">
       <c r="A229" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14827,8 +15072,10 @@
       <c r="J229" s="9" t="inlineStr">
         <is>
           <t>Bonjour Nathalie Petrowski,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -14840,7 +15087,7 @@
       <c r="L229" s="10" t="inlineStr"/>
       <c r="M229" s="10" t="inlineStr"/>
     </row>
-    <row r="230" ht="175" customHeight="1">
+    <row r="230" ht="230" customHeight="1">
       <c r="A230" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14889,8 +15136,10 @@
       <c r="J230" s="9" t="inlineStr">
         <is>
           <t>Bonjour Francis Plourde,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -14902,7 +15151,7 @@
       <c r="L230" s="10" t="inlineStr"/>
       <c r="M230" s="10" t="inlineStr"/>
     </row>
-    <row r="231" ht="175" customHeight="1">
+    <row r="231" ht="230" customHeight="1">
       <c r="A231" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14951,8 +15200,10 @@
       <c r="J231" s="9" t="inlineStr">
         <is>
           <t>Bonjour Raymonde Provencher,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -14964,7 +15215,7 @@
       <c r="L231" s="10" t="inlineStr"/>
       <c r="M231" s="10" t="inlineStr"/>
     </row>
-    <row r="232" ht="175" customHeight="1">
+    <row r="232" ht="230" customHeight="1">
       <c r="A232" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15013,12 +15264,13 @@
       <c r="J232" s="9" t="inlineStr">
         <is>
           <t>Bonjour Richard Prudhomme,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15027,7 +15279,7 @@
       <c r="L232" s="10" t="inlineStr"/>
       <c r="M232" s="10" t="inlineStr"/>
     </row>
-    <row r="233" ht="175" customHeight="1">
+    <row r="233" ht="230" customHeight="1">
       <c r="A233" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15076,12 +15328,13 @@
       <c r="J233" s="9" t="inlineStr">
         <is>
           <t>Bonjour Pascale Renaud,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15090,7 +15343,7 @@
       <c r="L233" s="10" t="inlineStr"/>
       <c r="M233" s="10" t="inlineStr"/>
     </row>
-    <row r="234" ht="175" customHeight="1">
+    <row r="234" ht="230" customHeight="1">
       <c r="A234" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15139,12 +15392,13 @@
       <c r="J234" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marc Sony Ricot,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15153,7 +15407,7 @@
       <c r="L234" s="10" t="inlineStr"/>
       <c r="M234" s="10" t="inlineStr"/>
     </row>
-    <row r="235" ht="175" customHeight="1">
+    <row r="235" ht="230" customHeight="1">
       <c r="A235" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15202,12 +15456,13 @@
       <c r="J235" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-Paul Rouleau,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15216,7 +15471,7 @@
       <c r="L235" s="10" t="inlineStr"/>
       <c r="M235" s="10" t="inlineStr"/>
     </row>
-    <row r="236" ht="175" customHeight="1">
+    <row r="236" ht="230" customHeight="1">
       <c r="A236" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15265,8 +15520,10 @@
       <c r="J236" s="9" t="inlineStr">
         <is>
           <t>Bonjour Emmalie Ruest,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -15278,7 +15535,7 @@
       <c r="L236" s="10" t="inlineStr"/>
       <c r="M236" s="10" t="inlineStr"/>
     </row>
-    <row r="237" ht="175" customHeight="1">
+    <row r="237" ht="230" customHeight="1">
       <c r="A237" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15327,9 +15584,10 @@
       <c r="J237" s="9" t="inlineStr">
         <is>
           <t>Bonjour Louis-Philippe Samson,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade se cultive dans votre région depuis la première vague de 2013, et plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -15341,7 +15599,7 @@
       <c r="L237" s="10" t="inlineStr"/>
       <c r="M237" s="10" t="inlineStr"/>
     </row>
-    <row r="238" ht="175" customHeight="1">
+    <row r="238" ht="230" customHeight="1">
       <c r="A238" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15390,12 +15648,13 @@
       <c r="J238" s="9" t="inlineStr">
         <is>
           <t>Bonjour Catherine Schlager,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la plante que les agriculteurs arrachent depuis 50 ans. La soie attachée à ses graines est ce qui isole nos manteaux, nos mitaines et nos tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. J'ai du matériel photo qui montre bien le contraste : la gousse dans le champ, la soie dans la main, le produit porté. L'atelier de Limoilou est ouvert si vous voulez voir la matière.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de Limoilou est ouvert si vous voulez voir la matière, et j'ai du matériel photo.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15404,7 +15663,7 @@
       <c r="L238" s="10" t="inlineStr"/>
       <c r="M238" s="10" t="inlineStr"/>
     </row>
-    <row r="239" ht="175" customHeight="1">
+    <row r="239" ht="230" customHeight="1">
       <c r="A239" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15453,12 +15712,13 @@
       <c r="J239" s="9" t="inlineStr">
         <is>
           <t>Bonjour Olivier Schmouker,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15467,7 +15727,7 @@
       <c r="L239" s="10" t="inlineStr"/>
       <c r="M239" s="10" t="inlineStr"/>
     </row>
-    <row r="240" ht="175" customHeight="1">
+    <row r="240" ht="230" customHeight="1">
       <c r="A240" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15516,8 +15776,10 @@
       <c r="J240" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jacques Sennechael,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -15529,7 +15791,7 @@
       <c r="L240" s="10" t="inlineStr"/>
       <c r="M240" s="10" t="inlineStr"/>
     </row>
-    <row r="241" ht="175" customHeight="1">
+    <row r="241" ht="230" customHeight="1">
       <c r="A241" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15578,12 +15840,13 @@
       <c r="J241" s="9" t="inlineStr">
         <is>
           <t>Bonjour Alexandre Shields,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15592,7 +15855,7 @@
       <c r="L241" s="10" t="inlineStr"/>
       <c r="M241" s="10" t="inlineStr"/>
     </row>
-    <row r="242" ht="175" customHeight="1">
+    <row r="242" ht="230" customHeight="1">
       <c r="A242" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15641,12 +15904,13 @@
       <c r="J242" s="9" t="inlineStr">
         <is>
           <t>Bonjour Chloé Sondervorst,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15655,7 +15919,7 @@
       <c r="L242" s="10" t="inlineStr"/>
       <c r="M242" s="10" t="inlineStr"/>
     </row>
-    <row r="243" ht="175" customHeight="1">
+    <row r="243" ht="230" customHeight="1">
       <c r="A243" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15704,9 +15968,10 @@
       <c r="J243" s="9" t="inlineStr">
         <is>
           <t>Bonjour Kimberley Sullivan,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -15718,7 +15983,7 @@
       <c r="L243" s="10" t="inlineStr"/>
       <c r="M243" s="10" t="inlineStr"/>
     </row>
-    <row r="244" ht="175" customHeight="1">
+    <row r="244" ht="230" customHeight="1">
       <c r="A244" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15767,12 +16032,13 @@
       <c r="J244" s="9" t="inlineStr">
         <is>
           <t>Bonjour William Thériault,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-La Montérégie est une des régions où l'asclépiade se cultive encore, et c'est de champs comme ceux-là que vient la fibre qu'on transforme.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15781,7 +16047,7 @@
       <c r="L244" s="10" t="inlineStr"/>
       <c r="M244" s="10" t="inlineStr"/>
     </row>
-    <row r="245" ht="175" customHeight="1">
+    <row r="245" ht="230" customHeight="1">
       <c r="A245" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15830,12 +16096,13 @@
       <c r="J245" s="9" t="inlineStr">
         <is>
           <t>Bonjour Katia Tobar,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15844,7 +16111,7 @@
       <c r="L245" s="10" t="inlineStr"/>
       <c r="M245" s="10" t="inlineStr"/>
     </row>
-    <row r="246" ht="175" customHeight="1">
+    <row r="246" ht="230" customHeight="1">
       <c r="A246" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15893,12 +16160,13 @@
       <c r="J246" s="9" t="inlineStr">
         <is>
           <t>Bonjour Martin Tremblay,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -15907,7 +16175,7 @@
       <c r="L246" s="10" t="inlineStr"/>
       <c r="M246" s="10" t="inlineStr"/>
     </row>
-    <row r="247" ht="175" customHeight="1">
+    <row r="247" ht="230" customHeight="1">
       <c r="A247" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15956,8 +16224,10 @@
       <c r="J247" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie-Christine Trottier,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -15969,7 +16239,7 @@
       <c r="L247" s="10" t="inlineStr"/>
       <c r="M247" s="10" t="inlineStr"/>
     </row>
-    <row r="248" ht="175" customHeight="1">
+    <row r="248" ht="230" customHeight="1">
       <c r="A248" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16018,12 +16288,13 @@
       <c r="J248" s="9" t="inlineStr">
         <is>
           <t>Bonjour Pierre-Luc Trudel,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a pas de chaîne d'approvisionnement.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de ce que ça demande d'industrialiser une matière qui n'a aucune chaîne d'approvisionnement.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16032,7 +16303,7 @@
       <c r="L248" s="10" t="inlineStr"/>
       <c r="M248" s="10" t="inlineStr"/>
     </row>
-    <row r="249" ht="175" customHeight="1">
+    <row r="249" ht="230" customHeight="1">
       <c r="A249" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16081,8 +16352,10 @@
       <c r="J249" s="9" t="inlineStr">
         <is>
           <t>Bonjour David Turbis,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -16094,7 +16367,7 @@
       <c r="L249" s="10" t="inlineStr"/>
       <c r="M249" s="10" t="inlineStr"/>
     </row>
-    <row r="250" ht="175" customHeight="1">
+    <row r="250" ht="230" customHeight="1">
       <c r="A250" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16143,9 +16416,10 @@
       <c r="J250" s="9" t="inlineStr">
         <is>
           <t>Bonjour Paule Vermot-Desroches,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec. La filière s'est cassée en 2018, mais des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -16157,7 +16431,7 @@
       <c r="L250" s="10" t="inlineStr"/>
       <c r="M250" s="10" t="inlineStr"/>
     </row>
-    <row r="251" ht="175" customHeight="1">
+    <row r="251" ht="230" customHeight="1">
       <c r="A251" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16206,8 +16480,10 @@
       <c r="J251" s="9" t="inlineStr">
         <is>
           <t>Bonjour Alexandra Viau,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -16219,7 +16495,7 @@
       <c r="L251" s="10" t="inlineStr"/>
       <c r="M251" s="10" t="inlineStr"/>
     </row>
-    <row r="252" ht="175" customHeight="1">
+    <row r="252" ht="230" customHeight="1">
       <c r="A252" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16268,12 +16544,13 @@
       <c r="J252" s="9" t="inlineStr">
         <is>
           <t>Bonjour Raymond Viger,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16282,7 +16559,7 @@
       <c r="L252" s="10" t="inlineStr"/>
       <c r="M252" s="10" t="inlineStr"/>
     </row>
-    <row r="253" ht="175" customHeight="1">
+    <row r="253" ht="230" customHeight="1">
       <c r="A253" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16331,8 +16608,10 @@
       <c r="J253" s="9" t="inlineStr">
         <is>
           <t>Bonjour Paul Émile d'Entremont,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je suis disponible pour une entrevue avant ou après la diffusion.
@@ -16344,7 +16623,7 @@
       <c r="L253" s="10" t="inlineStr"/>
       <c r="M253" s="10" t="inlineStr"/>
     </row>
-    <row r="254" ht="175" customHeight="1">
+    <row r="254" ht="230" customHeight="1">
       <c r="A254" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16393,12 +16672,13 @@
       <c r="J254" s="9" t="inlineStr">
         <is>
           <t>Bonjour Augustin de Baudinière,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16407,7 +16687,7 @@
       <c r="L254" s="10" t="inlineStr"/>
       <c r="M254" s="10" t="inlineStr"/>
     </row>
-    <row r="255" ht="175" customHeight="1">
+    <row r="255" ht="230" customHeight="1">
       <c r="A255" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16456,12 +16736,13 @@
       <c r="J255" s="9" t="inlineStr">
         <is>
           <t>Bonjour Ivan de Jacquelin-Dulphe,
-Je dirige Lasclay, une entreprise de Québec qui transforme la soie d'asclépiade en isolant textile : manteaux, mitaines, tuques, sacs isothermes.
-L'asclépiade est la seule plante que les chenilles du monarque peuvent manger, et le déclin du papillon suit celui de la plante dans les zones agricoles. Notre pari est simple : si l'asclépiade devient payante, les agriculteurs la gardent.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
-Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
-Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
-Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux parler de la campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
+On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
+Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
+Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
+Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. Je peux aussi parler de notre campagne de plantation, qui en est à sa 5e édition et qui a distribué environ 10 millions de graines en Amérique du Nord.
 J'espère vraiment un boom des ventes avec cette visibilité, ce qui, plus largement, sera extrêmement bénéfique pour les cultivateurs d'asclépiade du Québec chez qui on continue d'acheter, et pour les papillons monarques menacés qui continuent de se reproduire dans leurs plantations.
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
@@ -16470,7 +16751,7 @@
       <c r="L255" s="10" t="inlineStr"/>
       <c r="M255" s="10" t="inlineStr"/>
     </row>
-    <row r="256" ht="175" customHeight="1">
+    <row r="256" ht="230" customHeight="1">
       <c r="A256" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -16540,7 +16821,7 @@
       <c r="L256" s="10" t="inlineStr"/>
       <c r="M256" s="10" t="inlineStr"/>
     </row>
-    <row r="257" ht="175" customHeight="1">
+    <row r="257" ht="230" customHeight="1">
       <c r="A257" s="6" t="inlineStr">
         <is>
           <t>froide B</t>

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -494,13 +494,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="104" customWidth="1" min="2" max="2"/>
+    <col width="106" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Version 3 — après ta remarque sur Victor Carré</t>
+          <t>Version 3 — tout corrigé</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -509,107 +509,107 @@
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="52" customHeight="1">
+    <row r="3" ht="54" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Le reproche</t>
+          <t>Le registre</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>« Aucune présentation, mise en contexte. » Juste. Le courriel demandait à quelqu'un de s'intéresser à une entreprise dont il n'a jamais entendu parler et à une matière qu'il ne connaît pas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="52" customHeight="1">
+          <t>Plus d'excuses sur le virage manufacturier, plus de « un achat ne sauve pas un papillon », plus de « je ne peux pas dire comment ça s'est terminé ». Vérifié : zéro occurrence dans les 253 brouillons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="54" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Ce que j'ai ajouté</t>
+          <t>La présentation</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Une vraie présentation en tête de tous les courriels froids : qui je suis, ce qu'est Lasclay, ce qu'est l'asclépiade — sous le nom de « petits cochons », que tout le monde reconnaît ici — ce que la fibre fait, ce qu'on en fabrique, et le lien avec le monarque.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
+          <t>Les 217 courriels froids commencent par qui tu es, ce qu'est Lasclay et ce qu'est l'asclépiade — sous le nom de « petits cochons », que tout le monde reconnaît ici. Les 5 écrits à la main aussi, ils ne l'avaient pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Et un « pourquoi vous »</t>
+          <t>Le « pourquoi vous »</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chaque courriel dit maintenant explicitement pourquoi je lui écris à lui. La raison vient de sa région quand l'asclépiade y a une histoire réelle (Saint-Tite, Granby, le Lac-Saint-Jean), de son sujet sinon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
+          <t>Chaque courriel froid dit explicitement pourquoi il s'adresse à cette personne-là : sa région quand l'asclépiade y a une histoire réelle, son sujet sinon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Une accroche régionale retirée</t>
+          <t>Une fausse accroche retirée</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>« Notre atelier est dans Limoilou » n'est pas une accroche locale pour un journal de Charlevoix. La Capitale-Nationale passe au thématique.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
+          <t>« Notre atelier est dans Limoilou » ne dit rien à un journal de Charlevoix. La Capitale-Nationale passe au thématique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Les quatre de la liste chaude</t>
+          <t>Les quatre sans historique</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Roberge, Laforest, Goubau et Dostie n'avaient aucun historique documenté et donc aucune présentation. Ils en ont une maintenant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
+          <t>Roberge, Laforest, Goubau et Dostie n'avaient aucune présentation. Ils en ont une.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Les documents</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>04-gabarits-courriels.md est réécrit sur ton squelette. La matrice ne prescrit plus « nommer ce que le virage a coûté » ni la mise en garde sur les monarques.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Ce qui n'a pas bougé</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ce qui vient de toi</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Ton squelette</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Présentation, pourquoi vous, les 2 missions, l'annonce sur sa propre ligne, la rareté et la demande de suite, la chaîne ventes-cultivateurs-monarques, la clôture.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Larocque et Pouliot</t>
+          <t>Repris mot pour mot</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Repris mot pour mot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
+          <t>Larocque et Pouliot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Registre</t>
@@ -637,7 +637,7 @@
       <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="52" customHeight="1">
+    <row r="17" ht="54" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Diffusion</t>
@@ -649,7 +649,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="52" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Ne pas envoyer</t>
@@ -661,7 +661,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="52" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Courriels manquants</t>
@@ -673,7 +673,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Salutations à vérifier</t>
@@ -681,7 +681,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Six fiches FPJQ mal formées, signalées dans la colonne Précaution du chiffrier de travail.</t>
+          <t>Six fiches FPJQ mal formées (nom en majuscules, prénoms multiples).</t>
         </is>
       </c>
     </row>
@@ -708,8 +708,8 @@
     <col width="32" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="84" customWidth="1" min="10" max="10"/>
-    <col width="84" customWidth="1" min="11" max="11"/>
+    <col width="88" customWidth="1" min="10" max="10"/>
+    <col width="88" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
@@ -781,7 +781,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="230" customHeight="1">
+    <row r="2" ht="270" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -846,7 +846,7 @@
       <c r="L2" s="10" t="inlineStr"/>
       <c r="M2" s="10" t="inlineStr"/>
     </row>
-    <row r="3" ht="230" customHeight="1">
+    <row r="3" ht="270" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -904,7 +904,7 @@
       <c r="L3" s="10" t="inlineStr"/>
       <c r="M3" s="10" t="inlineStr"/>
     </row>
-    <row r="4" ht="230" customHeight="1">
+    <row r="4" ht="270" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -975,7 +975,7 @@
       <c r="L4" s="10" t="inlineStr"/>
       <c r="M4" s="10" t="inlineStr"/>
     </row>
-    <row r="5" ht="230" customHeight="1">
+    <row r="5" ht="270" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1032,7 +1032,7 @@
       <c r="L5" s="10" t="inlineStr"/>
       <c r="M5" s="10" t="inlineStr"/>
     </row>
-    <row r="6" ht="230" customHeight="1">
+    <row r="6" ht="270" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1090,7 +1090,7 @@
       <c r="L6" s="10" t="inlineStr"/>
       <c r="M6" s="10" t="inlineStr"/>
     </row>
-    <row r="7" ht="230" customHeight="1">
+    <row r="7" ht="270" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1148,7 +1148,7 @@
       <c r="L7" s="10" t="inlineStr"/>
       <c r="M7" s="10" t="inlineStr"/>
     </row>
-    <row r="8" ht="230" customHeight="1">
+    <row r="8" ht="270" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1206,7 +1206,7 @@
       <c r="L8" s="10" t="inlineStr"/>
       <c r="M8" s="10" t="inlineStr"/>
     </row>
-    <row r="9" ht="230" customHeight="1">
+    <row r="9" ht="270" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1264,7 +1264,7 @@
       <c r="L9" s="10" t="inlineStr"/>
       <c r="M9" s="10" t="inlineStr"/>
     </row>
-    <row r="10" ht="230" customHeight="1">
+    <row r="10" ht="270" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1322,7 +1322,7 @@
       <c r="L10" s="10" t="inlineStr"/>
       <c r="M10" s="10" t="inlineStr"/>
     </row>
-    <row r="11" ht="230" customHeight="1">
+    <row r="11" ht="270" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1380,7 +1380,7 @@
       <c r="L11" s="10" t="inlineStr"/>
       <c r="M11" s="10" t="inlineStr"/>
     </row>
-    <row r="12" ht="230" customHeight="1">
+    <row r="12" ht="270" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1438,7 +1438,7 @@
       <c r="L12" s="10" t="inlineStr"/>
       <c r="M12" s="10" t="inlineStr"/>
     </row>
-    <row r="13" ht="230" customHeight="1">
+    <row r="13" ht="270" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1496,7 +1496,7 @@
       <c r="L13" s="10" t="inlineStr"/>
       <c r="M13" s="10" t="inlineStr"/>
     </row>
-    <row r="14" ht="230" customHeight="1">
+    <row r="14" ht="270" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1554,7 +1554,7 @@
       <c r="L14" s="10" t="inlineStr"/>
       <c r="M14" s="10" t="inlineStr"/>
     </row>
-    <row r="15" ht="230" customHeight="1">
+    <row r="15" ht="270" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1612,7 +1612,7 @@
       <c r="L15" s="10" t="inlineStr"/>
       <c r="M15" s="10" t="inlineStr"/>
     </row>
-    <row r="16" ht="230" customHeight="1">
+    <row r="16" ht="270" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1669,7 +1669,7 @@
       <c r="L16" s="10" t="inlineStr"/>
       <c r="M16" s="10" t="inlineStr"/>
     </row>
-    <row r="17" ht="230" customHeight="1">
+    <row r="17" ht="270" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1727,7 +1727,7 @@
       <c r="L17" s="10" t="inlineStr"/>
       <c r="M17" s="10" t="inlineStr"/>
     </row>
-    <row r="18" ht="230" customHeight="1">
+    <row r="18" ht="270" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1785,7 +1785,7 @@
       <c r="L18" s="10" t="inlineStr"/>
       <c r="M18" s="10" t="inlineStr"/>
     </row>
-    <row r="19" ht="230" customHeight="1">
+    <row r="19" ht="270" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1843,7 +1843,7 @@
       <c r="L19" s="10" t="inlineStr"/>
       <c r="M19" s="10" t="inlineStr"/>
     </row>
-    <row r="20" ht="230" customHeight="1">
+    <row r="20" ht="270" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1901,7 +1901,7 @@
       <c r="L20" s="10" t="inlineStr"/>
       <c r="M20" s="10" t="inlineStr"/>
     </row>
-    <row r="21" ht="230" customHeight="1">
+    <row r="21" ht="270" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1959,7 +1959,7 @@
       <c r="L21" s="10" t="inlineStr"/>
       <c r="M21" s="10" t="inlineStr"/>
     </row>
-    <row r="22" ht="230" customHeight="1">
+    <row r="22" ht="270" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2017,7 +2017,7 @@
       <c r="L22" s="10" t="inlineStr"/>
       <c r="M22" s="10" t="inlineStr"/>
     </row>
-    <row r="23" ht="230" customHeight="1">
+    <row r="23" ht="270" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2075,7 +2075,7 @@
       <c r="L23" s="10" t="inlineStr"/>
       <c r="M23" s="10" t="inlineStr"/>
     </row>
-    <row r="24" ht="230" customHeight="1">
+    <row r="24" ht="270" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2133,7 +2133,7 @@
       <c r="L24" s="10" t="inlineStr"/>
       <c r="M24" s="10" t="inlineStr"/>
     </row>
-    <row r="25" ht="230" customHeight="1">
+    <row r="25" ht="270" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2191,7 +2191,7 @@
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr"/>
     </row>
-    <row r="26" ht="230" customHeight="1">
+    <row r="26" ht="270" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2242,7 +2242,7 @@
       <c r="L26" s="10" t="inlineStr"/>
       <c r="M26" s="10" t="inlineStr"/>
     </row>
-    <row r="27" ht="230" customHeight="1">
+    <row r="27" ht="270" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2300,7 +2300,7 @@
       <c r="L27" s="10" t="inlineStr"/>
       <c r="M27" s="10" t="inlineStr"/>
     </row>
-    <row r="28" ht="230" customHeight="1">
+    <row r="28" ht="270" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2350,7 +2350,7 @@
       <c r="L28" s="10" t="inlineStr"/>
       <c r="M28" s="10" t="inlineStr"/>
     </row>
-    <row r="29" ht="230" customHeight="1">
+    <row r="29" ht="270" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2400,7 +2400,7 @@
       <c r="L29" s="10" t="inlineStr"/>
       <c r="M29" s="10" t="inlineStr"/>
     </row>
-    <row r="30" ht="230" customHeight="1">
+    <row r="30" ht="270" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2450,7 +2450,7 @@
       <c r="L30" s="10" t="inlineStr"/>
       <c r="M30" s="10" t="inlineStr"/>
     </row>
-    <row r="31" ht="230" customHeight="1">
+    <row r="31" ht="270" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2508,7 +2508,7 @@
       <c r="L31" s="10" t="inlineStr"/>
       <c r="M31" s="10" t="inlineStr"/>
     </row>
-    <row r="32" ht="230" customHeight="1">
+    <row r="32" ht="270" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2558,7 +2558,7 @@
       <c r="L32" s="10" t="inlineStr"/>
       <c r="M32" s="10" t="inlineStr"/>
     </row>
-    <row r="33" ht="230" customHeight="1">
+    <row r="33" ht="270" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2608,7 +2608,7 @@
       <c r="L33" s="10" t="inlineStr"/>
       <c r="M33" s="10" t="inlineStr"/>
     </row>
-    <row r="34" ht="230" customHeight="1">
+    <row r="34" ht="270" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2658,7 +2658,7 @@
       <c r="L34" s="10" t="inlineStr"/>
       <c r="M34" s="10" t="inlineStr"/>
     </row>
-    <row r="35" ht="230" customHeight="1">
+    <row r="35" ht="270" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2708,7 +2708,7 @@
       <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr"/>
     </row>
-    <row r="36" ht="230" customHeight="1">
+    <row r="36" ht="270" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2762,7 +2762,7 @@
       <c r="L36" s="10" t="inlineStr"/>
       <c r="M36" s="10" t="inlineStr"/>
     </row>
-    <row r="37" ht="230" customHeight="1">
+    <row r="37" ht="270" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2816,7 +2816,7 @@
       <c r="L37" s="10" t="inlineStr"/>
       <c r="M37" s="10" t="inlineStr"/>
     </row>
-    <row r="38" ht="230" customHeight="1">
+    <row r="38" ht="270" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2870,7 +2870,7 @@
       <c r="L38" s="10" t="inlineStr"/>
       <c r="M38" s="10" t="inlineStr"/>
     </row>
-    <row r="39" ht="230" customHeight="1">
+    <row r="39" ht="270" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -2919,6 +2919,8 @@
       <c r="J39" s="9" t="inlineStr">
         <is>
           <t>Bonjour Marie Allard,
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
+Québec dont l'atelier est dans Limoilou.
 Il y a une belle histoire de sciences dans l'asclépiade. La soie attachée à ses graines n'est
 pas un poil : c'est un tube creux enduit d'une cire hydrophobe, et les fibres portent une
 charge qui les fait se repousser. C'est ce qui forme le parachute autour de la graine, et
@@ -2938,7 +2940,7 @@
       <c r="L39" s="10" t="inlineStr"/>
       <c r="M39" s="10" t="inlineStr"/>
     </row>
-    <row r="40" ht="230" customHeight="1">
+    <row r="40" ht="270" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3002,7 +3004,7 @@
       <c r="L40" s="10" t="inlineStr"/>
       <c r="M40" s="10" t="inlineStr"/>
     </row>
-    <row r="41" ht="230" customHeight="1">
+    <row r="41" ht="270" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3066,7 +3068,7 @@
       <c r="L41" s="10" t="inlineStr"/>
       <c r="M41" s="10" t="inlineStr"/>
     </row>
-    <row r="42" ht="230" customHeight="1">
+    <row r="42" ht="270" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3130,7 +3132,7 @@
       <c r="L42" s="10" t="inlineStr"/>
       <c r="M42" s="10" t="inlineStr"/>
     </row>
-    <row r="43" ht="230" customHeight="1">
+    <row r="43" ht="270" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3194,7 +3196,7 @@
       <c r="L43" s="10" t="inlineStr"/>
       <c r="M43" s="10" t="inlineStr"/>
     </row>
-    <row r="44" ht="230" customHeight="1">
+    <row r="44" ht="270" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3258,7 +3260,7 @@
       <c r="L44" s="10" t="inlineStr"/>
       <c r="M44" s="10" t="inlineStr"/>
     </row>
-    <row r="45" ht="230" customHeight="1">
+    <row r="45" ht="270" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3322,7 +3324,7 @@
       <c r="L45" s="10" t="inlineStr"/>
       <c r="M45" s="10" t="inlineStr"/>
     </row>
-    <row r="46" ht="230" customHeight="1">
+    <row r="46" ht="270" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3386,7 +3388,7 @@
       <c r="L46" s="10" t="inlineStr"/>
       <c r="M46" s="10" t="inlineStr"/>
     </row>
-    <row r="47" ht="230" customHeight="1">
+    <row r="47" ht="270" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3450,7 +3452,7 @@
       <c r="L47" s="10" t="inlineStr"/>
       <c r="M47" s="10" t="inlineStr"/>
     </row>
-    <row r="48" ht="230" customHeight="1">
+    <row r="48" ht="270" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3514,7 +3516,7 @@
       <c r="L48" s="10" t="inlineStr"/>
       <c r="M48" s="10" t="inlineStr"/>
     </row>
-    <row r="49" ht="230" customHeight="1">
+    <row r="49" ht="270" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3578,7 +3580,7 @@
       <c r="L49" s="10" t="inlineStr"/>
       <c r="M49" s="10" t="inlineStr"/>
     </row>
-    <row r="50" ht="230" customHeight="1">
+    <row r="50" ht="270" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3642,7 +3644,7 @@
       <c r="L50" s="10" t="inlineStr"/>
       <c r="M50" s="10" t="inlineStr"/>
     </row>
-    <row r="51" ht="230" customHeight="1">
+    <row r="51" ht="270" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3706,7 +3708,7 @@
       <c r="L51" s="10" t="inlineStr"/>
       <c r="M51" s="10" t="inlineStr"/>
     </row>
-    <row r="52" ht="230" customHeight="1">
+    <row r="52" ht="270" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3770,7 +3772,7 @@
       <c r="L52" s="10" t="inlineStr"/>
       <c r="M52" s="10" t="inlineStr"/>
     </row>
-    <row r="53" ht="230" customHeight="1">
+    <row r="53" ht="270" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3834,7 +3836,7 @@
       <c r="L53" s="10" t="inlineStr"/>
       <c r="M53" s="10" t="inlineStr"/>
     </row>
-    <row r="54" ht="230" customHeight="1">
+    <row r="54" ht="270" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3898,7 +3900,7 @@
       <c r="L54" s="10" t="inlineStr"/>
       <c r="M54" s="10" t="inlineStr"/>
     </row>
-    <row r="55" ht="230" customHeight="1">
+    <row r="55" ht="270" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3962,7 +3964,7 @@
       <c r="L55" s="10" t="inlineStr"/>
       <c r="M55" s="10" t="inlineStr"/>
     </row>
-    <row r="56" ht="230" customHeight="1">
+    <row r="56" ht="270" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4026,7 +4028,7 @@
       <c r="L56" s="10" t="inlineStr"/>
       <c r="M56" s="10" t="inlineStr"/>
     </row>
-    <row r="57" ht="230" customHeight="1">
+    <row r="57" ht="270" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4075,9 +4077,11 @@
       <c r="J57" s="9" t="inlineStr">
         <is>
           <t>Bonjour Gabriel Delisle,
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
+Québec dont l'atelier est dans Limoilou.
 L'asclépiade a été une histoire mauricienne avant d'être la nôtre : l'usine de Saint-Tite
-achetait 90 % des récoltes du Québec. On est l'entreprise qui a démarré après la chute de
-cette filière, et six ans plus tard on achète encore de l'asclépiade québécoise et on la
+achetait 90 % des récoltes du Québec. On a démarré après la chute de cette filière, et six ans
+plus tard on achète encore de l'asclépiade québécoise et on la
 transforme nous-mêmes à Québec.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la
 culture de l'asclépiade.
@@ -4093,7 +4097,7 @@
       <c r="L57" s="10" t="inlineStr"/>
       <c r="M57" s="10" t="inlineStr"/>
     </row>
-    <row r="58" ht="230" customHeight="1">
+    <row r="58" ht="270" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4157,7 +4161,7 @@
       <c r="L58" s="10" t="inlineStr"/>
       <c r="M58" s="10" t="inlineStr"/>
     </row>
-    <row r="59" ht="230" customHeight="1">
+    <row r="59" ht="270" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4221,7 +4225,7 @@
       <c r="L59" s="10" t="inlineStr"/>
       <c r="M59" s="10" t="inlineStr"/>
     </row>
-    <row r="60" ht="230" customHeight="1">
+    <row r="60" ht="270" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4285,7 +4289,7 @@
       <c r="L60" s="10" t="inlineStr"/>
       <c r="M60" s="10" t="inlineStr"/>
     </row>
-    <row r="61" ht="230" customHeight="1">
+    <row r="61" ht="270" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4349,7 +4353,7 @@
       <c r="L61" s="10" t="inlineStr"/>
       <c r="M61" s="10" t="inlineStr"/>
     </row>
-    <row r="62" ht="230" customHeight="1">
+    <row r="62" ht="270" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4413,7 +4417,7 @@
       <c r="L62" s="10" t="inlineStr"/>
       <c r="M62" s="10" t="inlineStr"/>
     </row>
-    <row r="63" ht="230" customHeight="1">
+    <row r="63" ht="270" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4477,7 +4481,7 @@
       <c r="L63" s="10" t="inlineStr"/>
       <c r="M63" s="10" t="inlineStr"/>
     </row>
-    <row r="64" ht="230" customHeight="1">
+    <row r="64" ht="270" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4541,7 +4545,7 @@
       <c r="L64" s="10" t="inlineStr"/>
       <c r="M64" s="10" t="inlineStr"/>
     </row>
-    <row r="65" ht="230" customHeight="1">
+    <row r="65" ht="270" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4605,7 +4609,7 @@
       <c r="L65" s="10" t="inlineStr"/>
       <c r="M65" s="10" t="inlineStr"/>
     </row>
-    <row r="66" ht="230" customHeight="1">
+    <row r="66" ht="270" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4669,7 +4673,7 @@
       <c r="L66" s="10" t="inlineStr"/>
       <c r="M66" s="10" t="inlineStr"/>
     </row>
-    <row r="67" ht="230" customHeight="1">
+    <row r="67" ht="270" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4733,7 +4737,7 @@
       <c r="L67" s="10" t="inlineStr"/>
       <c r="M67" s="10" t="inlineStr"/>
     </row>
-    <row r="68" ht="230" customHeight="1">
+    <row r="68" ht="270" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4797,7 +4801,7 @@
       <c r="L68" s="10" t="inlineStr"/>
       <c r="M68" s="10" t="inlineStr"/>
     </row>
-    <row r="69" ht="230" customHeight="1">
+    <row r="69" ht="270" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4861,7 +4865,7 @@
       <c r="L69" s="10" t="inlineStr"/>
       <c r="M69" s="10" t="inlineStr"/>
     </row>
-    <row r="70" ht="230" customHeight="1">
+    <row r="70" ht="270" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4925,7 +4929,7 @@
       <c r="L70" s="10" t="inlineStr"/>
       <c r="M70" s="10" t="inlineStr"/>
     </row>
-    <row r="71" ht="230" customHeight="1">
+    <row r="71" ht="270" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4989,7 +4993,7 @@
       <c r="L71" s="10" t="inlineStr"/>
       <c r="M71" s="10" t="inlineStr"/>
     </row>
-    <row r="72" ht="230" customHeight="1">
+    <row r="72" ht="270" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5053,7 +5057,7 @@
       <c r="L72" s="10" t="inlineStr"/>
       <c r="M72" s="10" t="inlineStr"/>
     </row>
-    <row r="73" ht="230" customHeight="1">
+    <row r="73" ht="270" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5117,7 +5121,7 @@
       <c r="L73" s="10" t="inlineStr"/>
       <c r="M73" s="10" t="inlineStr"/>
     </row>
-    <row r="74" ht="230" customHeight="1">
+    <row r="74" ht="270" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5181,7 +5185,7 @@
       <c r="L74" s="10" t="inlineStr"/>
       <c r="M74" s="10" t="inlineStr"/>
     </row>
-    <row r="75" ht="230" customHeight="1">
+    <row r="75" ht="270" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5245,7 +5249,7 @@
       <c r="L75" s="10" t="inlineStr"/>
       <c r="M75" s="10" t="inlineStr"/>
     </row>
-    <row r="76" ht="230" customHeight="1">
+    <row r="76" ht="270" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5309,7 +5313,7 @@
       <c r="L76" s="10" t="inlineStr"/>
       <c r="M76" s="10" t="inlineStr"/>
     </row>
-    <row r="77" ht="230" customHeight="1">
+    <row r="77" ht="270" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5373,7 +5377,7 @@
       <c r="L77" s="10" t="inlineStr"/>
       <c r="M77" s="10" t="inlineStr"/>
     </row>
-    <row r="78" ht="230" customHeight="1">
+    <row r="78" ht="270" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5437,7 +5441,7 @@
       <c r="L78" s="10" t="inlineStr"/>
       <c r="M78" s="10" t="inlineStr"/>
     </row>
-    <row r="79" ht="230" customHeight="1">
+    <row r="79" ht="270" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5501,7 +5505,7 @@
       <c r="L79" s="10" t="inlineStr"/>
       <c r="M79" s="10" t="inlineStr"/>
     </row>
-    <row r="80" ht="230" customHeight="1">
+    <row r="80" ht="270" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5565,7 +5569,7 @@
       <c r="L80" s="10" t="inlineStr"/>
       <c r="M80" s="10" t="inlineStr"/>
     </row>
-    <row r="81" ht="230" customHeight="1">
+    <row r="81" ht="270" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5629,7 +5633,7 @@
       <c r="L81" s="10" t="inlineStr"/>
       <c r="M81" s="10" t="inlineStr"/>
     </row>
-    <row r="82" ht="230" customHeight="1">
+    <row r="82" ht="270" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5678,11 +5682,13 @@
       <c r="J82" s="9" t="inlineStr">
         <is>
           <t>Bonjour Réjean Martin,
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
+Québec dont l'atelier est dans Limoilou.
 Vous couvrez Mékinac, donc Saint-Tite, donc l'endroit où l'asclépiade a eu son grand moment
 industriel au Québec. L'usine achetait 90 % des récoltes de la province avant que la filière
 se casse en 2018.
-On est l'entreprise qui a démarré après. Six ans plus tard, on achète encore de l'asclépiade
-québécoise et on la transforme nous-mêmes à Québec. Mes 2 grandes missions : faire connaître
+On a démarré après. Six ans plus tard, on achète encore de l'asclépiade québécoise et on la
+transforme nous-mêmes à Québec. Mes 2 grandes missions : faire connaître
 l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5697,7 +5703,7 @@
       <c r="L82" s="10" t="inlineStr"/>
       <c r="M82" s="10" t="inlineStr"/>
     </row>
-    <row r="83" ht="230" customHeight="1">
+    <row r="83" ht="270" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5761,7 +5767,7 @@
       <c r="L83" s="10" t="inlineStr"/>
       <c r="M83" s="10" t="inlineStr"/>
     </row>
-    <row r="84" ht="230" customHeight="1">
+    <row r="84" ht="270" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5825,7 +5831,7 @@
       <c r="L84" s="10" t="inlineStr"/>
       <c r="M84" s="10" t="inlineStr"/>
     </row>
-    <row r="85" ht="230" customHeight="1">
+    <row r="85" ht="270" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5889,7 +5895,7 @@
       <c r="L85" s="10" t="inlineStr"/>
       <c r="M85" s="10" t="inlineStr"/>
     </row>
-    <row r="86" ht="230" customHeight="1">
+    <row r="86" ht="270" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5953,7 +5959,7 @@
       <c r="L86" s="10" t="inlineStr"/>
       <c r="M86" s="10" t="inlineStr"/>
     </row>
-    <row r="87" ht="230" customHeight="1">
+    <row r="87" ht="270" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6017,7 +6023,7 @@
       <c r="L87" s="10" t="inlineStr"/>
       <c r="M87" s="10" t="inlineStr"/>
     </row>
-    <row r="88" ht="230" customHeight="1">
+    <row r="88" ht="270" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6081,7 +6087,7 @@
       <c r="L88" s="10" t="inlineStr"/>
       <c r="M88" s="10" t="inlineStr"/>
     </row>
-    <row r="89" ht="230" customHeight="1">
+    <row r="89" ht="270" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6145,7 +6151,7 @@
       <c r="L89" s="10" t="inlineStr"/>
       <c r="M89" s="10" t="inlineStr"/>
     </row>
-    <row r="90" ht="230" customHeight="1">
+    <row r="90" ht="270" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6209,7 +6215,7 @@
       <c r="L90" s="10" t="inlineStr"/>
       <c r="M90" s="10" t="inlineStr"/>
     </row>
-    <row r="91" ht="230" customHeight="1">
+    <row r="91" ht="270" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6273,7 +6279,7 @@
       <c r="L91" s="10" t="inlineStr"/>
       <c r="M91" s="10" t="inlineStr"/>
     </row>
-    <row r="92" ht="230" customHeight="1">
+    <row r="92" ht="270" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6337,7 +6343,7 @@
       <c r="L92" s="10" t="inlineStr"/>
       <c r="M92" s="10" t="inlineStr"/>
     </row>
-    <row r="93" ht="230" customHeight="1">
+    <row r="93" ht="270" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6401,7 +6407,7 @@
       <c r="L93" s="10" t="inlineStr"/>
       <c r="M93" s="10" t="inlineStr"/>
     </row>
-    <row r="94" ht="230" customHeight="1">
+    <row r="94" ht="270" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6465,7 +6471,7 @@
       <c r="L94" s="10" t="inlineStr"/>
       <c r="M94" s="10" t="inlineStr"/>
     </row>
-    <row r="95" ht="230" customHeight="1">
+    <row r="95" ht="270" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6529,7 +6535,7 @@
       <c r="L95" s="10" t="inlineStr"/>
       <c r="M95" s="10" t="inlineStr"/>
     </row>
-    <row r="96" ht="230" customHeight="1">
+    <row r="96" ht="270" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6593,7 +6599,7 @@
       <c r="L96" s="10" t="inlineStr"/>
       <c r="M96" s="10" t="inlineStr"/>
     </row>
-    <row r="97" ht="230" customHeight="1">
+    <row r="97" ht="270" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6657,7 +6663,7 @@
       <c r="L97" s="10" t="inlineStr"/>
       <c r="M97" s="10" t="inlineStr"/>
     </row>
-    <row r="98" ht="230" customHeight="1">
+    <row r="98" ht="270" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6721,7 +6727,7 @@
       <c r="L98" s="10" t="inlineStr"/>
       <c r="M98" s="10" t="inlineStr"/>
     </row>
-    <row r="99" ht="230" customHeight="1">
+    <row r="99" ht="270" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6785,7 +6791,7 @@
       <c r="L99" s="10" t="inlineStr"/>
       <c r="M99" s="10" t="inlineStr"/>
     </row>
-    <row r="100" ht="230" customHeight="1">
+    <row r="100" ht="270" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6849,7 +6855,7 @@
       <c r="L100" s="10" t="inlineStr"/>
       <c r="M100" s="10" t="inlineStr"/>
     </row>
-    <row r="101" ht="230" customHeight="1">
+    <row r="101" ht="270" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6913,7 +6919,7 @@
       <c r="L101" s="10" t="inlineStr"/>
       <c r="M101" s="10" t="inlineStr"/>
     </row>
-    <row r="102" ht="230" customHeight="1">
+    <row r="102" ht="270" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6977,7 +6983,7 @@
       <c r="L102" s="10" t="inlineStr"/>
       <c r="M102" s="10" t="inlineStr"/>
     </row>
-    <row r="103" ht="230" customHeight="1">
+    <row r="103" ht="270" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7041,7 +7047,7 @@
       <c r="L103" s="10" t="inlineStr"/>
       <c r="M103" s="10" t="inlineStr"/>
     </row>
-    <row r="104" ht="230" customHeight="1">
+    <row r="104" ht="270" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7105,7 +7111,7 @@
       <c r="L104" s="10" t="inlineStr"/>
       <c r="M104" s="10" t="inlineStr"/>
     </row>
-    <row r="105" ht="230" customHeight="1">
+    <row r="105" ht="270" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7169,7 +7175,7 @@
       <c r="L105" s="10" t="inlineStr"/>
       <c r="M105" s="10" t="inlineStr"/>
     </row>
-    <row r="106" ht="230" customHeight="1">
+    <row r="106" ht="270" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7233,7 +7239,7 @@
       <c r="L106" s="10" t="inlineStr"/>
       <c r="M106" s="10" t="inlineStr"/>
     </row>
-    <row r="107" ht="230" customHeight="1">
+    <row r="107" ht="270" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7297,7 +7303,7 @@
       <c r="L107" s="10" t="inlineStr"/>
       <c r="M107" s="10" t="inlineStr"/>
     </row>
-    <row r="108" ht="230" customHeight="1">
+    <row r="108" ht="270" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7361,7 +7367,7 @@
       <c r="L108" s="10" t="inlineStr"/>
       <c r="M108" s="10" t="inlineStr"/>
     </row>
-    <row r="109" ht="230" customHeight="1">
+    <row r="109" ht="270" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7425,7 +7431,7 @@
       <c r="L109" s="10" t="inlineStr"/>
       <c r="M109" s="10" t="inlineStr"/>
     </row>
-    <row r="110" ht="230" customHeight="1">
+    <row r="110" ht="270" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7489,7 +7495,7 @@
       <c r="L110" s="10" t="inlineStr"/>
       <c r="M110" s="10" t="inlineStr"/>
     </row>
-    <row r="111" ht="230" customHeight="1">
+    <row r="111" ht="270" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7553,7 +7559,7 @@
       <c r="L111" s="10" t="inlineStr"/>
       <c r="M111" s="10" t="inlineStr"/>
     </row>
-    <row r="112" ht="230" customHeight="1">
+    <row r="112" ht="270" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7617,7 +7623,7 @@
       <c r="L112" s="10" t="inlineStr"/>
       <c r="M112" s="10" t="inlineStr"/>
     </row>
-    <row r="113" ht="230" customHeight="1">
+    <row r="113" ht="270" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7681,7 +7687,7 @@
       <c r="L113" s="10" t="inlineStr"/>
       <c r="M113" s="10" t="inlineStr"/>
     </row>
-    <row r="114" ht="230" customHeight="1">
+    <row r="114" ht="270" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7745,7 +7751,7 @@
       <c r="L114" s="10" t="inlineStr"/>
       <c r="M114" s="10" t="inlineStr"/>
     </row>
-    <row r="115" ht="230" customHeight="1">
+    <row r="115" ht="270" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7809,7 +7815,7 @@
       <c r="L115" s="10" t="inlineStr"/>
       <c r="M115" s="10" t="inlineStr"/>
     </row>
-    <row r="116" ht="230" customHeight="1">
+    <row r="116" ht="270" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7873,7 +7879,7 @@
       <c r="L116" s="10" t="inlineStr"/>
       <c r="M116" s="10" t="inlineStr"/>
     </row>
-    <row r="117" ht="230" customHeight="1">
+    <row r="117" ht="270" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -7937,7 +7943,7 @@
       <c r="L117" s="10" t="inlineStr"/>
       <c r="M117" s="10" t="inlineStr"/>
     </row>
-    <row r="118" ht="230" customHeight="1">
+    <row r="118" ht="270" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8001,7 +8007,7 @@
       <c r="L118" s="10" t="inlineStr"/>
       <c r="M118" s="10" t="inlineStr"/>
     </row>
-    <row r="119" ht="230" customHeight="1">
+    <row r="119" ht="270" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8065,7 +8071,7 @@
       <c r="L119" s="10" t="inlineStr"/>
       <c r="M119" s="10" t="inlineStr"/>
     </row>
-    <row r="120" ht="230" customHeight="1">
+    <row r="120" ht="270" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8129,7 +8135,7 @@
       <c r="L120" s="10" t="inlineStr"/>
       <c r="M120" s="10" t="inlineStr"/>
     </row>
-    <row r="121" ht="230" customHeight="1">
+    <row r="121" ht="270" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8193,7 +8199,7 @@
       <c r="L121" s="10" t="inlineStr"/>
       <c r="M121" s="10" t="inlineStr"/>
     </row>
-    <row r="122" ht="230" customHeight="1">
+    <row r="122" ht="270" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8257,7 +8263,7 @@
       <c r="L122" s="10" t="inlineStr"/>
       <c r="M122" s="10" t="inlineStr"/>
     </row>
-    <row r="123" ht="230" customHeight="1">
+    <row r="123" ht="270" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8321,7 +8327,7 @@
       <c r="L123" s="10" t="inlineStr"/>
       <c r="M123" s="10" t="inlineStr"/>
     </row>
-    <row r="124" ht="230" customHeight="1">
+    <row r="124" ht="270" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8385,7 +8391,7 @@
       <c r="L124" s="10" t="inlineStr"/>
       <c r="M124" s="10" t="inlineStr"/>
     </row>
-    <row r="125" ht="230" customHeight="1">
+    <row r="125" ht="270" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8449,7 +8455,7 @@
       <c r="L125" s="10" t="inlineStr"/>
       <c r="M125" s="10" t="inlineStr"/>
     </row>
-    <row r="126" ht="230" customHeight="1">
+    <row r="126" ht="270" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8513,7 +8519,7 @@
       <c r="L126" s="10" t="inlineStr"/>
       <c r="M126" s="10" t="inlineStr"/>
     </row>
-    <row r="127" ht="230" customHeight="1">
+    <row r="127" ht="270" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8577,7 +8583,7 @@
       <c r="L127" s="10" t="inlineStr"/>
       <c r="M127" s="10" t="inlineStr"/>
     </row>
-    <row r="128" ht="230" customHeight="1">
+    <row r="128" ht="270" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8641,7 +8647,7 @@
       <c r="L128" s="10" t="inlineStr"/>
       <c r="M128" s="10" t="inlineStr"/>
     </row>
-    <row r="129" ht="230" customHeight="1">
+    <row r="129" ht="270" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8705,7 +8711,7 @@
       <c r="L129" s="10" t="inlineStr"/>
       <c r="M129" s="10" t="inlineStr"/>
     </row>
-    <row r="130" ht="230" customHeight="1">
+    <row r="130" ht="270" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8769,7 +8775,7 @@
       <c r="L130" s="10" t="inlineStr"/>
       <c r="M130" s="10" t="inlineStr"/>
     </row>
-    <row r="131" ht="230" customHeight="1">
+    <row r="131" ht="270" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8833,7 +8839,7 @@
       <c r="L131" s="10" t="inlineStr"/>
       <c r="M131" s="10" t="inlineStr"/>
     </row>
-    <row r="132" ht="230" customHeight="1">
+    <row r="132" ht="270" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8897,7 +8903,7 @@
       <c r="L132" s="10" t="inlineStr"/>
       <c r="M132" s="10" t="inlineStr"/>
     </row>
-    <row r="133" ht="230" customHeight="1">
+    <row r="133" ht="270" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8961,7 +8967,7 @@
       <c r="L133" s="10" t="inlineStr"/>
       <c r="M133" s="10" t="inlineStr"/>
     </row>
-    <row r="134" ht="230" customHeight="1">
+    <row r="134" ht="270" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9025,7 +9031,7 @@
       <c r="L134" s="10" t="inlineStr"/>
       <c r="M134" s="10" t="inlineStr"/>
     </row>
-    <row r="135" ht="230" customHeight="1">
+    <row r="135" ht="270" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9089,7 +9095,7 @@
       <c r="L135" s="10" t="inlineStr"/>
       <c r="M135" s="10" t="inlineStr"/>
     </row>
-    <row r="136" ht="230" customHeight="1">
+    <row r="136" ht="270" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9153,7 +9159,7 @@
       <c r="L136" s="10" t="inlineStr"/>
       <c r="M136" s="10" t="inlineStr"/>
     </row>
-    <row r="137" ht="230" customHeight="1">
+    <row r="137" ht="270" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9217,7 +9223,7 @@
       <c r="L137" s="10" t="inlineStr"/>
       <c r="M137" s="10" t="inlineStr"/>
     </row>
-    <row r="138" ht="230" customHeight="1">
+    <row r="138" ht="270" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9281,7 +9287,7 @@
       <c r="L138" s="10" t="inlineStr"/>
       <c r="M138" s="10" t="inlineStr"/>
     </row>
-    <row r="139" ht="230" customHeight="1">
+    <row r="139" ht="270" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9345,7 +9351,7 @@
       <c r="L139" s="10" t="inlineStr"/>
       <c r="M139" s="10" t="inlineStr"/>
     </row>
-    <row r="140" ht="230" customHeight="1">
+    <row r="140" ht="270" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9409,7 +9415,7 @@
       <c r="L140" s="10" t="inlineStr"/>
       <c r="M140" s="10" t="inlineStr"/>
     </row>
-    <row r="141" ht="230" customHeight="1">
+    <row r="141" ht="270" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9473,7 +9479,7 @@
       <c r="L141" s="10" t="inlineStr"/>
       <c r="M141" s="10" t="inlineStr"/>
     </row>
-    <row r="142" ht="230" customHeight="1">
+    <row r="142" ht="270" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9537,7 +9543,7 @@
       <c r="L142" s="10" t="inlineStr"/>
       <c r="M142" s="10" t="inlineStr"/>
     </row>
-    <row r="143" ht="230" customHeight="1">
+    <row r="143" ht="270" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9601,7 +9607,7 @@
       <c r="L143" s="10" t="inlineStr"/>
       <c r="M143" s="10" t="inlineStr"/>
     </row>
-    <row r="144" ht="230" customHeight="1">
+    <row r="144" ht="270" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9665,7 +9671,7 @@
       <c r="L144" s="10" t="inlineStr"/>
       <c r="M144" s="10" t="inlineStr"/>
     </row>
-    <row r="145" ht="230" customHeight="1">
+    <row r="145" ht="270" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9729,7 +9735,7 @@
       <c r="L145" s="10" t="inlineStr"/>
       <c r="M145" s="10" t="inlineStr"/>
     </row>
-    <row r="146" ht="230" customHeight="1">
+    <row r="146" ht="270" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9793,7 +9799,7 @@
       <c r="L146" s="10" t="inlineStr"/>
       <c r="M146" s="10" t="inlineStr"/>
     </row>
-    <row r="147" ht="230" customHeight="1">
+    <row r="147" ht="270" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9857,7 +9863,7 @@
       <c r="L147" s="10" t="inlineStr"/>
       <c r="M147" s="10" t="inlineStr"/>
     </row>
-    <row r="148" ht="230" customHeight="1">
+    <row r="148" ht="270" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9921,7 +9927,7 @@
       <c r="L148" s="10" t="inlineStr"/>
       <c r="M148" s="10" t="inlineStr"/>
     </row>
-    <row r="149" ht="230" customHeight="1">
+    <row r="149" ht="270" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9985,7 +9991,7 @@
       <c r="L149" s="10" t="inlineStr"/>
       <c r="M149" s="10" t="inlineStr"/>
     </row>
-    <row r="150" ht="230" customHeight="1">
+    <row r="150" ht="270" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10049,7 +10055,7 @@
       <c r="L150" s="10" t="inlineStr"/>
       <c r="M150" s="10" t="inlineStr"/>
     </row>
-    <row r="151" ht="230" customHeight="1">
+    <row r="151" ht="270" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10113,7 +10119,7 @@
       <c r="L151" s="10" t="inlineStr"/>
       <c r="M151" s="10" t="inlineStr"/>
     </row>
-    <row r="152" ht="230" customHeight="1">
+    <row r="152" ht="270" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10177,7 +10183,7 @@
       <c r="L152" s="10" t="inlineStr"/>
       <c r="M152" s="10" t="inlineStr"/>
     </row>
-    <row r="153" ht="230" customHeight="1">
+    <row r="153" ht="270" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10241,7 +10247,7 @@
       <c r="L153" s="10" t="inlineStr"/>
       <c r="M153" s="10" t="inlineStr"/>
     </row>
-    <row r="154" ht="230" customHeight="1">
+    <row r="154" ht="270" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10305,7 +10311,7 @@
       <c r="L154" s="10" t="inlineStr"/>
       <c r="M154" s="10" t="inlineStr"/>
     </row>
-    <row r="155" ht="230" customHeight="1">
+    <row r="155" ht="270" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10369,7 +10375,7 @@
       <c r="L155" s="10" t="inlineStr"/>
       <c r="M155" s="10" t="inlineStr"/>
     </row>
-    <row r="156" ht="230" customHeight="1">
+    <row r="156" ht="270" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10433,7 +10439,7 @@
       <c r="L156" s="10" t="inlineStr"/>
       <c r="M156" s="10" t="inlineStr"/>
     </row>
-    <row r="157" ht="230" customHeight="1">
+    <row r="157" ht="270" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10497,7 +10503,7 @@
       <c r="L157" s="10" t="inlineStr"/>
       <c r="M157" s="10" t="inlineStr"/>
     </row>
-    <row r="158" ht="230" customHeight="1">
+    <row r="158" ht="270" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10561,7 +10567,7 @@
       <c r="L158" s="10" t="inlineStr"/>
       <c r="M158" s="10" t="inlineStr"/>
     </row>
-    <row r="159" ht="230" customHeight="1">
+    <row r="159" ht="270" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10625,7 +10631,7 @@
       <c r="L159" s="10" t="inlineStr"/>
       <c r="M159" s="10" t="inlineStr"/>
     </row>
-    <row r="160" ht="230" customHeight="1">
+    <row r="160" ht="270" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10689,7 +10695,7 @@
       <c r="L160" s="10" t="inlineStr"/>
       <c r="M160" s="10" t="inlineStr"/>
     </row>
-    <row r="161" ht="230" customHeight="1">
+    <row r="161" ht="270" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10753,7 +10759,7 @@
       <c r="L161" s="10" t="inlineStr"/>
       <c r="M161" s="10" t="inlineStr"/>
     </row>
-    <row r="162" ht="230" customHeight="1">
+    <row r="162" ht="270" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10817,7 +10823,7 @@
       <c r="L162" s="10" t="inlineStr"/>
       <c r="M162" s="10" t="inlineStr"/>
     </row>
-    <row r="163" ht="230" customHeight="1">
+    <row r="163" ht="270" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -10881,7 +10887,7 @@
       <c r="L163" s="10" t="inlineStr"/>
       <c r="M163" s="10" t="inlineStr"/>
     </row>
-    <row r="164" ht="230" customHeight="1">
+    <row r="164" ht="270" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -10945,7 +10951,7 @@
       <c r="L164" s="10" t="inlineStr"/>
       <c r="M164" s="10" t="inlineStr"/>
     </row>
-    <row r="165" ht="230" customHeight="1">
+    <row r="165" ht="270" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11009,7 +11015,7 @@
       <c r="L165" s="10" t="inlineStr"/>
       <c r="M165" s="10" t="inlineStr"/>
     </row>
-    <row r="166" ht="230" customHeight="1">
+    <row r="166" ht="270" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11073,7 +11079,7 @@
       <c r="L166" s="10" t="inlineStr"/>
       <c r="M166" s="10" t="inlineStr"/>
     </row>
-    <row r="167" ht="230" customHeight="1">
+    <row r="167" ht="270" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11137,7 +11143,7 @@
       <c r="L167" s="10" t="inlineStr"/>
       <c r="M167" s="10" t="inlineStr"/>
     </row>
-    <row r="168" ht="230" customHeight="1">
+    <row r="168" ht="270" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11201,7 +11207,7 @@
       <c r="L168" s="10" t="inlineStr"/>
       <c r="M168" s="10" t="inlineStr"/>
     </row>
-    <row r="169" ht="230" customHeight="1">
+    <row r="169" ht="270" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11265,7 +11271,7 @@
       <c r="L169" s="10" t="inlineStr"/>
       <c r="M169" s="10" t="inlineStr"/>
     </row>
-    <row r="170" ht="230" customHeight="1">
+    <row r="170" ht="270" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11329,7 +11335,7 @@
       <c r="L170" s="10" t="inlineStr"/>
       <c r="M170" s="10" t="inlineStr"/>
     </row>
-    <row r="171" ht="230" customHeight="1">
+    <row r="171" ht="270" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11393,7 +11399,7 @@
       <c r="L171" s="10" t="inlineStr"/>
       <c r="M171" s="10" t="inlineStr"/>
     </row>
-    <row r="172" ht="230" customHeight="1">
+    <row r="172" ht="270" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11457,7 +11463,7 @@
       <c r="L172" s="10" t="inlineStr"/>
       <c r="M172" s="10" t="inlineStr"/>
     </row>
-    <row r="173" ht="230" customHeight="1">
+    <row r="173" ht="270" customHeight="1">
       <c r="A173" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11521,7 +11527,7 @@
       <c r="L173" s="10" t="inlineStr"/>
       <c r="M173" s="10" t="inlineStr"/>
     </row>
-    <row r="174" ht="230" customHeight="1">
+    <row r="174" ht="270" customHeight="1">
       <c r="A174" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11585,7 +11591,7 @@
       <c r="L174" s="10" t="inlineStr"/>
       <c r="M174" s="10" t="inlineStr"/>
     </row>
-    <row r="175" ht="230" customHeight="1">
+    <row r="175" ht="270" customHeight="1">
       <c r="A175" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11649,7 +11655,7 @@
       <c r="L175" s="10" t="inlineStr"/>
       <c r="M175" s="10" t="inlineStr"/>
     </row>
-    <row r="176" ht="230" customHeight="1">
+    <row r="176" ht="270" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11713,7 +11719,7 @@
       <c r="L176" s="10" t="inlineStr"/>
       <c r="M176" s="10" t="inlineStr"/>
     </row>
-    <row r="177" ht="230" customHeight="1">
+    <row r="177" ht="270" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11777,7 +11783,7 @@
       <c r="L177" s="10" t="inlineStr"/>
       <c r="M177" s="10" t="inlineStr"/>
     </row>
-    <row r="178" ht="230" customHeight="1">
+    <row r="178" ht="270" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11841,7 +11847,7 @@
       <c r="L178" s="10" t="inlineStr"/>
       <c r="M178" s="10" t="inlineStr"/>
     </row>
-    <row r="179" ht="230" customHeight="1">
+    <row r="179" ht="270" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11905,7 +11911,7 @@
       <c r="L179" s="10" t="inlineStr"/>
       <c r="M179" s="10" t="inlineStr"/>
     </row>
-    <row r="180" ht="230" customHeight="1">
+    <row r="180" ht="270" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11969,7 +11975,7 @@
       <c r="L180" s="10" t="inlineStr"/>
       <c r="M180" s="10" t="inlineStr"/>
     </row>
-    <row r="181" ht="230" customHeight="1">
+    <row r="181" ht="270" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12033,7 +12039,7 @@
       <c r="L181" s="10" t="inlineStr"/>
       <c r="M181" s="10" t="inlineStr"/>
     </row>
-    <row r="182" ht="230" customHeight="1">
+    <row r="182" ht="270" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12097,7 +12103,7 @@
       <c r="L182" s="10" t="inlineStr"/>
       <c r="M182" s="10" t="inlineStr"/>
     </row>
-    <row r="183" ht="230" customHeight="1">
+    <row r="183" ht="270" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12161,7 +12167,7 @@
       <c r="L183" s="10" t="inlineStr"/>
       <c r="M183" s="10" t="inlineStr"/>
     </row>
-    <row r="184" ht="230" customHeight="1">
+    <row r="184" ht="270" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12225,7 +12231,7 @@
       <c r="L184" s="10" t="inlineStr"/>
       <c r="M184" s="10" t="inlineStr"/>
     </row>
-    <row r="185" ht="230" customHeight="1">
+    <row r="185" ht="270" customHeight="1">
       <c r="A185" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12289,7 +12295,7 @@
       <c r="L185" s="10" t="inlineStr"/>
       <c r="M185" s="10" t="inlineStr"/>
     </row>
-    <row r="186" ht="230" customHeight="1">
+    <row r="186" ht="270" customHeight="1">
       <c r="A186" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12353,7 +12359,7 @@
       <c r="L186" s="10" t="inlineStr"/>
       <c r="M186" s="10" t="inlineStr"/>
     </row>
-    <row r="187" ht="230" customHeight="1">
+    <row r="187" ht="270" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12417,7 +12423,7 @@
       <c r="L187" s="10" t="inlineStr"/>
       <c r="M187" s="10" t="inlineStr"/>
     </row>
-    <row r="188" ht="230" customHeight="1">
+    <row r="188" ht="270" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12481,7 +12487,7 @@
       <c r="L188" s="10" t="inlineStr"/>
       <c r="M188" s="10" t="inlineStr"/>
     </row>
-    <row r="189" ht="230" customHeight="1">
+    <row r="189" ht="270" customHeight="1">
       <c r="A189" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12545,7 +12551,7 @@
       <c r="L189" s="10" t="inlineStr"/>
       <c r="M189" s="10" t="inlineStr"/>
     </row>
-    <row r="190" ht="230" customHeight="1">
+    <row r="190" ht="270" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12609,7 +12615,7 @@
       <c r="L190" s="10" t="inlineStr"/>
       <c r="M190" s="10" t="inlineStr"/>
     </row>
-    <row r="191" ht="230" customHeight="1">
+    <row r="191" ht="270" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12673,7 +12679,7 @@
       <c r="L191" s="10" t="inlineStr"/>
       <c r="M191" s="10" t="inlineStr"/>
     </row>
-    <row r="192" ht="230" customHeight="1">
+    <row r="192" ht="270" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12737,7 +12743,7 @@
       <c r="L192" s="10" t="inlineStr"/>
       <c r="M192" s="10" t="inlineStr"/>
     </row>
-    <row r="193" ht="230" customHeight="1">
+    <row r="193" ht="270" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12801,7 +12807,7 @@
       <c r="L193" s="10" t="inlineStr"/>
       <c r="M193" s="10" t="inlineStr"/>
     </row>
-    <row r="194" ht="230" customHeight="1">
+    <row r="194" ht="270" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12865,7 +12871,7 @@
       <c r="L194" s="10" t="inlineStr"/>
       <c r="M194" s="10" t="inlineStr"/>
     </row>
-    <row r="195" ht="230" customHeight="1">
+    <row r="195" ht="270" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12929,7 +12935,7 @@
       <c r="L195" s="10" t="inlineStr"/>
       <c r="M195" s="10" t="inlineStr"/>
     </row>
-    <row r="196" ht="230" customHeight="1">
+    <row r="196" ht="270" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12993,7 +12999,7 @@
       <c r="L196" s="10" t="inlineStr"/>
       <c r="M196" s="10" t="inlineStr"/>
     </row>
-    <row r="197" ht="230" customHeight="1">
+    <row r="197" ht="270" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13057,7 +13063,7 @@
       <c r="L197" s="10" t="inlineStr"/>
       <c r="M197" s="10" t="inlineStr"/>
     </row>
-    <row r="198" ht="230" customHeight="1">
+    <row r="198" ht="270" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13121,7 +13127,7 @@
       <c r="L198" s="10" t="inlineStr"/>
       <c r="M198" s="10" t="inlineStr"/>
     </row>
-    <row r="199" ht="230" customHeight="1">
+    <row r="199" ht="270" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13185,7 +13191,7 @@
       <c r="L199" s="10" t="inlineStr"/>
       <c r="M199" s="10" t="inlineStr"/>
     </row>
-    <row r="200" ht="230" customHeight="1">
+    <row r="200" ht="270" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13249,7 +13255,7 @@
       <c r="L200" s="10" t="inlineStr"/>
       <c r="M200" s="10" t="inlineStr"/>
     </row>
-    <row r="201" ht="230" customHeight="1">
+    <row r="201" ht="270" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13313,7 +13319,7 @@
       <c r="L201" s="10" t="inlineStr"/>
       <c r="M201" s="10" t="inlineStr"/>
     </row>
-    <row r="202" ht="230" customHeight="1">
+    <row r="202" ht="270" customHeight="1">
       <c r="A202" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13377,7 +13383,7 @@
       <c r="L202" s="10" t="inlineStr"/>
       <c r="M202" s="10" t="inlineStr"/>
     </row>
-    <row r="203" ht="230" customHeight="1">
+    <row r="203" ht="270" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13441,7 +13447,7 @@
       <c r="L203" s="10" t="inlineStr"/>
       <c r="M203" s="10" t="inlineStr"/>
     </row>
-    <row r="204" ht="230" customHeight="1">
+    <row r="204" ht="270" customHeight="1">
       <c r="A204" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13496,7 +13502,7 @@
       <c r="L204" s="10" t="inlineStr"/>
       <c r="M204" s="10" t="inlineStr"/>
     </row>
-    <row r="205" ht="230" customHeight="1">
+    <row r="205" ht="270" customHeight="1">
       <c r="A205" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13560,7 +13566,7 @@
       <c r="L205" s="10" t="inlineStr"/>
       <c r="M205" s="10" t="inlineStr"/>
     </row>
-    <row r="206" ht="230" customHeight="1">
+    <row r="206" ht="270" customHeight="1">
       <c r="A206" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13624,7 +13630,7 @@
       <c r="L206" s="10" t="inlineStr"/>
       <c r="M206" s="10" t="inlineStr"/>
     </row>
-    <row r="207" ht="230" customHeight="1">
+    <row r="207" ht="270" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13688,7 +13694,7 @@
       <c r="L207" s="10" t="inlineStr"/>
       <c r="M207" s="10" t="inlineStr"/>
     </row>
-    <row r="208" ht="230" customHeight="1">
+    <row r="208" ht="270" customHeight="1">
       <c r="A208" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13752,7 +13758,7 @@
       <c r="L208" s="10" t="inlineStr"/>
       <c r="M208" s="10" t="inlineStr"/>
     </row>
-    <row r="209" ht="230" customHeight="1">
+    <row r="209" ht="270" customHeight="1">
       <c r="A209" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13816,7 +13822,7 @@
       <c r="L209" s="10" t="inlineStr"/>
       <c r="M209" s="10" t="inlineStr"/>
     </row>
-    <row r="210" ht="230" customHeight="1">
+    <row r="210" ht="270" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13871,7 +13877,7 @@
       <c r="L210" s="10" t="inlineStr"/>
       <c r="M210" s="10" t="inlineStr"/>
     </row>
-    <row r="211" ht="230" customHeight="1">
+    <row r="211" ht="270" customHeight="1">
       <c r="A211" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13935,7 +13941,7 @@
       <c r="L211" s="10" t="inlineStr"/>
       <c r="M211" s="10" t="inlineStr"/>
     </row>
-    <row r="212" ht="230" customHeight="1">
+    <row r="212" ht="270" customHeight="1">
       <c r="A212" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13999,7 +14005,7 @@
       <c r="L212" s="10" t="inlineStr"/>
       <c r="M212" s="10" t="inlineStr"/>
     </row>
-    <row r="213" ht="230" customHeight="1">
+    <row r="213" ht="270" customHeight="1">
       <c r="A213" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14063,7 +14069,7 @@
       <c r="L213" s="10" t="inlineStr"/>
       <c r="M213" s="10" t="inlineStr"/>
     </row>
-    <row r="214" ht="230" customHeight="1">
+    <row r="214" ht="270" customHeight="1">
       <c r="A214" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14127,7 +14133,7 @@
       <c r="L214" s="10" t="inlineStr"/>
       <c r="M214" s="10" t="inlineStr"/>
     </row>
-    <row r="215" ht="230" customHeight="1">
+    <row r="215" ht="270" customHeight="1">
       <c r="A215" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14191,7 +14197,7 @@
       <c r="L215" s="10" t="inlineStr"/>
       <c r="M215" s="10" t="inlineStr"/>
     </row>
-    <row r="216" ht="230" customHeight="1">
+    <row r="216" ht="270" customHeight="1">
       <c r="A216" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14255,7 +14261,7 @@
       <c r="L216" s="10" t="inlineStr"/>
       <c r="M216" s="10" t="inlineStr"/>
     </row>
-    <row r="217" ht="230" customHeight="1">
+    <row r="217" ht="270" customHeight="1">
       <c r="A217" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14319,7 +14325,7 @@
       <c r="L217" s="10" t="inlineStr"/>
       <c r="M217" s="10" t="inlineStr"/>
     </row>
-    <row r="218" ht="230" customHeight="1">
+    <row r="218" ht="270" customHeight="1">
       <c r="A218" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14383,7 +14389,7 @@
       <c r="L218" s="10" t="inlineStr"/>
       <c r="M218" s="10" t="inlineStr"/>
     </row>
-    <row r="219" ht="230" customHeight="1">
+    <row r="219" ht="270" customHeight="1">
       <c r="A219" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14447,7 +14453,7 @@
       <c r="L219" s="10" t="inlineStr"/>
       <c r="M219" s="10" t="inlineStr"/>
     </row>
-    <row r="220" ht="230" customHeight="1">
+    <row r="220" ht="270" customHeight="1">
       <c r="A220" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14511,7 +14517,7 @@
       <c r="L220" s="10" t="inlineStr"/>
       <c r="M220" s="10" t="inlineStr"/>
     </row>
-    <row r="221" ht="230" customHeight="1">
+    <row r="221" ht="270" customHeight="1">
       <c r="A221" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14575,7 +14581,7 @@
       <c r="L221" s="10" t="inlineStr"/>
       <c r="M221" s="10" t="inlineStr"/>
     </row>
-    <row r="222" ht="230" customHeight="1">
+    <row r="222" ht="270" customHeight="1">
       <c r="A222" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14639,7 +14645,7 @@
       <c r="L222" s="10" t="inlineStr"/>
       <c r="M222" s="10" t="inlineStr"/>
     </row>
-    <row r="223" ht="230" customHeight="1">
+    <row r="223" ht="270" customHeight="1">
       <c r="A223" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14703,7 +14709,7 @@
       <c r="L223" s="10" t="inlineStr"/>
       <c r="M223" s="10" t="inlineStr"/>
     </row>
-    <row r="224" ht="230" customHeight="1">
+    <row r="224" ht="270" customHeight="1">
       <c r="A224" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14767,7 +14773,7 @@
       <c r="L224" s="10" t="inlineStr"/>
       <c r="M224" s="10" t="inlineStr"/>
     </row>
-    <row r="225" ht="230" customHeight="1">
+    <row r="225" ht="270" customHeight="1">
       <c r="A225" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14831,7 +14837,7 @@
       <c r="L225" s="10" t="inlineStr"/>
       <c r="M225" s="10" t="inlineStr"/>
     </row>
-    <row r="226" ht="230" customHeight="1">
+    <row r="226" ht="270" customHeight="1">
       <c r="A226" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14895,7 +14901,7 @@
       <c r="L226" s="10" t="inlineStr"/>
       <c r="M226" s="10" t="inlineStr"/>
     </row>
-    <row r="227" ht="230" customHeight="1">
+    <row r="227" ht="270" customHeight="1">
       <c r="A227" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14959,7 +14965,7 @@
       <c r="L227" s="10" t="inlineStr"/>
       <c r="M227" s="10" t="inlineStr"/>
     </row>
-    <row r="228" ht="230" customHeight="1">
+    <row r="228" ht="270" customHeight="1">
       <c r="A228" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15023,7 +15029,7 @@
       <c r="L228" s="10" t="inlineStr"/>
       <c r="M228" s="10" t="inlineStr"/>
     </row>
-    <row r="229" ht="230" customHeight="1">
+    <row r="229" ht="270" customHeight="1">
       <c r="A229" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15087,7 +15093,7 @@
       <c r="L229" s="10" t="inlineStr"/>
       <c r="M229" s="10" t="inlineStr"/>
     </row>
-    <row r="230" ht="230" customHeight="1">
+    <row r="230" ht="270" customHeight="1">
       <c r="A230" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15151,7 +15157,7 @@
       <c r="L230" s="10" t="inlineStr"/>
       <c r="M230" s="10" t="inlineStr"/>
     </row>
-    <row r="231" ht="230" customHeight="1">
+    <row r="231" ht="270" customHeight="1">
       <c r="A231" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15215,7 +15221,7 @@
       <c r="L231" s="10" t="inlineStr"/>
       <c r="M231" s="10" t="inlineStr"/>
     </row>
-    <row r="232" ht="230" customHeight="1">
+    <row r="232" ht="270" customHeight="1">
       <c r="A232" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15279,7 +15285,7 @@
       <c r="L232" s="10" t="inlineStr"/>
       <c r="M232" s="10" t="inlineStr"/>
     </row>
-    <row r="233" ht="230" customHeight="1">
+    <row r="233" ht="270" customHeight="1">
       <c r="A233" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15343,7 +15349,7 @@
       <c r="L233" s="10" t="inlineStr"/>
       <c r="M233" s="10" t="inlineStr"/>
     </row>
-    <row r="234" ht="230" customHeight="1">
+    <row r="234" ht="270" customHeight="1">
       <c r="A234" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15407,7 +15413,7 @@
       <c r="L234" s="10" t="inlineStr"/>
       <c r="M234" s="10" t="inlineStr"/>
     </row>
-    <row r="235" ht="230" customHeight="1">
+    <row r="235" ht="270" customHeight="1">
       <c r="A235" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15471,7 +15477,7 @@
       <c r="L235" s="10" t="inlineStr"/>
       <c r="M235" s="10" t="inlineStr"/>
     </row>
-    <row r="236" ht="230" customHeight="1">
+    <row r="236" ht="270" customHeight="1">
       <c r="A236" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15535,7 +15541,7 @@
       <c r="L236" s="10" t="inlineStr"/>
       <c r="M236" s="10" t="inlineStr"/>
     </row>
-    <row r="237" ht="230" customHeight="1">
+    <row r="237" ht="270" customHeight="1">
       <c r="A237" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15599,7 +15605,7 @@
       <c r="L237" s="10" t="inlineStr"/>
       <c r="M237" s="10" t="inlineStr"/>
     </row>
-    <row r="238" ht="230" customHeight="1">
+    <row r="238" ht="270" customHeight="1">
       <c r="A238" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15663,7 +15669,7 @@
       <c r="L238" s="10" t="inlineStr"/>
       <c r="M238" s="10" t="inlineStr"/>
     </row>
-    <row r="239" ht="230" customHeight="1">
+    <row r="239" ht="270" customHeight="1">
       <c r="A239" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15727,7 +15733,7 @@
       <c r="L239" s="10" t="inlineStr"/>
       <c r="M239" s="10" t="inlineStr"/>
     </row>
-    <row r="240" ht="230" customHeight="1">
+    <row r="240" ht="270" customHeight="1">
       <c r="A240" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15791,7 +15797,7 @@
       <c r="L240" s="10" t="inlineStr"/>
       <c r="M240" s="10" t="inlineStr"/>
     </row>
-    <row r="241" ht="230" customHeight="1">
+    <row r="241" ht="270" customHeight="1">
       <c r="A241" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15855,7 +15861,7 @@
       <c r="L241" s="10" t="inlineStr"/>
       <c r="M241" s="10" t="inlineStr"/>
     </row>
-    <row r="242" ht="230" customHeight="1">
+    <row r="242" ht="270" customHeight="1">
       <c r="A242" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15919,7 +15925,7 @@
       <c r="L242" s="10" t="inlineStr"/>
       <c r="M242" s="10" t="inlineStr"/>
     </row>
-    <row r="243" ht="230" customHeight="1">
+    <row r="243" ht="270" customHeight="1">
       <c r="A243" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15983,7 +15989,7 @@
       <c r="L243" s="10" t="inlineStr"/>
       <c r="M243" s="10" t="inlineStr"/>
     </row>
-    <row r="244" ht="230" customHeight="1">
+    <row r="244" ht="270" customHeight="1">
       <c r="A244" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16047,7 +16053,7 @@
       <c r="L244" s="10" t="inlineStr"/>
       <c r="M244" s="10" t="inlineStr"/>
     </row>
-    <row r="245" ht="230" customHeight="1">
+    <row r="245" ht="270" customHeight="1">
       <c r="A245" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16111,7 +16117,7 @@
       <c r="L245" s="10" t="inlineStr"/>
       <c r="M245" s="10" t="inlineStr"/>
     </row>
-    <row r="246" ht="230" customHeight="1">
+    <row r="246" ht="270" customHeight="1">
       <c r="A246" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16175,7 +16181,7 @@
       <c r="L246" s="10" t="inlineStr"/>
       <c r="M246" s="10" t="inlineStr"/>
     </row>
-    <row r="247" ht="230" customHeight="1">
+    <row r="247" ht="270" customHeight="1">
       <c r="A247" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16239,7 +16245,7 @@
       <c r="L247" s="10" t="inlineStr"/>
       <c r="M247" s="10" t="inlineStr"/>
     </row>
-    <row r="248" ht="230" customHeight="1">
+    <row r="248" ht="270" customHeight="1">
       <c r="A248" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16303,7 +16309,7 @@
       <c r="L248" s="10" t="inlineStr"/>
       <c r="M248" s="10" t="inlineStr"/>
     </row>
-    <row r="249" ht="230" customHeight="1">
+    <row r="249" ht="270" customHeight="1">
       <c r="A249" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16367,7 +16373,7 @@
       <c r="L249" s="10" t="inlineStr"/>
       <c r="M249" s="10" t="inlineStr"/>
     </row>
-    <row r="250" ht="230" customHeight="1">
+    <row r="250" ht="270" customHeight="1">
       <c r="A250" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16431,7 +16437,7 @@
       <c r="L250" s="10" t="inlineStr"/>
       <c r="M250" s="10" t="inlineStr"/>
     </row>
-    <row r="251" ht="230" customHeight="1">
+    <row r="251" ht="270" customHeight="1">
       <c r="A251" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16495,7 +16501,7 @@
       <c r="L251" s="10" t="inlineStr"/>
       <c r="M251" s="10" t="inlineStr"/>
     </row>
-    <row r="252" ht="230" customHeight="1">
+    <row r="252" ht="270" customHeight="1">
       <c r="A252" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16559,7 +16565,7 @@
       <c r="L252" s="10" t="inlineStr"/>
       <c r="M252" s="10" t="inlineStr"/>
     </row>
-    <row r="253" ht="230" customHeight="1">
+    <row r="253" ht="270" customHeight="1">
       <c r="A253" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16623,7 +16629,7 @@
       <c r="L253" s="10" t="inlineStr"/>
       <c r="M253" s="10" t="inlineStr"/>
     </row>
-    <row r="254" ht="230" customHeight="1">
+    <row r="254" ht="270" customHeight="1">
       <c r="A254" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16687,7 +16693,7 @@
       <c r="L254" s="10" t="inlineStr"/>
       <c r="M254" s="10" t="inlineStr"/>
     </row>
-    <row r="255" ht="230" customHeight="1">
+    <row r="255" ht="270" customHeight="1">
       <c r="A255" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16751,7 +16757,7 @@
       <c r="L255" s="10" t="inlineStr"/>
       <c r="M255" s="10" t="inlineStr"/>
     </row>
-    <row r="256" ht="230" customHeight="1">
+    <row r="256" ht="270" customHeight="1">
       <c r="A256" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -16800,12 +16806,13 @@
       <c r="J256" s="9" t="inlineStr">
         <is>
           <t>Bonjour Jean-Michel Leprince,
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
+Québec dont l'atelier est dans Limoilou.
 Vous couvrez l'asclépiade depuis au moins 2014 : le Téléjournal, la soie d'Amérique partie
 sur l'Everest, le pouvoir absorbant de la fibre sur les hydrocarbures, le lien avec le
 monarque. Vous avez suivi cette histoire plus longtemps que la plupart des entreprises qui
 s'y sont essayées.
-On est l'entreprise qui a démarré après la chute de la première filière. Six ans plus tard,
-on achète encore de l'asclépiade québécoise et on transforme l'isolant nous-mêmes à
+On a démarré après la chute de la première filière. Six ans plus tard, on achète encore de l'asclépiade québécoise et on transforme l'isolant nous-mêmes à
 Limoilou. Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques
 par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16821,7 +16828,7 @@
       <c r="L256" s="10" t="inlineStr"/>
       <c r="M256" s="10" t="inlineStr"/>
     </row>
-    <row r="257" ht="230" customHeight="1">
+    <row r="257" ht="270" customHeight="1">
       <c r="A257" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -16866,10 +16873,11 @@
       <c r="J257" s="9" t="inlineStr">
         <is>
           <t>Bonjour Antoine Stab,
+Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
+Québec dont l'atelier est dans Limoilou.
 Vous aviez écrit sur le soyer du Québec dans Espaces en février 2015, à l'époque où la fibre
 devait remplacer le duvet.
-On est l'entreprise qui a démarré après la chute de cette première filière. Six ans plus
-tard, on achète encore de l'asclépiade québécoise, on transforme l'isolant nous-mêmes, et il
+On a démarré après la chute de cette première filière. Six ans plus tard, on achète encore de l'asclépiade québécoise, on transforme l'isolant nous-mêmes, et il
 existe maintenant un manteau à inserts d'asclépiade amovibles autour de 300 $.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Brouillons à éditer" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$M$257</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Brouillons à éditer'!$A$1:$N$257</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +63,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DEEAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -119,10 +124,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -490,17 +498,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="106" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Version 3 — tout corrigé</t>
+          <t>Version 4 — les objets</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -509,95 +517,95 @@
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="54" customHeight="1">
+    <row r="3" ht="56" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Le registre</t>
+          <t>Le modèle</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Plus d'excuses sur le virage manufacturier, plus de « un achat ne sauve pas un papillon », plus de « je ne peux pas dire comment ça s'est terminé ». Vérifié : zéro occurrence dans les 253 brouillons.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="54" customHeight="1">
+          <t>« Nous serons diffusés à Dragons' Den le 17 septembre! » L'objet annonce la nouvelle, avec la date, et il a le droit d'être content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="56" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>La présentation</t>
+          <t>Ce qu'ils étaient</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Les 217 courriels froids commencent par qui tu es, ce qu'est Lasclay et ce qu'est l'asclépiade — sous le nom de « petits cochons », que tout le monde reconnaît ici. Les 5 écrits à la main aussi, ils ne l'avaient pas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="54" customHeight="1">
+          <t>« Le monarque, l'asclépiade, et l'idée qu'il faut la rendre payante ». Un titre d'essai, pas un objet de courriel. Et sans accents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Le « pourquoi vous »</t>
+          <t>Quatre variantes</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chaque courriel froid dit explicitement pourquoi il s'adresse à cette personne-là : sa région quand l'asclépiade y a une histoire réelle, son sujet sinon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1">
+          <t>A, B, E, G : Nous serons diffusés à Dragons' Den le 17 septembre!  |  C, F, J : L'asclépiade s'en va à Dragons' Den le 17 septembre!  |  D : L'asclépiade et les monarques à Dragons' Den le 17 septembre!  |  I : … — invité disponible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Une fausse accroche retirée</t>
+          <t>Pourquoi pas un seul</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>« Notre atelier est dans Limoilou » ne dit rien à un journal de Charlevoix. La Capitale-Nationale passe au thématique.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Les quatre sans historique</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Roberge, Laforest, Goubau et Dostie n'avaient aucune présentation. Ils en ont une.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Les documents</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>04-gabarits-courriels.md est réécrit sur ton squelette. La matrice ne prescrit plus « nommer ce que le virage a coûté » ni la mise en garde sur les monarques.</t>
-        </is>
-      </c>
+          <t>253 courriels avec exactement la même ligne d'objet se comportent comme du publipostage aux yeux des filtres, et « l'asclépiade s'en va » parle plus à un journaliste agricole qu'à un chroniqueur d'affaires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Rappel des versions précédentes</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ce qui vient de toi</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12" ht="54" customHeight="1">
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Présentation complète en tête des courriels froids, « pourquoi vous » explicite, fausse accroche régionale retirée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Registre de Gabriel : plus d'excuses sur le virage, plus de mise en garde sur les monarques, plus de rappel de confidentialité.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Repris mot pour mot</t>
@@ -609,79 +617,55 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Registre</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Liste déroulante tu/vous. Chloé au « tu », tout le reste au « vous ». Bascule, je relance.</t>
-        </is>
-      </c>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Rappels</t>
+        </is>
+      </c>
       <c r="B14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Rappels</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="54" customHeight="1">
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Diffusion</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Jeudi 17 septembre 2026, 20 h (20 h 30 NT), CBC et CBC Gem. Prévente le samedi 12 septembre à 9 h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Diffusion</t>
+          <t>Ne pas envoyer</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Jeudi 17 septembre 2026, 20 h (20 h 30 NT), CBC et CBC Gem. Prévente le samedi 12 septembre à 9 h.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="54" customHeight="1">
+          <t>Anne-Sophie Roy à l'adresse Québecor. Annie Lafrance et Francis Higgins en liste froide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Ne pas envoyer</t>
+          <t>Courriels manquants</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Anne-Sophie Roy à l'adresse Québecor. Annie Lafrance et Francis Higgins en liste froide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Courriels manquants</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
           <t>Sophie Poisson, Caroline Bertrand, Karine Benoist, Antoine Stab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Salutations à vérifier</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Six fiches FPJQ mal formées (nom en majuscules, prénoms multiples).</t>
         </is>
       </c>
     </row>
@@ -696,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M257"/>
+  <dimension ref="A1:N257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -705,13 +689,14 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="88" customWidth="1" min="10" max="10"/>
-    <col width="88" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="86" customWidth="1" min="11" max="11"/>
+    <col width="86" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -762,20 +747,25 @@
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>Brouillon v3</t>
+          <t>Objet</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
+          <t>Brouillon v4</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
           <t>TA VERSION</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>CE QUI N'ALLAIT PAS</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
@@ -824,6 +814,11 @@
         </is>
       </c>
       <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>Bonjour M. Larocque,
 En mai dernier, nous avons discuté au téléphone suite à quoi, votre article sur le
@@ -842,9 +837,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
+      <c r="L2" s="11" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr"/>
+      <c r="N2" s="11" t="inlineStr"/>
     </row>
     <row r="3" ht="270" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -889,6 +884,11 @@
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Bérubé,
 En février, vous avez signé « La sinueuse route de la soie du Nord ». C'est un des rares textes à avoir pris la filière au complet, et pas juste une entreprise.
@@ -900,9 +900,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr"/>
-      <c r="L3" s="10" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
+      <c r="L3" s="11" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr"/>
+      <c r="N3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="270" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -947,6 +947,11 @@
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Bonjour Chloé,
 J'espère que tu vas bien. Tu as peut-être vu passer mon vidéo portant sur notre changement
@@ -971,9 +976,9 @@
 Au plaisir et n'hésite pas à me contacter si tu as des questions.</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr"/>
-      <c r="L4" s="10" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
+      <c r="L4" s="11" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr"/>
+      <c r="N4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="270" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1018,6 +1023,11 @@
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Paquet,
 On s'était parlé en septembre dernier pour Pleins feux sur Québec. Cette année, la date tombe presque au même endroit.
@@ -1028,9 +1038,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="10" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
+      <c r="L5" s="11" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
+      <c r="N5" s="11" t="inlineStr"/>
     </row>
     <row r="6" ht="270" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1075,6 +1085,11 @@
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Roy,
 Vous nous aviez appelés en mars 2025 pour votre reportage sur le dropshipping, comme exemple d'une entreprise qui fabrique vraiment. Et en décembre 2020, vous aviez signé un des tout premiers articles sur nos mitaines.
@@ -1086,9 +1101,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
+      <c r="L6" s="11" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr"/>
     </row>
     <row r="7" ht="270" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1133,6 +1148,11 @@
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Lafrance,
 En avril 2024, vous aviez signé « L'asclépiade : plus que la fibre de demain » dans Le Soleil Affaires, où vous m'aviez cité disant qu'on croyait à cette matière depuis les débuts. On y croit encore.
@@ -1144,9 +1164,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K7" s="10" t="inlineStr"/>
-      <c r="L7" s="10" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="270" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1191,6 +1211,11 @@
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Tison,
 En novembre 2021, vous aviez écrit « Le timide retour de l'asclépiade ». Le retour est pas mal moins timide qu'à l'époque : il y a maintenant un manteau et une veste à inserts d'asclépiade amovibles, autour de 300 $.
@@ -1202,9 +1227,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr"/>
-      <c r="L8" s="10" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
+      <c r="L8" s="11" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr"/>
     </row>
     <row r="9" ht="270" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1249,6 +1274,11 @@
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Lacombe,
 En novembre 2023, vous nous aviez contactés pour le suivi d'une précommande qui traînait. Vous aviez raison de le faire. Depuis, on sort graduellement de la précommande pour vendre du déjà produit, et les délais n'ont plus rien à voir.
@@ -1260,9 +1290,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="10" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
+      <c r="L9" s="11" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="270" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Roulot-Ganzmann,
 On s'était parlé en novembre 2023 pour du matériel sur nos produits d'asclépiade.
@@ -1318,9 +1353,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr"/>
-      <c r="L10" s="10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
+      <c r="L10" s="11" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="270" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Brault,
 On s'était parlé en janvier 2023 pour Le Soleil. L'atelier est toujours dans Limoilou, et c'est encore là que la soie d'asclépiade devient de l'isolant.
@@ -1376,9 +1416,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="10" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
+      <c r="L11" s="11" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr"/>
     </row>
     <row r="12" ht="270" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1423,6 +1463,11 @@
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Fillion,
 On s'était parlé d'asclépiade en janvier 2023. Depuis, le statut du monarque comme espèce en voie de disparition a été confirmé au Canada, et les États-Unis ont proposé de l'inscrire comme menacée. La plante n'a jamais été aussi pertinente.
@@ -1434,9 +1479,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K12" s="10" t="inlineStr"/>
-      <c r="L12" s="10" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="270" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1481,6 +1526,11 @@
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Aubert Bonn,
 En novembre 2022, vous aviez couvert nos nouveaux produits d'asclépiade. Le catalogue compte maintenant plus de 40 produits, et La Tribune a repris en décembre dernier l'article de Chloé Pouliot sur notre changement de modèle manufacturier.
@@ -1492,9 +1542,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="10" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
+      <c r="L13" s="11" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr"/>
     </row>
     <row r="14" ht="270" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1539,6 +1589,11 @@
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Émond,
 En septembre 2022, on s'était parlé de notre glacière d'asclépiade imprimée en 3D. On a continué à inventer nos propres procédés depuis, parce que personne d'autre ne les fait.
@@ -1550,9 +1605,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr"/>
-      <c r="L14" s="10" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
+      <c r="L14" s="11" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="270" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1597,6 +1652,11 @@
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Portelance,
 On avait échangé en juillet 2022 pour le cahier Action climatique. L'asclépiade est une vivace indigène qui se cultive avec peu d'intrants et qui stocke du carbone dans un système racinaire pérenne.
@@ -1608,9 +1668,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="270" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1655,6 +1715,11 @@
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Elboujdaini,
 On s'était parlé du programme de semences en mai 2022. La Campagne nationale de plantation en est à sa 5e édition, et on a distribué environ 10 millions de graines d'asclépiade en Amérique du Nord.
@@ -1665,9 +1730,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K16" s="10" t="inlineStr"/>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
+      <c r="L16" s="11" t="inlineStr"/>
+      <c r="M16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="270" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1712,6 +1777,11 @@
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Haurio,
 On avait creusé l'impact climatique de l'asclépiade ensemble en janvier 2022.
@@ -1723,9 +1793,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="10" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
+      <c r="L17" s="11" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr"/>
     </row>
     <row r="18" ht="270" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1770,6 +1840,11 @@
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>Bonjour,
 En novembre 2021, votre équipe nous avait contactés pour une étude de marché sur les glacières. Nos sacs isothermes et nos glacières souples sont isolés à la soie d'asclépiade, une fibre creuse et naturellement hydrophobe.
@@ -1781,9 +1856,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr"/>
-      <c r="L18" s="10" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
+      <c r="L18" s="11" t="inlineStr"/>
+      <c r="M18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="270" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1828,6 +1903,11 @@
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>Bonjour M. Tison,
 On s'était parlé pour la section Affaires en septembre 2021, à l'époque où on venait de rapatrier notre production faute de sous-traitant prêt à toucher à la fibre. Le modèle a changé depuis : la vidéo est ici, https://www.youtube.com/watch?v=GKyHh-Ok9JU, et Sylvain Larocque en a parlé en mai.
@@ -1839,9 +1919,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="10" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="270" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1886,6 +1966,11 @@
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Simard,
 Vous aviez présenté nos moufles isolées à l'asclépiade le 17 septembre 2021. Drôle de coïncidence : la diffusion tombe cinq ans jour pour jour après votre article.
@@ -1897,9 +1982,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K20" s="10" t="inlineStr"/>
-      <c r="L20" s="10" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
+      <c r="L20" s="11" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="270" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1944,6 +2029,11 @@
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Friis,
 Vous aviez travaillé sur l'impact climatique de l'asclépiade en septembre 2021.
@@ -1955,9 +2045,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="10" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
+      <c r="L21" s="11" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
+      <c r="N21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="270" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2002,6 +2092,11 @@
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>Bonjour M. Perreault,
 On s'était parlé en juillet 2021.
@@ -2013,9 +2108,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K22" s="10" t="inlineStr"/>
-      <c r="L22" s="10" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
+      <c r="L22" s="11" t="inlineStr"/>
+      <c r="M22" s="11" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr"/>
     </row>
     <row r="23" ht="270" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -2060,6 +2155,11 @@
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>Bonjour M. Higgins,
 On s'était parlé pour Le Soleil en juillet 2021. L'atelier est toujours dans Limoilou.
@@ -2071,9 +2171,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="10" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
+      <c r="L23" s="11" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr"/>
+      <c r="N23" s="11" t="inlineStr"/>
     </row>
     <row r="24" ht="270" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -2118,6 +2218,11 @@
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Samson,
 En mars 2021, vous aviez signé « Les grandes promesses de l'asclépiade, la soie d'Amérique ». Cinq ans plus tard, je peux vous dire lesquelles ont été tenues : il y a des produits finis, l'isolant se transforme toujours au Québec, on achète encore de l'asclépiade québécoise, et un manteau se vend autour de 300 $.
@@ -2129,9 +2234,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K24" s="10" t="inlineStr"/>
-      <c r="L24" s="10" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr"/>
+      <c r="M24" s="11" t="inlineStr"/>
+      <c r="N24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="270" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2176,6 +2281,11 @@
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>Bonjour M. Ménard,
 On s'était parlé à La Terre en janvier 2021. Cinq ans plus tard, on achète encore de l'asclépiade québécoise et on la transforme nous-mêmes à Québec.
@@ -2187,9 +2297,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="10" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
+      <c r="L25" s="11" t="inlineStr"/>
+      <c r="M25" s="11" t="inlineStr"/>
+      <c r="N25" s="11" t="inlineStr"/>
     </row>
     <row r="26" ht="270" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -2235,12 +2345,17 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
           <t>NE PAS ENVOYER — même journaliste que la ligne Radio-Canada, à une ancienne adresse. Écrire à anne-sophie.roy@radio-canada.ca. Garder cette adresse en réserve si l'autre rebondit.</t>
         </is>
       </c>
-      <c r="K26" s="10" t="inlineStr"/>
-      <c r="L26" s="10" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
+      <c r="L26" s="11" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr"/>
+      <c r="N26" s="11" t="inlineStr"/>
     </row>
     <row r="27" ht="270" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -2285,6 +2400,11 @@
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Drouin,
 En janvier 2021, vous aviez écrit « Devenir viral avant même de se lancer en affaires ». Six ans plus tard, l'entreprise existe pour vrai, avec plus de 40 produits.
@@ -2296,9 +2416,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="10" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
+      <c r="L27" s="11" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr"/>
+      <c r="N27" s="11" t="inlineStr"/>
     </row>
     <row r="28" ht="270" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2336,6 +2456,11 @@
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
           <t>Bonjour M. Roy,
 En octobre 2020, vous avez écrit « La deuxième vie de l'asclépiade ». Vous avez été le tout premier journaliste à parler de nous. Et l'agriculteur du Lac-Saint-Jean qui vous avait donné envie du sujet est encore notre fournisseur aujourd'hui : six ans plus tard, l'asclépiade de chez vous se retrouve toujours dans nos produits.
 Depuis, tout mon temps va à mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
@@ -2346,9 +2471,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K28" s="10" t="inlineStr"/>
-      <c r="L28" s="10" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
+      <c r="L28" s="11" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr"/>
+      <c r="N28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="270" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -2386,6 +2511,11 @@
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Mme Roberge,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
@@ -2396,9 +2526,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="10" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
+      <c r="L29" s="11" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr"/>
+      <c r="N29" s="11" t="inlineStr"/>
     </row>
     <row r="30" ht="270" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -2436,6 +2566,11 @@
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Mme Laforest,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
@@ -2446,9 +2581,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K30" s="10" t="inlineStr"/>
-      <c r="L30" s="10" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
+      <c r="L30" s="11" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr"/>
+      <c r="N30" s="11" t="inlineStr"/>
     </row>
     <row r="31" ht="270" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -2493,6 +2628,11 @@
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>Bonjour M. McKenna,
 En décembre 2021, vous aviez écrit « Des écouteurs de Québec pour oublier les AirPods », sur Sounds Good. J'étais un des trois. J'ai vendu mes parts en 2022 pour me consacrer entièrement à Lasclay, l'autre entreprise que j'avais démarrée entretemps, qui transforme la soie d'asclépiade en isolant textile.
@@ -2504,9 +2644,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="10" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
+      <c r="L31" s="11" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr"/>
+      <c r="N31" s="11" t="inlineStr"/>
     </row>
     <row r="32" ht="270" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -2544,6 +2684,11 @@
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Mme Lemieux,
 En décembre 2021, vous aviez écrit « Les deux mains dans l'écoresponsabilité » pour le Journal de Montréal. Notre modèle manufacturier a changé depuis, et j'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Parmi les raisons de ce changement, il y avait clairement que j'avais besoin de temps pour me recentrer sur mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
@@ -2554,9 +2699,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K32" s="10" t="inlineStr"/>
-      <c r="L32" s="10" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
+      <c r="L32" s="11" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr"/>
+      <c r="N32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="270" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -2594,6 +2739,11 @@
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Mme Grenier-Héroux,
 En janvier 2021, vous aviez écrit « La soie d'Amérique, le pari de deux ambitieux » dans Le Devoir. Le pari a six ans, et il tient : plus de 40 produits, environ 10 millions de graines distribuées, et un isolant toujours transformé à Limoilou.
 Depuis, tout mon temps va à mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
@@ -2604,9 +2754,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="10" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
+      <c r="L33" s="11" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr"/>
+      <c r="N33" s="11" t="inlineStr"/>
     </row>
     <row r="34" ht="270" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -2644,6 +2794,11 @@
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Mme Goubau,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. Vous couvrez le textile et la mode, alors voici une matière que peu de gens ont vue de près : la soie d'asclépiade, une fibre creuse et naturellement hydrophobe attachée aux graines d'une plante que les agriculteurs arrachent de leurs champs depuis 50 ans. On la transforme en isolant, et on en fait des manteaux, des mitaines et des tuques.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
@@ -2654,9 +2809,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K34" s="10" t="inlineStr"/>
-      <c r="L34" s="10" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
+      <c r="L34" s="11" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr"/>
+      <c r="N34" s="11" t="inlineStr"/>
     </row>
     <row r="35" ht="270" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -2694,6 +2849,11 @@
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Mme Dostie,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
@@ -2704,9 +2864,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" s="10" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
+      <c r="L35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
+      <c r="N35" s="11" t="inlineStr"/>
     </row>
     <row r="36" ht="270" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -2747,6 +2907,11 @@
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Poisson,
 En novembre 2020, vous aviez présenté nos accessoires d'hiver isolés à l'asclépiade, quand il y en avait trois. Il y en a maintenant plus de 40, dont des manteaux et des vestes à inserts amovibles.
@@ -2758,9 +2923,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K36" s="10" t="inlineStr"/>
-      <c r="L36" s="10" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
+      <c r="L36" s="11" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr"/>
+      <c r="N36" s="11" t="inlineStr"/>
     </row>
     <row r="37" ht="270" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -2801,6 +2966,11 @@
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Bertrand,
 En septembre 2021, vous aviez écrit « L'asclépiade pour braver le froid » pour ICI Explora. Depuis, le statut du monarque comme espèce en voie de disparition a été confirmé au Canada, et les États-Unis ont proposé de l'inscrire comme menacée.
@@ -2812,9 +2982,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="10" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
+      <c r="L37" s="11" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr"/>
+      <c r="N37" s="11" t="inlineStr"/>
     </row>
     <row r="38" ht="270" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -2855,6 +3025,11 @@
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Benoist,
 En novembre 2023, vous aviez retenu notre foulard d'asclépiade dans vos cadeaux faits au Québec. Une précision utile pour la prochaine fois : notre modèle manufacturier a changé en 2025, et l'assemblage des produits finis se fait maintenant en Tunisie. L'asclépiade est cultivée au Québec et l'isolant transformé à Limoilou.
@@ -2866,9 +3041,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K38" s="10" t="inlineStr"/>
-      <c r="L38" s="10" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
+      <c r="L38" s="11" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr"/>
+      <c r="N38" s="11" t="inlineStr"/>
     </row>
     <row r="39" ht="270" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
@@ -2917,6 +3092,11 @@
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie Allard,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
@@ -2936,9 +3116,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="10" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
+      <c r="L39" s="11" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr"/>
+      <c r="N39" s="11" t="inlineStr"/>
     </row>
     <row r="40" ht="270" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
@@ -2988,6 +3168,11 @@
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Zoé Allemand,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3000,9 +3185,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K40" s="10" t="inlineStr"/>
-      <c r="L40" s="10" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
+      <c r="L40" s="11" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr"/>
+      <c r="N40" s="11" t="inlineStr"/>
     </row>
     <row r="41" ht="270" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
@@ -3052,6 +3237,11 @@
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Victoria Bakos,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3064,9 +3254,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
+      <c r="L41" s="11" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr"/>
+      <c r="N41" s="11" t="inlineStr"/>
     </row>
     <row r="42" ht="270" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
@@ -3116,6 +3306,11 @@
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-Émélie Bernier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3128,9 +3323,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr"/>
-      <c r="L42" s="10" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
+      <c r="L42" s="11" t="inlineStr"/>
+      <c r="M42" s="11" t="inlineStr"/>
+      <c r="N42" s="11" t="inlineStr"/>
     </row>
     <row r="43" ht="270" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
@@ -3180,6 +3375,11 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Normand Blouin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3192,9 +3392,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
+      <c r="L43" s="11" t="inlineStr"/>
+      <c r="M43" s="11" t="inlineStr"/>
+      <c r="N43" s="11" t="inlineStr"/>
     </row>
     <row r="44" ht="270" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -3244,6 +3444,11 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Louise Bourbonnais,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3256,9 +3461,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K44" s="10" t="inlineStr"/>
-      <c r="L44" s="10" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
+      <c r="L44" s="11" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr"/>
+      <c r="N44" s="11" t="inlineStr"/>
     </row>
     <row r="45" ht="270" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
@@ -3308,6 +3513,11 @@
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Francois Bourque,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3320,9 +3530,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="10" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
+      <c r="L45" s="11" t="inlineStr"/>
+      <c r="M45" s="11" t="inlineStr"/>
+      <c r="N45" s="11" t="inlineStr"/>
     </row>
     <row r="46" ht="270" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -3372,6 +3582,11 @@
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Ariane Boyer,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3384,9 +3599,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K46" s="10" t="inlineStr"/>
-      <c r="L46" s="10" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
+      <c r="L46" s="11" t="inlineStr"/>
+      <c r="M46" s="11" t="inlineStr"/>
+      <c r="N46" s="11" t="inlineStr"/>
     </row>
     <row r="47" ht="270" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
@@ -3436,6 +3651,11 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Gilbert Bégin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3448,9 +3668,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="10" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
+      <c r="L47" s="11" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr"/>
+      <c r="N47" s="11" t="inlineStr"/>
     </row>
     <row r="48" ht="270" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
@@ -3500,6 +3720,11 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Papa Moussa Camara,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3512,9 +3737,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K48" s="10" t="inlineStr"/>
-      <c r="L48" s="10" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
+      <c r="L48" s="11" t="inlineStr"/>
+      <c r="M48" s="11" t="inlineStr"/>
+      <c r="N48" s="11" t="inlineStr"/>
     </row>
     <row r="49" ht="270" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
@@ -3564,6 +3789,11 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Victor Carré,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3576,9 +3806,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="10" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
+      <c r="L49" s="11" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr"/>
+      <c r="N49" s="11" t="inlineStr"/>
     </row>
     <row r="50" ht="270" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
@@ -3628,6 +3858,11 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Eric Chabot,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3640,9 +3875,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K50" s="10" t="inlineStr"/>
-      <c r="L50" s="10" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
+      <c r="L50" s="11" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr"/>
+      <c r="N50" s="11" t="inlineStr"/>
     </row>
     <row r="51" ht="270" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
@@ -3692,6 +3927,11 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Tristan Champagne-Lessard,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3704,9 +3944,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="10" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
+      <c r="L51" s="11" t="inlineStr"/>
+      <c r="M51" s="11" t="inlineStr"/>
+      <c r="N51" s="11" t="inlineStr"/>
     </row>
     <row r="52" ht="270" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
@@ -3756,6 +3996,11 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jean-Marc Chevalier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3768,9 +4013,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K52" s="10" t="inlineStr"/>
-      <c r="L52" s="10" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
+      <c r="L52" s="11" t="inlineStr"/>
+      <c r="M52" s="11" t="inlineStr"/>
+      <c r="N52" s="11" t="inlineStr"/>
     </row>
     <row r="53" ht="270" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
@@ -3820,6 +4065,11 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Simon Chrétien,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3832,9 +4082,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
+      <c r="L53" s="11" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr"/>
+      <c r="N53" s="11" t="inlineStr"/>
     </row>
     <row r="54" ht="270" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
@@ -3884,6 +4134,11 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Maxime Corneau,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3896,9 +4151,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K54" s="10" t="inlineStr"/>
-      <c r="L54" s="10" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
+      <c r="L54" s="11" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr"/>
+      <c r="N54" s="11" t="inlineStr"/>
     </row>
     <row r="55" ht="270" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
@@ -3948,6 +4203,11 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Aurélia Crémoux,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -3960,9 +4220,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="10" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr"/>
+      <c r="N55" s="11" t="inlineStr"/>
     </row>
     <row r="56" ht="270" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -4012,6 +4272,11 @@
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Catherine Dallaire,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4024,9 +4289,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K56" s="10" t="inlineStr"/>
-      <c r="L56" s="10" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
+      <c r="L56" s="11" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr"/>
+      <c r="N56" s="11" t="inlineStr"/>
     </row>
     <row r="57" ht="270" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
@@ -4075,6 +4340,11 @@
         </is>
       </c>
       <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gabriel Delisle,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
@@ -4093,9 +4363,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="10" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
+      <c r="L57" s="11" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr"/>
+      <c r="N57" s="11" t="inlineStr"/>
     </row>
     <row r="58" ht="270" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -4145,6 +4415,11 @@
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Anaïs Desjardins,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4157,9 +4432,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K58" s="10" t="inlineStr"/>
-      <c r="L58" s="10" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
+      <c r="L58" s="11" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr"/>
+      <c r="N58" s="11" t="inlineStr"/>
     </row>
     <row r="59" ht="270" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
@@ -4209,6 +4484,11 @@
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Simon Dominé,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4221,9 +4501,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="10" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
+      <c r="L59" s="11" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr"/>
+      <c r="N59" s="11" t="inlineStr"/>
     </row>
     <row r="60" ht="270" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -4273,6 +4553,11 @@
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Karl-Ivann Dubé,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4285,9 +4570,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K60" s="10" t="inlineStr"/>
-      <c r="L60" s="10" t="inlineStr"/>
-      <c r="M60" s="10" t="inlineStr"/>
+      <c r="L60" s="11" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr"/>
+      <c r="N60" s="11" t="inlineStr"/>
     </row>
     <row r="61" ht="270" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
@@ -4337,6 +4622,11 @@
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="inlineStr">
+        <is>
           <t>Bonjour André Fauteux,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4349,9 +4639,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="10" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
+      <c r="L61" s="11" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr"/>
+      <c r="N61" s="11" t="inlineStr"/>
     </row>
     <row r="62" ht="270" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
@@ -4401,6 +4691,11 @@
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Myriam Fimbry,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4413,9 +4708,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K62" s="10" t="inlineStr"/>
-      <c r="L62" s="10" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr"/>
+      <c r="L62" s="11" t="inlineStr"/>
+      <c r="M62" s="11" t="inlineStr"/>
+      <c r="N62" s="11" t="inlineStr"/>
     </row>
     <row r="63" ht="270" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
@@ -4465,6 +4760,11 @@
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Étienne Fortin-Gauthier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4477,9 +4777,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="10" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr"/>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr"/>
+      <c r="N63" s="11" t="inlineStr"/>
     </row>
     <row r="64" ht="270" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
@@ -4529,6 +4829,11 @@
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Johanne Fournier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4541,9 +4846,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K64" s="10" t="inlineStr"/>
-      <c r="L64" s="10" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
+      <c r="L64" s="11" t="inlineStr"/>
+      <c r="M64" s="11" t="inlineStr"/>
+      <c r="N64" s="11" t="inlineStr"/>
     </row>
     <row r="65" ht="270" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
@@ -4593,6 +4898,11 @@
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jean Garon,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4605,9 +4915,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="10" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr"/>
+      <c r="L65" s="11" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr"/>
+      <c r="N65" s="11" t="inlineStr"/>
     </row>
     <row r="66" ht="270" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
@@ -4657,6 +4967,11 @@
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Cécile Gladel,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4669,9 +4984,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K66" s="10" t="inlineStr"/>
-      <c r="L66" s="10" t="inlineStr"/>
-      <c r="M66" s="10" t="inlineStr"/>
+      <c r="L66" s="11" t="inlineStr"/>
+      <c r="M66" s="11" t="inlineStr"/>
+      <c r="N66" s="11" t="inlineStr"/>
     </row>
     <row r="67" ht="270" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -4721,6 +5036,11 @@
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marieke Glorieux-Stryckman,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4733,9 +5053,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="10" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr"/>
+      <c r="L67" s="11" t="inlineStr"/>
+      <c r="M67" s="11" t="inlineStr"/>
+      <c r="N67" s="11" t="inlineStr"/>
     </row>
     <row r="68" ht="270" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
@@ -4785,6 +5105,11 @@
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Maude Goyer,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4797,9 +5122,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K68" s="10" t="inlineStr"/>
-      <c r="L68" s="10" t="inlineStr"/>
-      <c r="M68" s="10" t="inlineStr"/>
+      <c r="L68" s="11" t="inlineStr"/>
+      <c r="M68" s="11" t="inlineStr"/>
+      <c r="N68" s="11" t="inlineStr"/>
     </row>
     <row r="69" ht="270" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
@@ -4849,6 +5174,11 @@
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Pauline Gravel,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4861,9 +5191,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr"/>
+      <c r="L69" s="11" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr"/>
+      <c r="N69" s="11" t="inlineStr"/>
     </row>
     <row r="70" ht="270" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
@@ -4913,6 +5243,11 @@
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Bernard Hervieux,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4925,9 +5260,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K70" s="10" t="inlineStr"/>
-      <c r="L70" s="10" t="inlineStr"/>
-      <c r="M70" s="10" t="inlineStr"/>
+      <c r="L70" s="11" t="inlineStr"/>
+      <c r="M70" s="11" t="inlineStr"/>
+      <c r="N70" s="11" t="inlineStr"/>
     </row>
     <row r="71" ht="270" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -4977,6 +5312,11 @@
       </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Leïla Jolin-Dahel,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -4989,9 +5329,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="10" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr"/>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr"/>
+      <c r="N71" s="11" t="inlineStr"/>
     </row>
     <row r="72" ht="270" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
@@ -5041,6 +5381,11 @@
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Kodjo Edjinam Nulagnon LOGO,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5053,9 +5398,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K72" s="10" t="inlineStr"/>
-      <c r="L72" s="10" t="inlineStr"/>
-      <c r="M72" s="10" t="inlineStr"/>
+      <c r="L72" s="11" t="inlineStr"/>
+      <c r="M72" s="11" t="inlineStr"/>
+      <c r="N72" s="11" t="inlineStr"/>
     </row>
     <row r="73" ht="270" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
@@ -5105,6 +5450,11 @@
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Annie Labrecque,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5117,9 +5467,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="10" t="inlineStr"/>
-      <c r="M73" s="10" t="inlineStr"/>
+      <c r="L73" s="11" t="inlineStr"/>
+      <c r="M73" s="11" t="inlineStr"/>
+      <c r="N73" s="11" t="inlineStr"/>
     </row>
     <row r="74" ht="270" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -5169,6 +5519,11 @@
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marianne Lachapelle,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5181,9 +5536,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K74" s="10" t="inlineStr"/>
-      <c r="L74" s="10" t="inlineStr"/>
-      <c r="M74" s="10" t="inlineStr"/>
+      <c r="L74" s="11" t="inlineStr"/>
+      <c r="M74" s="11" t="inlineStr"/>
+      <c r="N74" s="11" t="inlineStr"/>
     </row>
     <row r="75" ht="270" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
@@ -5233,6 +5588,11 @@
       </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Sophie Lachapelle,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5245,9 +5605,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="10" t="inlineStr"/>
-      <c r="M75" s="10" t="inlineStr"/>
+      <c r="L75" s="11" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr"/>
+      <c r="N75" s="11" t="inlineStr"/>
     </row>
     <row r="76" ht="270" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
@@ -5297,6 +5657,11 @@
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Alain Laforest,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5309,9 +5674,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K76" s="10" t="inlineStr"/>
-      <c r="L76" s="10" t="inlineStr"/>
-      <c r="M76" s="10" t="inlineStr"/>
+      <c r="L76" s="11" t="inlineStr"/>
+      <c r="M76" s="11" t="inlineStr"/>
+      <c r="N76" s="11" t="inlineStr"/>
     </row>
     <row r="77" ht="270" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
@@ -5361,6 +5726,11 @@
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Mikaël Lalancette,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5373,9 +5743,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="10" t="inlineStr"/>
-      <c r="M77" s="10" t="inlineStr"/>
+      <c r="L77" s="11" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr"/>
+      <c r="N77" s="11" t="inlineStr"/>
     </row>
     <row r="78" ht="270" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
@@ -5425,6 +5795,11 @@
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jean-Luc Lavallée,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5437,9 +5812,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K78" s="10" t="inlineStr"/>
-      <c r="L78" s="10" t="inlineStr"/>
-      <c r="M78" s="10" t="inlineStr"/>
+      <c r="L78" s="11" t="inlineStr"/>
+      <c r="M78" s="11" t="inlineStr"/>
+      <c r="N78" s="11" t="inlineStr"/>
     </row>
     <row r="79" ht="270" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
@@ -5489,6 +5864,11 @@
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jean-Francois Leblanc,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5501,9 +5881,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="10" t="inlineStr"/>
-      <c r="M79" s="10" t="inlineStr"/>
+      <c r="L79" s="11" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr"/>
+      <c r="N79" s="11" t="inlineStr"/>
     </row>
     <row r="80" ht="270" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
@@ -5553,6 +5933,11 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Julie Leduc,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5565,9 +5950,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K80" s="10" t="inlineStr"/>
-      <c r="L80" s="10" t="inlineStr"/>
-      <c r="M80" s="10" t="inlineStr"/>
+      <c r="L80" s="11" t="inlineStr"/>
+      <c r="M80" s="11" t="inlineStr"/>
+      <c r="N80" s="11" t="inlineStr"/>
     </row>
     <row r="81" ht="270" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -5617,6 +6002,11 @@
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Annie Martin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5629,9 +6019,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K81" s="10" t="inlineStr"/>
-      <c r="L81" s="10" t="inlineStr"/>
-      <c r="M81" s="10" t="inlineStr"/>
+      <c r="L81" s="11" t="inlineStr"/>
+      <c r="M81" s="11" t="inlineStr"/>
+      <c r="N81" s="11" t="inlineStr"/>
     </row>
     <row r="82" ht="270" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
@@ -5680,6 +6070,11 @@
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
         <is>
           <t>Bonjour Réjean Martin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
@@ -5699,9 +6094,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K82" s="10" t="inlineStr"/>
-      <c r="L82" s="10" t="inlineStr"/>
-      <c r="M82" s="10" t="inlineStr"/>
+      <c r="L82" s="11" t="inlineStr"/>
+      <c r="M82" s="11" t="inlineStr"/>
+      <c r="N82" s="11" t="inlineStr"/>
     </row>
     <row r="83" ht="270" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -5751,6 +6146,11 @@
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Charles Mathieu,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5763,9 +6163,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K83" s="10" t="inlineStr"/>
-      <c r="L83" s="10" t="inlineStr"/>
-      <c r="M83" s="10" t="inlineStr"/>
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr"/>
+      <c r="N83" s="11" t="inlineStr"/>
     </row>
     <row r="84" ht="270" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
@@ -5815,6 +6215,11 @@
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K84" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Clara Matthey-Jonais,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5827,9 +6232,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K84" s="10" t="inlineStr"/>
-      <c r="L84" s="10" t="inlineStr"/>
-      <c r="M84" s="10" t="inlineStr"/>
+      <c r="L84" s="11" t="inlineStr"/>
+      <c r="M84" s="11" t="inlineStr"/>
+      <c r="N84" s="11" t="inlineStr"/>
     </row>
     <row r="85" ht="270" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
@@ -5879,6 +6284,11 @@
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K85" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Valérian Mazataud,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5891,9 +6301,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K85" s="10" t="inlineStr"/>
-      <c r="L85" s="10" t="inlineStr"/>
-      <c r="M85" s="10" t="inlineStr"/>
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr"/>
+      <c r="N85" s="11" t="inlineStr"/>
     </row>
     <row r="86" ht="270" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -5943,6 +6353,11 @@
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Lili Mercure,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -5955,9 +6370,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K86" s="10" t="inlineStr"/>
-      <c r="L86" s="10" t="inlineStr"/>
-      <c r="M86" s="10" t="inlineStr"/>
+      <c r="L86" s="11" t="inlineStr"/>
+      <c r="M86" s="11" t="inlineStr"/>
+      <c r="N86" s="11" t="inlineStr"/>
     </row>
     <row r="87" ht="270" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
@@ -6007,6 +6422,11 @@
       </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K87" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Nicolas Mesly,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6019,9 +6439,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K87" s="10" t="inlineStr"/>
-      <c r="L87" s="10" t="inlineStr"/>
-      <c r="M87" s="10" t="inlineStr"/>
+      <c r="L87" s="11" t="inlineStr"/>
+      <c r="M87" s="11" t="inlineStr"/>
+      <c r="N87" s="11" t="inlineStr"/>
     </row>
     <row r="88" ht="270" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
@@ -6071,6 +6491,11 @@
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Nicolas Michaud,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6083,9 +6508,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K88" s="10" t="inlineStr"/>
-      <c r="L88" s="10" t="inlineStr"/>
-      <c r="M88" s="10" t="inlineStr"/>
+      <c r="L88" s="11" t="inlineStr"/>
+      <c r="M88" s="11" t="inlineStr"/>
+      <c r="N88" s="11" t="inlineStr"/>
     </row>
     <row r="89" ht="270" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
@@ -6135,6 +6560,11 @@
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Véronique Morin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6147,9 +6577,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K89" s="10" t="inlineStr"/>
-      <c r="L89" s="10" t="inlineStr"/>
-      <c r="M89" s="10" t="inlineStr"/>
+      <c r="L89" s="11" t="inlineStr"/>
+      <c r="M89" s="11" t="inlineStr"/>
+      <c r="N89" s="11" t="inlineStr"/>
     </row>
     <row r="90" ht="270" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
@@ -6199,6 +6629,11 @@
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K90" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Lila Mouch,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6211,9 +6646,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K90" s="10" t="inlineStr"/>
-      <c r="L90" s="10" t="inlineStr"/>
-      <c r="M90" s="10" t="inlineStr"/>
+      <c r="L90" s="11" t="inlineStr"/>
+      <c r="M90" s="11" t="inlineStr"/>
+      <c r="N90" s="11" t="inlineStr"/>
     </row>
     <row r="91" ht="270" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
@@ -6263,6 +6698,11 @@
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Olivier Mougeot,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6275,9 +6715,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K91" s="10" t="inlineStr"/>
-      <c r="L91" s="10" t="inlineStr"/>
-      <c r="M91" s="10" t="inlineStr"/>
+      <c r="L91" s="11" t="inlineStr"/>
+      <c r="M91" s="11" t="inlineStr"/>
+      <c r="N91" s="11" t="inlineStr"/>
     </row>
     <row r="92" ht="270" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
@@ -6327,6 +6767,11 @@
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K92" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Emmanuelle Mozayan-Verschaeve,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6339,9 +6784,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K92" s="10" t="inlineStr"/>
-      <c r="L92" s="10" t="inlineStr"/>
-      <c r="M92" s="10" t="inlineStr"/>
+      <c r="L92" s="11" t="inlineStr"/>
+      <c r="M92" s="11" t="inlineStr"/>
+      <c r="N92" s="11" t="inlineStr"/>
     </row>
     <row r="93" ht="270" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
@@ -6391,6 +6836,11 @@
       </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K93" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jean-Benoît Nadeau,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6403,9 +6853,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K93" s="10" t="inlineStr"/>
-      <c r="L93" s="10" t="inlineStr"/>
-      <c r="M93" s="10" t="inlineStr"/>
+      <c r="L93" s="11" t="inlineStr"/>
+      <c r="M93" s="11" t="inlineStr"/>
+      <c r="N93" s="11" t="inlineStr"/>
     </row>
     <row r="94" ht="270" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
@@ -6455,6 +6905,11 @@
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K94" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Yves Ouellet,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6467,9 +6922,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K94" s="10" t="inlineStr"/>
-      <c r="L94" s="10" t="inlineStr"/>
-      <c r="M94" s="10" t="inlineStr"/>
+      <c r="L94" s="11" t="inlineStr"/>
+      <c r="M94" s="11" t="inlineStr"/>
+      <c r="N94" s="11" t="inlineStr"/>
     </row>
     <row r="95" ht="270" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
@@ -6519,6 +6974,11 @@
       </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K95" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Josée Panet-Raymond,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6531,9 +6991,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="10" t="inlineStr"/>
-      <c r="M95" s="10" t="inlineStr"/>
+      <c r="L95" s="11" t="inlineStr"/>
+      <c r="M95" s="11" t="inlineStr"/>
+      <c r="N95" s="11" t="inlineStr"/>
     </row>
     <row r="96" ht="270" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
@@ -6583,6 +7043,11 @@
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K96" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Yannick Patelli,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6595,9 +7060,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K96" s="10" t="inlineStr"/>
-      <c r="L96" s="10" t="inlineStr"/>
-      <c r="M96" s="10" t="inlineStr"/>
+      <c r="L96" s="11" t="inlineStr"/>
+      <c r="M96" s="11" t="inlineStr"/>
+      <c r="N96" s="11" t="inlineStr"/>
     </row>
     <row r="97" ht="270" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
@@ -6647,6 +7112,11 @@
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K97" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Félix Pedneault,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6659,9 +7129,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K97" s="10" t="inlineStr"/>
-      <c r="L97" s="10" t="inlineStr"/>
-      <c r="M97" s="10" t="inlineStr"/>
+      <c r="L97" s="11" t="inlineStr"/>
+      <c r="M97" s="11" t="inlineStr"/>
+      <c r="N97" s="11" t="inlineStr"/>
     </row>
     <row r="98" ht="270" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
@@ -6711,6 +7181,11 @@
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K98" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-Eve Poulin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6723,9 +7198,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K98" s="10" t="inlineStr"/>
-      <c r="L98" s="10" t="inlineStr"/>
-      <c r="M98" s="10" t="inlineStr"/>
+      <c r="L98" s="11" t="inlineStr"/>
+      <c r="M98" s="11" t="inlineStr"/>
+      <c r="N98" s="11" t="inlineStr"/>
     </row>
     <row r="99" ht="270" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -6775,6 +7250,11 @@
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K99" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-Hélène Proulx,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6787,9 +7267,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K99" s="10" t="inlineStr"/>
-      <c r="L99" s="10" t="inlineStr"/>
-      <c r="M99" s="10" t="inlineStr"/>
+      <c r="L99" s="11" t="inlineStr"/>
+      <c r="M99" s="11" t="inlineStr"/>
+      <c r="N99" s="11" t="inlineStr"/>
     </row>
     <row r="100" ht="270" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
@@ -6839,6 +7319,11 @@
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K100" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jean-Hugues Roy,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6851,9 +7336,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K100" s="10" t="inlineStr"/>
-      <c r="L100" s="10" t="inlineStr"/>
-      <c r="M100" s="10" t="inlineStr"/>
+      <c r="L100" s="11" t="inlineStr"/>
+      <c r="M100" s="11" t="inlineStr"/>
+      <c r="N100" s="11" t="inlineStr"/>
     </row>
     <row r="101" ht="270" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -6903,6 +7388,11 @@
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K101" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Martin Roy,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6915,9 +7405,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K101" s="10" t="inlineStr"/>
-      <c r="L101" s="10" t="inlineStr"/>
-      <c r="M101" s="10" t="inlineStr"/>
+      <c r="L101" s="11" t="inlineStr"/>
+      <c r="M101" s="11" t="inlineStr"/>
+      <c r="N101" s="11" t="inlineStr"/>
     </row>
     <row r="102" ht="270" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
@@ -6967,6 +7457,11 @@
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K102" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Sylvain Sarrazin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -6979,9 +7474,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K102" s="10" t="inlineStr"/>
-      <c r="L102" s="10" t="inlineStr"/>
-      <c r="M102" s="10" t="inlineStr"/>
+      <c r="L102" s="11" t="inlineStr"/>
+      <c r="M102" s="11" t="inlineStr"/>
+      <c r="N102" s="11" t="inlineStr"/>
     </row>
     <row r="103" ht="270" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
@@ -7031,6 +7526,11 @@
       </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K103" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Pierre Sormany,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7043,9 +7543,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K103" s="10" t="inlineStr"/>
-      <c r="L103" s="10" t="inlineStr"/>
-      <c r="M103" s="10" t="inlineStr"/>
+      <c r="L103" s="11" t="inlineStr"/>
+      <c r="M103" s="11" t="inlineStr"/>
+      <c r="N103" s="11" t="inlineStr"/>
     </row>
     <row r="104" ht="270" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
@@ -7095,6 +7595,11 @@
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Scott Stevenson,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7107,9 +7612,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K104" s="10" t="inlineStr"/>
-      <c r="L104" s="10" t="inlineStr"/>
-      <c r="M104" s="10" t="inlineStr"/>
+      <c r="L104" s="11" t="inlineStr"/>
+      <c r="M104" s="11" t="inlineStr"/>
+      <c r="N104" s="11" t="inlineStr"/>
     </row>
     <row r="105" ht="270" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
@@ -7159,6 +7664,11 @@
       </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K105" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Michèle Tanganika,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7171,9 +7681,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K105" s="10" t="inlineStr"/>
-      <c r="L105" s="10" t="inlineStr"/>
-      <c r="M105" s="10" t="inlineStr"/>
+      <c r="L105" s="11" t="inlineStr"/>
+      <c r="M105" s="11" t="inlineStr"/>
+      <c r="N105" s="11" t="inlineStr"/>
     </row>
     <row r="106" ht="270" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -7223,6 +7733,11 @@
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K106" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Stephane Tellier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7235,9 +7750,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K106" s="10" t="inlineStr"/>
-      <c r="L106" s="10" t="inlineStr"/>
-      <c r="M106" s="10" t="inlineStr"/>
+      <c r="L106" s="11" t="inlineStr"/>
+      <c r="M106" s="11" t="inlineStr"/>
+      <c r="N106" s="11" t="inlineStr"/>
     </row>
     <row r="107" ht="270" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
@@ -7287,6 +7802,11 @@
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K107" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Karine Tremblay,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7299,9 +7819,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K107" s="10" t="inlineStr"/>
-      <c r="L107" s="10" t="inlineStr"/>
-      <c r="M107" s="10" t="inlineStr"/>
+      <c r="L107" s="11" t="inlineStr"/>
+      <c r="M107" s="11" t="inlineStr"/>
+      <c r="N107" s="11" t="inlineStr"/>
     </row>
     <row r="108" ht="270" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -7351,6 +7871,11 @@
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K108" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jean-Francois Venne,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7363,9 +7888,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K108" s="10" t="inlineStr"/>
-      <c r="L108" s="10" t="inlineStr"/>
-      <c r="M108" s="10" t="inlineStr"/>
+      <c r="L108" s="11" t="inlineStr"/>
+      <c r="M108" s="11" t="inlineStr"/>
+      <c r="N108" s="11" t="inlineStr"/>
     </row>
     <row r="109" ht="270" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
@@ -7415,6 +7940,11 @@
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K109" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Shahram Yazdanpanah,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7427,9 +7957,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K109" s="10" t="inlineStr"/>
-      <c r="L109" s="10" t="inlineStr"/>
-      <c r="M109" s="10" t="inlineStr"/>
+      <c r="L109" s="11" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr"/>
+      <c r="N109" s="11" t="inlineStr"/>
     </row>
     <row r="110" ht="270" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -7479,6 +8009,11 @@
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K110" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Malika Alaoui,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7491,9 +8026,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K110" s="10" t="inlineStr"/>
-      <c r="L110" s="10" t="inlineStr"/>
-      <c r="M110" s="10" t="inlineStr"/>
+      <c r="L110" s="11" t="inlineStr"/>
+      <c r="M110" s="11" t="inlineStr"/>
+      <c r="N110" s="11" t="inlineStr"/>
     </row>
     <row r="111" ht="270" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
@@ -7543,6 +8078,11 @@
       </c>
       <c r="J111" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K111" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Yahia Arkat,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7555,9 +8095,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K111" s="10" t="inlineStr"/>
-      <c r="L111" s="10" t="inlineStr"/>
-      <c r="M111" s="10" t="inlineStr"/>
+      <c r="L111" s="11" t="inlineStr"/>
+      <c r="M111" s="11" t="inlineStr"/>
+      <c r="N111" s="11" t="inlineStr"/>
     </row>
     <row r="112" ht="270" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
@@ -7607,6 +8147,11 @@
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K112" s="10" t="inlineStr">
+        <is>
           <t>Bonjour MARC-OLIVIER BISSON,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7619,9 +8164,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K112" s="10" t="inlineStr"/>
-      <c r="L112" s="10" t="inlineStr"/>
-      <c r="M112" s="10" t="inlineStr"/>
+      <c r="L112" s="11" t="inlineStr"/>
+      <c r="M112" s="11" t="inlineStr"/>
+      <c r="N112" s="11" t="inlineStr"/>
     </row>
     <row r="113" ht="270" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
@@ -7671,6 +8216,11 @@
       </c>
       <c r="J113" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K113" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Maïté Belmir,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7683,9 +8233,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K113" s="10" t="inlineStr"/>
-      <c r="L113" s="10" t="inlineStr"/>
-      <c r="M113" s="10" t="inlineStr"/>
+      <c r="L113" s="11" t="inlineStr"/>
+      <c r="M113" s="11" t="inlineStr"/>
+      <c r="N113" s="11" t="inlineStr"/>
     </row>
     <row r="114" ht="270" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
@@ -7735,6 +8285,11 @@
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K114" s="10" t="inlineStr">
+        <is>
           <t>Bonjour André Bernard,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7747,9 +8302,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K114" s="10" t="inlineStr"/>
-      <c r="L114" s="10" t="inlineStr"/>
-      <c r="M114" s="10" t="inlineStr"/>
+      <c r="L114" s="11" t="inlineStr"/>
+      <c r="M114" s="11" t="inlineStr"/>
+      <c r="N114" s="11" t="inlineStr"/>
     </row>
     <row r="115" ht="270" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
@@ -7799,6 +8354,11 @@
       </c>
       <c r="J115" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K115" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Didier Bert,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7811,9 +8371,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K115" s="10" t="inlineStr"/>
-      <c r="L115" s="10" t="inlineStr"/>
-      <c r="M115" s="10" t="inlineStr"/>
+      <c r="L115" s="11" t="inlineStr"/>
+      <c r="M115" s="11" t="inlineStr"/>
+      <c r="N115" s="11" t="inlineStr"/>
     </row>
     <row r="116" ht="270" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
@@ -7863,6 +8423,11 @@
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K116" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Sophie-Andrée Blondin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7875,9 +8440,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K116" s="10" t="inlineStr"/>
-      <c r="L116" s="10" t="inlineStr"/>
-      <c r="M116" s="10" t="inlineStr"/>
+      <c r="L116" s="11" t="inlineStr"/>
+      <c r="M116" s="11" t="inlineStr"/>
+      <c r="N116" s="11" t="inlineStr"/>
     </row>
     <row r="117" ht="270" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
@@ -7927,6 +8492,11 @@
       </c>
       <c r="J117" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K117" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Pierre Brochu,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -7939,9 +8509,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K117" s="10" t="inlineStr"/>
-      <c r="L117" s="10" t="inlineStr"/>
-      <c r="M117" s="10" t="inlineStr"/>
+      <c r="L117" s="11" t="inlineStr"/>
+      <c r="M117" s="11" t="inlineStr"/>
+      <c r="N117" s="11" t="inlineStr"/>
     </row>
     <row r="118" ht="270" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
@@ -7991,6 +8561,11 @@
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Gilles Bérubé,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8003,9 +8578,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K118" s="10" t="inlineStr"/>
-      <c r="L118" s="10" t="inlineStr"/>
-      <c r="M118" s="10" t="inlineStr"/>
+      <c r="L118" s="11" t="inlineStr"/>
+      <c r="M118" s="11" t="inlineStr"/>
+      <c r="N118" s="11" t="inlineStr"/>
     </row>
     <row r="119" ht="270" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
@@ -8055,6 +8630,11 @@
       </c>
       <c r="J119" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K119" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Daphné Cameron,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8067,9 +8647,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K119" s="10" t="inlineStr"/>
-      <c r="L119" s="10" t="inlineStr"/>
-      <c r="M119" s="10" t="inlineStr"/>
+      <c r="L119" s="11" t="inlineStr"/>
+      <c r="M119" s="11" t="inlineStr"/>
+      <c r="N119" s="11" t="inlineStr"/>
     </row>
     <row r="120" ht="270" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
@@ -8119,6 +8699,11 @@
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K120" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Godefroy Macaire Chabi,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8131,9 +8716,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K120" s="10" t="inlineStr"/>
-      <c r="L120" s="10" t="inlineStr"/>
-      <c r="M120" s="10" t="inlineStr"/>
+      <c r="L120" s="11" t="inlineStr"/>
+      <c r="M120" s="11" t="inlineStr"/>
+      <c r="N120" s="11" t="inlineStr"/>
     </row>
     <row r="121" ht="270" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
@@ -8183,6 +8768,11 @@
       </c>
       <c r="J121" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Sara Champagne,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8195,9 +8785,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K121" s="10" t="inlineStr"/>
-      <c r="L121" s="10" t="inlineStr"/>
-      <c r="M121" s="10" t="inlineStr"/>
+      <c r="L121" s="11" t="inlineStr"/>
+      <c r="M121" s="11" t="inlineStr"/>
+      <c r="N121" s="11" t="inlineStr"/>
     </row>
     <row r="122" ht="270" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
@@ -8247,6 +8837,11 @@
       </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K122" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Sarah Champagne,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8259,9 +8854,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K122" s="10" t="inlineStr"/>
-      <c r="L122" s="10" t="inlineStr"/>
-      <c r="M122" s="10" t="inlineStr"/>
+      <c r="L122" s="11" t="inlineStr"/>
+      <c r="M122" s="11" t="inlineStr"/>
+      <c r="N122" s="11" t="inlineStr"/>
     </row>
     <row r="123" ht="270" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
@@ -8311,6 +8906,11 @@
       </c>
       <c r="J123" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Éric-Pierre Champagne,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8323,9 +8923,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K123" s="10" t="inlineStr"/>
-      <c r="L123" s="10" t="inlineStr"/>
-      <c r="M123" s="10" t="inlineStr"/>
+      <c r="L123" s="11" t="inlineStr"/>
+      <c r="M123" s="11" t="inlineStr"/>
+      <c r="N123" s="11" t="inlineStr"/>
     </row>
     <row r="124" ht="270" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
@@ -8375,6 +8975,11 @@
       </c>
       <c r="J124" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marine Corniou,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8387,9 +8992,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K124" s="10" t="inlineStr"/>
-      <c r="L124" s="10" t="inlineStr"/>
-      <c r="M124" s="10" t="inlineStr"/>
+      <c r="L124" s="11" t="inlineStr"/>
+      <c r="M124" s="11" t="inlineStr"/>
+      <c r="N124" s="11" t="inlineStr"/>
     </row>
     <row r="125" ht="270" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
@@ -8439,6 +9044,11 @@
       </c>
       <c r="J125" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K125" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Catherine Crépeau,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8451,9 +9061,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K125" s="10" t="inlineStr"/>
-      <c r="L125" s="10" t="inlineStr"/>
-      <c r="M125" s="10" t="inlineStr"/>
+      <c r="L125" s="11" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr"/>
+      <c r="N125" s="11" t="inlineStr"/>
     </row>
     <row r="126" ht="270" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
@@ -8503,6 +9113,11 @@
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K126" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Laurence Dami-Houle,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8515,9 +9130,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K126" s="10" t="inlineStr"/>
-      <c r="L126" s="10" t="inlineStr"/>
-      <c r="M126" s="10" t="inlineStr"/>
+      <c r="L126" s="11" t="inlineStr"/>
+      <c r="M126" s="11" t="inlineStr"/>
+      <c r="N126" s="11" t="inlineStr"/>
     </row>
     <row r="127" ht="270" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
@@ -8567,6 +9182,11 @@
       </c>
       <c r="J127" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Amélie Daoust-Boisvert,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8579,9 +9199,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K127" s="10" t="inlineStr"/>
-      <c r="L127" s="10" t="inlineStr"/>
-      <c r="M127" s="10" t="inlineStr"/>
+      <c r="L127" s="11" t="inlineStr"/>
+      <c r="M127" s="11" t="inlineStr"/>
+      <c r="N127" s="11" t="inlineStr"/>
     </row>
     <row r="128" ht="270" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
@@ -8631,6 +9251,11 @@
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K128" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Dominique Degré,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8643,9 +9268,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K128" s="10" t="inlineStr"/>
-      <c r="L128" s="10" t="inlineStr"/>
-      <c r="M128" s="10" t="inlineStr"/>
+      <c r="L128" s="11" t="inlineStr"/>
+      <c r="M128" s="11" t="inlineStr"/>
+      <c r="N128" s="11" t="inlineStr"/>
     </row>
     <row r="129" ht="270" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
@@ -8695,6 +9320,11 @@
       </c>
       <c r="J129" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K129" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Quentin Dufranne,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8707,9 +9337,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K129" s="10" t="inlineStr"/>
-      <c r="L129" s="10" t="inlineStr"/>
-      <c r="M129" s="10" t="inlineStr"/>
+      <c r="L129" s="11" t="inlineStr"/>
+      <c r="M129" s="11" t="inlineStr"/>
+      <c r="N129" s="11" t="inlineStr"/>
     </row>
     <row r="130" ht="270" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
@@ -8759,6 +9389,11 @@
       </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K130" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Ève Dumas,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8771,9 +9406,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K130" s="10" t="inlineStr"/>
-      <c r="L130" s="10" t="inlineStr"/>
-      <c r="M130" s="10" t="inlineStr"/>
+      <c r="L130" s="11" t="inlineStr"/>
+      <c r="M130" s="11" t="inlineStr"/>
+      <c r="N130" s="11" t="inlineStr"/>
     </row>
     <row r="131" ht="270" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
@@ -8823,6 +9458,11 @@
       </c>
       <c r="J131" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K131" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Michel Fortier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8835,9 +9475,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K131" s="10" t="inlineStr"/>
-      <c r="L131" s="10" t="inlineStr"/>
-      <c r="M131" s="10" t="inlineStr"/>
+      <c r="L131" s="11" t="inlineStr"/>
+      <c r="M131" s="11" t="inlineStr"/>
+      <c r="N131" s="11" t="inlineStr"/>
     </row>
     <row r="132" ht="270" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
@@ -8887,6 +9527,11 @@
       </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K132" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-Eve Fournier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8899,9 +9544,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K132" s="10" t="inlineStr"/>
-      <c r="L132" s="10" t="inlineStr"/>
-      <c r="M132" s="10" t="inlineStr"/>
+      <c r="L132" s="11" t="inlineStr"/>
+      <c r="M132" s="11" t="inlineStr"/>
+      <c r="N132" s="11" t="inlineStr"/>
     </row>
     <row r="133" ht="270" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
@@ -8951,6 +9596,11 @@
       </c>
       <c r="J133" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K133" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Raymond Fournier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -8963,9 +9613,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K133" s="10" t="inlineStr"/>
-      <c r="L133" s="10" t="inlineStr"/>
-      <c r="M133" s="10" t="inlineStr"/>
+      <c r="L133" s="11" t="inlineStr"/>
+      <c r="M133" s="11" t="inlineStr"/>
+      <c r="N133" s="11" t="inlineStr"/>
     </row>
     <row r="134" ht="270" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
@@ -9015,6 +9665,11 @@
       </c>
       <c r="J134" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K134" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-Pier Frappier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9027,9 +9682,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K134" s="10" t="inlineStr"/>
-      <c r="L134" s="10" t="inlineStr"/>
-      <c r="M134" s="10" t="inlineStr"/>
+      <c r="L134" s="11" t="inlineStr"/>
+      <c r="M134" s="11" t="inlineStr"/>
+      <c r="N134" s="11" t="inlineStr"/>
     </row>
     <row r="135" ht="270" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
@@ -9079,6 +9734,11 @@
       </c>
       <c r="J135" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K135" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-Julie Gagnon,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9091,9 +9751,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K135" s="10" t="inlineStr"/>
-      <c r="L135" s="10" t="inlineStr"/>
-      <c r="M135" s="10" t="inlineStr"/>
+      <c r="L135" s="11" t="inlineStr"/>
+      <c r="M135" s="11" t="inlineStr"/>
+      <c r="N135" s="11" t="inlineStr"/>
     </row>
     <row r="136" ht="270" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
@@ -9143,6 +9803,11 @@
       </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K136" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Chloé Germain-Thérien,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9155,9 +9820,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K136" s="10" t="inlineStr"/>
-      <c r="L136" s="10" t="inlineStr"/>
-      <c r="M136" s="10" t="inlineStr"/>
+      <c r="L136" s="11" t="inlineStr"/>
+      <c r="M136" s="11" t="inlineStr"/>
+      <c r="N136" s="11" t="inlineStr"/>
     </row>
     <row r="137" ht="270" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
@@ -9207,6 +9872,11 @@
       </c>
       <c r="J137" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K137" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Charlotte Glorieux,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9219,9 +9889,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K137" s="10" t="inlineStr"/>
-      <c r="L137" s="10" t="inlineStr"/>
-      <c r="M137" s="10" t="inlineStr"/>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr"/>
+      <c r="N137" s="11" t="inlineStr"/>
     </row>
     <row r="138" ht="270" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
@@ -9271,6 +9941,11 @@
       </c>
       <c r="J138" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K138" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Annie Hudon,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9283,9 +9958,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K138" s="10" t="inlineStr"/>
-      <c r="L138" s="10" t="inlineStr"/>
-      <c r="M138" s="10" t="inlineStr"/>
+      <c r="L138" s="11" t="inlineStr"/>
+      <c r="M138" s="11" t="inlineStr"/>
+      <c r="N138" s="11" t="inlineStr"/>
     </row>
     <row r="139" ht="270" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
@@ -9335,6 +10010,11 @@
       </c>
       <c r="J139" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K139" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Ahmed Kouaou,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9347,9 +10027,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K139" s="10" t="inlineStr"/>
-      <c r="L139" s="10" t="inlineStr"/>
-      <c r="M139" s="10" t="inlineStr"/>
+      <c r="L139" s="11" t="inlineStr"/>
+      <c r="M139" s="11" t="inlineStr"/>
+      <c r="N139" s="11" t="inlineStr"/>
     </row>
     <row r="140" ht="270" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
@@ -9399,6 +10079,11 @@
       </c>
       <c r="J140" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K140" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Tania Krywiak,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9411,9 +10096,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K140" s="10" t="inlineStr"/>
-      <c r="L140" s="10" t="inlineStr"/>
-      <c r="M140" s="10" t="inlineStr"/>
+      <c r="L140" s="11" t="inlineStr"/>
+      <c r="M140" s="11" t="inlineStr"/>
+      <c r="N140" s="11" t="inlineStr"/>
     </row>
     <row r="141" ht="270" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
@@ -9463,6 +10148,11 @@
       </c>
       <c r="J141" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K141" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jacinthe Lafrance,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9475,9 +10165,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K141" s="10" t="inlineStr"/>
-      <c r="L141" s="10" t="inlineStr"/>
-      <c r="M141" s="10" t="inlineStr"/>
+      <c r="L141" s="11" t="inlineStr"/>
+      <c r="M141" s="11" t="inlineStr"/>
+      <c r="N141" s="11" t="inlineStr"/>
     </row>
     <row r="142" ht="270" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
@@ -9527,6 +10217,11 @@
       </c>
       <c r="J142" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K142" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Bruno Lamolet,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9539,9 +10234,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K142" s="10" t="inlineStr"/>
-      <c r="L142" s="10" t="inlineStr"/>
-      <c r="M142" s="10" t="inlineStr"/>
+      <c r="L142" s="11" t="inlineStr"/>
+      <c r="M142" s="11" t="inlineStr"/>
+      <c r="N142" s="11" t="inlineStr"/>
     </row>
     <row r="143" ht="270" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
@@ -9591,6 +10286,11 @@
       </c>
       <c r="J143" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K143" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Yvan Lamontagne,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9603,9 +10303,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K143" s="10" t="inlineStr"/>
-      <c r="L143" s="10" t="inlineStr"/>
-      <c r="M143" s="10" t="inlineStr"/>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
+      <c r="N143" s="11" t="inlineStr"/>
     </row>
     <row r="144" ht="270" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
@@ -9655,6 +10355,11 @@
       </c>
       <c r="J144" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K144" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Yves Langlois,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9667,9 +10372,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K144" s="10" t="inlineStr"/>
-      <c r="L144" s="10" t="inlineStr"/>
-      <c r="M144" s="10" t="inlineStr"/>
+      <c r="L144" s="11" t="inlineStr"/>
+      <c r="M144" s="11" t="inlineStr"/>
+      <c r="N144" s="11" t="inlineStr"/>
     </row>
     <row r="145" ht="270" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
@@ -9719,6 +10424,11 @@
       </c>
       <c r="J145" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K145" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Anne Marie Lecomte,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9731,9 +10441,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K145" s="10" t="inlineStr"/>
-      <c r="L145" s="10" t="inlineStr"/>
-      <c r="M145" s="10" t="inlineStr"/>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
+      <c r="N145" s="11" t="inlineStr"/>
     </row>
     <row r="146" ht="270" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
@@ -9783,6 +10493,11 @@
       </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K146" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Stéphanie Mac Farlane,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9795,9 +10510,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K146" s="10" t="inlineStr"/>
-      <c r="L146" s="10" t="inlineStr"/>
-      <c r="M146" s="10" t="inlineStr"/>
+      <c r="L146" s="11" t="inlineStr"/>
+      <c r="M146" s="11" t="inlineStr"/>
+      <c r="N146" s="11" t="inlineStr"/>
     </row>
     <row r="147" ht="270" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
@@ -9847,6 +10562,11 @@
       </c>
       <c r="J147" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K147" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Philippe Marois,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9859,9 +10579,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K147" s="10" t="inlineStr"/>
-      <c r="L147" s="10" t="inlineStr"/>
-      <c r="M147" s="10" t="inlineStr"/>
+      <c r="L147" s="11" t="inlineStr"/>
+      <c r="M147" s="11" t="inlineStr"/>
+      <c r="N147" s="11" t="inlineStr"/>
     </row>
     <row r="148" ht="270" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
@@ -9911,6 +10631,11 @@
       </c>
       <c r="J148" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K148" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Gildas Meneu,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9923,9 +10648,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K148" s="10" t="inlineStr"/>
-      <c r="L148" s="10" t="inlineStr"/>
-      <c r="M148" s="10" t="inlineStr"/>
+      <c r="L148" s="11" t="inlineStr"/>
+      <c r="M148" s="11" t="inlineStr"/>
+      <c r="N148" s="11" t="inlineStr"/>
     </row>
     <row r="149" ht="270" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
@@ -9975,6 +10700,11 @@
       </c>
       <c r="J149" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K149" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Louis-Xavier Michaud,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -9987,9 +10717,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K149" s="10" t="inlineStr"/>
-      <c r="L149" s="10" t="inlineStr"/>
-      <c r="M149" s="10" t="inlineStr"/>
+      <c r="L149" s="11" t="inlineStr"/>
+      <c r="M149" s="11" t="inlineStr"/>
+      <c r="N149" s="11" t="inlineStr"/>
     </row>
     <row r="150" ht="270" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
@@ -10039,6 +10769,11 @@
       </c>
       <c r="J150" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K150" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Anne Montplaisir,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10051,9 +10786,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K150" s="10" t="inlineStr"/>
-      <c r="L150" s="10" t="inlineStr"/>
-      <c r="M150" s="10" t="inlineStr"/>
+      <c r="L150" s="11" t="inlineStr"/>
+      <c r="M150" s="11" t="inlineStr"/>
+      <c r="N150" s="11" t="inlineStr"/>
     </row>
     <row r="151" ht="270" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
@@ -10103,6 +10838,11 @@
       </c>
       <c r="J151" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K151" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Karianne Nepton-Philippe,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10115,9 +10855,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K151" s="10" t="inlineStr"/>
-      <c r="L151" s="10" t="inlineStr"/>
-      <c r="M151" s="10" t="inlineStr"/>
+      <c r="L151" s="11" t="inlineStr"/>
+      <c r="M151" s="11" t="inlineStr"/>
+      <c r="N151" s="11" t="inlineStr"/>
     </row>
     <row r="152" ht="270" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
@@ -10167,6 +10907,11 @@
       </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K152" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Geneviève Normand,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10179,9 +10924,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K152" s="10" t="inlineStr"/>
-      <c r="L152" s="10" t="inlineStr"/>
-      <c r="M152" s="10" t="inlineStr"/>
+      <c r="L152" s="11" t="inlineStr"/>
+      <c r="M152" s="11" t="inlineStr"/>
+      <c r="N152" s="11" t="inlineStr"/>
     </row>
     <row r="153" ht="270" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
@@ -10231,6 +10976,11 @@
       </c>
       <c r="J153" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K153" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Carole Payer,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10243,9 +10993,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K153" s="10" t="inlineStr"/>
-      <c r="L153" s="10" t="inlineStr"/>
-      <c r="M153" s="10" t="inlineStr"/>
+      <c r="L153" s="11" t="inlineStr"/>
+      <c r="M153" s="11" t="inlineStr"/>
+      <c r="N153" s="11" t="inlineStr"/>
     </row>
     <row r="154" ht="270" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
@@ -10295,6 +11045,11 @@
       </c>
       <c r="J154" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K154" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Boris Proulx,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10307,9 +11062,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K154" s="10" t="inlineStr"/>
-      <c r="L154" s="10" t="inlineStr"/>
-      <c r="M154" s="10" t="inlineStr"/>
+      <c r="L154" s="11" t="inlineStr"/>
+      <c r="M154" s="11" t="inlineStr"/>
+      <c r="N154" s="11" t="inlineStr"/>
     </row>
     <row r="155" ht="270" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
@@ -10359,6 +11114,11 @@
       </c>
       <c r="J155" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K155" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Philippe Robitaille-Grou,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10371,9 +11131,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K155" s="10" t="inlineStr"/>
-      <c r="L155" s="10" t="inlineStr"/>
-      <c r="M155" s="10" t="inlineStr"/>
+      <c r="L155" s="11" t="inlineStr"/>
+      <c r="M155" s="11" t="inlineStr"/>
+      <c r="N155" s="11" t="inlineStr"/>
     </row>
     <row r="156" ht="270" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
@@ -10423,6 +11183,11 @@
       </c>
       <c r="J156" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K156" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Gwen Roley,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10435,9 +11200,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K156" s="10" t="inlineStr"/>
-      <c r="L156" s="10" t="inlineStr"/>
-      <c r="M156" s="10" t="inlineStr"/>
+      <c r="L156" s="11" t="inlineStr"/>
+      <c r="M156" s="11" t="inlineStr"/>
+      <c r="N156" s="11" t="inlineStr"/>
     </row>
     <row r="157" ht="270" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
@@ -10487,6 +11252,11 @@
       </c>
       <c r="J157" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K157" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Mathieu-Robert Sauvé,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10499,9 +11269,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K157" s="10" t="inlineStr"/>
-      <c r="L157" s="10" t="inlineStr"/>
-      <c r="M157" s="10" t="inlineStr"/>
+      <c r="L157" s="11" t="inlineStr"/>
+      <c r="M157" s="11" t="inlineStr"/>
+      <c r="N157" s="11" t="inlineStr"/>
     </row>
     <row r="158" ht="270" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
@@ -10551,6 +11321,11 @@
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K158" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Pierre St-Arnaud,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10563,9 +11338,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K158" s="10" t="inlineStr"/>
-      <c r="L158" s="10" t="inlineStr"/>
-      <c r="M158" s="10" t="inlineStr"/>
+      <c r="L158" s="11" t="inlineStr"/>
+      <c r="M158" s="11" t="inlineStr"/>
+      <c r="N158" s="11" t="inlineStr"/>
     </row>
     <row r="159" ht="270" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
@@ -10615,6 +11390,11 @@
       </c>
       <c r="J159" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K159" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Katherine Tremblay,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10627,9 +11407,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K159" s="10" t="inlineStr"/>
-      <c r="L159" s="10" t="inlineStr"/>
-      <c r="M159" s="10" t="inlineStr"/>
+      <c r="L159" s="11" t="inlineStr"/>
+      <c r="M159" s="11" t="inlineStr"/>
+      <c r="N159" s="11" t="inlineStr"/>
     </row>
     <row r="160" ht="270" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
@@ -10679,6 +11459,11 @@
       </c>
       <c r="J160" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K160" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Michel Tremblay,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10691,9 +11476,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K160" s="10" t="inlineStr"/>
-      <c r="L160" s="10" t="inlineStr"/>
-      <c r="M160" s="10" t="inlineStr"/>
+      <c r="L160" s="11" t="inlineStr"/>
+      <c r="M160" s="11" t="inlineStr"/>
+      <c r="N160" s="11" t="inlineStr"/>
     </row>
     <row r="161" ht="270" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
@@ -10743,6 +11528,11 @@
       </c>
       <c r="J161" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K161" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Martin Vallières,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10755,9 +11545,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K161" s="10" t="inlineStr"/>
-      <c r="L161" s="10" t="inlineStr"/>
-      <c r="M161" s="10" t="inlineStr"/>
+      <c r="L161" s="11" t="inlineStr"/>
+      <c r="M161" s="11" t="inlineStr"/>
+      <c r="N161" s="11" t="inlineStr"/>
     </row>
     <row r="162" ht="270" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
@@ -10807,6 +11597,11 @@
       </c>
       <c r="J162" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K162" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Yanick Villedieu,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10819,9 +11614,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K162" s="10" t="inlineStr"/>
-      <c r="L162" s="10" t="inlineStr"/>
-      <c r="M162" s="10" t="inlineStr"/>
+      <c r="L162" s="11" t="inlineStr"/>
+      <c r="M162" s="11" t="inlineStr"/>
+      <c r="N162" s="11" t="inlineStr"/>
     </row>
     <row r="163" ht="270" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
@@ -10871,6 +11666,11 @@
       </c>
       <c r="J163" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K163" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jonathan Allard,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10883,9 +11683,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K163" s="10" t="inlineStr"/>
-      <c r="L163" s="10" t="inlineStr"/>
-      <c r="M163" s="10" t="inlineStr"/>
+      <c r="L163" s="11" t="inlineStr"/>
+      <c r="M163" s="11" t="inlineStr"/>
+      <c r="N163" s="11" t="inlineStr"/>
     </row>
     <row r="164" ht="270" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
@@ -10935,6 +11735,11 @@
       </c>
       <c r="J164" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K164" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Anick Baribeau,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -10947,9 +11752,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K164" s="10" t="inlineStr"/>
-      <c r="L164" s="10" t="inlineStr"/>
-      <c r="M164" s="10" t="inlineStr"/>
+      <c r="L164" s="11" t="inlineStr"/>
+      <c r="M164" s="11" t="inlineStr"/>
+      <c r="N164" s="11" t="inlineStr"/>
     </row>
     <row r="165" ht="270" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
@@ -10999,6 +11804,11 @@
       </c>
       <c r="J165" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K165" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Félix-Antoine Beauchemin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11011,9 +11821,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K165" s="10" t="inlineStr"/>
-      <c r="L165" s="10" t="inlineStr"/>
-      <c r="M165" s="10" t="inlineStr"/>
+      <c r="L165" s="11" t="inlineStr"/>
+      <c r="M165" s="11" t="inlineStr"/>
+      <c r="N165" s="11" t="inlineStr"/>
     </row>
     <row r="166" ht="270" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
@@ -11063,6 +11873,11 @@
       </c>
       <c r="J166" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K166" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Karim Benessaieh,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11075,9 +11890,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K166" s="10" t="inlineStr"/>
-      <c r="L166" s="10" t="inlineStr"/>
-      <c r="M166" s="10" t="inlineStr"/>
+      <c r="L166" s="11" t="inlineStr"/>
+      <c r="M166" s="11" t="inlineStr"/>
+      <c r="N166" s="11" t="inlineStr"/>
     </row>
     <row r="167" ht="270" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
@@ -11127,6 +11942,11 @@
       </c>
       <c r="J167" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K167" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Julia Bernier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11139,9 +11959,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K167" s="10" t="inlineStr"/>
-      <c r="L167" s="10" t="inlineStr"/>
-      <c r="M167" s="10" t="inlineStr"/>
+      <c r="L167" s="11" t="inlineStr"/>
+      <c r="M167" s="11" t="inlineStr"/>
+      <c r="N167" s="11" t="inlineStr"/>
     </row>
     <row r="168" ht="270" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
@@ -11191,6 +12011,11 @@
       </c>
       <c r="J168" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K168" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Karine Boivin Forcier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11203,9 +12028,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K168" s="10" t="inlineStr"/>
-      <c r="L168" s="10" t="inlineStr"/>
-      <c r="M168" s="10" t="inlineStr"/>
+      <c r="L168" s="11" t="inlineStr"/>
+      <c r="M168" s="11" t="inlineStr"/>
+      <c r="N168" s="11" t="inlineStr"/>
     </row>
     <row r="169" ht="270" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
@@ -11255,6 +12080,11 @@
       </c>
       <c r="J169" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K169" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Audrey Bonaque,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11267,9 +12097,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K169" s="10" t="inlineStr"/>
-      <c r="L169" s="10" t="inlineStr"/>
-      <c r="M169" s="10" t="inlineStr"/>
+      <c r="L169" s="11" t="inlineStr"/>
+      <c r="M169" s="11" t="inlineStr"/>
+      <c r="N169" s="11" t="inlineStr"/>
     </row>
     <row r="170" ht="270" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
@@ -11319,6 +12149,11 @@
       </c>
       <c r="J170" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K170" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Luc Boulanger,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11331,9 +12166,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K170" s="10" t="inlineStr"/>
-      <c r="L170" s="10" t="inlineStr"/>
-      <c r="M170" s="10" t="inlineStr"/>
+      <c r="L170" s="11" t="inlineStr"/>
+      <c r="M170" s="11" t="inlineStr"/>
+      <c r="N170" s="11" t="inlineStr"/>
     </row>
     <row r="171" ht="270" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
@@ -11383,6 +12218,11 @@
       </c>
       <c r="J171" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K171" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Mario Boulianne,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11395,9 +12235,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K171" s="10" t="inlineStr"/>
-      <c r="L171" s="10" t="inlineStr"/>
-      <c r="M171" s="10" t="inlineStr"/>
+      <c r="L171" s="11" t="inlineStr"/>
+      <c r="M171" s="11" t="inlineStr"/>
+      <c r="N171" s="11" t="inlineStr"/>
     </row>
     <row r="172" ht="270" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
@@ -11447,6 +12287,11 @@
       </c>
       <c r="J172" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K172" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Bernard Brault,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11459,9 +12304,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K172" s="10" t="inlineStr"/>
-      <c r="L172" s="10" t="inlineStr"/>
-      <c r="M172" s="10" t="inlineStr"/>
+      <c r="L172" s="11" t="inlineStr"/>
+      <c r="M172" s="11" t="inlineStr"/>
+      <c r="N172" s="11" t="inlineStr"/>
     </row>
     <row r="173" ht="270" customHeight="1">
       <c r="A173" s="6" t="inlineStr">
@@ -11511,6 +12356,11 @@
       </c>
       <c r="J173" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K173" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Pierre Brisson,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11523,9 +12373,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K173" s="10" t="inlineStr"/>
-      <c r="L173" s="10" t="inlineStr"/>
-      <c r="M173" s="10" t="inlineStr"/>
+      <c r="L173" s="11" t="inlineStr"/>
+      <c r="M173" s="11" t="inlineStr"/>
+      <c r="N173" s="11" t="inlineStr"/>
     </row>
     <row r="174" ht="270" customHeight="1">
       <c r="A174" s="6" t="inlineStr">
@@ -11575,6 +12425,11 @@
       </c>
       <c r="J174" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K174" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Laurence Brisson Dubreuil,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11587,9 +12442,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K174" s="10" t="inlineStr"/>
-      <c r="L174" s="10" t="inlineStr"/>
-      <c r="M174" s="10" t="inlineStr"/>
+      <c r="L174" s="11" t="inlineStr"/>
+      <c r="M174" s="11" t="inlineStr"/>
+      <c r="N174" s="11" t="inlineStr"/>
     </row>
     <row r="175" ht="270" customHeight="1">
       <c r="A175" s="6" t="inlineStr">
@@ -11639,6 +12494,11 @@
       </c>
       <c r="J175" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K175" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Nathaniel Bronner,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11651,9 +12511,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K175" s="10" t="inlineStr"/>
-      <c r="L175" s="10" t="inlineStr"/>
-      <c r="M175" s="10" t="inlineStr"/>
+      <c r="L175" s="11" t="inlineStr"/>
+      <c r="M175" s="11" t="inlineStr"/>
+      <c r="N175" s="11" t="inlineStr"/>
     </row>
     <row r="176" ht="270" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
@@ -11703,6 +12563,11 @@
       </c>
       <c r="J176" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K176" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-France Bélanger,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11715,9 +12580,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K176" s="10" t="inlineStr"/>
-      <c r="L176" s="10" t="inlineStr"/>
-      <c r="M176" s="10" t="inlineStr"/>
+      <c r="L176" s="11" t="inlineStr"/>
+      <c r="M176" s="11" t="inlineStr"/>
+      <c r="N176" s="11" t="inlineStr"/>
     </row>
     <row r="177" ht="270" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
@@ -11767,6 +12632,11 @@
       </c>
       <c r="J177" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K177" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Diane Bérard,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11779,9 +12649,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K177" s="10" t="inlineStr"/>
-      <c r="L177" s="10" t="inlineStr"/>
-      <c r="M177" s="10" t="inlineStr"/>
+      <c r="L177" s="11" t="inlineStr"/>
+      <c r="M177" s="11" t="inlineStr"/>
+      <c r="N177" s="11" t="inlineStr"/>
     </row>
     <row r="178" ht="270" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
@@ -11831,6 +12701,11 @@
       </c>
       <c r="J178" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K178" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Julien Cayouette,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11843,9 +12718,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K178" s="10" t="inlineStr"/>
-      <c r="L178" s="10" t="inlineStr"/>
-      <c r="M178" s="10" t="inlineStr"/>
+      <c r="L178" s="11" t="inlineStr"/>
+      <c r="M178" s="11" t="inlineStr"/>
+      <c r="N178" s="11" t="inlineStr"/>
     </row>
     <row r="179" ht="270" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
@@ -11895,6 +12770,11 @@
       </c>
       <c r="J179" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K179" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Rudy Chabannes,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11907,9 +12787,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K179" s="10" t="inlineStr"/>
-      <c r="L179" s="10" t="inlineStr"/>
-      <c r="M179" s="10" t="inlineStr"/>
+      <c r="L179" s="11" t="inlineStr"/>
+      <c r="M179" s="11" t="inlineStr"/>
+      <c r="N179" s="11" t="inlineStr"/>
     </row>
     <row r="180" ht="270" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
@@ -11959,6 +12839,11 @@
       </c>
       <c r="J180" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K180" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Denis-Martin Chabot,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -11971,9 +12856,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K180" s="10" t="inlineStr"/>
-      <c r="L180" s="10" t="inlineStr"/>
-      <c r="M180" s="10" t="inlineStr"/>
+      <c r="L180" s="11" t="inlineStr"/>
+      <c r="M180" s="11" t="inlineStr"/>
+      <c r="N180" s="11" t="inlineStr"/>
     </row>
     <row r="181" ht="270" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
@@ -12023,6 +12908,11 @@
       </c>
       <c r="J181" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K181" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Loubna Majda Chourouk,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12035,9 +12925,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K181" s="10" t="inlineStr"/>
-      <c r="L181" s="10" t="inlineStr"/>
-      <c r="M181" s="10" t="inlineStr"/>
+      <c r="L181" s="11" t="inlineStr"/>
+      <c r="M181" s="11" t="inlineStr"/>
+      <c r="N181" s="11" t="inlineStr"/>
     </row>
     <row r="182" ht="270" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
@@ -12087,6 +12977,11 @@
       </c>
       <c r="J182" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K182" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Sarah Collardey,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12099,9 +12994,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K182" s="10" t="inlineStr"/>
-      <c r="L182" s="10" t="inlineStr"/>
-      <c r="M182" s="10" t="inlineStr"/>
+      <c r="L182" s="11" t="inlineStr"/>
+      <c r="M182" s="11" t="inlineStr"/>
+      <c r="N182" s="11" t="inlineStr"/>
     </row>
     <row r="183" ht="270" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
@@ -12151,6 +13046,11 @@
       </c>
       <c r="J183" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K183" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Kathleen Couillard,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12163,9 +13063,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K183" s="10" t="inlineStr"/>
-      <c r="L183" s="10" t="inlineStr"/>
-      <c r="M183" s="10" t="inlineStr"/>
+      <c r="L183" s="11" t="inlineStr"/>
+      <c r="M183" s="11" t="inlineStr"/>
+      <c r="N183" s="11" t="inlineStr"/>
     </row>
     <row r="184" ht="270" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
@@ -12215,6 +13115,11 @@
       </c>
       <c r="J184" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K184" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Oumou DIAKITÉ,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12227,9 +13132,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K184" s="10" t="inlineStr"/>
-      <c r="L184" s="10" t="inlineStr"/>
-      <c r="M184" s="10" t="inlineStr"/>
+      <c r="L184" s="11" t="inlineStr"/>
+      <c r="M184" s="11" t="inlineStr"/>
+      <c r="N184" s="11" t="inlineStr"/>
     </row>
     <row r="185" ht="270" customHeight="1">
       <c r="A185" s="6" t="inlineStr">
@@ -12279,6 +13184,11 @@
       </c>
       <c r="J185" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K185" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Agnès Delavault,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12291,9 +13201,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K185" s="10" t="inlineStr"/>
-      <c r="L185" s="10" t="inlineStr"/>
-      <c r="M185" s="10" t="inlineStr"/>
+      <c r="L185" s="11" t="inlineStr"/>
+      <c r="M185" s="11" t="inlineStr"/>
+      <c r="N185" s="11" t="inlineStr"/>
     </row>
     <row r="186" ht="270" customHeight="1">
       <c r="A186" s="6" t="inlineStr">
@@ -12343,6 +13253,11 @@
       </c>
       <c r="J186" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K186" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marcelin Delice,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12355,9 +13270,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K186" s="10" t="inlineStr"/>
-      <c r="L186" s="10" t="inlineStr"/>
-      <c r="M186" s="10" t="inlineStr"/>
+      <c r="L186" s="11" t="inlineStr"/>
+      <c r="M186" s="11" t="inlineStr"/>
+      <c r="N186" s="11" t="inlineStr"/>
     </row>
     <row r="187" ht="270" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
@@ -12407,6 +13322,11 @@
       </c>
       <c r="J187" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K187" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Alain Demers,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12419,9 +13339,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K187" s="10" t="inlineStr"/>
-      <c r="L187" s="10" t="inlineStr"/>
-      <c r="M187" s="10" t="inlineStr"/>
+      <c r="L187" s="11" t="inlineStr"/>
+      <c r="M187" s="11" t="inlineStr"/>
+      <c r="N187" s="11" t="inlineStr"/>
     </row>
     <row r="188" ht="270" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
@@ -12471,6 +13391,11 @@
       </c>
       <c r="J188" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K188" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Ivanoh Demers,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12483,9 +13408,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K188" s="10" t="inlineStr"/>
-      <c r="L188" s="10" t="inlineStr"/>
-      <c r="M188" s="10" t="inlineStr"/>
+      <c r="L188" s="11" t="inlineStr"/>
+      <c r="M188" s="11" t="inlineStr"/>
+      <c r="N188" s="11" t="inlineStr"/>
     </row>
     <row r="189" ht="270" customHeight="1">
       <c r="A189" s="6" t="inlineStr">
@@ -12535,6 +13460,11 @@
       </c>
       <c r="J189" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K189" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Claude Deschênes,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12547,9 +13477,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K189" s="10" t="inlineStr"/>
-      <c r="L189" s="10" t="inlineStr"/>
-      <c r="M189" s="10" t="inlineStr"/>
+      <c r="L189" s="11" t="inlineStr"/>
+      <c r="M189" s="11" t="inlineStr"/>
+      <c r="N189" s="11" t="inlineStr"/>
     </row>
     <row r="190" ht="270" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
@@ -12599,6 +13529,11 @@
       </c>
       <c r="J190" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K190" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Thomas Deshaies,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12611,9 +13546,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K190" s="10" t="inlineStr"/>
-      <c r="L190" s="10" t="inlineStr"/>
-      <c r="M190" s="10" t="inlineStr"/>
+      <c r="L190" s="11" t="inlineStr"/>
+      <c r="M190" s="11" t="inlineStr"/>
+      <c r="N190" s="11" t="inlineStr"/>
     </row>
     <row r="191" ht="270" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
@@ -12663,6 +13598,11 @@
       </c>
       <c r="J191" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K191" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Claude Desjardins,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12675,9 +13615,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K191" s="10" t="inlineStr"/>
-      <c r="L191" s="10" t="inlineStr"/>
-      <c r="M191" s="10" t="inlineStr"/>
+      <c r="L191" s="11" t="inlineStr"/>
+      <c r="M191" s="11" t="inlineStr"/>
+      <c r="N191" s="11" t="inlineStr"/>
     </row>
     <row r="192" ht="270" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
@@ -12727,6 +13667,11 @@
       </c>
       <c r="J192" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K192" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Martine Deslauriers,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12739,9 +13684,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K192" s="10" t="inlineStr"/>
-      <c r="L192" s="10" t="inlineStr"/>
-      <c r="M192" s="10" t="inlineStr"/>
+      <c r="L192" s="11" t="inlineStr"/>
+      <c r="M192" s="11" t="inlineStr"/>
+      <c r="N192" s="11" t="inlineStr"/>
     </row>
     <row r="193" ht="270" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
@@ -12791,6 +13736,11 @@
       </c>
       <c r="J193" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K193" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-Claude Di Lillo,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12803,9 +13753,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K193" s="10" t="inlineStr"/>
-      <c r="L193" s="10" t="inlineStr"/>
-      <c r="M193" s="10" t="inlineStr"/>
+      <c r="L193" s="11" t="inlineStr"/>
+      <c r="M193" s="11" t="inlineStr"/>
+      <c r="N193" s="11" t="inlineStr"/>
     </row>
     <row r="194" ht="270" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
@@ -12855,6 +13805,11 @@
       </c>
       <c r="J194" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K194" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jean-René Dufort,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12867,9 +13822,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K194" s="10" t="inlineStr"/>
-      <c r="L194" s="10" t="inlineStr"/>
-      <c r="M194" s="10" t="inlineStr"/>
+      <c r="L194" s="11" t="inlineStr"/>
+      <c r="M194" s="11" t="inlineStr"/>
+      <c r="N194" s="11" t="inlineStr"/>
     </row>
     <row r="195" ht="270" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
@@ -12919,6 +13874,11 @@
       </c>
       <c r="J195" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K195" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Richard Dupaul,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12931,9 +13891,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K195" s="10" t="inlineStr"/>
-      <c r="L195" s="10" t="inlineStr"/>
-      <c r="M195" s="10" t="inlineStr"/>
+      <c r="L195" s="11" t="inlineStr"/>
+      <c r="M195" s="11" t="inlineStr"/>
+      <c r="N195" s="11" t="inlineStr"/>
     </row>
     <row r="196" ht="270" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
@@ -12983,6 +13943,11 @@
       </c>
       <c r="J196" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K196" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Stéphanie Dupuis,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -12995,9 +13960,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K196" s="10" t="inlineStr"/>
-      <c r="L196" s="10" t="inlineStr"/>
-      <c r="M196" s="10" t="inlineStr"/>
+      <c r="L196" s="11" t="inlineStr"/>
+      <c r="M196" s="11" t="inlineStr"/>
+      <c r="N196" s="11" t="inlineStr"/>
     </row>
     <row r="197" ht="270" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
@@ -13047,6 +14012,11 @@
       </c>
       <c r="J197" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K197" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Maxim Fauteux,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13059,9 +14029,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K197" s="10" t="inlineStr"/>
-      <c r="L197" s="10" t="inlineStr"/>
-      <c r="M197" s="10" t="inlineStr"/>
+      <c r="L197" s="11" t="inlineStr"/>
+      <c r="M197" s="11" t="inlineStr"/>
+      <c r="N197" s="11" t="inlineStr"/>
     </row>
     <row r="198" ht="270" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
@@ -13111,6 +14081,11 @@
       </c>
       <c r="J198" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K198" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Ronald Georges,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13123,9 +14098,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K198" s="10" t="inlineStr"/>
-      <c r="L198" s="10" t="inlineStr"/>
-      <c r="M198" s="10" t="inlineStr"/>
+      <c r="L198" s="11" t="inlineStr"/>
+      <c r="M198" s="11" t="inlineStr"/>
+      <c r="N198" s="11" t="inlineStr"/>
     </row>
     <row r="199" ht="270" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
@@ -13175,6 +14150,11 @@
       </c>
       <c r="J199" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K199" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Stéphane Giroux,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13187,9 +14167,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K199" s="10" t="inlineStr"/>
-      <c r="L199" s="10" t="inlineStr"/>
-      <c r="M199" s="10" t="inlineStr"/>
+      <c r="L199" s="11" t="inlineStr"/>
+      <c r="M199" s="11" t="inlineStr"/>
+      <c r="N199" s="11" t="inlineStr"/>
     </row>
     <row r="200" ht="270" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
@@ -13239,6 +14219,11 @@
       </c>
       <c r="J200" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K200" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Zacharie Goudreault,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13251,9 +14236,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K200" s="10" t="inlineStr"/>
-      <c r="L200" s="10" t="inlineStr"/>
-      <c r="M200" s="10" t="inlineStr"/>
+      <c r="L200" s="11" t="inlineStr"/>
+      <c r="M200" s="11" t="inlineStr"/>
+      <c r="N200" s="11" t="inlineStr"/>
     </row>
     <row r="201" ht="270" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
@@ -13303,6 +14288,11 @@
       </c>
       <c r="J201" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K201" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Isabelle Grégoire,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13315,9 +14305,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K201" s="10" t="inlineStr"/>
-      <c r="L201" s="10" t="inlineStr"/>
-      <c r="M201" s="10" t="inlineStr"/>
+      <c r="L201" s="11" t="inlineStr"/>
+      <c r="M201" s="11" t="inlineStr"/>
+      <c r="N201" s="11" t="inlineStr"/>
     </row>
     <row r="202" ht="270" customHeight="1">
       <c r="A202" s="6" t="inlineStr">
@@ -13367,6 +14357,11 @@
       </c>
       <c r="J202" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K202" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Chantal Guy,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13379,9 +14374,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K202" s="10" t="inlineStr"/>
-      <c r="L202" s="10" t="inlineStr"/>
-      <c r="M202" s="10" t="inlineStr"/>
+      <c r="L202" s="11" t="inlineStr"/>
+      <c r="M202" s="11" t="inlineStr"/>
+      <c r="N202" s="11" t="inlineStr"/>
     </row>
     <row r="203" ht="270" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
@@ -13431,6 +14426,11 @@
       </c>
       <c r="J203" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K203" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Matthieu Hains,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13443,9 +14443,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K203" s="10" t="inlineStr"/>
-      <c r="L203" s="10" t="inlineStr"/>
-      <c r="M203" s="10" t="inlineStr"/>
+      <c r="L203" s="11" t="inlineStr"/>
+      <c r="M203" s="11" t="inlineStr"/>
+      <c r="N203" s="11" t="inlineStr"/>
     </row>
     <row r="204" ht="270" customHeight="1">
       <c r="A204" s="6" t="inlineStr">
@@ -13493,14 +14493,15 @@
           <t>vous</t>
         </is>
       </c>
-      <c r="J204" s="9" t="inlineStr">
+      <c r="J204" s="9" t="inlineStr"/>
+      <c r="K204" s="10" t="inlineStr">
         <is>
           <t>NE PAS ENVOYER — doublon de la liste chaude. Le message écrit à la main a préséance.</t>
         </is>
       </c>
-      <c r="K204" s="10" t="inlineStr"/>
-      <c r="L204" s="10" t="inlineStr"/>
-      <c r="M204" s="10" t="inlineStr"/>
+      <c r="L204" s="11" t="inlineStr"/>
+      <c r="M204" s="11" t="inlineStr"/>
+      <c r="N204" s="11" t="inlineStr"/>
     </row>
     <row r="205" ht="270" customHeight="1">
       <c r="A205" s="6" t="inlineStr">
@@ -13550,6 +14551,11 @@
       </c>
       <c r="J205" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K205" s="10" t="inlineStr">
+        <is>
           <t>Bonjour ANGELO JEAN-BAPTISTE,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13562,9 +14568,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K205" s="10" t="inlineStr"/>
-      <c r="L205" s="10" t="inlineStr"/>
-      <c r="M205" s="10" t="inlineStr"/>
+      <c r="L205" s="11" t="inlineStr"/>
+      <c r="M205" s="11" t="inlineStr"/>
+      <c r="N205" s="11" t="inlineStr"/>
     </row>
     <row r="206" ht="270" customHeight="1">
       <c r="A206" s="6" t="inlineStr">
@@ -13614,6 +14620,11 @@
       </c>
       <c r="J206" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K206" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Andréanne Joly,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13626,9 +14637,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K206" s="10" t="inlineStr"/>
-      <c r="L206" s="10" t="inlineStr"/>
-      <c r="M206" s="10" t="inlineStr"/>
+      <c r="L206" s="11" t="inlineStr"/>
+      <c r="M206" s="11" t="inlineStr"/>
+      <c r="N206" s="11" t="inlineStr"/>
     </row>
     <row r="207" ht="270" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
@@ -13678,6 +14689,11 @@
       </c>
       <c r="J207" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K207" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Hugo Joncas,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13690,9 +14706,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K207" s="10" t="inlineStr"/>
-      <c r="L207" s="10" t="inlineStr"/>
-      <c r="M207" s="10" t="inlineStr"/>
+      <c r="L207" s="11" t="inlineStr"/>
+      <c r="M207" s="11" t="inlineStr"/>
+      <c r="N207" s="11" t="inlineStr"/>
     </row>
     <row r="208" ht="270" customHeight="1">
       <c r="A208" s="6" t="inlineStr">
@@ -13742,6 +14758,11 @@
       </c>
       <c r="J208" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K208" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Philémon La Frenière-Prémont,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13754,9 +14775,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K208" s="10" t="inlineStr"/>
-      <c r="L208" s="10" t="inlineStr"/>
-      <c r="M208" s="10" t="inlineStr"/>
+      <c r="L208" s="11" t="inlineStr"/>
+      <c r="M208" s="11" t="inlineStr"/>
+      <c r="N208" s="11" t="inlineStr"/>
     </row>
     <row r="209" ht="270" customHeight="1">
       <c r="A209" s="6" t="inlineStr">
@@ -13806,6 +14827,11 @@
       </c>
       <c r="J209" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K209" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Henri Laban,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13818,9 +14844,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K209" s="10" t="inlineStr"/>
-      <c r="L209" s="10" t="inlineStr"/>
-      <c r="M209" s="10" t="inlineStr"/>
+      <c r="L209" s="11" t="inlineStr"/>
+      <c r="M209" s="11" t="inlineStr"/>
+      <c r="N209" s="11" t="inlineStr"/>
     </row>
     <row r="210" ht="270" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
@@ -13868,14 +14894,15 @@
           <t>vous</t>
         </is>
       </c>
-      <c r="J210" s="9" t="inlineStr">
+      <c r="J210" s="9" t="inlineStr"/>
+      <c r="K210" s="10" t="inlineStr">
         <is>
           <t>NE PAS ENVOYER — doublon de la liste chaude. Le message écrit à la main a préséance.</t>
         </is>
       </c>
-      <c r="K210" s="10" t="inlineStr"/>
-      <c r="L210" s="10" t="inlineStr"/>
-      <c r="M210" s="10" t="inlineStr"/>
+      <c r="L210" s="11" t="inlineStr"/>
+      <c r="M210" s="11" t="inlineStr"/>
+      <c r="N210" s="11" t="inlineStr"/>
     </row>
     <row r="211" ht="270" customHeight="1">
       <c r="A211" s="6" t="inlineStr">
@@ -13925,6 +14952,11 @@
       </c>
       <c r="J211" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K211" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Joannie Lafrenière,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -13937,9 +14969,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K211" s="10" t="inlineStr"/>
-      <c r="L211" s="10" t="inlineStr"/>
-      <c r="M211" s="10" t="inlineStr"/>
+      <c r="L211" s="11" t="inlineStr"/>
+      <c r="M211" s="11" t="inlineStr"/>
+      <c r="N211" s="11" t="inlineStr"/>
     </row>
     <row r="212" ht="270" customHeight="1">
       <c r="A212" s="6" t="inlineStr">
@@ -13989,6 +15021,11 @@
       </c>
       <c r="J212" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K212" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Angie Landry,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14001,9 +15038,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K212" s="10" t="inlineStr"/>
-      <c r="L212" s="10" t="inlineStr"/>
-      <c r="M212" s="10" t="inlineStr"/>
+      <c r="L212" s="11" t="inlineStr"/>
+      <c r="M212" s="11" t="inlineStr"/>
+      <c r="N212" s="11" t="inlineStr"/>
     </row>
     <row r="213" ht="270" customHeight="1">
       <c r="A213" s="6" t="inlineStr">
@@ -14053,6 +15090,11 @@
       </c>
       <c r="J213" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K213" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Camille Langlade,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14065,9 +15107,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K213" s="10" t="inlineStr"/>
-      <c r="L213" s="10" t="inlineStr"/>
-      <c r="M213" s="10" t="inlineStr"/>
+      <c r="L213" s="11" t="inlineStr"/>
+      <c r="M213" s="11" t="inlineStr"/>
+      <c r="N213" s="11" t="inlineStr"/>
     </row>
     <row r="214" ht="270" customHeight="1">
       <c r="A214" s="6" t="inlineStr">
@@ -14117,6 +15159,11 @@
       </c>
       <c r="J214" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K214" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Claudia Larochelle,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14129,9 +15176,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K214" s="10" t="inlineStr"/>
-      <c r="L214" s="10" t="inlineStr"/>
-      <c r="M214" s="10" t="inlineStr"/>
+      <c r="L214" s="11" t="inlineStr"/>
+      <c r="M214" s="11" t="inlineStr"/>
+      <c r="N214" s="11" t="inlineStr"/>
     </row>
     <row r="215" ht="270" customHeight="1">
       <c r="A215" s="6" t="inlineStr">
@@ -14181,6 +15228,11 @@
       </c>
       <c r="J215" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K215" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Étienne Leblanc,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14193,9 +15245,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K215" s="10" t="inlineStr"/>
-      <c r="L215" s="10" t="inlineStr"/>
-      <c r="M215" s="10" t="inlineStr"/>
+      <c r="L215" s="11" t="inlineStr"/>
+      <c r="M215" s="11" t="inlineStr"/>
+      <c r="N215" s="11" t="inlineStr"/>
     </row>
     <row r="216" ht="270" customHeight="1">
       <c r="A216" s="6" t="inlineStr">
@@ -14245,6 +15297,11 @@
       </c>
       <c r="J216" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K216" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Louise Leduc,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14257,9 +15314,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K216" s="10" t="inlineStr"/>
-      <c r="L216" s="10" t="inlineStr"/>
-      <c r="M216" s="10" t="inlineStr"/>
+      <c r="L216" s="11" t="inlineStr"/>
+      <c r="M216" s="11" t="inlineStr"/>
+      <c r="N216" s="11" t="inlineStr"/>
     </row>
     <row r="217" ht="270" customHeight="1">
       <c r="A217" s="6" t="inlineStr">
@@ -14309,6 +15366,11 @@
       </c>
       <c r="J217" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K217" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Guillaume Longuépée,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14321,9 +15383,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K217" s="10" t="inlineStr"/>
-      <c r="L217" s="10" t="inlineStr"/>
-      <c r="M217" s="10" t="inlineStr"/>
+      <c r="L217" s="11" t="inlineStr"/>
+      <c r="M217" s="11" t="inlineStr"/>
+      <c r="N217" s="11" t="inlineStr"/>
     </row>
     <row r="218" ht="270" customHeight="1">
       <c r="A218" s="6" t="inlineStr">
@@ -14373,6 +15435,11 @@
       </c>
       <c r="J218" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K218" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Roxane Léouzon,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14385,9 +15452,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K218" s="10" t="inlineStr"/>
-      <c r="L218" s="10" t="inlineStr"/>
-      <c r="M218" s="10" t="inlineStr"/>
+      <c r="L218" s="11" t="inlineStr"/>
+      <c r="M218" s="11" t="inlineStr"/>
+      <c r="N218" s="11" t="inlineStr"/>
     </row>
     <row r="219" ht="270" customHeight="1">
       <c r="A219" s="6" t="inlineStr">
@@ -14437,6 +15504,11 @@
       </c>
       <c r="J219" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K219" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Ève Lévesque,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14449,9 +15521,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K219" s="10" t="inlineStr"/>
-      <c r="L219" s="10" t="inlineStr"/>
-      <c r="M219" s="10" t="inlineStr"/>
+      <c r="L219" s="11" t="inlineStr"/>
+      <c r="M219" s="11" t="inlineStr"/>
+      <c r="N219" s="11" t="inlineStr"/>
     </row>
     <row r="220" ht="270" customHeight="1">
       <c r="A220" s="6" t="inlineStr">
@@ -14501,6 +15573,11 @@
       </c>
       <c r="J220" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K220" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Sophie Mangado,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14513,9 +15590,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K220" s="10" t="inlineStr"/>
-      <c r="L220" s="10" t="inlineStr"/>
-      <c r="M220" s="10" t="inlineStr"/>
+      <c r="L220" s="11" t="inlineStr"/>
+      <c r="M220" s="11" t="inlineStr"/>
+      <c r="N220" s="11" t="inlineStr"/>
     </row>
     <row r="221" ht="270" customHeight="1">
       <c r="A221" s="6" t="inlineStr">
@@ -14565,6 +15642,11 @@
       </c>
       <c r="J221" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K221" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Colin McGregor,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14577,9 +15659,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K221" s="10" t="inlineStr"/>
-      <c r="L221" s="10" t="inlineStr"/>
-      <c r="M221" s="10" t="inlineStr"/>
+      <c r="L221" s="11" t="inlineStr"/>
+      <c r="M221" s="11" t="inlineStr"/>
+      <c r="N221" s="11" t="inlineStr"/>
     </row>
     <row r="222" ht="270" customHeight="1">
       <c r="A222" s="6" t="inlineStr">
@@ -14629,6 +15711,11 @@
       </c>
       <c r="J222" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K222" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Isabelle Morin,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14641,9 +15728,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K222" s="10" t="inlineStr"/>
-      <c r="L222" s="10" t="inlineStr"/>
-      <c r="M222" s="10" t="inlineStr"/>
+      <c r="L222" s="11" t="inlineStr"/>
+      <c r="M222" s="11" t="inlineStr"/>
+      <c r="N222" s="11" t="inlineStr"/>
     </row>
     <row r="223" ht="270" customHeight="1">
       <c r="A223" s="6" t="inlineStr">
@@ -14693,6 +15780,11 @@
       </c>
       <c r="J223" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K223" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Timothy Morson,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14705,9 +15797,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K223" s="10" t="inlineStr"/>
-      <c r="L223" s="10" t="inlineStr"/>
-      <c r="M223" s="10" t="inlineStr"/>
+      <c r="L223" s="11" t="inlineStr"/>
+      <c r="M223" s="11" t="inlineStr"/>
+      <c r="N223" s="11" t="inlineStr"/>
     </row>
     <row r="224" ht="270" customHeight="1">
       <c r="A224" s="6" t="inlineStr">
@@ -14757,6 +15849,11 @@
       </c>
       <c r="J224" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K224" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Rachid Najahi,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14769,9 +15866,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K224" s="10" t="inlineStr"/>
-      <c r="L224" s="10" t="inlineStr"/>
-      <c r="M224" s="10" t="inlineStr"/>
+      <c r="L224" s="11" t="inlineStr"/>
+      <c r="M224" s="11" t="inlineStr"/>
+      <c r="N224" s="11" t="inlineStr"/>
     </row>
     <row r="225" ht="270" customHeight="1">
       <c r="A225" s="6" t="inlineStr">
@@ -14821,6 +15918,11 @@
       </c>
       <c r="J225" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K225" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Richard Olivier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14833,9 +15935,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K225" s="10" t="inlineStr"/>
-      <c r="L225" s="10" t="inlineStr"/>
-      <c r="M225" s="10" t="inlineStr"/>
+      <c r="L225" s="11" t="inlineStr"/>
+      <c r="M225" s="11" t="inlineStr"/>
+      <c r="N225" s="11" t="inlineStr"/>
     </row>
     <row r="226" ht="270" customHeight="1">
       <c r="A226" s="6" t="inlineStr">
@@ -14885,6 +15987,11 @@
       </c>
       <c r="J226" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K226" s="10" t="inlineStr">
+        <is>
           <t>Bonjour MELISSA PELLETIER,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14897,9 +16004,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K226" s="10" t="inlineStr"/>
-      <c r="L226" s="10" t="inlineStr"/>
-      <c r="M226" s="10" t="inlineStr"/>
+      <c r="L226" s="11" t="inlineStr"/>
+      <c r="M226" s="11" t="inlineStr"/>
+      <c r="N226" s="11" t="inlineStr"/>
     </row>
     <row r="227" ht="270" customHeight="1">
       <c r="A227" s="6" t="inlineStr">
@@ -14949,6 +16056,11 @@
       </c>
       <c r="J227" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K227" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Isaac Peltz,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -14961,9 +16073,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K227" s="10" t="inlineStr"/>
-      <c r="L227" s="10" t="inlineStr"/>
-      <c r="M227" s="10" t="inlineStr"/>
+      <c r="L227" s="11" t="inlineStr"/>
+      <c r="M227" s="11" t="inlineStr"/>
+      <c r="N227" s="11" t="inlineStr"/>
     </row>
     <row r="228" ht="270" customHeight="1">
       <c r="A228" s="6" t="inlineStr">
@@ -15013,6 +16125,11 @@
       </c>
       <c r="J228" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K228" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Frédéric Perron,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15025,9 +16142,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K228" s="10" t="inlineStr"/>
-      <c r="L228" s="10" t="inlineStr"/>
-      <c r="M228" s="10" t="inlineStr"/>
+      <c r="L228" s="11" t="inlineStr"/>
+      <c r="M228" s="11" t="inlineStr"/>
+      <c r="N228" s="11" t="inlineStr"/>
     </row>
     <row r="229" ht="270" customHeight="1">
       <c r="A229" s="6" t="inlineStr">
@@ -15077,6 +16194,11 @@
       </c>
       <c r="J229" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K229" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Nathalie Petrowski,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15089,9 +16211,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K229" s="10" t="inlineStr"/>
-      <c r="L229" s="10" t="inlineStr"/>
-      <c r="M229" s="10" t="inlineStr"/>
+      <c r="L229" s="11" t="inlineStr"/>
+      <c r="M229" s="11" t="inlineStr"/>
+      <c r="N229" s="11" t="inlineStr"/>
     </row>
     <row r="230" ht="270" customHeight="1">
       <c r="A230" s="6" t="inlineStr">
@@ -15141,6 +16263,11 @@
       </c>
       <c r="J230" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K230" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Francis Plourde,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15153,9 +16280,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K230" s="10" t="inlineStr"/>
-      <c r="L230" s="10" t="inlineStr"/>
-      <c r="M230" s="10" t="inlineStr"/>
+      <c r="L230" s="11" t="inlineStr"/>
+      <c r="M230" s="11" t="inlineStr"/>
+      <c r="N230" s="11" t="inlineStr"/>
     </row>
     <row r="231" ht="270" customHeight="1">
       <c r="A231" s="6" t="inlineStr">
@@ -15205,6 +16332,11 @@
       </c>
       <c r="J231" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K231" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Raymonde Provencher,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15217,9 +16349,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K231" s="10" t="inlineStr"/>
-      <c r="L231" s="10" t="inlineStr"/>
-      <c r="M231" s="10" t="inlineStr"/>
+      <c r="L231" s="11" t="inlineStr"/>
+      <c r="M231" s="11" t="inlineStr"/>
+      <c r="N231" s="11" t="inlineStr"/>
     </row>
     <row r="232" ht="270" customHeight="1">
       <c r="A232" s="6" t="inlineStr">
@@ -15269,6 +16401,11 @@
       </c>
       <c r="J232" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K232" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Richard Prudhomme,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15281,9 +16418,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K232" s="10" t="inlineStr"/>
-      <c r="L232" s="10" t="inlineStr"/>
-      <c r="M232" s="10" t="inlineStr"/>
+      <c r="L232" s="11" t="inlineStr"/>
+      <c r="M232" s="11" t="inlineStr"/>
+      <c r="N232" s="11" t="inlineStr"/>
     </row>
     <row r="233" ht="270" customHeight="1">
       <c r="A233" s="6" t="inlineStr">
@@ -15333,6 +16470,11 @@
       </c>
       <c r="J233" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K233" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Pascale Renaud,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15345,9 +16487,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K233" s="10" t="inlineStr"/>
-      <c r="L233" s="10" t="inlineStr"/>
-      <c r="M233" s="10" t="inlineStr"/>
+      <c r="L233" s="11" t="inlineStr"/>
+      <c r="M233" s="11" t="inlineStr"/>
+      <c r="N233" s="11" t="inlineStr"/>
     </row>
     <row r="234" ht="270" customHeight="1">
       <c r="A234" s="6" t="inlineStr">
@@ -15397,6 +16539,11 @@
       </c>
       <c r="J234" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K234" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marc Sony Ricot,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15409,9 +16556,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K234" s="10" t="inlineStr"/>
-      <c r="L234" s="10" t="inlineStr"/>
-      <c r="M234" s="10" t="inlineStr"/>
+      <c r="L234" s="11" t="inlineStr"/>
+      <c r="M234" s="11" t="inlineStr"/>
+      <c r="N234" s="11" t="inlineStr"/>
     </row>
     <row r="235" ht="270" customHeight="1">
       <c r="A235" s="6" t="inlineStr">
@@ -15461,6 +16608,11 @@
       </c>
       <c r="J235" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K235" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-Paul Rouleau,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15473,9 +16625,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K235" s="10" t="inlineStr"/>
-      <c r="L235" s="10" t="inlineStr"/>
-      <c r="M235" s="10" t="inlineStr"/>
+      <c r="L235" s="11" t="inlineStr"/>
+      <c r="M235" s="11" t="inlineStr"/>
+      <c r="N235" s="11" t="inlineStr"/>
     </row>
     <row r="236" ht="270" customHeight="1">
       <c r="A236" s="6" t="inlineStr">
@@ -15525,6 +16677,11 @@
       </c>
       <c r="J236" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K236" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Emmalie Ruest,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15537,9 +16694,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K236" s="10" t="inlineStr"/>
-      <c r="L236" s="10" t="inlineStr"/>
-      <c r="M236" s="10" t="inlineStr"/>
+      <c r="L236" s="11" t="inlineStr"/>
+      <c r="M236" s="11" t="inlineStr"/>
+      <c r="N236" s="11" t="inlineStr"/>
     </row>
     <row r="237" ht="270" customHeight="1">
       <c r="A237" s="6" t="inlineStr">
@@ -15589,6 +16746,11 @@
       </c>
       <c r="J237" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K237" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Louis-Philippe Samson,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15601,9 +16763,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K237" s="10" t="inlineStr"/>
-      <c r="L237" s="10" t="inlineStr"/>
-      <c r="M237" s="10" t="inlineStr"/>
+      <c r="L237" s="11" t="inlineStr"/>
+      <c r="M237" s="11" t="inlineStr"/>
+      <c r="N237" s="11" t="inlineStr"/>
     </row>
     <row r="238" ht="270" customHeight="1">
       <c r="A238" s="6" t="inlineStr">
@@ -15653,6 +16815,11 @@
       </c>
       <c r="J238" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K238" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Catherine Schlager,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15665,9 +16832,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K238" s="10" t="inlineStr"/>
-      <c r="L238" s="10" t="inlineStr"/>
-      <c r="M238" s="10" t="inlineStr"/>
+      <c r="L238" s="11" t="inlineStr"/>
+      <c r="M238" s="11" t="inlineStr"/>
+      <c r="N238" s="11" t="inlineStr"/>
     </row>
     <row r="239" ht="270" customHeight="1">
       <c r="A239" s="6" t="inlineStr">
@@ -15717,6 +16884,11 @@
       </c>
       <c r="J239" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K239" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Olivier Schmouker,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15729,9 +16901,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K239" s="10" t="inlineStr"/>
-      <c r="L239" s="10" t="inlineStr"/>
-      <c r="M239" s="10" t="inlineStr"/>
+      <c r="L239" s="11" t="inlineStr"/>
+      <c r="M239" s="11" t="inlineStr"/>
+      <c r="N239" s="11" t="inlineStr"/>
     </row>
     <row r="240" ht="270" customHeight="1">
       <c r="A240" s="6" t="inlineStr">
@@ -15781,6 +16953,11 @@
       </c>
       <c r="J240" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K240" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Jacques Sennechael,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15793,9 +16970,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K240" s="10" t="inlineStr"/>
-      <c r="L240" s="10" t="inlineStr"/>
-      <c r="M240" s="10" t="inlineStr"/>
+      <c r="L240" s="11" t="inlineStr"/>
+      <c r="M240" s="11" t="inlineStr"/>
+      <c r="N240" s="11" t="inlineStr"/>
     </row>
     <row r="241" ht="270" customHeight="1">
       <c r="A241" s="6" t="inlineStr">
@@ -15845,6 +17022,11 @@
       </c>
       <c r="J241" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K241" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Alexandre Shields,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15857,9 +17039,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K241" s="10" t="inlineStr"/>
-      <c r="L241" s="10" t="inlineStr"/>
-      <c r="M241" s="10" t="inlineStr"/>
+      <c r="L241" s="11" t="inlineStr"/>
+      <c r="M241" s="11" t="inlineStr"/>
+      <c r="N241" s="11" t="inlineStr"/>
     </row>
     <row r="242" ht="270" customHeight="1">
       <c r="A242" s="6" t="inlineStr">
@@ -15909,6 +17091,11 @@
       </c>
       <c r="J242" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K242" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Chloé Sondervorst,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15921,9 +17108,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K242" s="10" t="inlineStr"/>
-      <c r="L242" s="10" t="inlineStr"/>
-      <c r="M242" s="10" t="inlineStr"/>
+      <c r="L242" s="11" t="inlineStr"/>
+      <c r="M242" s="11" t="inlineStr"/>
+      <c r="N242" s="11" t="inlineStr"/>
     </row>
     <row r="243" ht="270" customHeight="1">
       <c r="A243" s="6" t="inlineStr">
@@ -15973,6 +17160,11 @@
       </c>
       <c r="J243" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K243" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Kimberley Sullivan,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -15985,9 +17177,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K243" s="10" t="inlineStr"/>
-      <c r="L243" s="10" t="inlineStr"/>
-      <c r="M243" s="10" t="inlineStr"/>
+      <c r="L243" s="11" t="inlineStr"/>
+      <c r="M243" s="11" t="inlineStr"/>
+      <c r="N243" s="11" t="inlineStr"/>
     </row>
     <row r="244" ht="270" customHeight="1">
       <c r="A244" s="6" t="inlineStr">
@@ -16037,6 +17229,11 @@
       </c>
       <c r="J244" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K244" s="10" t="inlineStr">
+        <is>
           <t>Bonjour William Thériault,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16049,9 +17246,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K244" s="10" t="inlineStr"/>
-      <c r="L244" s="10" t="inlineStr"/>
-      <c r="M244" s="10" t="inlineStr"/>
+      <c r="L244" s="11" t="inlineStr"/>
+      <c r="M244" s="11" t="inlineStr"/>
+      <c r="N244" s="11" t="inlineStr"/>
     </row>
     <row r="245" ht="270" customHeight="1">
       <c r="A245" s="6" t="inlineStr">
@@ -16101,6 +17298,11 @@
       </c>
       <c r="J245" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K245" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Katia Tobar,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16113,9 +17315,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K245" s="10" t="inlineStr"/>
-      <c r="L245" s="10" t="inlineStr"/>
-      <c r="M245" s="10" t="inlineStr"/>
+      <c r="L245" s="11" t="inlineStr"/>
+      <c r="M245" s="11" t="inlineStr"/>
+      <c r="N245" s="11" t="inlineStr"/>
     </row>
     <row r="246" ht="270" customHeight="1">
       <c r="A246" s="6" t="inlineStr">
@@ -16165,6 +17367,11 @@
       </c>
       <c r="J246" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K246" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Martin Tremblay,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16177,9 +17384,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K246" s="10" t="inlineStr"/>
-      <c r="L246" s="10" t="inlineStr"/>
-      <c r="M246" s="10" t="inlineStr"/>
+      <c r="L246" s="11" t="inlineStr"/>
+      <c r="M246" s="11" t="inlineStr"/>
+      <c r="N246" s="11" t="inlineStr"/>
     </row>
     <row r="247" ht="270" customHeight="1">
       <c r="A247" s="6" t="inlineStr">
@@ -16229,6 +17436,11 @@
       </c>
       <c r="J247" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K247" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Marie-Christine Trottier,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16241,9 +17453,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K247" s="10" t="inlineStr"/>
-      <c r="L247" s="10" t="inlineStr"/>
-      <c r="M247" s="10" t="inlineStr"/>
+      <c r="L247" s="11" t="inlineStr"/>
+      <c r="M247" s="11" t="inlineStr"/>
+      <c r="N247" s="11" t="inlineStr"/>
     </row>
     <row r="248" ht="270" customHeight="1">
       <c r="A248" s="6" t="inlineStr">
@@ -16293,6 +17505,11 @@
       </c>
       <c r="J248" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K248" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Pierre-Luc Trudel,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16305,9 +17522,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K248" s="10" t="inlineStr"/>
-      <c r="L248" s="10" t="inlineStr"/>
-      <c r="M248" s="10" t="inlineStr"/>
+      <c r="L248" s="11" t="inlineStr"/>
+      <c r="M248" s="11" t="inlineStr"/>
+      <c r="N248" s="11" t="inlineStr"/>
     </row>
     <row r="249" ht="270" customHeight="1">
       <c r="A249" s="6" t="inlineStr">
@@ -16357,6 +17574,11 @@
       </c>
       <c r="J249" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K249" s="10" t="inlineStr">
+        <is>
           <t>Bonjour David Turbis,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16369,9 +17591,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K249" s="10" t="inlineStr"/>
-      <c r="L249" s="10" t="inlineStr"/>
-      <c r="M249" s="10" t="inlineStr"/>
+      <c r="L249" s="11" t="inlineStr"/>
+      <c r="M249" s="11" t="inlineStr"/>
+      <c r="N249" s="11" t="inlineStr"/>
     </row>
     <row r="250" ht="270" customHeight="1">
       <c r="A250" s="6" t="inlineStr">
@@ -16421,6 +17643,11 @@
       </c>
       <c r="J250" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K250" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Paule Vermot-Desroches,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16433,9 +17660,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K250" s="10" t="inlineStr"/>
-      <c r="L250" s="10" t="inlineStr"/>
-      <c r="M250" s="10" t="inlineStr"/>
+      <c r="L250" s="11" t="inlineStr"/>
+      <c r="M250" s="11" t="inlineStr"/>
+      <c r="N250" s="11" t="inlineStr"/>
     </row>
     <row r="251" ht="270" customHeight="1">
       <c r="A251" s="6" t="inlineStr">
@@ -16485,6 +17712,11 @@
       </c>
       <c r="J251" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+        </is>
+      </c>
+      <c r="K251" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Alexandra Viau,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16497,9 +17729,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K251" s="10" t="inlineStr"/>
-      <c r="L251" s="10" t="inlineStr"/>
-      <c r="M251" s="10" t="inlineStr"/>
+      <c r="L251" s="11" t="inlineStr"/>
+      <c r="M251" s="11" t="inlineStr"/>
+      <c r="N251" s="11" t="inlineStr"/>
     </row>
     <row r="252" ht="270" customHeight="1">
       <c r="A252" s="6" t="inlineStr">
@@ -16549,6 +17781,11 @@
       </c>
       <c r="J252" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K252" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Raymond Viger,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16561,9 +17798,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K252" s="10" t="inlineStr"/>
-      <c r="L252" s="10" t="inlineStr"/>
-      <c r="M252" s="10" t="inlineStr"/>
+      <c r="L252" s="11" t="inlineStr"/>
+      <c r="M252" s="11" t="inlineStr"/>
+      <c r="N252" s="11" t="inlineStr"/>
     </row>
     <row r="253" ht="270" customHeight="1">
       <c r="A253" s="6" t="inlineStr">
@@ -16613,6 +17850,11 @@
       </c>
       <c r="J253" s="9" t="inlineStr">
         <is>
+          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K253" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Paul Émile d'Entremont,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16625,9 +17867,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K253" s="10" t="inlineStr"/>
-      <c r="L253" s="10" t="inlineStr"/>
-      <c r="M253" s="10" t="inlineStr"/>
+      <c r="L253" s="11" t="inlineStr"/>
+      <c r="M253" s="11" t="inlineStr"/>
+      <c r="N253" s="11" t="inlineStr"/>
     </row>
     <row r="254" ht="270" customHeight="1">
       <c r="A254" s="6" t="inlineStr">
@@ -16677,6 +17919,11 @@
       </c>
       <c r="J254" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K254" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Augustin de Baudinière,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16689,9 +17936,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K254" s="10" t="inlineStr"/>
-      <c r="L254" s="10" t="inlineStr"/>
-      <c r="M254" s="10" t="inlineStr"/>
+      <c r="L254" s="11" t="inlineStr"/>
+      <c r="M254" s="11" t="inlineStr"/>
+      <c r="N254" s="11" t="inlineStr"/>
     </row>
     <row r="255" ht="270" customHeight="1">
       <c r="A255" s="6" t="inlineStr">
@@ -16741,6 +17988,11 @@
       </c>
       <c r="J255" s="9" t="inlineStr">
         <is>
+          <t>L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K255" s="10" t="inlineStr">
+        <is>
           <t>Bonjour Ivan de Jacquelin-Dulphe,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
 On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
@@ -16753,9 +18005,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K255" s="10" t="inlineStr"/>
-      <c r="L255" s="10" t="inlineStr"/>
-      <c r="M255" s="10" t="inlineStr"/>
+      <c r="L255" s="11" t="inlineStr"/>
+      <c r="M255" s="11" t="inlineStr"/>
+      <c r="N255" s="11" t="inlineStr"/>
     </row>
     <row r="256" ht="270" customHeight="1">
       <c r="A256" s="6" t="inlineStr">
@@ -16804,6 +18056,11 @@
         </is>
       </c>
       <c r="J256" s="9" t="inlineStr">
+        <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K256" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Michel Leprince,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
@@ -16824,9 +18081,9 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K256" s="10" t="inlineStr"/>
-      <c r="L256" s="10" t="inlineStr"/>
-      <c r="M256" s="10" t="inlineStr"/>
+      <c r="L256" s="11" t="inlineStr"/>
+      <c r="M256" s="11" t="inlineStr"/>
+      <c r="N256" s="11" t="inlineStr"/>
     </row>
     <row r="257" ht="270" customHeight="1">
       <c r="A257" s="6" t="inlineStr">
@@ -16871,6 +18128,11 @@
         </is>
       </c>
       <c r="J257" s="9" t="inlineStr">
+        <is>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+      <c r="K257" s="10" t="inlineStr">
         <is>
           <t>Bonjour Antoine Stab,
 Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
@@ -16887,14 +18149,14 @@
 Au plaisir et n'hésitez pas à me contacter si vous avez des questions.</t>
         </is>
       </c>
-      <c r="K257" s="10" t="inlineStr"/>
-      <c r="L257" s="10" t="inlineStr"/>
-      <c r="M257" s="10" t="inlineStr"/>
+      <c r="L257" s="11" t="inlineStr"/>
+      <c r="M257" s="11" t="inlineStr"/>
+      <c r="N257" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M257"/>
+  <autoFilter ref="A1:N257"/>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"à réécrire au complet,à corriger,bon,ne pas envoyer"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Version 4 — les objets</t>
+          <t>Version 5 — les objets, suite</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -520,66 +520,66 @@
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Le modèle</t>
+          <t>« Invité disponible »</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>« Nous serons diffusés à Dragons' Den le 17 septembre! » L'objet annonce la nouvelle, avec la date, et il a le droit d'être content.</t>
+          <t>Retiré. Zéro occurrence.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Ce qu'ils étaient</t>
+          <t>L'asclépiade en tête</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>« Le monarque, l'asclépiade, et l'idée qu'il faut la rendre payante ». Un titre d'essai, pas un objet de courriel. Et sans accents.</t>
+          <t>Tu as aimé la formule, alors elle passe de 54 à 149 contacts. « Nous serons diffusés » suppose que la personne sait déjà qui est « nous » : ça ne vaut que pour ceux qui nous connaissent, la liste chaude et les journalistes d'affaires.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Quatre variantes</t>
+          <t>Les trois objets</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>A, B, E, G : Nous serons diffusés à Dragons' Den le 17 septembre!  |  C, F, J : L'asclépiade s'en va à Dragons' Den le 17 septembre!  |  D : L'asclépiade et les monarques à Dragons' Den le 17 septembre!  |  I : … — invité disponible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Pourquoi pas un seul</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>253 courriels avec exactement la même ligne d'objet se comportent comme du publipostage aux yeux des filtres, et « l'asclépiade s'en va » parle plus à un journaliste agricole qu'à un chroniqueur d'affaires.</t>
-        </is>
-      </c>
+          <t>149 : L'asclépiade s'en va à Dragons' Den le 17 septembre!  |  59 : Nous serons diffusés à Dragons' Den le 17 septembre!  |  45 : L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Les versions précédentes</t>
+        </is>
+      </c>
       <c r="B7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Rappel des versions précédentes</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Objets refaits : de « titre d'essai » à annonce datée.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Présentation complète en tête des courriels froids, « pourquoi vous » explicite, fausse accroche régionale retirée.</t>
+          <t>Présentation complète en tête des courriels froids, « pourquoi vous » explicite.</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Registre de Gabriel : plus d'excuses sur le virage, plus de mise en garde sur les monarques, plus de rappel de confidentialité.</t>
+          <t>Registre de Gabriel : plus d'excuses, plus de mise en garde, plus de rappel de confidentialité.</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>Brouillon v4</t>
+          <t>Brouillon v5</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K42" s="10" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K48" s="10" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K60" s="10" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K61" s="10" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K64" s="10" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K66" s="10" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K70" s="10" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K74" s="10" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K76" s="10" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K86" s="10" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K90" s="10" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K91" s="10" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K100" s="10" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K101" s="10" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K106" s="10" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K107" s="10" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K110" s="10" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K116" s="10" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K117" s="10" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K120" s="10" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K126" s="10" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K128" s="10" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="J131" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K131" s="10" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="J133" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K133" s="10" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="J135" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K135" s="10" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="J141" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K141" s="10" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K146" s="10" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="J147" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K147" s="10" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="J149" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K149" s="10" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="J151" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K151" s="10" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K152" s="10" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="J153" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K153" s="10" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="J167" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K167" s="10" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="J169" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K169" s="10" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="J170" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K170" s="10" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="J171" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K171" s="10" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="J174" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K174" s="10" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="J175" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K175" s="10" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="J176" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K176" s="10" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="J179" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K179" s="10" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="J180" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K180" s="10" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="J181" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K181" s="10" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="J183" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K183" s="10" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="J184" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K184" s="10" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="J185" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K185" s="10" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="J189" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K189" s="10" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="J190" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K190" s="10" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="J193" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K193" s="10" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="J194" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K194" s="10" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="J196" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K196" s="10" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="J198" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K198" s="10" t="inlineStr">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="J201" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K201" s="10" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="J202" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K202" s="10" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="J206" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K206" s="10" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="J208" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K208" s="10" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="J209" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K209" s="10" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="J211" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K211" s="10" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="J214" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K214" s="10" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="J216" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K216" s="10" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="J219" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K219" s="10" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="J220" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K220" s="10" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="J222" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K222" s="10" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="J224" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K224" s="10" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="J225" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K225" s="10" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="J226" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K226" s="10" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="J227" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K227" s="10" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="J228" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K228" s="10" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="J229" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K229" s="10" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="J230" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K230" s="10" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="J231" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K231" s="10" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="J232" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K232" s="10" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="J233" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K233" s="10" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="J234" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K234" s="10" t="inlineStr">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="J236" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K236" s="10" t="inlineStr">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="J237" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K237" s="10" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="J238" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K238" s="10" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="J240" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K240" s="10" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="J243" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K243" s="10" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="J247" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K247" s="10" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="J249" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K249" s="10" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="J250" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K250" s="10" t="inlineStr">
@@ -17712,7 +17712,7 @@
       </c>
       <c r="J251" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre — invité disponible</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K251" s="10" t="inlineStr">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="J253" s="9" t="inlineStr">
         <is>
-          <t>Nous serons diffusés à Dragons' Den le 17 septembre!</t>
+          <t>L'asclépiade s'en va à Dragons' Den le 17 septembre!</t>
         </is>
       </c>
       <c r="K253" s="10" t="inlineStr">

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Version 5 — les objets, suite</t>
+          <t>Version 6 — la première ligne</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -520,150 +520,186 @@
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>« Invité disponible »</t>
+          <t>Le reproche</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Retiré. Zéro occurrence.</t>
+          <t>Limoilou est impertinent pour décrire l'entreprise. Un quartier ne dit rien à quelqu'un qui ne nous connaît pas, et ça brûlait la seule ligne qu'un journaliste lit à coup sûr.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>L'asclépiade en tête</t>
+          <t>Avant</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Tu as aimé la formule, alors elle passe de 54 à 149 contacts. « Nous serons diffusés » suppose que la personne sait déjà qui est « nous » : ça ne vaut que pour ceux qui nous connaissent, la liste chaude et les journalistes d'affaires.</t>
+          <t>« Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. »</t>
         </is>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Les trois objets</t>
+          <t>Maintenant</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>149 : L'asclépiade s'en va à Dragons' Den le 17 septembre!  |  59 : Nous serons diffusés à Dragons' Den le 17 septembre!  |  45 : L'asclépiade et les monarques à Dragons' Den le 17 septembre!</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Les versions précédentes</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr"/>
+          <t>« Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe. »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Le paragraphe suivant</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Resserré aussi : l'asclépiade et les « petits cochons » arrivent en tête de phrase au lieu d'être annoncés. « On la transforme en isolant à Québec » garde le lieu là où il compte, sans le quartier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Limoilou reste</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Là où c'est une invitation — « l'atelier de Limoilou est ouvert si vous voulez voir la matière » — et dans les courriels aux journalistes de Québec, qui savent où c'est.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>v4</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Objets refaits : de « titre d'essai » à annonce datée.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Présentation complète en tête des courriels froids, « pourquoi vous » explicite.</t>
-        </is>
-      </c>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Les versions précédentes</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Registre de Gabriel : plus d'excuses, plus de mise en garde, plus de rappel de confidentialité.</t>
+          <t>« Invité disponible » retiré, l'asclépiade en tête des objets pour 149 contacts.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Objets refaits : de titre d'essai à annonce datée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Présentation et « pourquoi vous » dans les courriels froids.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Registre de Gabriel : plus d'excuses, plus de mise en garde, plus de confidentialité.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Repris mot pour mot</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Larocque et Pouliot.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>Rappels</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Diffusion</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Jeudi 17 septembre 2026, 20 h (20 h 30 NT), CBC et CBC Gem. Prévente le samedi 12 septembre à 9 h.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Ne pas envoyer</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Anne-Sophie Roy à l'adresse Québecor. Annie Lafrance et Francis Higgins en liste froide.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Courriels manquants</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Sophie Poisson, Caroline Bertrand, Karine Benoist, Antoine Stab.</t>
         </is>
@@ -752,7 +788,7 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>Brouillon v5</t>
+          <t>Brouillon v6</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
@@ -2517,7 +2553,7 @@
       <c r="K29" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Roberge,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe : l'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2572,7 +2608,7 @@
       <c r="K30" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Laforest,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe : l'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2800,7 +2836,7 @@
       <c r="K34" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Goubau,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. Vous couvrez le textile et la mode, alors voici une matière que peu de gens ont vue de près : la soie d'asclépiade, une fibre creuse et naturellement hydrophobe attachée aux graines d'une plante que les agriculteurs arrachent de leurs champs depuis 50 ans. On la transforme en isolant, et on en fait des manteaux, des mitaines et des tuques.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe. Vous couvrez le textile et la mode, alors voici une matière que peu de gens ont vue de près : la soie d'asclépiade, une fibre creuse et naturellement hydrophobe attachée aux graines d'une plante que les agriculteurs arrachent de leurs champs depuis 50 ans. On la transforme en isolant, et on en fait des manteaux, des mitaines et des tuques.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -2855,7 +2891,7 @@
       <c r="K35" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Dostie,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe : l'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3099,8 +3135,8 @@
       <c r="K39" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie Allard,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
-Québec dont l'atelier est dans Limoilou.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
+mauvaise herbe.
 Il y a une belle histoire de sciences dans l'asclépiade. La soie attachée à ses graines n'est
 pas un poil : c'est un tube creux enduit d'une cire hydrophobe, et les fibres portent une
 charge qui les fait se repousser. C'est ce qui forme le parachute autour de la graine, et
@@ -3174,8 +3210,8 @@
       <c r="K40" s="10" t="inlineStr">
         <is>
           <t>Bonjour Zoé Allemand,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3243,8 +3279,8 @@
       <c r="K41" s="10" t="inlineStr">
         <is>
           <t>Bonjour Victoria Bakos,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3312,8 +3348,8 @@
       <c r="K42" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Émélie Bernier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3381,8 +3417,8 @@
       <c r="K43" s="10" t="inlineStr">
         <is>
           <t>Bonjour Normand Blouin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3450,8 +3486,8 @@
       <c r="K44" s="10" t="inlineStr">
         <is>
           <t>Bonjour Louise Bourbonnais,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3519,8 +3555,8 @@
       <c r="K45" s="10" t="inlineStr">
         <is>
           <t>Bonjour Francois Bourque,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3588,8 +3624,8 @@
       <c r="K46" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ariane Boyer,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3657,8 +3693,8 @@
       <c r="K47" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gilbert Bégin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3726,8 +3762,8 @@
       <c r="K48" s="10" t="inlineStr">
         <is>
           <t>Bonjour Papa Moussa Camara,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3795,8 +3831,8 @@
       <c r="K49" s="10" t="inlineStr">
         <is>
           <t>Bonjour Victor Carré,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3864,8 +3900,8 @@
       <c r="K50" s="10" t="inlineStr">
         <is>
           <t>Bonjour Eric Chabot,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -3933,8 +3969,8 @@
       <c r="K51" s="10" t="inlineStr">
         <is>
           <t>Bonjour Tristan Champagne-Lessard,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4002,8 +4038,8 @@
       <c r="K52" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Marc Chevalier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4071,8 +4107,8 @@
       <c r="K53" s="10" t="inlineStr">
         <is>
           <t>Bonjour Simon Chrétien,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4140,8 +4176,8 @@
       <c r="K54" s="10" t="inlineStr">
         <is>
           <t>Bonjour Maxime Corneau,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4209,8 +4245,8 @@
       <c r="K55" s="10" t="inlineStr">
         <is>
           <t>Bonjour Aurélia Crémoux,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4278,8 +4314,8 @@
       <c r="K56" s="10" t="inlineStr">
         <is>
           <t>Bonjour Catherine Dallaire,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4347,8 +4383,8 @@
       <c r="K57" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gabriel Delisle,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
-Québec dont l'atelier est dans Limoilou.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
+mauvaise herbe.
 L'asclépiade a été une histoire mauricienne avant d'être la nôtre : l'usine de Saint-Tite
 achetait 90 % des récoltes du Québec. On a démarré après la chute de cette filière, et six ans
 plus tard on achète encore de l'asclépiade québécoise et on la
@@ -4421,8 +4457,8 @@
       <c r="K58" s="10" t="inlineStr">
         <is>
           <t>Bonjour Anaïs Desjardins,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4490,8 +4526,8 @@
       <c r="K59" s="10" t="inlineStr">
         <is>
           <t>Bonjour Simon Dominé,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4559,8 +4595,8 @@
       <c r="K60" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karl-Ivann Dubé,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4628,8 +4664,8 @@
       <c r="K61" s="10" t="inlineStr">
         <is>
           <t>Bonjour André Fauteux,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4697,8 +4733,8 @@
       <c r="K62" s="10" t="inlineStr">
         <is>
           <t>Bonjour Myriam Fimbry,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4766,8 +4802,8 @@
       <c r="K63" s="10" t="inlineStr">
         <is>
           <t>Bonjour Étienne Fortin-Gauthier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4835,8 +4871,8 @@
       <c r="K64" s="10" t="inlineStr">
         <is>
           <t>Bonjour Johanne Fournier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4904,8 +4940,8 @@
       <c r="K65" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean Garon,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -4973,8 +5009,8 @@
       <c r="K66" s="10" t="inlineStr">
         <is>
           <t>Bonjour Cécile Gladel,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5042,8 +5078,8 @@
       <c r="K67" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marieke Glorieux-Stryckman,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5111,8 +5147,8 @@
       <c r="K68" s="10" t="inlineStr">
         <is>
           <t>Bonjour Maude Goyer,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5180,8 +5216,8 @@
       <c r="K69" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pauline Gravel,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5249,8 +5285,8 @@
       <c r="K70" s="10" t="inlineStr">
         <is>
           <t>Bonjour Bernard Hervieux,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5318,8 +5354,8 @@
       <c r="K71" s="10" t="inlineStr">
         <is>
           <t>Bonjour Leïla Jolin-Dahel,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5387,8 +5423,8 @@
       <c r="K72" s="10" t="inlineStr">
         <is>
           <t>Bonjour Kodjo Edjinam Nulagnon LOGO,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5456,8 +5492,8 @@
       <c r="K73" s="10" t="inlineStr">
         <is>
           <t>Bonjour Annie Labrecque,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5525,8 +5561,8 @@
       <c r="K74" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marianne Lachapelle,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5594,8 +5630,8 @@
       <c r="K75" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sophie Lachapelle,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5663,8 +5699,8 @@
       <c r="K76" s="10" t="inlineStr">
         <is>
           <t>Bonjour Alain Laforest,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5732,8 +5768,8 @@
       <c r="K77" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mikaël Lalancette,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5801,8 +5837,8 @@
       <c r="K78" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Luc Lavallée,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5870,8 +5906,8 @@
       <c r="K79" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Francois Leblanc,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -5939,8 +5975,8 @@
       <c r="K80" s="10" t="inlineStr">
         <is>
           <t>Bonjour Julie Leduc,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6008,8 +6044,8 @@
       <c r="K81" s="10" t="inlineStr">
         <is>
           <t>Bonjour Annie Martin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6077,8 +6113,8 @@
       <c r="K82" s="10" t="inlineStr">
         <is>
           <t>Bonjour Réjean Martin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
-Québec dont l'atelier est dans Limoilou.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
+mauvaise herbe.
 Vous couvrez Mékinac, donc Saint-Tite, donc l'endroit où l'asclépiade a eu son grand moment
 industriel au Québec. L'usine achetait 90 % des récoltes de la province avant que la filière
 se casse en 2018.
@@ -6152,8 +6188,8 @@
       <c r="K83" s="10" t="inlineStr">
         <is>
           <t>Bonjour Charles Mathieu,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6221,8 +6257,8 @@
       <c r="K84" s="10" t="inlineStr">
         <is>
           <t>Bonjour Clara Matthey-Jonais,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6290,8 +6326,8 @@
       <c r="K85" s="10" t="inlineStr">
         <is>
           <t>Bonjour Valérian Mazataud,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6359,8 +6395,8 @@
       <c r="K86" s="10" t="inlineStr">
         <is>
           <t>Bonjour Lili Mercure,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6428,8 +6464,8 @@
       <c r="K87" s="10" t="inlineStr">
         <is>
           <t>Bonjour Nicolas Mesly,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6497,8 +6533,8 @@
       <c r="K88" s="10" t="inlineStr">
         <is>
           <t>Bonjour Nicolas Michaud,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6566,8 +6602,8 @@
       <c r="K89" s="10" t="inlineStr">
         <is>
           <t>Bonjour Véronique Morin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6635,8 +6671,8 @@
       <c r="K90" s="10" t="inlineStr">
         <is>
           <t>Bonjour Lila Mouch,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6704,8 +6740,8 @@
       <c r="K91" s="10" t="inlineStr">
         <is>
           <t>Bonjour Olivier Mougeot,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6773,8 +6809,8 @@
       <c r="K92" s="10" t="inlineStr">
         <is>
           <t>Bonjour Emmanuelle Mozayan-Verschaeve,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6842,8 +6878,8 @@
       <c r="K93" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Benoît Nadeau,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6911,8 +6947,8 @@
       <c r="K94" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yves Ouellet,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -6980,8 +7016,8 @@
       <c r="K95" s="10" t="inlineStr">
         <is>
           <t>Bonjour Josée Panet-Raymond,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7049,8 +7085,8 @@
       <c r="K96" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yannick Patelli,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7118,8 +7154,8 @@
       <c r="K97" s="10" t="inlineStr">
         <is>
           <t>Bonjour Félix Pedneault,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7187,8 +7223,8 @@
       <c r="K98" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Eve Poulin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7256,8 +7292,8 @@
       <c r="K99" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Hélène Proulx,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7325,8 +7361,8 @@
       <c r="K100" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Hugues Roy,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7394,8 +7430,8 @@
       <c r="K101" s="10" t="inlineStr">
         <is>
           <t>Bonjour Martin Roy,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7463,8 +7499,8 @@
       <c r="K102" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sylvain Sarrazin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7532,8 +7568,8 @@
       <c r="K103" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre Sormany,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7601,8 +7637,8 @@
       <c r="K104" s="10" t="inlineStr">
         <is>
           <t>Bonjour Scott Stevenson,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7670,8 +7706,8 @@
       <c r="K105" s="10" t="inlineStr">
         <is>
           <t>Bonjour Michèle Tanganika,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7739,8 +7775,8 @@
       <c r="K106" s="10" t="inlineStr">
         <is>
           <t>Bonjour Stephane Tellier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7808,8 +7844,8 @@
       <c r="K107" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karine Tremblay,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7877,8 +7913,8 @@
       <c r="K108" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Francois Venne,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -7946,8 +7982,8 @@
       <c r="K109" s="10" t="inlineStr">
         <is>
           <t>Bonjour Shahram Yazdanpanah,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8015,8 +8051,8 @@
       <c r="K110" s="10" t="inlineStr">
         <is>
           <t>Bonjour Malika Alaoui,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8084,8 +8120,8 @@
       <c r="K111" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yahia Arkat,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8153,8 +8189,8 @@
       <c r="K112" s="10" t="inlineStr">
         <is>
           <t>Bonjour MARC-OLIVIER BISSON,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8222,8 +8258,8 @@
       <c r="K113" s="10" t="inlineStr">
         <is>
           <t>Bonjour Maïté Belmir,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8291,8 +8327,8 @@
       <c r="K114" s="10" t="inlineStr">
         <is>
           <t>Bonjour André Bernard,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8360,8 +8396,8 @@
       <c r="K115" s="10" t="inlineStr">
         <is>
           <t>Bonjour Didier Bert,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8429,8 +8465,8 @@
       <c r="K116" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sophie-Andrée Blondin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8498,8 +8534,8 @@
       <c r="K117" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre Brochu,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8567,8 +8603,8 @@
       <c r="K118" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gilles Bérubé,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8636,8 +8672,8 @@
       <c r="K119" s="10" t="inlineStr">
         <is>
           <t>Bonjour Daphné Cameron,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8705,8 +8741,8 @@
       <c r="K120" s="10" t="inlineStr">
         <is>
           <t>Bonjour Godefroy Macaire Chabi,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8774,8 +8810,8 @@
       <c r="K121" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sara Champagne,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8843,8 +8879,8 @@
       <c r="K122" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sarah Champagne,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8912,8 +8948,8 @@
       <c r="K123" s="10" t="inlineStr">
         <is>
           <t>Bonjour Éric-Pierre Champagne,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -8981,8 +9017,8 @@
       <c r="K124" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marine Corniou,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9050,8 +9086,8 @@
       <c r="K125" s="10" t="inlineStr">
         <is>
           <t>Bonjour Catherine Crépeau,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9119,8 +9155,8 @@
       <c r="K126" s="10" t="inlineStr">
         <is>
           <t>Bonjour Laurence Dami-Houle,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9188,8 +9224,8 @@
       <c r="K127" s="10" t="inlineStr">
         <is>
           <t>Bonjour Amélie Daoust-Boisvert,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9257,8 +9293,8 @@
       <c r="K128" s="10" t="inlineStr">
         <is>
           <t>Bonjour Dominique Degré,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9326,8 +9362,8 @@
       <c r="K129" s="10" t="inlineStr">
         <is>
           <t>Bonjour Quentin Dufranne,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9395,8 +9431,8 @@
       <c r="K130" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ève Dumas,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9464,8 +9500,8 @@
       <c r="K131" s="10" t="inlineStr">
         <is>
           <t>Bonjour Michel Fortier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9533,8 +9569,8 @@
       <c r="K132" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Eve Fournier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9602,8 +9638,8 @@
       <c r="K133" s="10" t="inlineStr">
         <is>
           <t>Bonjour Raymond Fournier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9671,8 +9707,8 @@
       <c r="K134" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Pier Frappier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9740,8 +9776,8 @@
       <c r="K135" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Julie Gagnon,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9809,8 +9845,8 @@
       <c r="K136" s="10" t="inlineStr">
         <is>
           <t>Bonjour Chloé Germain-Thérien,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9878,8 +9914,8 @@
       <c r="K137" s="10" t="inlineStr">
         <is>
           <t>Bonjour Charlotte Glorieux,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -9947,8 +9983,8 @@
       <c r="K138" s="10" t="inlineStr">
         <is>
           <t>Bonjour Annie Hudon,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10016,8 +10052,8 @@
       <c r="K139" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ahmed Kouaou,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10085,8 +10121,8 @@
       <c r="K140" s="10" t="inlineStr">
         <is>
           <t>Bonjour Tania Krywiak,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10154,8 +10190,8 @@
       <c r="K141" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jacinthe Lafrance,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10223,8 +10259,8 @@
       <c r="K142" s="10" t="inlineStr">
         <is>
           <t>Bonjour Bruno Lamolet,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10292,8 +10328,8 @@
       <c r="K143" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yvan Lamontagne,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10361,8 +10397,8 @@
       <c r="K144" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yves Langlois,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10430,8 +10466,8 @@
       <c r="K145" s="10" t="inlineStr">
         <is>
           <t>Bonjour Anne Marie Lecomte,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10499,8 +10535,8 @@
       <c r="K146" s="10" t="inlineStr">
         <is>
           <t>Bonjour Stéphanie Mac Farlane,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10568,8 +10604,8 @@
       <c r="K147" s="10" t="inlineStr">
         <is>
           <t>Bonjour Philippe Marois,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10637,8 +10673,8 @@
       <c r="K148" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gildas Meneu,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10706,8 +10742,8 @@
       <c r="K149" s="10" t="inlineStr">
         <is>
           <t>Bonjour Louis-Xavier Michaud,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10775,8 +10811,8 @@
       <c r="K150" s="10" t="inlineStr">
         <is>
           <t>Bonjour Anne Montplaisir,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10844,8 +10880,8 @@
       <c r="K151" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karianne Nepton-Philippe,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10913,8 +10949,8 @@
       <c r="K152" s="10" t="inlineStr">
         <is>
           <t>Bonjour Geneviève Normand,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -10982,8 +11018,8 @@
       <c r="K153" s="10" t="inlineStr">
         <is>
           <t>Bonjour Carole Payer,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11051,8 +11087,8 @@
       <c r="K154" s="10" t="inlineStr">
         <is>
           <t>Bonjour Boris Proulx,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11120,8 +11156,8 @@
       <c r="K155" s="10" t="inlineStr">
         <is>
           <t>Bonjour Philippe Robitaille-Grou,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11189,8 +11225,8 @@
       <c r="K156" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gwen Roley,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11258,8 +11294,8 @@
       <c r="K157" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mathieu-Robert Sauvé,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11327,8 +11363,8 @@
       <c r="K158" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre St-Arnaud,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11396,8 +11432,8 @@
       <c r="K159" s="10" t="inlineStr">
         <is>
           <t>Bonjour Katherine Tremblay,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11465,8 +11501,8 @@
       <c r="K160" s="10" t="inlineStr">
         <is>
           <t>Bonjour Michel Tremblay,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11534,8 +11570,8 @@
       <c r="K161" s="10" t="inlineStr">
         <is>
           <t>Bonjour Martin Vallières,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11603,8 +11639,8 @@
       <c r="K162" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yanick Villedieu,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11672,8 +11708,8 @@
       <c r="K163" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jonathan Allard,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11741,8 +11777,8 @@
       <c r="K164" s="10" t="inlineStr">
         <is>
           <t>Bonjour Anick Baribeau,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11810,8 +11846,8 @@
       <c r="K165" s="10" t="inlineStr">
         <is>
           <t>Bonjour Félix-Antoine Beauchemin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11879,8 +11915,8 @@
       <c r="K166" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karim Benessaieh,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -11948,8 +11984,8 @@
       <c r="K167" s="10" t="inlineStr">
         <is>
           <t>Bonjour Julia Bernier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12017,8 +12053,8 @@
       <c r="K168" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karine Boivin Forcier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12086,8 +12122,8 @@
       <c r="K169" s="10" t="inlineStr">
         <is>
           <t>Bonjour Audrey Bonaque,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12155,8 +12191,8 @@
       <c r="K170" s="10" t="inlineStr">
         <is>
           <t>Bonjour Luc Boulanger,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12224,8 +12260,8 @@
       <c r="K171" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mario Boulianne,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12293,8 +12329,8 @@
       <c r="K172" s="10" t="inlineStr">
         <is>
           <t>Bonjour Bernard Brault,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12362,8 +12398,8 @@
       <c r="K173" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre Brisson,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12431,8 +12467,8 @@
       <c r="K174" s="10" t="inlineStr">
         <is>
           <t>Bonjour Laurence Brisson Dubreuil,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12500,8 +12536,8 @@
       <c r="K175" s="10" t="inlineStr">
         <is>
           <t>Bonjour Nathaniel Bronner,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12569,8 +12605,8 @@
       <c r="K176" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-France Bélanger,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12638,8 +12674,8 @@
       <c r="K177" s="10" t="inlineStr">
         <is>
           <t>Bonjour Diane Bérard,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12707,8 +12743,8 @@
       <c r="K178" s="10" t="inlineStr">
         <is>
           <t>Bonjour Julien Cayouette,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12776,8 +12812,8 @@
       <c r="K179" s="10" t="inlineStr">
         <is>
           <t>Bonjour Rudy Chabannes,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12845,8 +12881,8 @@
       <c r="K180" s="10" t="inlineStr">
         <is>
           <t>Bonjour Denis-Martin Chabot,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12914,8 +12950,8 @@
       <c r="K181" s="10" t="inlineStr">
         <is>
           <t>Bonjour Loubna Majda Chourouk,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -12983,8 +13019,8 @@
       <c r="K182" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sarah Collardey,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13052,8 +13088,8 @@
       <c r="K183" s="10" t="inlineStr">
         <is>
           <t>Bonjour Kathleen Couillard,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13121,8 +13157,8 @@
       <c r="K184" s="10" t="inlineStr">
         <is>
           <t>Bonjour Oumou DIAKITÉ,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13190,8 +13226,8 @@
       <c r="K185" s="10" t="inlineStr">
         <is>
           <t>Bonjour Agnès Delavault,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13259,8 +13295,8 @@
       <c r="K186" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marcelin Delice,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13328,8 +13364,8 @@
       <c r="K187" s="10" t="inlineStr">
         <is>
           <t>Bonjour Alain Demers,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13397,8 +13433,8 @@
       <c r="K188" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ivanoh Demers,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13466,8 +13502,8 @@
       <c r="K189" s="10" t="inlineStr">
         <is>
           <t>Bonjour Claude Deschênes,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13535,8 +13571,8 @@
       <c r="K190" s="10" t="inlineStr">
         <is>
           <t>Bonjour Thomas Deshaies,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13604,8 +13640,8 @@
       <c r="K191" s="10" t="inlineStr">
         <is>
           <t>Bonjour Claude Desjardins,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13673,8 +13709,8 @@
       <c r="K192" s="10" t="inlineStr">
         <is>
           <t>Bonjour Martine Deslauriers,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13742,8 +13778,8 @@
       <c r="K193" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Claude Di Lillo,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13811,8 +13847,8 @@
       <c r="K194" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-René Dufort,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13880,8 +13916,8 @@
       <c r="K195" s="10" t="inlineStr">
         <is>
           <t>Bonjour Richard Dupaul,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -13949,8 +13985,8 @@
       <c r="K196" s="10" t="inlineStr">
         <is>
           <t>Bonjour Stéphanie Dupuis,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14018,8 +14054,8 @@
       <c r="K197" s="10" t="inlineStr">
         <is>
           <t>Bonjour Maxim Fauteux,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14087,8 +14123,8 @@
       <c r="K198" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ronald Georges,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14156,8 +14192,8 @@
       <c r="K199" s="10" t="inlineStr">
         <is>
           <t>Bonjour Stéphane Giroux,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14225,8 +14261,8 @@
       <c r="K200" s="10" t="inlineStr">
         <is>
           <t>Bonjour Zacharie Goudreault,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14294,8 +14330,8 @@
       <c r="K201" s="10" t="inlineStr">
         <is>
           <t>Bonjour Isabelle Grégoire,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14363,8 +14399,8 @@
       <c r="K202" s="10" t="inlineStr">
         <is>
           <t>Bonjour Chantal Guy,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14432,8 +14468,8 @@
       <c r="K203" s="10" t="inlineStr">
         <is>
           <t>Bonjour Matthieu Hains,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14557,8 +14593,8 @@
       <c r="K205" s="10" t="inlineStr">
         <is>
           <t>Bonjour ANGELO JEAN-BAPTISTE,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14626,8 +14662,8 @@
       <c r="K206" s="10" t="inlineStr">
         <is>
           <t>Bonjour Andréanne Joly,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14695,8 +14731,8 @@
       <c r="K207" s="10" t="inlineStr">
         <is>
           <t>Bonjour Hugo Joncas,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14764,8 +14800,8 @@
       <c r="K208" s="10" t="inlineStr">
         <is>
           <t>Bonjour Philémon La Frenière-Prémont,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14833,8 +14869,8 @@
       <c r="K209" s="10" t="inlineStr">
         <is>
           <t>Bonjour Henri Laban,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -14958,8 +14994,8 @@
       <c r="K211" s="10" t="inlineStr">
         <is>
           <t>Bonjour Joannie Lafrenière,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15027,8 +15063,8 @@
       <c r="K212" s="10" t="inlineStr">
         <is>
           <t>Bonjour Angie Landry,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15096,8 +15132,8 @@
       <c r="K213" s="10" t="inlineStr">
         <is>
           <t>Bonjour Camille Langlade,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15165,8 +15201,8 @@
       <c r="K214" s="10" t="inlineStr">
         <is>
           <t>Bonjour Claudia Larochelle,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15234,8 +15270,8 @@
       <c r="K215" s="10" t="inlineStr">
         <is>
           <t>Bonjour Étienne Leblanc,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15303,8 +15339,8 @@
       <c r="K216" s="10" t="inlineStr">
         <is>
           <t>Bonjour Louise Leduc,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15372,8 +15408,8 @@
       <c r="K217" s="10" t="inlineStr">
         <is>
           <t>Bonjour Guillaume Longuépée,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15441,8 +15477,8 @@
       <c r="K218" s="10" t="inlineStr">
         <is>
           <t>Bonjour Roxane Léouzon,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15510,8 +15546,8 @@
       <c r="K219" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ève Lévesque,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15579,8 +15615,8 @@
       <c r="K220" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sophie Mangado,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15648,8 +15684,8 @@
       <c r="K221" s="10" t="inlineStr">
         <is>
           <t>Bonjour Colin McGregor,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15717,8 +15753,8 @@
       <c r="K222" s="10" t="inlineStr">
         <is>
           <t>Bonjour Isabelle Morin,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15786,8 +15822,8 @@
       <c r="K223" s="10" t="inlineStr">
         <is>
           <t>Bonjour Timothy Morson,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15855,8 +15891,8 @@
       <c r="K224" s="10" t="inlineStr">
         <is>
           <t>Bonjour Rachid Najahi,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15924,8 +15960,8 @@
       <c r="K225" s="10" t="inlineStr">
         <is>
           <t>Bonjour Richard Olivier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -15993,8 +16029,8 @@
       <c r="K226" s="10" t="inlineStr">
         <is>
           <t>Bonjour MELISSA PELLETIER,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16062,8 +16098,8 @@
       <c r="K227" s="10" t="inlineStr">
         <is>
           <t>Bonjour Isaac Peltz,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16131,8 +16167,8 @@
       <c r="K228" s="10" t="inlineStr">
         <is>
           <t>Bonjour Frédéric Perron,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16200,8 +16236,8 @@
       <c r="K229" s="10" t="inlineStr">
         <is>
           <t>Bonjour Nathalie Petrowski,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16269,8 +16305,8 @@
       <c r="K230" s="10" t="inlineStr">
         <is>
           <t>Bonjour Francis Plourde,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16338,8 +16374,8 @@
       <c r="K231" s="10" t="inlineStr">
         <is>
           <t>Bonjour Raymonde Provencher,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16407,8 +16443,8 @@
       <c r="K232" s="10" t="inlineStr">
         <is>
           <t>Bonjour Richard Prudhomme,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16476,8 +16512,8 @@
       <c r="K233" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pascale Renaud,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16545,8 +16581,8 @@
       <c r="K234" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marc Sony Ricot,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16614,8 +16650,8 @@
       <c r="K235" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Paul Rouleau,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16683,8 +16719,8 @@
       <c r="K236" s="10" t="inlineStr">
         <is>
           <t>Bonjour Emmalie Ruest,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16752,8 +16788,8 @@
       <c r="K237" s="10" t="inlineStr">
         <is>
           <t>Bonjour Louis-Philippe Samson,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16821,8 +16857,8 @@
       <c r="K238" s="10" t="inlineStr">
         <is>
           <t>Bonjour Catherine Schlager,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16890,8 +16926,8 @@
       <c r="K239" s="10" t="inlineStr">
         <is>
           <t>Bonjour Olivier Schmouker,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -16959,8 +16995,8 @@
       <c r="K240" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jacques Sennechael,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17028,8 +17064,8 @@
       <c r="K241" s="10" t="inlineStr">
         <is>
           <t>Bonjour Alexandre Shields,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17097,8 +17133,8 @@
       <c r="K242" s="10" t="inlineStr">
         <is>
           <t>Bonjour Chloé Sondervorst,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17166,8 +17202,8 @@
       <c r="K243" s="10" t="inlineStr">
         <is>
           <t>Bonjour Kimberley Sullivan,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17235,8 +17271,8 @@
       <c r="K244" s="10" t="inlineStr">
         <is>
           <t>Bonjour William Thériault,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17304,8 +17340,8 @@
       <c r="K245" s="10" t="inlineStr">
         <is>
           <t>Bonjour Katia Tobar,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17373,8 +17409,8 @@
       <c r="K246" s="10" t="inlineStr">
         <is>
           <t>Bonjour Martin Tremblay,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17442,8 +17478,8 @@
       <c r="K247" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Christine Trottier,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17511,8 +17547,8 @@
       <c r="K248" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre-Luc Trudel,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17580,8 +17616,8 @@
       <c r="K249" s="10" t="inlineStr">
         <is>
           <t>Bonjour David Turbis,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17649,8 +17685,8 @@
       <c r="K250" s="10" t="inlineStr">
         <is>
           <t>Bonjour Paule Vermot-Desroches,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17718,8 +17754,8 @@
       <c r="K251" s="10" t="inlineStr">
         <is>
           <t>Bonjour Alexandra Viau,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17787,8 +17823,8 @@
       <c r="K252" s="10" t="inlineStr">
         <is>
           <t>Bonjour Raymond Viger,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17856,8 +17892,8 @@
       <c r="K253" s="10" t="inlineStr">
         <is>
           <t>Bonjour Paul Émile d'Entremont,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17925,8 +17961,8 @@
       <c r="K254" s="10" t="inlineStr">
         <is>
           <t>Bonjour Augustin de Baudinière,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -17994,8 +18030,8 @@
       <c r="K255" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ivan de Jacquelin-Dulphe,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou.
-On travaille l'asclépiade, cette plante que tout le monde connaît ici sous le nom de « petits cochons » et que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe : on la transforme en isolant, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes, vendus en ligne au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
+L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
 Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
@@ -18063,8 +18099,8 @@
       <c r="K256" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Michel Leprince,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
-Québec dont l'atelier est dans Limoilou.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
+mauvaise herbe.
 Vous couvrez l'asclépiade depuis au moins 2014 : le Téléjournal, la soie d'Amérique partie
 sur l'Everest, le pouvoir absorbant de la fibre sur les hydrocarbures, le lien avec le
 monarque. Vous avez suivi cette histoire plus longtemps que la plupart des entreprises qui
@@ -18135,8 +18171,8 @@
       <c r="K257" s="10" t="inlineStr">
         <is>
           <t>Bonjour Antoine Stab,
-Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de
-Québec dont l'atelier est dans Limoilou.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
+mauvaise herbe.
 Vous aviez écrit sur le soyer du Québec dans Espaces en février 2015, à l'époque où la fibre
 devait remplacer le duvet.
 On a démarré après la chute de cette première filière. Six ans plus tard, on achète encore de l'asclépiade québécoise, on transforme l'isolant nous-mêmes, et il

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Version 6 — la première ligne</t>
+          <t>Version 7 — ta phrase d'ouverture</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -517,189 +517,177 @@
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Le reproche</t>
+          <t>L'ouverture</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Limoilou est impertinent pour décrire l'entreprise. Un quartier ne dit rien à quelqu'un qui ne nous connaît pas, et ça brûlait la seule ligne qu'un journaliste lit à coup sûr.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="56" customHeight="1">
+          <t>« On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. » Elle porte le produit, la plante et la mission d'un seul coup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Avant</t>
+          <t>Le courriel raccourcit</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>« Je m'appelle Gabriel Gouveia et je suis le fondateur de Lasclay, une entreprise de Québec dont l'atelier est dans Limoilou. »</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="56" customHeight="1">
+          <t>Comme l'ouverture dit déjà la mission, le paragraphe « Mes 2 grandes missions » saute de toute la liste froide et des quatre contacts chauds sans historique. Zéro répétition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Maintenant</t>
+          <t>Un détail corrigé</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>« Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe. »</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Le paragraphe suivant</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Resserré aussi : l'asclépiade et les « petits cochons » arrivent en tête de phrase au lieu d'être annoncés. « On la transforme en isolant à Québec » garde le lieu là où il compte, sans le quartier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Limoilou reste</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Là où c'est une invitation — « l'atelier de Limoilou est ouvert si vous voulez voir la matière » — et dans les courriels aux journalistes de Québec, qui savent où c'est.</t>
-        </is>
-      </c>
+          <t>Les « petits cochons » sont les gousses, pas la soie. La phrase le dit maintenant dans le bon ordre : « Ses gousses, les petits cochons…, sont remplies d'une soie creuse. »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Les versions précédentes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Les versions précédentes</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Limoilou sorti de la présentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>v5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>« Invité disponible » retiré, l'asclépiade en tête des objets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v4</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>« Invité disponible » retiré, l'asclépiade en tête des objets pour 149 contacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="56" customHeight="1">
+          <t>Objets refaits : de titre d'essai à annonce datée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>v4</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Objets refaits : de titre d'essai à annonce datée.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="56" customHeight="1">
+          <t>Présentation et « pourquoi vous » dans les courriels froids.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Présentation et « pourquoi vous » dans les courriels froids.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="56" customHeight="1">
+          <t>Registre de Gabriel : plus d'excuses, plus de mise en garde, plus de confidentialité.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>Repris mot pour mot</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Registre de Gabriel : plus d'excuses, plus de mise en garde, plus de confidentialité.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Repris mot pour mot</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
           <t>Larocque et Pouliot.</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+    </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Rappels</t>
+        </is>
+      </c>
       <c r="B16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Rappels</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Diffusion</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Jeudi 17 septembre 2026, 20 h (20 h 30 NT), CBC et CBC Gem. Prévente le samedi 12 septembre à 9 h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Diffusion</t>
+          <t>Ne pas envoyer</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Jeudi 17 septembre 2026, 20 h (20 h 30 NT), CBC et CBC Gem. Prévente le samedi 12 septembre à 9 h.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="56" customHeight="1">
+          <t>Anne-Sophie Roy à l'adresse Québecor. Annie Lafrance et Francis Higgins en liste froide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Ne pas envoyer</t>
+          <t>Courriels manquants</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Anne-Sophie Roy à l'adresse Québecor. Annie Lafrance et Francis Higgins en liste froide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Courriels manquants</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Sophie Poisson, Caroline Bertrand, Karine Benoist, Antoine Stab.</t>
         </is>
@@ -788,7 +776,7 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>Brouillon v6</t>
+          <t>Brouillon v7</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
@@ -807,7 +795,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="270" customHeight="1">
+    <row r="2" ht="250" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -877,7 +865,7 @@
       <c r="M2" s="11" t="inlineStr"/>
       <c r="N2" s="11" t="inlineStr"/>
     </row>
-    <row r="3" ht="270" customHeight="1">
+    <row r="3" ht="250" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -940,7 +928,7 @@
       <c r="M3" s="11" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr"/>
     </row>
-    <row r="4" ht="270" customHeight="1">
+    <row r="4" ht="250" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1016,7 +1004,7 @@
       <c r="M4" s="11" t="inlineStr"/>
       <c r="N4" s="11" t="inlineStr"/>
     </row>
-    <row r="5" ht="270" customHeight="1">
+    <row r="5" ht="250" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1078,7 +1066,7 @@
       <c r="M5" s="11" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr"/>
     </row>
-    <row r="6" ht="270" customHeight="1">
+    <row r="6" ht="250" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1141,7 +1129,7 @@
       <c r="M6" s="11" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr"/>
     </row>
-    <row r="7" ht="270" customHeight="1">
+    <row r="7" ht="250" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1204,7 +1192,7 @@
       <c r="M7" s="11" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr"/>
     </row>
-    <row r="8" ht="270" customHeight="1">
+    <row r="8" ht="250" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1267,7 +1255,7 @@
       <c r="M8" s="11" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr"/>
     </row>
-    <row r="9" ht="270" customHeight="1">
+    <row r="9" ht="250" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1330,7 +1318,7 @@
       <c r="M9" s="11" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr"/>
     </row>
-    <row r="10" ht="270" customHeight="1">
+    <row r="10" ht="250" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1393,7 +1381,7 @@
       <c r="M10" s="11" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr"/>
     </row>
-    <row r="11" ht="270" customHeight="1">
+    <row r="11" ht="250" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1456,7 +1444,7 @@
       <c r="M11" s="11" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr"/>
     </row>
-    <row r="12" ht="270" customHeight="1">
+    <row r="12" ht="250" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1519,7 +1507,7 @@
       <c r="M12" s="11" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr"/>
     </row>
-    <row r="13" ht="270" customHeight="1">
+    <row r="13" ht="250" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1582,7 +1570,7 @@
       <c r="M13" s="11" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
     </row>
-    <row r="14" ht="270" customHeight="1">
+    <row r="14" ht="250" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1645,7 +1633,7 @@
       <c r="M14" s="11" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
     </row>
-    <row r="15" ht="270" customHeight="1">
+    <row r="15" ht="250" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1708,7 +1696,7 @@
       <c r="M15" s="11" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr"/>
     </row>
-    <row r="16" ht="270" customHeight="1">
+    <row r="16" ht="250" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1770,7 +1758,7 @@
       <c r="M16" s="11" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr"/>
     </row>
-    <row r="17" ht="270" customHeight="1">
+    <row r="17" ht="250" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1833,7 +1821,7 @@
       <c r="M17" s="11" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr"/>
     </row>
-    <row r="18" ht="270" customHeight="1">
+    <row r="18" ht="250" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1896,7 +1884,7 @@
       <c r="M18" s="11" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr"/>
     </row>
-    <row r="19" ht="270" customHeight="1">
+    <row r="19" ht="250" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1959,7 +1947,7 @@
       <c r="M19" s="11" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr"/>
     </row>
-    <row r="20" ht="270" customHeight="1">
+    <row r="20" ht="250" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2022,7 +2010,7 @@
       <c r="M20" s="11" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr"/>
     </row>
-    <row r="21" ht="270" customHeight="1">
+    <row r="21" ht="250" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2085,7 +2073,7 @@
       <c r="M21" s="11" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr"/>
     </row>
-    <row r="22" ht="270" customHeight="1">
+    <row r="22" ht="250" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2148,7 +2136,7 @@
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr"/>
     </row>
-    <row r="23" ht="270" customHeight="1">
+    <row r="23" ht="250" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2211,7 +2199,7 @@
       <c r="M23" s="11" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr"/>
     </row>
-    <row r="24" ht="270" customHeight="1">
+    <row r="24" ht="250" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2274,7 +2262,7 @@
       <c r="M24" s="11" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr"/>
     </row>
-    <row r="25" ht="270" customHeight="1">
+    <row r="25" ht="250" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2337,7 +2325,7 @@
       <c r="M25" s="11" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr"/>
     </row>
-    <row r="26" ht="270" customHeight="1">
+    <row r="26" ht="250" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2393,7 +2381,7 @@
       <c r="M26" s="11" t="inlineStr"/>
       <c r="N26" s="11" t="inlineStr"/>
     </row>
-    <row r="27" ht="270" customHeight="1">
+    <row r="27" ht="250" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2456,7 +2444,7 @@
       <c r="M27" s="11" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr"/>
     </row>
-    <row r="28" ht="270" customHeight="1">
+    <row r="28" ht="250" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2511,7 +2499,7 @@
       <c r="M28" s="11" t="inlineStr"/>
       <c r="N28" s="11" t="inlineStr"/>
     </row>
-    <row r="29" ht="270" customHeight="1">
+    <row r="29" ht="250" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2553,8 +2541,7 @@
       <c r="K29" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Roberge,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe : l'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe, qu'on transforme en isolant à Québec.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part : je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -2566,7 +2553,7 @@
       <c r="M29" s="11" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr"/>
     </row>
-    <row r="30" ht="270" customHeight="1">
+    <row r="30" ht="250" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2608,8 +2595,7 @@
       <c r="K30" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Laforest,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe : l'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe, qu'on transforme en isolant à Québec.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part : je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -2621,7 +2607,7 @@
       <c r="M30" s="11" t="inlineStr"/>
       <c r="N30" s="11" t="inlineStr"/>
     </row>
-    <row r="31" ht="270" customHeight="1">
+    <row r="31" ht="250" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2684,7 +2670,7 @@
       <c r="M31" s="11" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr"/>
     </row>
-    <row r="32" ht="270" customHeight="1">
+    <row r="32" ht="250" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2739,7 +2725,7 @@
       <c r="M32" s="11" t="inlineStr"/>
       <c r="N32" s="11" t="inlineStr"/>
     </row>
-    <row r="33" ht="270" customHeight="1">
+    <row r="33" ht="250" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2794,7 +2780,7 @@
       <c r="M33" s="11" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr"/>
     </row>
-    <row r="34" ht="270" customHeight="1">
+    <row r="34" ht="250" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2836,8 +2822,7 @@
       <c r="K34" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Goubau,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe. Vous couvrez le textile et la mode, alors voici une matière que peu de gens ont vue de près : la soie d'asclépiade, une fibre creuse et naturellement hydrophobe attachée aux graines d'une plante que les agriculteurs arrachent de leurs champs depuis 50 ans. On la transforme en isolant, et on en fait des manteaux, des mitaines et des tuques.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Vous couvrez le textile et la mode, alors voici une matière que peu de gens ont vue de près : la soie d'asclépiade, une fibre creuse et naturellement hydrophobe attachée aux graines d'une plante que les agriculteurs arrachent de leurs champs depuis 50 ans. On la transforme en isolant, et on en fait des manteaux, des mitaines et des tuques.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet.
@@ -2849,7 +2834,7 @@
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr"/>
     </row>
-    <row r="35" ht="270" customHeight="1">
+    <row r="35" ht="250" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2891,8 +2876,7 @@
       <c r="K35" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Dostie,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe : l'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans. La soie attachée à ses graines est creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe, qu'on transforme en isolant à Québec.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet.
@@ -2904,7 +2888,7 @@
       <c r="M35" s="11" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr"/>
     </row>
-    <row r="36" ht="270" customHeight="1">
+    <row r="36" ht="250" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2963,7 +2947,7 @@
       <c r="M36" s="11" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr"/>
     </row>
-    <row r="37" ht="270" customHeight="1">
+    <row r="37" ht="250" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -3022,7 +3006,7 @@
       <c r="M37" s="11" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr"/>
     </row>
-    <row r="38" ht="270" customHeight="1">
+    <row r="38" ht="250" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -3081,7 +3065,7 @@
       <c r="M38" s="11" t="inlineStr"/>
       <c r="N38" s="11" t="inlineStr"/>
     </row>
-    <row r="39" ht="270" customHeight="1">
+    <row r="39" ht="250" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3135,15 +3119,15 @@
       <c r="K39" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie Allard,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
-mauvaise herbe.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une
+mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et
+menacé : le papillon monarque.
 Il y a une belle histoire de sciences dans l'asclépiade. La soie attachée à ses graines n'est
 pas un poil : c'est un tube creux enduit d'une cire hydrophobe, et les fibres portent une
 charge qui les fait se repousser. C'est ce qui forme le parachute autour de la graine, et
 c'est ce qui emprisonne l'air. Chaque follicule en produit plus de 200.
-On en fait de l'isolant pour des manteaux et des mitaines. Mes 2 grandes missions : faire
-connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade, parce
-que c'est la seule plante que leurs chenilles peuvent manger.
+On en fait de l'isolant pour des manteaux et des mitaines. Et c'est la seule plante que les
+chenilles du monarque peuvent manger, ce qui est toute la raison d'être de l'entreprise.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet. L'atelier de
@@ -3156,7 +3140,7 @@
       <c r="M39" s="11" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr"/>
     </row>
-    <row r="40" ht="270" customHeight="1">
+    <row r="40" ht="250" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3210,9 +3194,8 @@
       <c r="K40" s="10" t="inlineStr">
         <is>
           <t>Bonjour Zoé Allemand,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3225,7 +3208,7 @@
       <c r="M40" s="11" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr"/>
     </row>
-    <row r="41" ht="270" customHeight="1">
+    <row r="41" ht="250" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3279,9 +3262,8 @@
       <c r="K41" s="10" t="inlineStr">
         <is>
           <t>Bonjour Victoria Bakos,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3294,7 +3276,7 @@
       <c r="M41" s="11" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr"/>
     </row>
-    <row r="42" ht="270" customHeight="1">
+    <row r="42" ht="250" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3348,9 +3330,8 @@
       <c r="K42" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Émélie Bernier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3363,7 +3344,7 @@
       <c r="M42" s="11" t="inlineStr"/>
       <c r="N42" s="11" t="inlineStr"/>
     </row>
-    <row r="43" ht="270" customHeight="1">
+    <row r="43" ht="250" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3417,9 +3398,8 @@
       <c r="K43" s="10" t="inlineStr">
         <is>
           <t>Bonjour Normand Blouin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3432,7 +3412,7 @@
       <c r="M43" s="11" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr"/>
     </row>
-    <row r="44" ht="270" customHeight="1">
+    <row r="44" ht="250" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3486,9 +3466,8 @@
       <c r="K44" s="10" t="inlineStr">
         <is>
           <t>Bonjour Louise Bourbonnais,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3501,7 +3480,7 @@
       <c r="M44" s="11" t="inlineStr"/>
       <c r="N44" s="11" t="inlineStr"/>
     </row>
-    <row r="45" ht="270" customHeight="1">
+    <row r="45" ht="250" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3555,9 +3534,8 @@
       <c r="K45" s="10" t="inlineStr">
         <is>
           <t>Bonjour Francois Bourque,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3570,7 +3548,7 @@
       <c r="M45" s="11" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr"/>
     </row>
-    <row r="46" ht="270" customHeight="1">
+    <row r="46" ht="250" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3624,9 +3602,8 @@
       <c r="K46" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ariane Boyer,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3639,7 +3616,7 @@
       <c r="M46" s="11" t="inlineStr"/>
       <c r="N46" s="11" t="inlineStr"/>
     </row>
-    <row r="47" ht="270" customHeight="1">
+    <row r="47" ht="250" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3693,9 +3670,8 @@
       <c r="K47" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gilbert Bégin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3708,7 +3684,7 @@
       <c r="M47" s="11" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr"/>
     </row>
-    <row r="48" ht="270" customHeight="1">
+    <row r="48" ht="250" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3762,9 +3738,8 @@
       <c r="K48" s="10" t="inlineStr">
         <is>
           <t>Bonjour Papa Moussa Camara,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3777,7 +3752,7 @@
       <c r="M48" s="11" t="inlineStr"/>
       <c r="N48" s="11" t="inlineStr"/>
     </row>
-    <row r="49" ht="270" customHeight="1">
+    <row r="49" ht="250" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3831,9 +3806,8 @@
       <c r="K49" s="10" t="inlineStr">
         <is>
           <t>Bonjour Victor Carré,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3846,7 +3820,7 @@
       <c r="M49" s="11" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr"/>
     </row>
-    <row r="50" ht="270" customHeight="1">
+    <row r="50" ht="250" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3900,9 +3874,8 @@
       <c r="K50" s="10" t="inlineStr">
         <is>
           <t>Bonjour Eric Chabot,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3915,7 +3888,7 @@
       <c r="M50" s="11" t="inlineStr"/>
       <c r="N50" s="11" t="inlineStr"/>
     </row>
-    <row r="51" ht="270" customHeight="1">
+    <row r="51" ht="250" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3969,9 +3942,8 @@
       <c r="K51" s="10" t="inlineStr">
         <is>
           <t>Bonjour Tristan Champagne-Lessard,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3984,7 +3956,7 @@
       <c r="M51" s="11" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr"/>
     </row>
-    <row r="52" ht="270" customHeight="1">
+    <row r="52" ht="250" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4038,9 +4010,8 @@
       <c r="K52" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Marc Chevalier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4053,7 +4024,7 @@
       <c r="M52" s="11" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr"/>
     </row>
-    <row r="53" ht="270" customHeight="1">
+    <row r="53" ht="250" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4107,9 +4078,8 @@
       <c r="K53" s="10" t="inlineStr">
         <is>
           <t>Bonjour Simon Chrétien,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4122,7 +4092,7 @@
       <c r="M53" s="11" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr"/>
     </row>
-    <row r="54" ht="270" customHeight="1">
+    <row r="54" ht="250" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4176,9 +4146,8 @@
       <c r="K54" s="10" t="inlineStr">
         <is>
           <t>Bonjour Maxime Corneau,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4191,7 +4160,7 @@
       <c r="M54" s="11" t="inlineStr"/>
       <c r="N54" s="11" t="inlineStr"/>
     </row>
-    <row r="55" ht="270" customHeight="1">
+    <row r="55" ht="250" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4245,9 +4214,8 @@
       <c r="K55" s="10" t="inlineStr">
         <is>
           <t>Bonjour Aurélia Crémoux,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4260,7 +4228,7 @@
       <c r="M55" s="11" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr"/>
     </row>
-    <row r="56" ht="270" customHeight="1">
+    <row r="56" ht="250" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4314,9 +4282,8 @@
       <c r="K56" s="10" t="inlineStr">
         <is>
           <t>Bonjour Catherine Dallaire,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4329,7 +4296,7 @@
       <c r="M56" s="11" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr"/>
     </row>
-    <row r="57" ht="270" customHeight="1">
+    <row r="57" ht="250" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4383,14 +4350,13 @@
       <c r="K57" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gabriel Delisle,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
-mauvaise herbe.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une
+mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et
+menacé : le papillon monarque.
 L'asclépiade a été une histoire mauricienne avant d'être la nôtre : l'usine de Saint-Tite
 achetait 90 % des récoltes du Québec. On a démarré après la chute de cette filière, et six ans
 plus tard on achète encore de l'asclépiade québécoise et on la
 transforme nous-mêmes à Québec.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la
-culture de l'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet : huit ans après
@@ -4403,7 +4369,7 @@
       <c r="M57" s="11" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr"/>
     </row>
-    <row r="58" ht="270" customHeight="1">
+    <row r="58" ht="250" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4457,9 +4423,8 @@
       <c r="K58" s="10" t="inlineStr">
         <is>
           <t>Bonjour Anaïs Desjardins,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4472,7 +4437,7 @@
       <c r="M58" s="11" t="inlineStr"/>
       <c r="N58" s="11" t="inlineStr"/>
     </row>
-    <row r="59" ht="270" customHeight="1">
+    <row r="59" ht="250" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4526,9 +4491,8 @@
       <c r="K59" s="10" t="inlineStr">
         <is>
           <t>Bonjour Simon Dominé,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4541,7 +4505,7 @@
       <c r="M59" s="11" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr"/>
     </row>
-    <row r="60" ht="270" customHeight="1">
+    <row r="60" ht="250" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4595,9 +4559,8 @@
       <c r="K60" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karl-Ivann Dubé,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4610,7 +4573,7 @@
       <c r="M60" s="11" t="inlineStr"/>
       <c r="N60" s="11" t="inlineStr"/>
     </row>
-    <row r="61" ht="270" customHeight="1">
+    <row r="61" ht="250" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4664,9 +4627,8 @@
       <c r="K61" s="10" t="inlineStr">
         <is>
           <t>Bonjour André Fauteux,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4679,7 +4641,7 @@
       <c r="M61" s="11" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr"/>
     </row>
-    <row r="62" ht="270" customHeight="1">
+    <row r="62" ht="250" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4733,9 +4695,8 @@
       <c r="K62" s="10" t="inlineStr">
         <is>
           <t>Bonjour Myriam Fimbry,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4748,7 +4709,7 @@
       <c r="M62" s="11" t="inlineStr"/>
       <c r="N62" s="11" t="inlineStr"/>
     </row>
-    <row r="63" ht="270" customHeight="1">
+    <row r="63" ht="250" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4802,9 +4763,8 @@
       <c r="K63" s="10" t="inlineStr">
         <is>
           <t>Bonjour Étienne Fortin-Gauthier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4817,7 +4777,7 @@
       <c r="M63" s="11" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr"/>
     </row>
-    <row r="64" ht="270" customHeight="1">
+    <row r="64" ht="250" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4871,9 +4831,8 @@
       <c r="K64" s="10" t="inlineStr">
         <is>
           <t>Bonjour Johanne Fournier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4886,7 +4845,7 @@
       <c r="M64" s="11" t="inlineStr"/>
       <c r="N64" s="11" t="inlineStr"/>
     </row>
-    <row r="65" ht="270" customHeight="1">
+    <row r="65" ht="250" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4940,9 +4899,8 @@
       <c r="K65" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean Garon,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4955,7 +4913,7 @@
       <c r="M65" s="11" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr"/>
     </row>
-    <row r="66" ht="270" customHeight="1">
+    <row r="66" ht="250" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5009,9 +4967,8 @@
       <c r="K66" s="10" t="inlineStr">
         <is>
           <t>Bonjour Cécile Gladel,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5024,7 +4981,7 @@
       <c r="M66" s="11" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr"/>
     </row>
-    <row r="67" ht="270" customHeight="1">
+    <row r="67" ht="250" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5078,9 +5035,8 @@
       <c r="K67" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marieke Glorieux-Stryckman,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5093,7 +5049,7 @@
       <c r="M67" s="11" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr"/>
     </row>
-    <row r="68" ht="270" customHeight="1">
+    <row r="68" ht="250" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5147,9 +5103,8 @@
       <c r="K68" s="10" t="inlineStr">
         <is>
           <t>Bonjour Maude Goyer,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5162,7 +5117,7 @@
       <c r="M68" s="11" t="inlineStr"/>
       <c r="N68" s="11" t="inlineStr"/>
     </row>
-    <row r="69" ht="270" customHeight="1">
+    <row r="69" ht="250" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5216,9 +5171,8 @@
       <c r="K69" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pauline Gravel,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5231,7 +5185,7 @@
       <c r="M69" s="11" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr"/>
     </row>
-    <row r="70" ht="270" customHeight="1">
+    <row r="70" ht="250" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5285,9 +5239,8 @@
       <c r="K70" s="10" t="inlineStr">
         <is>
           <t>Bonjour Bernard Hervieux,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5300,7 +5253,7 @@
       <c r="M70" s="11" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr"/>
     </row>
-    <row r="71" ht="270" customHeight="1">
+    <row r="71" ht="250" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5354,9 +5307,8 @@
       <c r="K71" s="10" t="inlineStr">
         <is>
           <t>Bonjour Leïla Jolin-Dahel,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5369,7 +5321,7 @@
       <c r="M71" s="11" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr"/>
     </row>
-    <row r="72" ht="270" customHeight="1">
+    <row r="72" ht="250" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5423,9 +5375,8 @@
       <c r="K72" s="10" t="inlineStr">
         <is>
           <t>Bonjour Kodjo Edjinam Nulagnon LOGO,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5438,7 +5389,7 @@
       <c r="M72" s="11" t="inlineStr"/>
       <c r="N72" s="11" t="inlineStr"/>
     </row>
-    <row r="73" ht="270" customHeight="1">
+    <row r="73" ht="250" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5492,9 +5443,8 @@
       <c r="K73" s="10" t="inlineStr">
         <is>
           <t>Bonjour Annie Labrecque,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5507,7 +5457,7 @@
       <c r="M73" s="11" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr"/>
     </row>
-    <row r="74" ht="270" customHeight="1">
+    <row r="74" ht="250" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5561,9 +5511,8 @@
       <c r="K74" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marianne Lachapelle,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5576,7 +5525,7 @@
       <c r="M74" s="11" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr"/>
     </row>
-    <row r="75" ht="270" customHeight="1">
+    <row r="75" ht="250" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5630,9 +5579,8 @@
       <c r="K75" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sophie Lachapelle,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5645,7 +5593,7 @@
       <c r="M75" s="11" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr"/>
     </row>
-    <row r="76" ht="270" customHeight="1">
+    <row r="76" ht="250" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5699,9 +5647,8 @@
       <c r="K76" s="10" t="inlineStr">
         <is>
           <t>Bonjour Alain Laforest,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5714,7 +5661,7 @@
       <c r="M76" s="11" t="inlineStr"/>
       <c r="N76" s="11" t="inlineStr"/>
     </row>
-    <row r="77" ht="270" customHeight="1">
+    <row r="77" ht="250" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5768,9 +5715,8 @@
       <c r="K77" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mikaël Lalancette,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5783,7 +5729,7 @@
       <c r="M77" s="11" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr"/>
     </row>
-    <row r="78" ht="270" customHeight="1">
+    <row r="78" ht="250" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5837,9 +5783,8 @@
       <c r="K78" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Luc Lavallée,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5852,7 +5797,7 @@
       <c r="M78" s="11" t="inlineStr"/>
       <c r="N78" s="11" t="inlineStr"/>
     </row>
-    <row r="79" ht="270" customHeight="1">
+    <row r="79" ht="250" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5906,9 +5851,8 @@
       <c r="K79" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Francois Leblanc,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5921,7 +5865,7 @@
       <c r="M79" s="11" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr"/>
     </row>
-    <row r="80" ht="270" customHeight="1">
+    <row r="80" ht="250" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5975,9 +5919,8 @@
       <c r="K80" s="10" t="inlineStr">
         <is>
           <t>Bonjour Julie Leduc,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5990,7 +5933,7 @@
       <c r="M80" s="11" t="inlineStr"/>
       <c r="N80" s="11" t="inlineStr"/>
     </row>
-    <row r="81" ht="270" customHeight="1">
+    <row r="81" ht="250" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6044,9 +5987,8 @@
       <c r="K81" s="10" t="inlineStr">
         <is>
           <t>Bonjour Annie Martin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6059,7 +6001,7 @@
       <c r="M81" s="11" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr"/>
     </row>
-    <row r="82" ht="270" customHeight="1">
+    <row r="82" ht="250" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6113,14 +6055,14 @@
       <c r="K82" s="10" t="inlineStr">
         <is>
           <t>Bonjour Réjean Martin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
-mauvaise herbe.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une
+mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et
+menacé : le papillon monarque.
 Vous couvrez Mékinac, donc Saint-Tite, donc l'endroit où l'asclépiade a eu son grand moment
 industriel au Québec. L'usine achetait 90 % des récoltes de la province avant que la filière
 se casse en 2018.
 On a démarré après. Six ans plus tard, on achète encore de l'asclépiade québécoise et on la
-transforme nous-mêmes à Québec. Mes 2 grandes missions : faire connaître
-l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+transforme nous-mêmes à Québec.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Je voulais vous en faire part parce que vos lecteurs ont vu la promesse de l'asclépiade de
@@ -6134,7 +6076,7 @@
       <c r="M82" s="11" t="inlineStr"/>
       <c r="N82" s="11" t="inlineStr"/>
     </row>
-    <row r="83" ht="270" customHeight="1">
+    <row r="83" ht="250" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6188,9 +6130,8 @@
       <c r="K83" s="10" t="inlineStr">
         <is>
           <t>Bonjour Charles Mathieu,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6203,7 +6144,7 @@
       <c r="M83" s="11" t="inlineStr"/>
       <c r="N83" s="11" t="inlineStr"/>
     </row>
-    <row r="84" ht="270" customHeight="1">
+    <row r="84" ht="250" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6257,9 +6198,8 @@
       <c r="K84" s="10" t="inlineStr">
         <is>
           <t>Bonjour Clara Matthey-Jonais,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6272,7 +6212,7 @@
       <c r="M84" s="11" t="inlineStr"/>
       <c r="N84" s="11" t="inlineStr"/>
     </row>
-    <row r="85" ht="270" customHeight="1">
+    <row r="85" ht="250" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6326,9 +6266,8 @@
       <c r="K85" s="10" t="inlineStr">
         <is>
           <t>Bonjour Valérian Mazataud,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6341,7 +6280,7 @@
       <c r="M85" s="11" t="inlineStr"/>
       <c r="N85" s="11" t="inlineStr"/>
     </row>
-    <row r="86" ht="270" customHeight="1">
+    <row r="86" ht="250" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6395,9 +6334,8 @@
       <c r="K86" s="10" t="inlineStr">
         <is>
           <t>Bonjour Lili Mercure,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6410,7 +6348,7 @@
       <c r="M86" s="11" t="inlineStr"/>
       <c r="N86" s="11" t="inlineStr"/>
     </row>
-    <row r="87" ht="270" customHeight="1">
+    <row r="87" ht="250" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6464,9 +6402,8 @@
       <c r="K87" s="10" t="inlineStr">
         <is>
           <t>Bonjour Nicolas Mesly,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6479,7 +6416,7 @@
       <c r="M87" s="11" t="inlineStr"/>
       <c r="N87" s="11" t="inlineStr"/>
     </row>
-    <row r="88" ht="270" customHeight="1">
+    <row r="88" ht="250" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6533,9 +6470,8 @@
       <c r="K88" s="10" t="inlineStr">
         <is>
           <t>Bonjour Nicolas Michaud,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6548,7 +6484,7 @@
       <c r="M88" s="11" t="inlineStr"/>
       <c r="N88" s="11" t="inlineStr"/>
     </row>
-    <row r="89" ht="270" customHeight="1">
+    <row r="89" ht="250" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6602,9 +6538,8 @@
       <c r="K89" s="10" t="inlineStr">
         <is>
           <t>Bonjour Véronique Morin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6617,7 +6552,7 @@
       <c r="M89" s="11" t="inlineStr"/>
       <c r="N89" s="11" t="inlineStr"/>
     </row>
-    <row r="90" ht="270" customHeight="1">
+    <row r="90" ht="250" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6671,9 +6606,8 @@
       <c r="K90" s="10" t="inlineStr">
         <is>
           <t>Bonjour Lila Mouch,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6686,7 +6620,7 @@
       <c r="M90" s="11" t="inlineStr"/>
       <c r="N90" s="11" t="inlineStr"/>
     </row>
-    <row r="91" ht="270" customHeight="1">
+    <row r="91" ht="250" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6740,9 +6674,8 @@
       <c r="K91" s="10" t="inlineStr">
         <is>
           <t>Bonjour Olivier Mougeot,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6755,7 +6688,7 @@
       <c r="M91" s="11" t="inlineStr"/>
       <c r="N91" s="11" t="inlineStr"/>
     </row>
-    <row r="92" ht="270" customHeight="1">
+    <row r="92" ht="250" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6809,9 +6742,8 @@
       <c r="K92" s="10" t="inlineStr">
         <is>
           <t>Bonjour Emmanuelle Mozayan-Verschaeve,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6824,7 +6756,7 @@
       <c r="M92" s="11" t="inlineStr"/>
       <c r="N92" s="11" t="inlineStr"/>
     </row>
-    <row r="93" ht="270" customHeight="1">
+    <row r="93" ht="250" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6878,9 +6810,8 @@
       <c r="K93" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Benoît Nadeau,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6893,7 +6824,7 @@
       <c r="M93" s="11" t="inlineStr"/>
       <c r="N93" s="11" t="inlineStr"/>
     </row>
-    <row r="94" ht="270" customHeight="1">
+    <row r="94" ht="250" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -6947,9 +6878,8 @@
       <c r="K94" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yves Ouellet,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -6962,7 +6892,7 @@
       <c r="M94" s="11" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr"/>
     </row>
-    <row r="95" ht="270" customHeight="1">
+    <row r="95" ht="250" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7016,9 +6946,8 @@
       <c r="K95" s="10" t="inlineStr">
         <is>
           <t>Bonjour Josée Panet-Raymond,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7031,7 +6960,7 @@
       <c r="M95" s="11" t="inlineStr"/>
       <c r="N95" s="11" t="inlineStr"/>
     </row>
-    <row r="96" ht="270" customHeight="1">
+    <row r="96" ht="250" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7085,9 +7014,8 @@
       <c r="K96" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yannick Patelli,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7100,7 +7028,7 @@
       <c r="M96" s="11" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr"/>
     </row>
-    <row r="97" ht="270" customHeight="1">
+    <row r="97" ht="250" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7154,9 +7082,8 @@
       <c r="K97" s="10" t="inlineStr">
         <is>
           <t>Bonjour Félix Pedneault,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7169,7 +7096,7 @@
       <c r="M97" s="11" t="inlineStr"/>
       <c r="N97" s="11" t="inlineStr"/>
     </row>
-    <row r="98" ht="270" customHeight="1">
+    <row r="98" ht="250" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7223,9 +7150,8 @@
       <c r="K98" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Eve Poulin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7238,7 +7164,7 @@
       <c r="M98" s="11" t="inlineStr"/>
       <c r="N98" s="11" t="inlineStr"/>
     </row>
-    <row r="99" ht="270" customHeight="1">
+    <row r="99" ht="250" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7292,9 +7218,8 @@
       <c r="K99" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Hélène Proulx,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7307,7 +7232,7 @@
       <c r="M99" s="11" t="inlineStr"/>
       <c r="N99" s="11" t="inlineStr"/>
     </row>
-    <row r="100" ht="270" customHeight="1">
+    <row r="100" ht="250" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7361,9 +7286,8 @@
       <c r="K100" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Hugues Roy,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7376,7 +7300,7 @@
       <c r="M100" s="11" t="inlineStr"/>
       <c r="N100" s="11" t="inlineStr"/>
     </row>
-    <row r="101" ht="270" customHeight="1">
+    <row r="101" ht="250" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7430,9 +7354,8 @@
       <c r="K101" s="10" t="inlineStr">
         <is>
           <t>Bonjour Martin Roy,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7445,7 +7368,7 @@
       <c r="M101" s="11" t="inlineStr"/>
       <c r="N101" s="11" t="inlineStr"/>
     </row>
-    <row r="102" ht="270" customHeight="1">
+    <row r="102" ht="250" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7499,9 +7422,8 @@
       <c r="K102" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sylvain Sarrazin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7514,7 +7436,7 @@
       <c r="M102" s="11" t="inlineStr"/>
       <c r="N102" s="11" t="inlineStr"/>
     </row>
-    <row r="103" ht="270" customHeight="1">
+    <row r="103" ht="250" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7568,9 +7490,8 @@
       <c r="K103" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre Sormany,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7583,7 +7504,7 @@
       <c r="M103" s="11" t="inlineStr"/>
       <c r="N103" s="11" t="inlineStr"/>
     </row>
-    <row r="104" ht="270" customHeight="1">
+    <row r="104" ht="250" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7637,9 +7558,8 @@
       <c r="K104" s="10" t="inlineStr">
         <is>
           <t>Bonjour Scott Stevenson,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7652,7 +7572,7 @@
       <c r="M104" s="11" t="inlineStr"/>
       <c r="N104" s="11" t="inlineStr"/>
     </row>
-    <row r="105" ht="270" customHeight="1">
+    <row r="105" ht="250" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7706,9 +7626,8 @@
       <c r="K105" s="10" t="inlineStr">
         <is>
           <t>Bonjour Michèle Tanganika,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7721,7 +7640,7 @@
       <c r="M105" s="11" t="inlineStr"/>
       <c r="N105" s="11" t="inlineStr"/>
     </row>
-    <row r="106" ht="270" customHeight="1">
+    <row r="106" ht="250" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7775,9 +7694,8 @@
       <c r="K106" s="10" t="inlineStr">
         <is>
           <t>Bonjour Stephane Tellier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7790,7 +7708,7 @@
       <c r="M106" s="11" t="inlineStr"/>
       <c r="N106" s="11" t="inlineStr"/>
     </row>
-    <row r="107" ht="270" customHeight="1">
+    <row r="107" ht="250" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7844,9 +7762,8 @@
       <c r="K107" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karine Tremblay,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7859,7 +7776,7 @@
       <c r="M107" s="11" t="inlineStr"/>
       <c r="N107" s="11" t="inlineStr"/>
     </row>
-    <row r="108" ht="270" customHeight="1">
+    <row r="108" ht="250" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7913,9 +7830,8 @@
       <c r="K108" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Francois Venne,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7928,7 +7844,7 @@
       <c r="M108" s="11" t="inlineStr"/>
       <c r="N108" s="11" t="inlineStr"/>
     </row>
-    <row r="109" ht="270" customHeight="1">
+    <row r="109" ht="250" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -7982,9 +7898,8 @@
       <c r="K109" s="10" t="inlineStr">
         <is>
           <t>Bonjour Shahram Yazdanpanah,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -7997,7 +7912,7 @@
       <c r="M109" s="11" t="inlineStr"/>
       <c r="N109" s="11" t="inlineStr"/>
     </row>
-    <row r="110" ht="270" customHeight="1">
+    <row r="110" ht="250" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8051,9 +7966,8 @@
       <c r="K110" s="10" t="inlineStr">
         <is>
           <t>Bonjour Malika Alaoui,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8066,7 +7980,7 @@
       <c r="M110" s="11" t="inlineStr"/>
       <c r="N110" s="11" t="inlineStr"/>
     </row>
-    <row r="111" ht="270" customHeight="1">
+    <row r="111" ht="250" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8120,9 +8034,8 @@
       <c r="K111" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yahia Arkat,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8135,7 +8048,7 @@
       <c r="M111" s="11" t="inlineStr"/>
       <c r="N111" s="11" t="inlineStr"/>
     </row>
-    <row r="112" ht="270" customHeight="1">
+    <row r="112" ht="250" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8189,9 +8102,8 @@
       <c r="K112" s="10" t="inlineStr">
         <is>
           <t>Bonjour MARC-OLIVIER BISSON,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8204,7 +8116,7 @@
       <c r="M112" s="11" t="inlineStr"/>
       <c r="N112" s="11" t="inlineStr"/>
     </row>
-    <row r="113" ht="270" customHeight="1">
+    <row r="113" ht="250" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8258,9 +8170,8 @@
       <c r="K113" s="10" t="inlineStr">
         <is>
           <t>Bonjour Maïté Belmir,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8273,7 +8184,7 @@
       <c r="M113" s="11" t="inlineStr"/>
       <c r="N113" s="11" t="inlineStr"/>
     </row>
-    <row r="114" ht="270" customHeight="1">
+    <row r="114" ht="250" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8327,9 +8238,8 @@
       <c r="K114" s="10" t="inlineStr">
         <is>
           <t>Bonjour André Bernard,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8342,7 +8252,7 @@
       <c r="M114" s="11" t="inlineStr"/>
       <c r="N114" s="11" t="inlineStr"/>
     </row>
-    <row r="115" ht="270" customHeight="1">
+    <row r="115" ht="250" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8396,9 +8306,8 @@
       <c r="K115" s="10" t="inlineStr">
         <is>
           <t>Bonjour Didier Bert,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8411,7 +8320,7 @@
       <c r="M115" s="11" t="inlineStr"/>
       <c r="N115" s="11" t="inlineStr"/>
     </row>
-    <row r="116" ht="270" customHeight="1">
+    <row r="116" ht="250" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8465,9 +8374,8 @@
       <c r="K116" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sophie-Andrée Blondin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8480,7 +8388,7 @@
       <c r="M116" s="11" t="inlineStr"/>
       <c r="N116" s="11" t="inlineStr"/>
     </row>
-    <row r="117" ht="270" customHeight="1">
+    <row r="117" ht="250" customHeight="1">
       <c r="A117" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8534,9 +8442,8 @@
       <c r="K117" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre Brochu,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8549,7 +8456,7 @@
       <c r="M117" s="11" t="inlineStr"/>
       <c r="N117" s="11" t="inlineStr"/>
     </row>
-    <row r="118" ht="270" customHeight="1">
+    <row r="118" ht="250" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8603,9 +8510,8 @@
       <c r="K118" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gilles Bérubé,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8618,7 +8524,7 @@
       <c r="M118" s="11" t="inlineStr"/>
       <c r="N118" s="11" t="inlineStr"/>
     </row>
-    <row r="119" ht="270" customHeight="1">
+    <row r="119" ht="250" customHeight="1">
       <c r="A119" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8672,9 +8578,8 @@
       <c r="K119" s="10" t="inlineStr">
         <is>
           <t>Bonjour Daphné Cameron,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8687,7 +8592,7 @@
       <c r="M119" s="11" t="inlineStr"/>
       <c r="N119" s="11" t="inlineStr"/>
     </row>
-    <row r="120" ht="270" customHeight="1">
+    <row r="120" ht="250" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8741,9 +8646,8 @@
       <c r="K120" s="10" t="inlineStr">
         <is>
           <t>Bonjour Godefroy Macaire Chabi,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8756,7 +8660,7 @@
       <c r="M120" s="11" t="inlineStr"/>
       <c r="N120" s="11" t="inlineStr"/>
     </row>
-    <row r="121" ht="270" customHeight="1">
+    <row r="121" ht="250" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8810,9 +8714,8 @@
       <c r="K121" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sara Champagne,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8825,7 +8728,7 @@
       <c r="M121" s="11" t="inlineStr"/>
       <c r="N121" s="11" t="inlineStr"/>
     </row>
-    <row r="122" ht="270" customHeight="1">
+    <row r="122" ht="250" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8879,9 +8782,8 @@
       <c r="K122" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sarah Champagne,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8894,7 +8796,7 @@
       <c r="M122" s="11" t="inlineStr"/>
       <c r="N122" s="11" t="inlineStr"/>
     </row>
-    <row r="123" ht="270" customHeight="1">
+    <row r="123" ht="250" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -8948,9 +8850,8 @@
       <c r="K123" s="10" t="inlineStr">
         <is>
           <t>Bonjour Éric-Pierre Champagne,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -8963,7 +8864,7 @@
       <c r="M123" s="11" t="inlineStr"/>
       <c r="N123" s="11" t="inlineStr"/>
     </row>
-    <row r="124" ht="270" customHeight="1">
+    <row r="124" ht="250" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9017,9 +8918,8 @@
       <c r="K124" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marine Corniou,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9032,7 +8932,7 @@
       <c r="M124" s="11" t="inlineStr"/>
       <c r="N124" s="11" t="inlineStr"/>
     </row>
-    <row r="125" ht="270" customHeight="1">
+    <row r="125" ht="250" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9086,9 +8986,8 @@
       <c r="K125" s="10" t="inlineStr">
         <is>
           <t>Bonjour Catherine Crépeau,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9101,7 +9000,7 @@
       <c r="M125" s="11" t="inlineStr"/>
       <c r="N125" s="11" t="inlineStr"/>
     </row>
-    <row r="126" ht="270" customHeight="1">
+    <row r="126" ht="250" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9155,9 +9054,8 @@
       <c r="K126" s="10" t="inlineStr">
         <is>
           <t>Bonjour Laurence Dami-Houle,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9170,7 +9068,7 @@
       <c r="M126" s="11" t="inlineStr"/>
       <c r="N126" s="11" t="inlineStr"/>
     </row>
-    <row r="127" ht="270" customHeight="1">
+    <row r="127" ht="250" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9224,9 +9122,8 @@
       <c r="K127" s="10" t="inlineStr">
         <is>
           <t>Bonjour Amélie Daoust-Boisvert,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9239,7 +9136,7 @@
       <c r="M127" s="11" t="inlineStr"/>
       <c r="N127" s="11" t="inlineStr"/>
     </row>
-    <row r="128" ht="270" customHeight="1">
+    <row r="128" ht="250" customHeight="1">
       <c r="A128" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9293,9 +9190,8 @@
       <c r="K128" s="10" t="inlineStr">
         <is>
           <t>Bonjour Dominique Degré,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9308,7 +9204,7 @@
       <c r="M128" s="11" t="inlineStr"/>
       <c r="N128" s="11" t="inlineStr"/>
     </row>
-    <row r="129" ht="270" customHeight="1">
+    <row r="129" ht="250" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9362,9 +9258,8 @@
       <c r="K129" s="10" t="inlineStr">
         <is>
           <t>Bonjour Quentin Dufranne,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9377,7 +9272,7 @@
       <c r="M129" s="11" t="inlineStr"/>
       <c r="N129" s="11" t="inlineStr"/>
     </row>
-    <row r="130" ht="270" customHeight="1">
+    <row r="130" ht="250" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9431,9 +9326,8 @@
       <c r="K130" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ève Dumas,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9446,7 +9340,7 @@
       <c r="M130" s="11" t="inlineStr"/>
       <c r="N130" s="11" t="inlineStr"/>
     </row>
-    <row r="131" ht="270" customHeight="1">
+    <row r="131" ht="250" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9500,9 +9394,8 @@
       <c r="K131" s="10" t="inlineStr">
         <is>
           <t>Bonjour Michel Fortier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9515,7 +9408,7 @@
       <c r="M131" s="11" t="inlineStr"/>
       <c r="N131" s="11" t="inlineStr"/>
     </row>
-    <row r="132" ht="270" customHeight="1">
+    <row r="132" ht="250" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9569,9 +9462,8 @@
       <c r="K132" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Eve Fournier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9584,7 +9476,7 @@
       <c r="M132" s="11" t="inlineStr"/>
       <c r="N132" s="11" t="inlineStr"/>
     </row>
-    <row r="133" ht="270" customHeight="1">
+    <row r="133" ht="250" customHeight="1">
       <c r="A133" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9638,9 +9530,8 @@
       <c r="K133" s="10" t="inlineStr">
         <is>
           <t>Bonjour Raymond Fournier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9653,7 +9544,7 @@
       <c r="M133" s="11" t="inlineStr"/>
       <c r="N133" s="11" t="inlineStr"/>
     </row>
-    <row r="134" ht="270" customHeight="1">
+    <row r="134" ht="250" customHeight="1">
       <c r="A134" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9707,9 +9598,8 @@
       <c r="K134" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Pier Frappier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9722,7 +9612,7 @@
       <c r="M134" s="11" t="inlineStr"/>
       <c r="N134" s="11" t="inlineStr"/>
     </row>
-    <row r="135" ht="270" customHeight="1">
+    <row r="135" ht="250" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9776,9 +9666,8 @@
       <c r="K135" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Julie Gagnon,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9791,7 +9680,7 @@
       <c r="M135" s="11" t="inlineStr"/>
       <c r="N135" s="11" t="inlineStr"/>
     </row>
-    <row r="136" ht="270" customHeight="1">
+    <row r="136" ht="250" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9845,9 +9734,8 @@
       <c r="K136" s="10" t="inlineStr">
         <is>
           <t>Bonjour Chloé Germain-Thérien,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9860,7 +9748,7 @@
       <c r="M136" s="11" t="inlineStr"/>
       <c r="N136" s="11" t="inlineStr"/>
     </row>
-    <row r="137" ht="270" customHeight="1">
+    <row r="137" ht="250" customHeight="1">
       <c r="A137" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9914,9 +9802,8 @@
       <c r="K137" s="10" t="inlineStr">
         <is>
           <t>Bonjour Charlotte Glorieux,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9929,7 +9816,7 @@
       <c r="M137" s="11" t="inlineStr"/>
       <c r="N137" s="11" t="inlineStr"/>
     </row>
-    <row r="138" ht="270" customHeight="1">
+    <row r="138" ht="250" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -9983,9 +9870,8 @@
       <c r="K138" s="10" t="inlineStr">
         <is>
           <t>Bonjour Annie Hudon,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -9998,7 +9884,7 @@
       <c r="M138" s="11" t="inlineStr"/>
       <c r="N138" s="11" t="inlineStr"/>
     </row>
-    <row r="139" ht="270" customHeight="1">
+    <row r="139" ht="250" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10052,9 +9938,8 @@
       <c r="K139" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ahmed Kouaou,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10067,7 +9952,7 @@
       <c r="M139" s="11" t="inlineStr"/>
       <c r="N139" s="11" t="inlineStr"/>
     </row>
-    <row r="140" ht="270" customHeight="1">
+    <row r="140" ht="250" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10121,9 +10006,8 @@
       <c r="K140" s="10" t="inlineStr">
         <is>
           <t>Bonjour Tania Krywiak,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10136,7 +10020,7 @@
       <c r="M140" s="11" t="inlineStr"/>
       <c r="N140" s="11" t="inlineStr"/>
     </row>
-    <row r="141" ht="270" customHeight="1">
+    <row r="141" ht="250" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10190,9 +10074,8 @@
       <c r="K141" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jacinthe Lafrance,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10205,7 +10088,7 @@
       <c r="M141" s="11" t="inlineStr"/>
       <c r="N141" s="11" t="inlineStr"/>
     </row>
-    <row r="142" ht="270" customHeight="1">
+    <row r="142" ht="250" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10259,9 +10142,8 @@
       <c r="K142" s="10" t="inlineStr">
         <is>
           <t>Bonjour Bruno Lamolet,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10274,7 +10156,7 @@
       <c r="M142" s="11" t="inlineStr"/>
       <c r="N142" s="11" t="inlineStr"/>
     </row>
-    <row r="143" ht="270" customHeight="1">
+    <row r="143" ht="250" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10328,9 +10210,8 @@
       <c r="K143" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yvan Lamontagne,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10343,7 +10224,7 @@
       <c r="M143" s="11" t="inlineStr"/>
       <c r="N143" s="11" t="inlineStr"/>
     </row>
-    <row r="144" ht="270" customHeight="1">
+    <row r="144" ht="250" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10397,9 +10278,8 @@
       <c r="K144" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yves Langlois,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10412,7 +10292,7 @@
       <c r="M144" s="11" t="inlineStr"/>
       <c r="N144" s="11" t="inlineStr"/>
     </row>
-    <row r="145" ht="270" customHeight="1">
+    <row r="145" ht="250" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10466,9 +10346,8 @@
       <c r="K145" s="10" t="inlineStr">
         <is>
           <t>Bonjour Anne Marie Lecomte,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10481,7 +10360,7 @@
       <c r="M145" s="11" t="inlineStr"/>
       <c r="N145" s="11" t="inlineStr"/>
     </row>
-    <row r="146" ht="270" customHeight="1">
+    <row r="146" ht="250" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10535,9 +10414,8 @@
       <c r="K146" s="10" t="inlineStr">
         <is>
           <t>Bonjour Stéphanie Mac Farlane,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10550,7 +10428,7 @@
       <c r="M146" s="11" t="inlineStr"/>
       <c r="N146" s="11" t="inlineStr"/>
     </row>
-    <row r="147" ht="270" customHeight="1">
+    <row r="147" ht="250" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10604,9 +10482,8 @@
       <c r="K147" s="10" t="inlineStr">
         <is>
           <t>Bonjour Philippe Marois,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10619,7 +10496,7 @@
       <c r="M147" s="11" t="inlineStr"/>
       <c r="N147" s="11" t="inlineStr"/>
     </row>
-    <row r="148" ht="270" customHeight="1">
+    <row r="148" ht="250" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10673,9 +10550,8 @@
       <c r="K148" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gildas Meneu,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10688,7 +10564,7 @@
       <c r="M148" s="11" t="inlineStr"/>
       <c r="N148" s="11" t="inlineStr"/>
     </row>
-    <row r="149" ht="270" customHeight="1">
+    <row r="149" ht="250" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10742,9 +10618,8 @@
       <c r="K149" s="10" t="inlineStr">
         <is>
           <t>Bonjour Louis-Xavier Michaud,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10757,7 +10632,7 @@
       <c r="M149" s="11" t="inlineStr"/>
       <c r="N149" s="11" t="inlineStr"/>
     </row>
-    <row r="150" ht="270" customHeight="1">
+    <row r="150" ht="250" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10811,9 +10686,8 @@
       <c r="K150" s="10" t="inlineStr">
         <is>
           <t>Bonjour Anne Montplaisir,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10826,7 +10700,7 @@
       <c r="M150" s="11" t="inlineStr"/>
       <c r="N150" s="11" t="inlineStr"/>
     </row>
-    <row r="151" ht="270" customHeight="1">
+    <row r="151" ht="250" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10880,9 +10754,8 @@
       <c r="K151" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karianne Nepton-Philippe,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10895,7 +10768,7 @@
       <c r="M151" s="11" t="inlineStr"/>
       <c r="N151" s="11" t="inlineStr"/>
     </row>
-    <row r="152" ht="270" customHeight="1">
+    <row r="152" ht="250" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -10949,9 +10822,8 @@
       <c r="K152" s="10" t="inlineStr">
         <is>
           <t>Bonjour Geneviève Normand,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -10964,7 +10836,7 @@
       <c r="M152" s="11" t="inlineStr"/>
       <c r="N152" s="11" t="inlineStr"/>
     </row>
-    <row r="153" ht="270" customHeight="1">
+    <row r="153" ht="250" customHeight="1">
       <c r="A153" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11018,9 +10890,8 @@
       <c r="K153" s="10" t="inlineStr">
         <is>
           <t>Bonjour Carole Payer,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11033,7 +10904,7 @@
       <c r="M153" s="11" t="inlineStr"/>
       <c r="N153" s="11" t="inlineStr"/>
     </row>
-    <row r="154" ht="270" customHeight="1">
+    <row r="154" ht="250" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11087,9 +10958,8 @@
       <c r="K154" s="10" t="inlineStr">
         <is>
           <t>Bonjour Boris Proulx,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11102,7 +10972,7 @@
       <c r="M154" s="11" t="inlineStr"/>
       <c r="N154" s="11" t="inlineStr"/>
     </row>
-    <row r="155" ht="270" customHeight="1">
+    <row r="155" ht="250" customHeight="1">
       <c r="A155" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11156,9 +11026,8 @@
       <c r="K155" s="10" t="inlineStr">
         <is>
           <t>Bonjour Philippe Robitaille-Grou,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11171,7 +11040,7 @@
       <c r="M155" s="11" t="inlineStr"/>
       <c r="N155" s="11" t="inlineStr"/>
     </row>
-    <row r="156" ht="270" customHeight="1">
+    <row r="156" ht="250" customHeight="1">
       <c r="A156" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11225,9 +11094,8 @@
       <c r="K156" s="10" t="inlineStr">
         <is>
           <t>Bonjour Gwen Roley,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11240,7 +11108,7 @@
       <c r="M156" s="11" t="inlineStr"/>
       <c r="N156" s="11" t="inlineStr"/>
     </row>
-    <row r="157" ht="270" customHeight="1">
+    <row r="157" ht="250" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11294,9 +11162,8 @@
       <c r="K157" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mathieu-Robert Sauvé,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11309,7 +11176,7 @@
       <c r="M157" s="11" t="inlineStr"/>
       <c r="N157" s="11" t="inlineStr"/>
     </row>
-    <row r="158" ht="270" customHeight="1">
+    <row r="158" ht="250" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11363,9 +11230,8 @@
       <c r="K158" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre St-Arnaud,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11378,7 +11244,7 @@
       <c r="M158" s="11" t="inlineStr"/>
       <c r="N158" s="11" t="inlineStr"/>
     </row>
-    <row r="159" ht="270" customHeight="1">
+    <row r="159" ht="250" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11432,9 +11298,8 @@
       <c r="K159" s="10" t="inlineStr">
         <is>
           <t>Bonjour Katherine Tremblay,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11447,7 +11312,7 @@
       <c r="M159" s="11" t="inlineStr"/>
       <c r="N159" s="11" t="inlineStr"/>
     </row>
-    <row r="160" ht="270" customHeight="1">
+    <row r="160" ht="250" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11501,9 +11366,8 @@
       <c r="K160" s="10" t="inlineStr">
         <is>
           <t>Bonjour Michel Tremblay,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11516,7 +11380,7 @@
       <c r="M160" s="11" t="inlineStr"/>
       <c r="N160" s="11" t="inlineStr"/>
     </row>
-    <row r="161" ht="270" customHeight="1">
+    <row r="161" ht="250" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11570,9 +11434,8 @@
       <c r="K161" s="10" t="inlineStr">
         <is>
           <t>Bonjour Martin Vallières,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11585,7 +11448,7 @@
       <c r="M161" s="11" t="inlineStr"/>
       <c r="N161" s="11" t="inlineStr"/>
     </row>
-    <row r="162" ht="270" customHeight="1">
+    <row r="162" ht="250" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -11639,9 +11502,8 @@
       <c r="K162" s="10" t="inlineStr">
         <is>
           <t>Bonjour Yanick Villedieu,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11654,7 +11516,7 @@
       <c r="M162" s="11" t="inlineStr"/>
       <c r="N162" s="11" t="inlineStr"/>
     </row>
-    <row r="163" ht="270" customHeight="1">
+    <row r="163" ht="250" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11708,9 +11570,8 @@
       <c r="K163" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jonathan Allard,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11723,7 +11584,7 @@
       <c r="M163" s="11" t="inlineStr"/>
       <c r="N163" s="11" t="inlineStr"/>
     </row>
-    <row r="164" ht="270" customHeight="1">
+    <row r="164" ht="250" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11777,9 +11638,8 @@
       <c r="K164" s="10" t="inlineStr">
         <is>
           <t>Bonjour Anick Baribeau,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11792,7 +11652,7 @@
       <c r="M164" s="11" t="inlineStr"/>
       <c r="N164" s="11" t="inlineStr"/>
     </row>
-    <row r="165" ht="270" customHeight="1">
+    <row r="165" ht="250" customHeight="1">
       <c r="A165" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11846,9 +11706,8 @@
       <c r="K165" s="10" t="inlineStr">
         <is>
           <t>Bonjour Félix-Antoine Beauchemin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11861,7 +11720,7 @@
       <c r="M165" s="11" t="inlineStr"/>
       <c r="N165" s="11" t="inlineStr"/>
     </row>
-    <row r="166" ht="270" customHeight="1">
+    <row r="166" ht="250" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11915,9 +11774,8 @@
       <c r="K166" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karim Benessaieh,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11930,7 +11788,7 @@
       <c r="M166" s="11" t="inlineStr"/>
       <c r="N166" s="11" t="inlineStr"/>
     </row>
-    <row r="167" ht="270" customHeight="1">
+    <row r="167" ht="250" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -11984,9 +11842,8 @@
       <c r="K167" s="10" t="inlineStr">
         <is>
           <t>Bonjour Julia Bernier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -11999,7 +11856,7 @@
       <c r="M167" s="11" t="inlineStr"/>
       <c r="N167" s="11" t="inlineStr"/>
     </row>
-    <row r="168" ht="270" customHeight="1">
+    <row r="168" ht="250" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12053,9 +11910,8 @@
       <c r="K168" s="10" t="inlineStr">
         <is>
           <t>Bonjour Karine Boivin Forcier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12068,7 +11924,7 @@
       <c r="M168" s="11" t="inlineStr"/>
       <c r="N168" s="11" t="inlineStr"/>
     </row>
-    <row r="169" ht="270" customHeight="1">
+    <row r="169" ht="250" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12122,9 +11978,8 @@
       <c r="K169" s="10" t="inlineStr">
         <is>
           <t>Bonjour Audrey Bonaque,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12137,7 +11992,7 @@
       <c r="M169" s="11" t="inlineStr"/>
       <c r="N169" s="11" t="inlineStr"/>
     </row>
-    <row r="170" ht="270" customHeight="1">
+    <row r="170" ht="250" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12191,9 +12046,8 @@
       <c r="K170" s="10" t="inlineStr">
         <is>
           <t>Bonjour Luc Boulanger,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12206,7 +12060,7 @@
       <c r="M170" s="11" t="inlineStr"/>
       <c r="N170" s="11" t="inlineStr"/>
     </row>
-    <row r="171" ht="270" customHeight="1">
+    <row r="171" ht="250" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12260,9 +12114,8 @@
       <c r="K171" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mario Boulianne,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12275,7 +12128,7 @@
       <c r="M171" s="11" t="inlineStr"/>
       <c r="N171" s="11" t="inlineStr"/>
     </row>
-    <row r="172" ht="270" customHeight="1">
+    <row r="172" ht="250" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12329,9 +12182,8 @@
       <c r="K172" s="10" t="inlineStr">
         <is>
           <t>Bonjour Bernard Brault,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12344,7 +12196,7 @@
       <c r="M172" s="11" t="inlineStr"/>
       <c r="N172" s="11" t="inlineStr"/>
     </row>
-    <row r="173" ht="270" customHeight="1">
+    <row r="173" ht="250" customHeight="1">
       <c r="A173" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12398,9 +12250,8 @@
       <c r="K173" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre Brisson,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12413,7 +12264,7 @@
       <c r="M173" s="11" t="inlineStr"/>
       <c r="N173" s="11" t="inlineStr"/>
     </row>
-    <row r="174" ht="270" customHeight="1">
+    <row r="174" ht="250" customHeight="1">
       <c r="A174" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12467,9 +12318,8 @@
       <c r="K174" s="10" t="inlineStr">
         <is>
           <t>Bonjour Laurence Brisson Dubreuil,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12482,7 +12332,7 @@
       <c r="M174" s="11" t="inlineStr"/>
       <c r="N174" s="11" t="inlineStr"/>
     </row>
-    <row r="175" ht="270" customHeight="1">
+    <row r="175" ht="250" customHeight="1">
       <c r="A175" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12536,9 +12386,8 @@
       <c r="K175" s="10" t="inlineStr">
         <is>
           <t>Bonjour Nathaniel Bronner,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12551,7 +12400,7 @@
       <c r="M175" s="11" t="inlineStr"/>
       <c r="N175" s="11" t="inlineStr"/>
     </row>
-    <row r="176" ht="270" customHeight="1">
+    <row r="176" ht="250" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12605,9 +12454,8 @@
       <c r="K176" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-France Bélanger,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12620,7 +12468,7 @@
       <c r="M176" s="11" t="inlineStr"/>
       <c r="N176" s="11" t="inlineStr"/>
     </row>
-    <row r="177" ht="270" customHeight="1">
+    <row r="177" ht="250" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12674,9 +12522,8 @@
       <c r="K177" s="10" t="inlineStr">
         <is>
           <t>Bonjour Diane Bérard,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12689,7 +12536,7 @@
       <c r="M177" s="11" t="inlineStr"/>
       <c r="N177" s="11" t="inlineStr"/>
     </row>
-    <row r="178" ht="270" customHeight="1">
+    <row r="178" ht="250" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12743,9 +12590,8 @@
       <c r="K178" s="10" t="inlineStr">
         <is>
           <t>Bonjour Julien Cayouette,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12758,7 +12604,7 @@
       <c r="M178" s="11" t="inlineStr"/>
       <c r="N178" s="11" t="inlineStr"/>
     </row>
-    <row r="179" ht="270" customHeight="1">
+    <row r="179" ht="250" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12812,9 +12658,8 @@
       <c r="K179" s="10" t="inlineStr">
         <is>
           <t>Bonjour Rudy Chabannes,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12827,7 +12672,7 @@
       <c r="M179" s="11" t="inlineStr"/>
       <c r="N179" s="11" t="inlineStr"/>
     </row>
-    <row r="180" ht="270" customHeight="1">
+    <row r="180" ht="250" customHeight="1">
       <c r="A180" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12881,9 +12726,8 @@
       <c r="K180" s="10" t="inlineStr">
         <is>
           <t>Bonjour Denis-Martin Chabot,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12896,7 +12740,7 @@
       <c r="M180" s="11" t="inlineStr"/>
       <c r="N180" s="11" t="inlineStr"/>
     </row>
-    <row r="181" ht="270" customHeight="1">
+    <row r="181" ht="250" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -12950,9 +12794,8 @@
       <c r="K181" s="10" t="inlineStr">
         <is>
           <t>Bonjour Loubna Majda Chourouk,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -12965,7 +12808,7 @@
       <c r="M181" s="11" t="inlineStr"/>
       <c r="N181" s="11" t="inlineStr"/>
     </row>
-    <row r="182" ht="270" customHeight="1">
+    <row r="182" ht="250" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13019,9 +12862,8 @@
       <c r="K182" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sarah Collardey,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13034,7 +12876,7 @@
       <c r="M182" s="11" t="inlineStr"/>
       <c r="N182" s="11" t="inlineStr"/>
     </row>
-    <row r="183" ht="270" customHeight="1">
+    <row r="183" ht="250" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13088,9 +12930,8 @@
       <c r="K183" s="10" t="inlineStr">
         <is>
           <t>Bonjour Kathleen Couillard,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13103,7 +12944,7 @@
       <c r="M183" s="11" t="inlineStr"/>
       <c r="N183" s="11" t="inlineStr"/>
     </row>
-    <row r="184" ht="270" customHeight="1">
+    <row r="184" ht="250" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13157,9 +12998,8 @@
       <c r="K184" s="10" t="inlineStr">
         <is>
           <t>Bonjour Oumou DIAKITÉ,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13172,7 +13012,7 @@
       <c r="M184" s="11" t="inlineStr"/>
       <c r="N184" s="11" t="inlineStr"/>
     </row>
-    <row r="185" ht="270" customHeight="1">
+    <row r="185" ht="250" customHeight="1">
       <c r="A185" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13226,9 +13066,8 @@
       <c r="K185" s="10" t="inlineStr">
         <is>
           <t>Bonjour Agnès Delavault,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13241,7 +13080,7 @@
       <c r="M185" s="11" t="inlineStr"/>
       <c r="N185" s="11" t="inlineStr"/>
     </row>
-    <row r="186" ht="270" customHeight="1">
+    <row r="186" ht="250" customHeight="1">
       <c r="A186" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13295,9 +13134,8 @@
       <c r="K186" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marcelin Delice,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13310,7 +13148,7 @@
       <c r="M186" s="11" t="inlineStr"/>
       <c r="N186" s="11" t="inlineStr"/>
     </row>
-    <row r="187" ht="270" customHeight="1">
+    <row r="187" ht="250" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13364,9 +13202,8 @@
       <c r="K187" s="10" t="inlineStr">
         <is>
           <t>Bonjour Alain Demers,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13379,7 +13216,7 @@
       <c r="M187" s="11" t="inlineStr"/>
       <c r="N187" s="11" t="inlineStr"/>
     </row>
-    <row r="188" ht="270" customHeight="1">
+    <row r="188" ht="250" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13433,9 +13270,8 @@
       <c r="K188" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ivanoh Demers,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13448,7 +13284,7 @@
       <c r="M188" s="11" t="inlineStr"/>
       <c r="N188" s="11" t="inlineStr"/>
     </row>
-    <row r="189" ht="270" customHeight="1">
+    <row r="189" ht="250" customHeight="1">
       <c r="A189" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13502,9 +13338,8 @@
       <c r="K189" s="10" t="inlineStr">
         <is>
           <t>Bonjour Claude Deschênes,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13517,7 +13352,7 @@
       <c r="M189" s="11" t="inlineStr"/>
       <c r="N189" s="11" t="inlineStr"/>
     </row>
-    <row r="190" ht="270" customHeight="1">
+    <row r="190" ht="250" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13571,9 +13406,8 @@
       <c r="K190" s="10" t="inlineStr">
         <is>
           <t>Bonjour Thomas Deshaies,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13586,7 +13420,7 @@
       <c r="M190" s="11" t="inlineStr"/>
       <c r="N190" s="11" t="inlineStr"/>
     </row>
-    <row r="191" ht="270" customHeight="1">
+    <row r="191" ht="250" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13640,9 +13474,8 @@
       <c r="K191" s="10" t="inlineStr">
         <is>
           <t>Bonjour Claude Desjardins,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13655,7 +13488,7 @@
       <c r="M191" s="11" t="inlineStr"/>
       <c r="N191" s="11" t="inlineStr"/>
     </row>
-    <row r="192" ht="270" customHeight="1">
+    <row r="192" ht="250" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13709,9 +13542,8 @@
       <c r="K192" s="10" t="inlineStr">
         <is>
           <t>Bonjour Martine Deslauriers,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13724,7 +13556,7 @@
       <c r="M192" s="11" t="inlineStr"/>
       <c r="N192" s="11" t="inlineStr"/>
     </row>
-    <row r="193" ht="270" customHeight="1">
+    <row r="193" ht="250" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13778,9 +13610,8 @@
       <c r="K193" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Claude Di Lillo,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13793,7 +13624,7 @@
       <c r="M193" s="11" t="inlineStr"/>
       <c r="N193" s="11" t="inlineStr"/>
     </row>
-    <row r="194" ht="270" customHeight="1">
+    <row r="194" ht="250" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13847,9 +13678,8 @@
       <c r="K194" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-René Dufort,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13862,7 +13692,7 @@
       <c r="M194" s="11" t="inlineStr"/>
       <c r="N194" s="11" t="inlineStr"/>
     </row>
-    <row r="195" ht="270" customHeight="1">
+    <row r="195" ht="250" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13916,9 +13746,8 @@
       <c r="K195" s="10" t="inlineStr">
         <is>
           <t>Bonjour Richard Dupaul,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -13931,7 +13760,7 @@
       <c r="M195" s="11" t="inlineStr"/>
       <c r="N195" s="11" t="inlineStr"/>
     </row>
-    <row r="196" ht="270" customHeight="1">
+    <row r="196" ht="250" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -13985,9 +13814,8 @@
       <c r="K196" s="10" t="inlineStr">
         <is>
           <t>Bonjour Stéphanie Dupuis,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14000,7 +13828,7 @@
       <c r="M196" s="11" t="inlineStr"/>
       <c r="N196" s="11" t="inlineStr"/>
     </row>
-    <row r="197" ht="270" customHeight="1">
+    <row r="197" ht="250" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14054,9 +13882,8 @@
       <c r="K197" s="10" t="inlineStr">
         <is>
           <t>Bonjour Maxim Fauteux,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14069,7 +13896,7 @@
       <c r="M197" s="11" t="inlineStr"/>
       <c r="N197" s="11" t="inlineStr"/>
     </row>
-    <row r="198" ht="270" customHeight="1">
+    <row r="198" ht="250" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14123,9 +13950,8 @@
       <c r="K198" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ronald Georges,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14138,7 +13964,7 @@
       <c r="M198" s="11" t="inlineStr"/>
       <c r="N198" s="11" t="inlineStr"/>
     </row>
-    <row r="199" ht="270" customHeight="1">
+    <row r="199" ht="250" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14192,9 +14018,8 @@
       <c r="K199" s="10" t="inlineStr">
         <is>
           <t>Bonjour Stéphane Giroux,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14207,7 +14032,7 @@
       <c r="M199" s="11" t="inlineStr"/>
       <c r="N199" s="11" t="inlineStr"/>
     </row>
-    <row r="200" ht="270" customHeight="1">
+    <row r="200" ht="250" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14261,9 +14086,8 @@
       <c r="K200" s="10" t="inlineStr">
         <is>
           <t>Bonjour Zacharie Goudreault,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14276,7 +14100,7 @@
       <c r="M200" s="11" t="inlineStr"/>
       <c r="N200" s="11" t="inlineStr"/>
     </row>
-    <row r="201" ht="270" customHeight="1">
+    <row r="201" ht="250" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14330,9 +14154,8 @@
       <c r="K201" s="10" t="inlineStr">
         <is>
           <t>Bonjour Isabelle Grégoire,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14345,7 +14168,7 @@
       <c r="M201" s="11" t="inlineStr"/>
       <c r="N201" s="11" t="inlineStr"/>
     </row>
-    <row r="202" ht="270" customHeight="1">
+    <row r="202" ht="250" customHeight="1">
       <c r="A202" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14399,9 +14222,8 @@
       <c r="K202" s="10" t="inlineStr">
         <is>
           <t>Bonjour Chantal Guy,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14414,7 +14236,7 @@
       <c r="M202" s="11" t="inlineStr"/>
       <c r="N202" s="11" t="inlineStr"/>
     </row>
-    <row r="203" ht="270" customHeight="1">
+    <row r="203" ht="250" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14468,9 +14290,8 @@
       <c r="K203" s="10" t="inlineStr">
         <is>
           <t>Bonjour Matthieu Hains,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14483,7 +14304,7 @@
       <c r="M203" s="11" t="inlineStr"/>
       <c r="N203" s="11" t="inlineStr"/>
     </row>
-    <row r="204" ht="270" customHeight="1">
+    <row r="204" ht="250" customHeight="1">
       <c r="A204" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14539,7 +14360,7 @@
       <c r="M204" s="11" t="inlineStr"/>
       <c r="N204" s="11" t="inlineStr"/>
     </row>
-    <row r="205" ht="270" customHeight="1">
+    <row r="205" ht="250" customHeight="1">
       <c r="A205" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14593,9 +14414,8 @@
       <c r="K205" s="10" t="inlineStr">
         <is>
           <t>Bonjour ANGELO JEAN-BAPTISTE,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14608,7 +14428,7 @@
       <c r="M205" s="11" t="inlineStr"/>
       <c r="N205" s="11" t="inlineStr"/>
     </row>
-    <row r="206" ht="270" customHeight="1">
+    <row r="206" ht="250" customHeight="1">
       <c r="A206" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14662,9 +14482,8 @@
       <c r="K206" s="10" t="inlineStr">
         <is>
           <t>Bonjour Andréanne Joly,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14677,7 +14496,7 @@
       <c r="M206" s="11" t="inlineStr"/>
       <c r="N206" s="11" t="inlineStr"/>
     </row>
-    <row r="207" ht="270" customHeight="1">
+    <row r="207" ht="250" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14731,9 +14550,8 @@
       <c r="K207" s="10" t="inlineStr">
         <is>
           <t>Bonjour Hugo Joncas,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14746,7 +14564,7 @@
       <c r="M207" s="11" t="inlineStr"/>
       <c r="N207" s="11" t="inlineStr"/>
     </row>
-    <row r="208" ht="270" customHeight="1">
+    <row r="208" ht="250" customHeight="1">
       <c r="A208" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14800,9 +14618,8 @@
       <c r="K208" s="10" t="inlineStr">
         <is>
           <t>Bonjour Philémon La Frenière-Prémont,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14815,7 +14632,7 @@
       <c r="M208" s="11" t="inlineStr"/>
       <c r="N208" s="11" t="inlineStr"/>
     </row>
-    <row r="209" ht="270" customHeight="1">
+    <row r="209" ht="250" customHeight="1">
       <c r="A209" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14869,9 +14686,8 @@
       <c r="K209" s="10" t="inlineStr">
         <is>
           <t>Bonjour Henri Laban,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -14884,7 +14700,7 @@
       <c r="M209" s="11" t="inlineStr"/>
       <c r="N209" s="11" t="inlineStr"/>
     </row>
-    <row r="210" ht="270" customHeight="1">
+    <row r="210" ht="250" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14940,7 +14756,7 @@
       <c r="M210" s="11" t="inlineStr"/>
       <c r="N210" s="11" t="inlineStr"/>
     </row>
-    <row r="211" ht="270" customHeight="1">
+    <row r="211" ht="250" customHeight="1">
       <c r="A211" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -14994,9 +14810,8 @@
       <c r="K211" s="10" t="inlineStr">
         <is>
           <t>Bonjour Joannie Lafrenière,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15009,7 +14824,7 @@
       <c r="M211" s="11" t="inlineStr"/>
       <c r="N211" s="11" t="inlineStr"/>
     </row>
-    <row r="212" ht="270" customHeight="1">
+    <row r="212" ht="250" customHeight="1">
       <c r="A212" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15063,9 +14878,8 @@
       <c r="K212" s="10" t="inlineStr">
         <is>
           <t>Bonjour Angie Landry,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15078,7 +14892,7 @@
       <c r="M212" s="11" t="inlineStr"/>
       <c r="N212" s="11" t="inlineStr"/>
     </row>
-    <row r="213" ht="270" customHeight="1">
+    <row r="213" ht="250" customHeight="1">
       <c r="A213" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15132,9 +14946,8 @@
       <c r="K213" s="10" t="inlineStr">
         <is>
           <t>Bonjour Camille Langlade,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15147,7 +14960,7 @@
       <c r="M213" s="11" t="inlineStr"/>
       <c r="N213" s="11" t="inlineStr"/>
     </row>
-    <row r="214" ht="270" customHeight="1">
+    <row r="214" ht="250" customHeight="1">
       <c r="A214" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15201,9 +15014,8 @@
       <c r="K214" s="10" t="inlineStr">
         <is>
           <t>Bonjour Claudia Larochelle,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15216,7 +15028,7 @@
       <c r="M214" s="11" t="inlineStr"/>
       <c r="N214" s="11" t="inlineStr"/>
     </row>
-    <row r="215" ht="270" customHeight="1">
+    <row r="215" ht="250" customHeight="1">
       <c r="A215" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15270,9 +15082,8 @@
       <c r="K215" s="10" t="inlineStr">
         <is>
           <t>Bonjour Étienne Leblanc,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15285,7 +15096,7 @@
       <c r="M215" s="11" t="inlineStr"/>
       <c r="N215" s="11" t="inlineStr"/>
     </row>
-    <row r="216" ht="270" customHeight="1">
+    <row r="216" ht="250" customHeight="1">
       <c r="A216" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15339,9 +15150,8 @@
       <c r="K216" s="10" t="inlineStr">
         <is>
           <t>Bonjour Louise Leduc,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15354,7 +15164,7 @@
       <c r="M216" s="11" t="inlineStr"/>
       <c r="N216" s="11" t="inlineStr"/>
     </row>
-    <row r="217" ht="270" customHeight="1">
+    <row r="217" ht="250" customHeight="1">
       <c r="A217" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15408,9 +15218,8 @@
       <c r="K217" s="10" t="inlineStr">
         <is>
           <t>Bonjour Guillaume Longuépée,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15423,7 +15232,7 @@
       <c r="M217" s="11" t="inlineStr"/>
       <c r="N217" s="11" t="inlineStr"/>
     </row>
-    <row r="218" ht="270" customHeight="1">
+    <row r="218" ht="250" customHeight="1">
       <c r="A218" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15477,9 +15286,8 @@
       <c r="K218" s="10" t="inlineStr">
         <is>
           <t>Bonjour Roxane Léouzon,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15492,7 +15300,7 @@
       <c r="M218" s="11" t="inlineStr"/>
       <c r="N218" s="11" t="inlineStr"/>
     </row>
-    <row r="219" ht="270" customHeight="1">
+    <row r="219" ht="250" customHeight="1">
       <c r="A219" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15546,9 +15354,8 @@
       <c r="K219" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ève Lévesque,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15561,7 +15368,7 @@
       <c r="M219" s="11" t="inlineStr"/>
       <c r="N219" s="11" t="inlineStr"/>
     </row>
-    <row r="220" ht="270" customHeight="1">
+    <row r="220" ht="250" customHeight="1">
       <c r="A220" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15615,9 +15422,8 @@
       <c r="K220" s="10" t="inlineStr">
         <is>
           <t>Bonjour Sophie Mangado,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15630,7 +15436,7 @@
       <c r="M220" s="11" t="inlineStr"/>
       <c r="N220" s="11" t="inlineStr"/>
     </row>
-    <row r="221" ht="270" customHeight="1">
+    <row r="221" ht="250" customHeight="1">
       <c r="A221" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15684,9 +15490,8 @@
       <c r="K221" s="10" t="inlineStr">
         <is>
           <t>Bonjour Colin McGregor,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15699,7 +15504,7 @@
       <c r="M221" s="11" t="inlineStr"/>
       <c r="N221" s="11" t="inlineStr"/>
     </row>
-    <row r="222" ht="270" customHeight="1">
+    <row r="222" ht="250" customHeight="1">
       <c r="A222" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15753,9 +15558,8 @@
       <c r="K222" s="10" t="inlineStr">
         <is>
           <t>Bonjour Isabelle Morin,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15768,7 +15572,7 @@
       <c r="M222" s="11" t="inlineStr"/>
       <c r="N222" s="11" t="inlineStr"/>
     </row>
-    <row r="223" ht="270" customHeight="1">
+    <row r="223" ht="250" customHeight="1">
       <c r="A223" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15822,9 +15626,8 @@
       <c r="K223" s="10" t="inlineStr">
         <is>
           <t>Bonjour Timothy Morson,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15837,7 +15640,7 @@
       <c r="M223" s="11" t="inlineStr"/>
       <c r="N223" s="11" t="inlineStr"/>
     </row>
-    <row r="224" ht="270" customHeight="1">
+    <row r="224" ht="250" customHeight="1">
       <c r="A224" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15891,9 +15694,8 @@
       <c r="K224" s="10" t="inlineStr">
         <is>
           <t>Bonjour Rachid Najahi,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15906,7 +15708,7 @@
       <c r="M224" s="11" t="inlineStr"/>
       <c r="N224" s="11" t="inlineStr"/>
     </row>
-    <row r="225" ht="270" customHeight="1">
+    <row r="225" ht="250" customHeight="1">
       <c r="A225" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -15960,9 +15762,8 @@
       <c r="K225" s="10" t="inlineStr">
         <is>
           <t>Bonjour Richard Olivier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -15975,7 +15776,7 @@
       <c r="M225" s="11" t="inlineStr"/>
       <c r="N225" s="11" t="inlineStr"/>
     </row>
-    <row r="226" ht="270" customHeight="1">
+    <row r="226" ht="250" customHeight="1">
       <c r="A226" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16029,9 +15830,8 @@
       <c r="K226" s="10" t="inlineStr">
         <is>
           <t>Bonjour MELISSA PELLETIER,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16044,7 +15844,7 @@
       <c r="M226" s="11" t="inlineStr"/>
       <c r="N226" s="11" t="inlineStr"/>
     </row>
-    <row r="227" ht="270" customHeight="1">
+    <row r="227" ht="250" customHeight="1">
       <c r="A227" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16098,9 +15898,8 @@
       <c r="K227" s="10" t="inlineStr">
         <is>
           <t>Bonjour Isaac Peltz,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16113,7 +15912,7 @@
       <c r="M227" s="11" t="inlineStr"/>
       <c r="N227" s="11" t="inlineStr"/>
     </row>
-    <row r="228" ht="270" customHeight="1">
+    <row r="228" ht="250" customHeight="1">
       <c r="A228" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16167,9 +15966,8 @@
       <c r="K228" s="10" t="inlineStr">
         <is>
           <t>Bonjour Frédéric Perron,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16182,7 +15980,7 @@
       <c r="M228" s="11" t="inlineStr"/>
       <c r="N228" s="11" t="inlineStr"/>
     </row>
-    <row r="229" ht="270" customHeight="1">
+    <row r="229" ht="250" customHeight="1">
       <c r="A229" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16236,9 +16034,8 @@
       <c r="K229" s="10" t="inlineStr">
         <is>
           <t>Bonjour Nathalie Petrowski,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16251,7 +16048,7 @@
       <c r="M229" s="11" t="inlineStr"/>
       <c r="N229" s="11" t="inlineStr"/>
     </row>
-    <row r="230" ht="270" customHeight="1">
+    <row r="230" ht="250" customHeight="1">
       <c r="A230" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16305,9 +16102,8 @@
       <c r="K230" s="10" t="inlineStr">
         <is>
           <t>Bonjour Francis Plourde,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16320,7 +16116,7 @@
       <c r="M230" s="11" t="inlineStr"/>
       <c r="N230" s="11" t="inlineStr"/>
     </row>
-    <row r="231" ht="270" customHeight="1">
+    <row r="231" ht="250" customHeight="1">
       <c r="A231" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16374,9 +16170,8 @@
       <c r="K231" s="10" t="inlineStr">
         <is>
           <t>Bonjour Raymonde Provencher,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16389,7 +16184,7 @@
       <c r="M231" s="11" t="inlineStr"/>
       <c r="N231" s="11" t="inlineStr"/>
     </row>
-    <row r="232" ht="270" customHeight="1">
+    <row r="232" ht="250" customHeight="1">
       <c r="A232" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16443,9 +16238,8 @@
       <c r="K232" s="10" t="inlineStr">
         <is>
           <t>Bonjour Richard Prudhomme,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16458,7 +16252,7 @@
       <c r="M232" s="11" t="inlineStr"/>
       <c r="N232" s="11" t="inlineStr"/>
     </row>
-    <row r="233" ht="270" customHeight="1">
+    <row r="233" ht="250" customHeight="1">
       <c r="A233" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16512,9 +16306,8 @@
       <c r="K233" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pascale Renaud,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16527,7 +16320,7 @@
       <c r="M233" s="11" t="inlineStr"/>
       <c r="N233" s="11" t="inlineStr"/>
     </row>
-    <row r="234" ht="270" customHeight="1">
+    <row r="234" ht="250" customHeight="1">
       <c r="A234" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16581,9 +16374,8 @@
       <c r="K234" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marc Sony Ricot,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16596,7 +16388,7 @@
       <c r="M234" s="11" t="inlineStr"/>
       <c r="N234" s="11" t="inlineStr"/>
     </row>
-    <row r="235" ht="270" customHeight="1">
+    <row r="235" ht="250" customHeight="1">
       <c r="A235" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16650,9 +16442,8 @@
       <c r="K235" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Paul Rouleau,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16665,7 +16456,7 @@
       <c r="M235" s="11" t="inlineStr"/>
       <c r="N235" s="11" t="inlineStr"/>
     </row>
-    <row r="236" ht="270" customHeight="1">
+    <row r="236" ht="250" customHeight="1">
       <c r="A236" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16719,9 +16510,8 @@
       <c r="K236" s="10" t="inlineStr">
         <is>
           <t>Bonjour Emmalie Ruest,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16734,7 +16524,7 @@
       <c r="M236" s="11" t="inlineStr"/>
       <c r="N236" s="11" t="inlineStr"/>
     </row>
-    <row r="237" ht="270" customHeight="1">
+    <row r="237" ht="250" customHeight="1">
       <c r="A237" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16788,9 +16578,8 @@
       <c r="K237" s="10" t="inlineStr">
         <is>
           <t>Bonjour Louis-Philippe Samson,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade se cultive dans votre région depuis la première vague de 2013, et que plusieurs des producteurs qui ont tenu bon nous vendent encore leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16803,7 +16592,7 @@
       <c r="M237" s="11" t="inlineStr"/>
       <c r="N237" s="11" t="inlineStr"/>
     </row>
-    <row r="238" ht="270" customHeight="1">
+    <row r="238" ht="250" customHeight="1">
       <c r="A238" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16857,9 +16646,8 @@
       <c r="K238" s="10" t="inlineStr">
         <is>
           <t>Bonjour Catherine Schlager,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16872,7 +16660,7 @@
       <c r="M238" s="11" t="inlineStr"/>
       <c r="N238" s="11" t="inlineStr"/>
     </row>
-    <row r="239" ht="270" customHeight="1">
+    <row r="239" ht="250" customHeight="1">
       <c r="A239" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16926,9 +16714,8 @@
       <c r="K239" s="10" t="inlineStr">
         <is>
           <t>Bonjour Olivier Schmouker,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -16941,7 +16728,7 @@
       <c r="M239" s="11" t="inlineStr"/>
       <c r="N239" s="11" t="inlineStr"/>
     </row>
-    <row r="240" ht="270" customHeight="1">
+    <row r="240" ht="250" customHeight="1">
       <c r="A240" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -16995,9 +16782,8 @@
       <c r="K240" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jacques Sennechael,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17010,7 +16796,7 @@
       <c r="M240" s="11" t="inlineStr"/>
       <c r="N240" s="11" t="inlineStr"/>
     </row>
-    <row r="241" ht="270" customHeight="1">
+    <row r="241" ht="250" customHeight="1">
       <c r="A241" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17064,9 +16850,8 @@
       <c r="K241" s="10" t="inlineStr">
         <is>
           <t>Bonjour Alexandre Shields,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17079,7 +16864,7 @@
       <c r="M241" s="11" t="inlineStr"/>
       <c r="N241" s="11" t="inlineStr"/>
     </row>
-    <row r="242" ht="270" customHeight="1">
+    <row r="242" ht="250" customHeight="1">
       <c r="A242" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17133,9 +16918,8 @@
       <c r="K242" s="10" t="inlineStr">
         <is>
           <t>Bonjour Chloé Sondervorst,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17148,7 +16932,7 @@
       <c r="M242" s="11" t="inlineStr"/>
       <c r="N242" s="11" t="inlineStr"/>
     </row>
-    <row r="243" ht="270" customHeight="1">
+    <row r="243" ht="250" customHeight="1">
       <c r="A243" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17202,9 +16986,8 @@
       <c r="K243" s="10" t="inlineStr">
         <is>
           <t>Bonjour Kimberley Sullivan,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17217,7 +17000,7 @@
       <c r="M243" s="11" t="inlineStr"/>
       <c r="N243" s="11" t="inlineStr"/>
     </row>
-    <row r="244" ht="270" customHeight="1">
+    <row r="244" ht="250" customHeight="1">
       <c r="A244" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17271,9 +17054,8 @@
       <c r="K244" s="10" t="inlineStr">
         <is>
           <t>Bonjour William Thériault,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17286,7 +17068,7 @@
       <c r="M244" s="11" t="inlineStr"/>
       <c r="N244" s="11" t="inlineStr"/>
     </row>
-    <row r="245" ht="270" customHeight="1">
+    <row r="245" ht="250" customHeight="1">
       <c r="A245" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17340,9 +17122,8 @@
       <c r="K245" s="10" t="inlineStr">
         <is>
           <t>Bonjour Katia Tobar,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17355,7 +17136,7 @@
       <c r="M245" s="11" t="inlineStr"/>
       <c r="N245" s="11" t="inlineStr"/>
     </row>
-    <row r="246" ht="270" customHeight="1">
+    <row r="246" ht="250" customHeight="1">
       <c r="A246" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17409,9 +17190,8 @@
       <c r="K246" s="10" t="inlineStr">
         <is>
           <t>Bonjour Martin Tremblay,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17424,7 +17204,7 @@
       <c r="M246" s="11" t="inlineStr"/>
       <c r="N246" s="11" t="inlineStr"/>
     </row>
-    <row r="247" ht="270" customHeight="1">
+    <row r="247" ht="250" customHeight="1">
       <c r="A247" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17478,9 +17258,8 @@
       <c r="K247" s="10" t="inlineStr">
         <is>
           <t>Bonjour Marie-Christine Trottier,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17493,7 +17272,7 @@
       <c r="M247" s="11" t="inlineStr"/>
       <c r="N247" s="11" t="inlineStr"/>
     </row>
-    <row r="248" ht="270" customHeight="1">
+    <row r="248" ht="250" customHeight="1">
       <c r="A248" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17547,9 +17326,8 @@
       <c r="K248" s="10" t="inlineStr">
         <is>
           <t>Bonjour Pierre-Luc Trudel,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17562,7 +17340,7 @@
       <c r="M248" s="11" t="inlineStr"/>
       <c r="N248" s="11" t="inlineStr"/>
     </row>
-    <row r="249" ht="270" customHeight="1">
+    <row r="249" ht="250" customHeight="1">
       <c r="A249" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17616,9 +17394,8 @@
       <c r="K249" s="10" t="inlineStr">
         <is>
           <t>Bonjour David Turbis,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17631,7 +17408,7 @@
       <c r="M249" s="11" t="inlineStr"/>
       <c r="N249" s="11" t="inlineStr"/>
     </row>
-    <row r="250" ht="270" customHeight="1">
+    <row r="250" ht="250" customHeight="1">
       <c r="A250" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17685,9 +17462,8 @@
       <c r="K250" s="10" t="inlineStr">
         <is>
           <t>Bonjour Paule Vermot-Desroches,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que l'asclépiade a eu son grand moment industriel chez vous : l'usine de Saint-Tite achetait 90 % des récoltes du Québec avant que la filière se casse en 2018. Des producteurs de la Mauricie cultivent encore, et on continue d'acheter leur récolte.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17700,7 +17476,7 @@
       <c r="M250" s="11" t="inlineStr"/>
       <c r="N250" s="11" t="inlineStr"/>
     </row>
-    <row r="251" ht="270" customHeight="1">
+    <row r="251" ht="250" customHeight="1">
       <c r="A251" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17754,9 +17530,8 @@
       <c r="K251" s="10" t="inlineStr">
         <is>
           <t>Bonjour Alexandra Viau,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17769,7 +17544,7 @@
       <c r="M251" s="11" t="inlineStr"/>
       <c r="N251" s="11" t="inlineStr"/>
     </row>
-    <row r="252" ht="270" customHeight="1">
+    <row r="252" ht="250" customHeight="1">
       <c r="A252" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17823,9 +17598,8 @@
       <c r="K252" s="10" t="inlineStr">
         <is>
           <t>Bonjour Raymond Viger,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17838,7 +17612,7 @@
       <c r="M252" s="11" t="inlineStr"/>
       <c r="N252" s="11" t="inlineStr"/>
     </row>
-    <row r="253" ht="270" customHeight="1">
+    <row r="253" ht="250" customHeight="1">
       <c r="A253" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17892,9 +17666,8 @@
       <c r="K253" s="10" t="inlineStr">
         <is>
           <t>Bonjour Paul Émile d'Entremont,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17907,7 +17680,7 @@
       <c r="M253" s="11" t="inlineStr"/>
       <c r="N253" s="11" t="inlineStr"/>
     </row>
-    <row r="254" ht="270" customHeight="1">
+    <row r="254" ht="250" customHeight="1">
       <c r="A254" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -17961,9 +17734,8 @@
       <c r="K254" s="10" t="inlineStr">
         <is>
           <t>Bonjour Augustin de Baudinière,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -17976,7 +17748,7 @@
       <c r="M254" s="11" t="inlineStr"/>
       <c r="N254" s="11" t="inlineStr"/>
     </row>
-    <row r="255" ht="270" customHeight="1">
+    <row r="255" ht="250" customHeight="1">
       <c r="A255" s="6" t="inlineStr">
         <is>
           <t>froide C</t>
@@ -18030,9 +17802,8 @@
       <c r="K255" s="10" t="inlineStr">
         <is>
           <t>Bonjour Ivan de Jacquelin-Dulphe,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une mauvaise herbe.
-L'asclépiade, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, produit une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis. C'est aussi la seule plante que les chenilles du papillon monarque peuvent manger.
-Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques par la culture de l'asclépiade.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
+Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -18045,7 +17816,7 @@
       <c r="M255" s="11" t="inlineStr"/>
       <c r="N255" s="11" t="inlineStr"/>
     </row>
-    <row r="256" ht="270" customHeight="1">
+    <row r="256" ht="250" customHeight="1">
       <c r="A256" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -18099,15 +17870,15 @@
       <c r="K256" s="10" t="inlineStr">
         <is>
           <t>Bonjour Jean-Michel Leprince,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
-mauvaise herbe.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une
+mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et
+menacé : le papillon monarque.
 Vous couvrez l'asclépiade depuis au moins 2014 : le Téléjournal, la soie d'Amérique partie
 sur l'Everest, le pouvoir absorbant de la fibre sur les hydrocarbures, le lien avec le
 monarque. Vous avez suivi cette histoire plus longtemps que la plupart des entreprises qui
 s'y sont essayées.
 On a démarré après la chute de la première filière. Six ans plus tard, on achète encore de l'asclépiade québécoise et on transforme l'isolant nous-mêmes à
-Limoilou. Mes 2 grandes missions : faire connaître l'asclépiade et sauvegarder les monarques
-par la culture de l'asclépiade.
+Limoilou.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Vous êtes probablement la personne au Québec qui a le plus longtemps suivi cette plante-là.
@@ -18121,7 +17892,7 @@
       <c r="M256" s="11" t="inlineStr"/>
       <c r="N256" s="11" t="inlineStr"/>
     </row>
-    <row r="257" ht="270" customHeight="1">
+    <row r="257" ht="250" customHeight="1">
       <c r="A257" s="6" t="inlineStr">
         <is>
           <t>froide B</t>
@@ -18171,8 +17942,9 @@
       <c r="K257" s="10" t="inlineStr">
         <is>
           <t>Bonjour Antoine Stab,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des manteaux avec une
-mauvaise herbe.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une
+mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et
+menacé : le papillon monarque.
 Vous aviez écrit sur le soyer du Québec dans Espaces en février 2015, à l'époque où la fibre
 devait remplacer le duvet.
 On a démarré après la chute de cette première filière. Six ans plus tard, on achète encore de l'asclépiade québécoise, on transforme l'isolant nous-mêmes, et il

--- a/communique-dragons/Lasclay_brouillons_a_editer.xlsx
+++ b/communique-dragons/Lasclay_brouillons_a_editer.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Version 7 — ta phrase d'ouverture</t>
+          <t>Version 8</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -520,54 +520,54 @@
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>L'ouverture</t>
+          <t>Les « petits cochons »</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>« On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. » Elle porte le produit, la plante et la mission d'un seul coup.</t>
+          <t>Retirés partout. Zéro occurrence dans les 253 brouillons et dans les documents.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Le courriel raccourcit</t>
+          <t>L'ouverture</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Comme l'ouverture dit déjà la mission, le paragraphe « Mes 2 grandes missions » saute de toute la liste froide et des quatre contacts chauds sans historique. Zéro répétition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Un détail corrigé</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Les « petits cochons » sont les gousses, pas la soie. La phrase le dit maintenant dans le bon ordre : « Ses gousses, les petits cochons…, sont remplies d'une soie creuse. »</t>
-        </is>
-      </c>
+          <t>« On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. » Puis, directement : « Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. »</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Les versions précédentes</t>
+        </is>
+      </c>
       <c r="B6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Les versions précédentes</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>v7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ton ouverture adoptée, paragraphe des missions retiré.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>Brouillon v7</t>
+          <t>Brouillon v8</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="250" customHeight="1">
+    <row r="2" ht="240" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -865,7 +865,7 @@
       <c r="M2" s="11" t="inlineStr"/>
       <c r="N2" s="11" t="inlineStr"/>
     </row>
-    <row r="3" ht="250" customHeight="1">
+    <row r="3" ht="240" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -928,7 +928,7 @@
       <c r="M3" s="11" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr"/>
     </row>
-    <row r="4" ht="250" customHeight="1">
+    <row r="4" ht="240" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1004,7 +1004,7 @@
       <c r="M4" s="11" t="inlineStr"/>
       <c r="N4" s="11" t="inlineStr"/>
     </row>
-    <row r="5" ht="250" customHeight="1">
+    <row r="5" ht="240" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1066,7 +1066,7 @@
       <c r="M5" s="11" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr"/>
     </row>
-    <row r="6" ht="250" customHeight="1">
+    <row r="6" ht="240" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1129,7 +1129,7 @@
       <c r="M6" s="11" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr"/>
     </row>
-    <row r="7" ht="250" customHeight="1">
+    <row r="7" ht="240" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1192,7 +1192,7 @@
       <c r="M7" s="11" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr"/>
     </row>
-    <row r="8" ht="250" customHeight="1">
+    <row r="8" ht="240" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1255,7 +1255,7 @@
       <c r="M8" s="11" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr"/>
     </row>
-    <row r="9" ht="250" customHeight="1">
+    <row r="9" ht="240" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1318,7 +1318,7 @@
       <c r="M9" s="11" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr"/>
     </row>
-    <row r="10" ht="250" customHeight="1">
+    <row r="10" ht="240" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1381,7 +1381,7 @@
       <c r="M10" s="11" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr"/>
     </row>
-    <row r="11" ht="250" customHeight="1">
+    <row r="11" ht="240" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1444,7 +1444,7 @@
       <c r="M11" s="11" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr"/>
     </row>
-    <row r="12" ht="250" customHeight="1">
+    <row r="12" ht="240" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1507,7 +1507,7 @@
       <c r="M12" s="11" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr"/>
     </row>
-    <row r="13" ht="250" customHeight="1">
+    <row r="13" ht="240" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1570,7 +1570,7 @@
       <c r="M13" s="11" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
     </row>
-    <row r="14" ht="250" customHeight="1">
+    <row r="14" ht="240" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1633,7 +1633,7 @@
       <c r="M14" s="11" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
     </row>
-    <row r="15" ht="250" customHeight="1">
+    <row r="15" ht="240" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1696,7 +1696,7 @@
       <c r="M15" s="11" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr"/>
     </row>
-    <row r="16" ht="250" customHeight="1">
+    <row r="16" ht="240" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1758,7 +1758,7 @@
       <c r="M16" s="11" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr"/>
     </row>
-    <row r="17" ht="250" customHeight="1">
+    <row r="17" ht="240" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1821,7 +1821,7 @@
       <c r="M17" s="11" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr"/>
     </row>
-    <row r="18" ht="250" customHeight="1">
+    <row r="18" ht="240" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1884,7 +1884,7 @@
       <c r="M18" s="11" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr"/>
     </row>
-    <row r="19" ht="250" customHeight="1">
+    <row r="19" ht="240" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -1947,7 +1947,7 @@
       <c r="M19" s="11" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr"/>
     </row>
-    <row r="20" ht="250" customHeight="1">
+    <row r="20" ht="240" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2010,7 +2010,7 @@
       <c r="M20" s="11" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr"/>
     </row>
-    <row r="21" ht="250" customHeight="1">
+    <row r="21" ht="240" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2073,7 +2073,7 @@
       <c r="M21" s="11" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr"/>
     </row>
-    <row r="22" ht="250" customHeight="1">
+    <row r="22" ht="240" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2136,7 +2136,7 @@
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr"/>
     </row>
-    <row r="23" ht="250" customHeight="1">
+    <row r="23" ht="240" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2199,7 +2199,7 @@
       <c r="M23" s="11" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr"/>
     </row>
-    <row r="24" ht="250" customHeight="1">
+    <row r="24" ht="240" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2262,7 +2262,7 @@
       <c r="M24" s="11" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr"/>
     </row>
-    <row r="25" ht="250" customHeight="1">
+    <row r="25" ht="240" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2325,7 +2325,7 @@
       <c r="M25" s="11" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr"/>
     </row>
-    <row r="26" ht="250" customHeight="1">
+    <row r="26" ht="240" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2381,7 +2381,7 @@
       <c r="M26" s="11" t="inlineStr"/>
       <c r="N26" s="11" t="inlineStr"/>
     </row>
-    <row r="27" ht="250" customHeight="1">
+    <row r="27" ht="240" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2444,7 +2444,7 @@
       <c r="M27" s="11" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr"/>
     </row>
-    <row r="28" ht="250" customHeight="1">
+    <row r="28" ht="240" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2499,7 +2499,7 @@
       <c r="M28" s="11" t="inlineStr"/>
       <c r="N28" s="11" t="inlineStr"/>
     </row>
-    <row r="29" ht="250" customHeight="1">
+    <row r="29" ht="240" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2541,7 +2541,7 @@
       <c r="K29" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Roberge,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe, qu'on transforme en isolant à Québec.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe, qu'on transforme en isolant à Québec.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part : je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -2553,7 +2553,7 @@
       <c r="M29" s="11" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr"/>
     </row>
-    <row r="30" ht="250" customHeight="1">
+    <row r="30" ht="240" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2595,7 +2595,7 @@
       <c r="K30" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Laforest,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe, qu'on transforme en isolant à Québec.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe, qu'on transforme en isolant à Québec.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part : je suis disponible pour une entrevue la semaine du 14 septembre et le vendredi 18 au matin.
@@ -2607,7 +2607,7 @@
       <c r="M30" s="11" t="inlineStr"/>
       <c r="N30" s="11" t="inlineStr"/>
     </row>
-    <row r="31" ht="250" customHeight="1">
+    <row r="31" ht="240" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2670,7 +2670,7 @@
       <c r="M31" s="11" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr"/>
     </row>
-    <row r="32" ht="250" customHeight="1">
+    <row r="32" ht="240" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2725,7 +2725,7 @@
       <c r="M32" s="11" t="inlineStr"/>
       <c r="N32" s="11" t="inlineStr"/>
     </row>
-    <row r="33" ht="250" customHeight="1">
+    <row r="33" ht="240" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2780,7 +2780,7 @@
       <c r="M33" s="11" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr"/>
     </row>
-    <row r="34" ht="250" customHeight="1">
+    <row r="34" ht="240" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2834,7 +2834,7 @@
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr"/>
     </row>
-    <row r="35" ht="250" customHeight="1">
+    <row r="35" ht="240" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2876,7 +2876,7 @@
       <c r="K35" s="10" t="inlineStr">
         <is>
           <t>Bonjour Mme Dostie,
-Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe, qu'on transforme en isolant à Québec.
+Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque. Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe, qu'on transforme en isolant à Québec.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
 Aller présenter notre entreprise et sa mission à la télévision nationale est une opportunité qui arrive bien rarement. Je voulais vous en faire part et qui sait, peut-être vous inspirer un sujet.
@@ -2888,7 +2888,7 @@
       <c r="M35" s="11" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr"/>
     </row>
-    <row r="36" ht="250" customHeight="1">
+    <row r="36" ht="240" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -2947,7 +2947,7 @@
       <c r="M36" s="11" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr"/>
     </row>
-    <row r="37" ht="250" customHeight="1">
+    <row r="37" ht="240" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -3006,7 +3006,7 @@
       <c r="M37" s="11" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr"/>
     </row>
-    <row r="38" ht="250" customHeight="1">
+    <row r="38" ht="240" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>chaude</t>
@@ -3065,7 +3065,7 @@
       <c r="M38" s="11" t="inlineStr"/>
       <c r="N38" s="11" t="inlineStr"/>
     </row>
-    <row r="39" ht="250" customHeight="1">
+    <row r="39" ht="240" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3140,7 +3140,7 @@
       <c r="M39" s="11" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr"/>
     </row>
-    <row r="40" ht="250" customHeight="1">
+    <row r="40" ht="240" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3195,7 +3195,7 @@
         <is>
           <t>Bonjour Zoé Allemand,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3208,7 +3208,7 @@
       <c r="M40" s="11" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr"/>
     </row>
-    <row r="41" ht="250" customHeight="1">
+    <row r="41" ht="240" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3263,7 +3263,7 @@
         <is>
           <t>Bonjour Victoria Bakos,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'art de vivre et la consommation. Le contraste se photographie bien : la gousse dans le champ, la soie blanche dans la main, le manteau porté en ville.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3276,7 +3276,7 @@
       <c r="M41" s="11" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr"/>
     </row>
-    <row r="42" ht="250" customHeight="1">
+    <row r="42" ht="240" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3331,7 +3331,7 @@
         <is>
           <t>Bonjour Marie-Émélie Bernier,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3344,7 +3344,7 @@
       <c r="M42" s="11" t="inlineStr"/>
       <c r="N42" s="11" t="inlineStr"/>
     </row>
-    <row r="43" ht="250" customHeight="1">
+    <row r="43" ht="240" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3399,7 +3399,7 @@
         <is>
           <t>Bonjour Normand Blouin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3412,7 +3412,7 @@
       <c r="M43" s="11" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr"/>
     </row>
-    <row r="44" ht="250" customHeight="1">
+    <row r="44" ht="240" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3467,7 +3467,7 @@
         <is>
           <t>Bonjour Louise Bourbonnais,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3480,7 +3480,7 @@
       <c r="M44" s="11" t="inlineStr"/>
       <c r="N44" s="11" t="inlineStr"/>
     </row>
-    <row r="45" ht="250" customHeight="1">
+    <row r="45" ht="240" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3535,7 +3535,7 @@
         <is>
           <t>Bonjour Francois Bourque,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3548,7 +3548,7 @@
       <c r="M45" s="11" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr"/>
     </row>
-    <row r="46" ht="250" customHeight="1">
+    <row r="46" ht="240" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3603,7 +3603,7 @@
         <is>
           <t>Bonjour Ariane Boyer,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3616,7 +3616,7 @@
       <c r="M46" s="11" t="inlineStr"/>
       <c r="N46" s="11" t="inlineStr"/>
     </row>
-    <row r="47" ht="250" customHeight="1">
+    <row r="47" ht="240" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3671,7 +3671,7 @@
         <is>
           <t>Bonjour Gilbert Bégin,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3684,7 +3684,7 @@
       <c r="M47" s="11" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr"/>
     </row>
-    <row r="48" ht="250" customHeight="1">
+    <row r="48" ht="240" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3739,7 +3739,7 @@
         <is>
           <t>Bonjour Papa Moussa Camara,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3752,7 +3752,7 @@
       <c r="M48" s="11" t="inlineStr"/>
       <c r="N48" s="11" t="inlineStr"/>
     </row>
-    <row r="49" ht="250" customHeight="1">
+    <row r="49" ht="240" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3807,7 +3807,7 @@
         <is>
           <t>Bonjour Victor Carré,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3820,7 +3820,7 @@
       <c r="M49" s="11" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr"/>
     </row>
-    <row r="50" ht="250" customHeight="1">
+    <row r="50" ht="240" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3875,7 +3875,7 @@
         <is>
           <t>Bonjour Eric Chabot,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3888,7 +3888,7 @@
       <c r="M50" s="11" t="inlineStr"/>
       <c r="N50" s="11" t="inlineStr"/>
     </row>
-    <row r="51" ht="250" customHeight="1">
+    <row r="51" ht="240" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -3943,7 +3943,7 @@
         <is>
           <t>Bonjour Tristan Champagne-Lessard,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -3956,7 +3956,7 @@
       <c r="M51" s="11" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr"/>
     </row>
-    <row r="52" ht="250" customHeight="1">
+    <row r="52" ht="240" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4011,7 +4011,7 @@
         <is>
           <t>Bonjour Jean-Marc Chevalier,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce que la Montérégie est une des régions où l'asclépiade se cultive encore, et que c'est de champs comme ceux-là que vient la fibre qu'on transforme.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4024,7 +4024,7 @@
       <c r="M52" s="11" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr"/>
     </row>
-    <row r="53" ht="250" customHeight="1">
+    <row r="53" ht="240" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4079,7 +4079,7 @@
         <is>
           <t>Bonjour Simon Chrétien,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4092,7 +4092,7 @@
       <c r="M53" s="11" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr"/>
     </row>
-    <row r="54" ht="250" customHeight="1">
+    <row r="54" ht="240" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4147,7 +4147,7 @@
         <is>
           <t>Bonjour Maxime Corneau,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'un de nos fournisseurs d'asclépiade cultive au Lac-Saint-Jean depuis nos tout débuts, et qu'il l'est encore aujourd'hui. La fibre de chez vous se retrouve dans nos produits.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4160,7 +4160,7 @@
       <c r="M54" s="11" t="inlineStr"/>
       <c r="N54" s="11" t="inlineStr"/>
     </row>
-    <row r="55" ht="250" customHeight="1">
+    <row r="55" ht="240" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4215,7 +4215,7 @@
         <is>
           <t>Bonjour Aurélia Crémoux,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4228,7 +4228,7 @@
       <c r="M55" s="11" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr"/>
     </row>
-    <row r="56" ht="250" customHeight="1">
+    <row r="56" ht="240" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4283,7 +4283,7 @@
         <is>
           <t>Bonjour Catherine Dallaire,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4296,7 +4296,7 @@
       <c r="M56" s="11" t="inlineStr"/>
       <c r="N56" s="11" t="inlineStr"/>
     </row>
-    <row r="57" ht="250" customHeight="1">
+    <row r="57" ht="240" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4369,7 +4369,7 @@
       <c r="M57" s="11" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr"/>
     </row>
-    <row r="58" ht="250" customHeight="1">
+    <row r="58" ht="240" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4424,7 +4424,7 @@
         <is>
           <t>Bonjour Anaïs Desjardins,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4437,7 +4437,7 @@
       <c r="M58" s="11" t="inlineStr"/>
       <c r="N58" s="11" t="inlineStr"/>
     </row>
-    <row r="59" ht="250" customHeight="1">
+    <row r="59" ht="240" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4492,7 +4492,7 @@
         <is>
           <t>Bonjour Simon Dominé,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4505,7 +4505,7 @@
       <c r="M59" s="11" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr"/>
     </row>
-    <row r="60" ht="250" customHeight="1">
+    <row r="60" ht="240" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4560,7 +4560,7 @@
         <is>
           <t>Bonjour Karl-Ivann Dubé,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4573,7 +4573,7 @@
       <c r="M60" s="11" t="inlineStr"/>
       <c r="N60" s="11" t="inlineStr"/>
     </row>
-    <row r="61" ht="250" customHeight="1">
+    <row r="61" ht="240" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4628,7 +4628,7 @@
         <is>
           <t>Bonjour André Fauteux,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4641,7 +4641,7 @@
       <c r="M61" s="11" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr"/>
     </row>
-    <row r="62" ht="250" customHeight="1">
+    <row r="62" ht="240" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4696,7 +4696,7 @@
         <is>
           <t>Bonjour Myriam Fimbry,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4709,7 +4709,7 @@
       <c r="M62" s="11" t="inlineStr"/>
       <c r="N62" s="11" t="inlineStr"/>
     </row>
-    <row r="63" ht="250" customHeight="1">
+    <row r="63" ht="240" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4764,7 +4764,7 @@
         <is>
           <t>Bonjour Étienne Fortin-Gauthier,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4777,7 +4777,7 @@
       <c r="M63" s="11" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr"/>
     </row>
-    <row r="64" ht="250" customHeight="1">
+    <row r="64" ht="240" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4832,7 +4832,7 @@
         <is>
           <t>Bonjour Johanne Fournier,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4845,7 +4845,7 @@
       <c r="M64" s="11" t="inlineStr"/>
       <c r="N64" s="11" t="inlineStr"/>
     </row>
-    <row r="65" ht="250" customHeight="1">
+    <row r="65" ht="240" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4900,7 +4900,7 @@
         <is>
           <t>Bonjour Jean Garon,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4913,7 +4913,7 @@
       <c r="M65" s="11" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr"/>
     </row>
-    <row r="66" ht="250" customHeight="1">
+    <row r="66" ht="240" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -4968,7 +4968,7 @@
         <is>
           <t>Bonjour Cécile Gladel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -4981,7 +4981,7 @@
       <c r="M66" s="11" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr"/>
     </row>
-    <row r="67" ht="250" customHeight="1">
+    <row r="67" ht="240" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5036,7 +5036,7 @@
         <is>
           <t>Bonjour Marieke Glorieux-Stryckman,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5049,7 +5049,7 @@
       <c r="M67" s="11" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr"/>
     </row>
-    <row r="68" ht="250" customHeight="1">
+    <row r="68" ht="240" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5104,7 +5104,7 @@
         <is>
           <t>Bonjour Maude Goyer,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez le plein air. À poids égal, la littérature donne la soie d'asclépiade pour environ 10 % plus isolante que le duvet. C'est un repère de laboratoire, pas une promesse de manteau, et c'est exactement pour ça que je préfère qu'on la teste.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5117,7 +5117,7 @@
       <c r="M68" s="11" t="inlineStr"/>
       <c r="N68" s="11" t="inlineStr"/>
     </row>
-    <row r="69" ht="250" customHeight="1">
+    <row r="69" ht="240" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5172,7 +5172,7 @@
         <is>
           <t>Bonjour Pauline Gravel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5185,7 +5185,7 @@
       <c r="M69" s="11" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr"/>
     </row>
-    <row r="70" ht="250" customHeight="1">
+    <row r="70" ht="240" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5240,7 +5240,7 @@
         <is>
           <t>Bonjour Bernard Hervieux,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5253,7 +5253,7 @@
       <c r="M70" s="11" t="inlineStr"/>
       <c r="N70" s="11" t="inlineStr"/>
     </row>
-    <row r="71" ht="250" customHeight="1">
+    <row r="71" ht="240" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5308,7 +5308,7 @@
         <is>
           <t>Bonjour Leïla Jolin-Dahel,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5321,7 +5321,7 @@
       <c r="M71" s="11" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr"/>
     </row>
-    <row r="72" ht="250" customHeight="1">
+    <row r="72" ht="240" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5376,7 +5376,7 @@
         <is>
           <t>Bonjour Kodjo Edjinam Nulagnon LOGO,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'environnement. Notre pari est économique avant d'être militant : si l'asclépiade devient payante, les agriculteurs la gardent dans leurs champs, et les monarques retrouvent de l'habitat de reproduction.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5389,7 +5389,7 @@
       <c r="M72" s="11" t="inlineStr"/>
       <c r="N72" s="11" t="inlineStr"/>
     </row>
-    <row r="73" ht="250" customHeight="1">
+    <row r="73" ht="240" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5444,7 +5444,7 @@
         <is>
           <t>Bonjour Annie Labrecque,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5457,7 +5457,7 @@
       <c r="M73" s="11" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr"/>
     </row>
-    <row r="74" ht="250" customHeight="1">
+    <row r="74" ht="240" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5512,7 +5512,7 @@
         <is>
           <t>Bonjour Marianne Lachapelle,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris entre autres parce qu'une des premières usines de transformation de la fibre était à Granby, et que l'Estrie compte encore des producteurs d'asclépiade.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5525,7 +5525,7 @@
       <c r="M74" s="11" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr"/>
     </row>
-    <row r="75" ht="250" customHeight="1">
+    <row r="75" ht="240" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5580,7 +5580,7 @@
         <is>
           <t>Bonjour Sophie Lachapelle,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'agriculture. La question qui compte pour les producteurs n'a pas changé depuis l'effondrement de la filière en 2018 : est-ce qu'il y a un acheteur stable au bout du champ. On achète encore la récolte de producteurs d'ici et on la transforme nous-mêmes.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5593,7 +5593,7 @@
       <c r="M75" s="11" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr"/>
     </row>
-    <row r="76" ht="250" customHeight="1">
+    <row r="76" ht="240" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5648,7 +5648,7 @@
         <is>
           <t>Bonjour Alain Laforest,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que le sujet se raconte bien en ondes : une entreprise de Québec qui va expliquer à un auditoire pancanadien pourquoi la mauvaise herbe des champs de maïs peut isoler un manteau.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5661,7 +5661,7 @@
       <c r="M76" s="11" t="inlineStr"/>
       <c r="N76" s="11" t="inlineStr"/>
     </row>
-    <row r="77" ht="250" customHeight="1">
+    <row r="77" ht="240" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5716,7 +5716,7 @@
         <is>
           <t>Bonjour Mikaël Lalancette,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que c'est une nouvelle de chez nous qui passe au national.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5729,7 +5729,7 @@
       <c r="M77" s="11" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr"/>
     </row>
-    <row r="78" ht="250" customHeight="1">
+    <row r="78" ht="240" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
           <t>froide A</t>
@@ -5784,7 +5784,7 @@
         <is>
           <t>Bonjour Jean-Luc Lavallée,
 Je m'appelle Gabriel Gouveia, fondateur de Lasclay. On isole des vêtements d'hiver avec une mauvaise herbe, l'asclépiade, qu'on cultive pour sauvegarder un pollinisateur emblématique et menacé : le papillon monarque.
-Ses gousses, les « petits cochons » que les agriculteurs arrachent de leurs champs depuis 50 ans, sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
+Ses gousses sont remplies d'une soie creuse, très légère et naturellement hydrophobe. On la transforme en isolant à Québec, et on en fait des manteaux, des mitaines, des tuques et des sacs isothermes vendus au Canada et aux États-Unis.
 Je vous écris parce que vous couvrez l'économie. On a bâti nos propres procédés de transformation parce qu'aucun sous-traitant ne voulait toucher à l'asclépiade, puis on a changé de modèle manufacturier l'an dernier pour rendre un manteau accessible à 300 $. J'en ai fait une vidéo ici : https://www.youtube.com/watch?v=GKyHh-Ok9JU.
 Le 17 septembre prochain, on va faire un énorme pas dans la bonne direction :
 Je vais présenter Lasclay dans le premier épisode de la 21e saison de Dragons' Den, sur CBC et CBC Gem.
@@ -5797,7 +5797,7 @@
       <c r="M78" s="11" t="inlineStr"/>
       <c r="N78" s="11" t="inlineStr"/>
     </row>
-    <row r="79" ht="250" customHeight="1">
+    <row r="79" ht="240" customHeight="1